--- a/output.xlsx
+++ b/output.xlsx
@@ -482,21 +482,9 @@
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -516,21 +504,9 @@
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>OK</t>
@@ -550,21 +526,9 @@
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>OK</t>
@@ -584,21 +548,9 @@
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>OK</t>
@@ -618,21 +570,9 @@
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>OK</t>
@@ -652,21 +592,9 @@
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>OK</t>
@@ -686,21 +614,9 @@
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>OK</t>
@@ -720,21 +636,9 @@
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>OK</t>
@@ -754,21 +658,9 @@
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>OK</t>
@@ -788,21 +680,9 @@
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>OK</t>
@@ -822,21 +702,9 @@
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>OK</t>
@@ -856,21 +724,9 @@
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>OK</t>
@@ -890,21 +746,9 @@
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>OK</t>
@@ -924,21 +768,9 @@
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>OK</t>
@@ -960,16 +792,8 @@
       <c r="C16" t="n">
         <v>3369</v>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
@@ -994,21 +818,9 @@
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>OK</t>
@@ -1132,11 +944,7 @@
       <c r="E21" t="n">
         <v>142</v>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>OK</t>
@@ -1164,11 +972,7 @@
       <c r="E22" t="n">
         <v>142</v>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>OK</t>
@@ -1228,11 +1032,7 @@
       <c r="E24" t="n">
         <v>142</v>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>OK</t>
@@ -1388,11 +1188,7 @@
       <c r="E29" t="n">
         <v>142</v>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>OK</t>
@@ -1420,11 +1216,7 @@
       <c r="E30" t="n">
         <v>142</v>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>OK</t>
@@ -1452,11 +1244,7 @@
       <c r="E31" t="n">
         <v>142</v>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>OK</t>
@@ -1516,11 +1304,7 @@
       <c r="E33" t="n">
         <v>142</v>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>OK</t>
@@ -1548,11 +1332,7 @@
       <c r="E34" t="n">
         <v>142</v>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>OK</t>
@@ -1644,11 +1424,7 @@
       <c r="E37" t="n">
         <v>142</v>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>OK</t>
@@ -1708,11 +1484,7 @@
       <c r="E39" t="n">
         <v>142</v>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
           <t>OK</t>
@@ -1732,21 +1504,9 @@
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>OK</t>
@@ -1774,11 +1534,7 @@
       <c r="E41" t="n">
         <v>1</v>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
           <t>OK</t>
@@ -1806,11 +1562,7 @@
       <c r="E42" t="n">
         <v>7</v>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
           <t>OK</t>
@@ -1928,21 +1680,9 @@
       <c r="C46" t="n">
         <v>2089</v>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
           <t>OK</t>
@@ -1964,21 +1704,9 @@
       <c r="C47" t="n">
         <v>2089</v>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
           <t>OK</t>
@@ -2000,21 +1728,9 @@
       <c r="C48" t="n">
         <v>2089</v>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>OK</t>
@@ -2138,11 +1854,7 @@
       <c r="E52" t="n">
         <v>3</v>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>OK</t>
@@ -2162,21 +1874,9 @@
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
           <t>OK</t>
@@ -2204,11 +1904,7 @@
       <c r="E54" t="n">
         <v>2</v>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
           <t>OK</t>
@@ -2236,11 +1932,7 @@
       <c r="E55" t="n">
         <v>22</v>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
           <t>OK</t>
@@ -2260,21 +1952,9 @@
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
           <t>OK</t>
@@ -2296,16 +1976,8 @@
       <c r="C57" t="n">
         <v>2899</v>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>Only 1 left in stock.</t>
@@ -2338,11 +2010,7 @@
       <c r="E58" t="n">
         <v>6</v>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
           <t>OK</t>
@@ -2370,11 +2038,7 @@
       <c r="E59" t="n">
         <v>6</v>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
           <t>OK</t>
@@ -2402,11 +2066,7 @@
       <c r="E60" t="n">
         <v>6</v>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
           <t>OK</t>
@@ -2428,21 +2088,9 @@
       <c r="C61" t="n">
         <v>3529</v>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
           <t>OK</t>
@@ -2534,11 +2182,7 @@
       <c r="E64" t="n">
         <v>185</v>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
           <t>OK</t>
@@ -2558,21 +2202,9 @@
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
           <t>OK</t>
@@ -2688,21 +2320,9 @@
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
           <t>OK</t>
@@ -2722,21 +2342,9 @@
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
           <t>OK</t>
@@ -2756,21 +2364,9 @@
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
           <t>OK</t>
@@ -2790,21 +2386,9 @@
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
           <t>OK</t>
@@ -2832,11 +2416,7 @@
       <c r="E73" t="n">
         <v>3</v>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
           <t>OK</t>
@@ -2856,21 +2436,9 @@
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
           <t>OK</t>
@@ -2898,11 +2466,7 @@
       <c r="E75" t="n">
         <v>3</v>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
           <t>OK</t>
@@ -2930,11 +2494,7 @@
       <c r="E76" t="n">
         <v>3</v>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
           <t>OK</t>
@@ -2962,11 +2522,7 @@
       <c r="E77" t="n">
         <v>3</v>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
           <t>OK</t>
@@ -2994,11 +2550,7 @@
       <c r="E78" t="n">
         <v>3</v>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
           <t>OK</t>
@@ -3026,11 +2578,7 @@
       <c r="E79" t="n">
         <v>3</v>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
           <t>OK</t>
@@ -3058,11 +2606,7 @@
       <c r="E80" t="n">
         <v>3</v>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
           <t>OK</t>
@@ -3090,11 +2634,7 @@
       <c r="E81" t="n">
         <v>3</v>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
           <t>OK</t>
@@ -3122,11 +2662,7 @@
       <c r="E82" t="n">
         <v>3</v>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
           <t>OK</t>
@@ -3154,11 +2690,7 @@
       <c r="E83" t="n">
         <v>3</v>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
           <t>OK</t>
@@ -3186,11 +2718,7 @@
       <c r="E84" t="n">
         <v>3</v>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
           <t>OK</t>
@@ -3218,11 +2746,7 @@
       <c r="E85" t="n">
         <v>3</v>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
           <t>OK</t>
@@ -3250,11 +2774,7 @@
       <c r="E86" t="n">
         <v>3</v>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
           <t>OK</t>
@@ -3282,11 +2802,7 @@
       <c r="E87" t="n">
         <v>3</v>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
           <t>OK</t>
@@ -3346,11 +2862,7 @@
       <c r="E89" t="n">
         <v>3</v>
       </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
           <t>OK</t>
@@ -3378,11 +2890,7 @@
       <c r="E90" t="n">
         <v>3</v>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
           <t>OK</t>
@@ -3410,11 +2918,7 @@
       <c r="E91" t="n">
         <v>3</v>
       </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
           <t>OK</t>
@@ -3442,11 +2946,7 @@
       <c r="E92" t="n">
         <v>3</v>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
           <t>OK</t>
@@ -3538,11 +3038,7 @@
       <c r="E95" t="n">
         <v>3</v>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
           <t>OK</t>
@@ -3562,21 +3058,9 @@
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
           <t>OK</t>
@@ -3596,21 +3080,9 @@
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
           <t>OK</t>
@@ -3726,21 +3198,9 @@
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
           <t>OK</t>
@@ -3824,21 +3284,9 @@
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
           <t>OK</t>
@@ -3892,21 +3340,9 @@
       <c r="C106" t="n">
         <v>1889</v>
       </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
           <t>OK</t>
@@ -3934,11 +3370,7 @@
       <c r="E107" t="n">
         <v>594</v>
       </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
           <t>OK</t>
@@ -3966,11 +3398,7 @@
       <c r="E108" t="n">
         <v>28</v>
       </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
           <t>OK</t>
@@ -3990,21 +3418,9 @@
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
           <t>OK</t>
@@ -4024,21 +3440,9 @@
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
           <t>OK</t>
@@ -4090,21 +3494,9 @@
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
           <t>OK</t>
@@ -4124,21 +3516,9 @@
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
           <t>OK</t>
@@ -4166,11 +3546,7 @@
       <c r="E114" t="n">
         <v>6</v>
       </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
           <t>OK</t>
@@ -4190,21 +3566,9 @@
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
           <t>OK</t>
@@ -4256,21 +3620,9 @@
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
           <t>OK</t>
@@ -4290,21 +3642,9 @@
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
           <t>OK</t>
@@ -4324,21 +3664,9 @@
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
           <t>OK</t>
@@ -4846,11 +4174,7 @@
       <c r="E135" t="n">
         <v>178</v>
       </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
           <t>OK</t>
@@ -4878,11 +4202,7 @@
       <c r="E136" t="n">
         <v>14</v>
       </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
           <t>OK</t>
@@ -4910,11 +4230,7 @@
       <c r="E137" t="n">
         <v>14</v>
       </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
           <t>OK</t>
@@ -4942,11 +4258,7 @@
       <c r="E138" t="n">
         <v>14</v>
       </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
           <t>OK</t>
@@ -4966,21 +4278,9 @@
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
           <t>OK</t>
@@ -5000,21 +4300,9 @@
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
           <t>OK</t>
@@ -5034,21 +4322,9 @@
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
           <t>OK</t>
@@ -5076,11 +4352,7 @@
       <c r="E142" t="n">
         <v>6</v>
       </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
           <t>OK</t>
@@ -5108,11 +4380,7 @@
       <c r="E143" t="n">
         <v>6</v>
       </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
           <t>OK</t>
@@ -5140,11 +4408,7 @@
       <c r="E144" t="n">
         <v>6</v>
       </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
         <is>
           <t>OK</t>
@@ -5172,11 +4436,7 @@
       <c r="E145" t="n">
         <v>237</v>
       </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr">
         <is>
           <t>OK</t>
@@ -5204,11 +4464,7 @@
       <c r="E146" t="n">
         <v>20</v>
       </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
         <is>
           <t>OK</t>
@@ -5228,21 +4484,9 @@
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr">
         <is>
           <t>OK</t>
@@ -5262,21 +4506,9 @@
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr">
         <is>
           <t>OK</t>
@@ -5304,11 +4536,7 @@
       <c r="E149" t="n">
         <v>20</v>
       </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr">
         <is>
           <t>OK</t>
@@ -5360,21 +4588,9 @@
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr">
         <is>
           <t>OK</t>
@@ -5434,11 +4650,7 @@
       <c r="E153" t="n">
         <v>59</v>
       </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr">
         <is>
           <t>OK</t>
@@ -5498,11 +4710,7 @@
       <c r="E155" t="n">
         <v>66</v>
       </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr">
         <is>
           <t>OK</t>
@@ -5562,11 +4770,7 @@
       <c r="E157" t="n">
         <v>90</v>
       </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr">
         <is>
           <t>OK</t>
@@ -5658,11 +4862,7 @@
       <c r="E160" t="n">
         <v>18</v>
       </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F160" t="inlineStr"/>
       <c r="G160" t="inlineStr">
         <is>
           <t>OK</t>
@@ -5714,21 +4914,9 @@
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr">
         <is>
           <t>OK</t>
@@ -5748,21 +4936,9 @@
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr">
         <is>
           <t>OK</t>
@@ -5790,11 +4966,7 @@
       <c r="E164" t="n">
         <v>27</v>
       </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr">
         <is>
           <t>OK</t>
@@ -5816,16 +4988,8 @@
       <c r="C165" t="n">
         <v>3269</v>
       </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
           <t>Only 2 left</t>
@@ -5850,32 +5014,27 @@
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
-      <c r="D166" t="inlineStr"/>
-      <c r="E166" t="inlineStr"/>
-      <c r="F166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
-  (Session info: chrome=150.0.7871.114)
-Stacktrace:
-#0 0x561e1cc3941a &lt;unknown&gt;
-#1 0x561e1c611689 &lt;unknown&gt;
-#2 0x561e1c5f921a &lt;unknown&gt;
-#3 0x561e1c5f8e96 &lt;unknown&gt;
-#4 0x561e1c5f6a7e &lt;unknown&gt;
-#5 0x561e1c5f73ff &lt;unknown&gt;
-#6 0x561e1c6064e0 &lt;unknown&gt;
-#7 0x561e1c6203e7 &lt;unknown&gt;
-#8 0x561e1c627c5b &lt;unknown&gt;
-#9 0x561e1c5f7b59 &lt;unknown&gt;
-</t>
-        </is>
-      </c>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5889,32 +5048,27 @@
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
-      <c r="D167" t="inlineStr"/>
-      <c r="E167" t="inlineStr"/>
-      <c r="F167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
-  (Session info: chrome=150.0.7871.114)
-Stacktrace:
-#0 0x561e1cc3941a &lt;unknown&gt;
-#1 0x561e1c611689 &lt;unknown&gt;
-#2 0x561e1c5f921a &lt;unknown&gt;
-#3 0x561e1c5f8e96 &lt;unknown&gt;
-#4 0x561e1c5f6a7e &lt;unknown&gt;
-#5 0x561e1c5f73ff &lt;unknown&gt;
-#6 0x561e1c6064e0 &lt;unknown&gt;
-#7 0x561e1c6203e7 &lt;unknown&gt;
-#8 0x561e1c627c5b &lt;unknown&gt;
-#9 0x561e1c5f7b59 &lt;unknown&gt;
-</t>
-        </is>
-      </c>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5928,32 +5082,27 @@
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
-      <c r="D168" t="inlineStr"/>
-      <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
-  (Session info: chrome=150.0.7871.114)
-Stacktrace:
-#0 0x561e1cc3941a &lt;unknown&gt;
-#1 0x561e1c611689 &lt;unknown&gt;
-#2 0x561e1c5f921a &lt;unknown&gt;
-#3 0x561e1c5f8e96 &lt;unknown&gt;
-#4 0x561e1c5f6a7e &lt;unknown&gt;
-#5 0x561e1c5f73ff &lt;unknown&gt;
-#6 0x561e1c6064e0 &lt;unknown&gt;
-#7 0x561e1c6203e7 &lt;unknown&gt;
-#8 0x561e1c627c5b &lt;unknown&gt;
-#9 0x561e1c5f7b59 &lt;unknown&gt;
-</t>
-        </is>
-      </c>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5967,32 +5116,27 @@
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
-      <c r="D169" t="inlineStr"/>
-      <c r="E169" t="inlineStr"/>
-      <c r="F169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
-  (Session info: chrome=150.0.7871.114)
-Stacktrace:
-#0 0x561e1cc3941a &lt;unknown&gt;
-#1 0x561e1c611689 &lt;unknown&gt;
-#2 0x561e1c5f921a &lt;unknown&gt;
-#3 0x561e1c5f8e96 &lt;unknown&gt;
-#4 0x561e1c5f6a7e &lt;unknown&gt;
-#5 0x561e1c5f73ff &lt;unknown&gt;
-#6 0x561e1c6064e0 &lt;unknown&gt;
-#7 0x561e1c6203e7 &lt;unknown&gt;
-#8 0x561e1c627c5b &lt;unknown&gt;
-#9 0x561e1c5f7b59 &lt;unknown&gt;
-</t>
-        </is>
-      </c>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -6006,32 +5150,27 @@
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
-      <c r="D170" t="inlineStr"/>
-      <c r="E170" t="inlineStr"/>
-      <c r="F170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
-  (Session info: chrome=150.0.7871.114)
-Stacktrace:
-#0 0x561e1cc3941a &lt;unknown&gt;
-#1 0x561e1c611689 &lt;unknown&gt;
-#2 0x561e1c5f921a &lt;unknown&gt;
-#3 0x561e1c5f8e96 &lt;unknown&gt;
-#4 0x561e1c5f6a7e &lt;unknown&gt;
-#5 0x561e1c5f73ff &lt;unknown&gt;
-#6 0x561e1c6064e0 &lt;unknown&gt;
-#7 0x561e1c6203e7 &lt;unknown&gt;
-#8 0x561e1c627c5b &lt;unknown&gt;
-#9 0x561e1c5f7b59 &lt;unknown&gt;
-</t>
-        </is>
-      </c>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -6045,32 +5184,27 @@
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr"/>
-      <c r="F171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
-  (Session info: chrome=150.0.7871.114)
-Stacktrace:
-#0 0x561e1cc3941a &lt;unknown&gt;
-#1 0x561e1c611689 &lt;unknown&gt;
-#2 0x561e1c5f921a &lt;unknown&gt;
-#3 0x561e1c5f8e96 &lt;unknown&gt;
-#4 0x561e1c5f6a7e &lt;unknown&gt;
-#5 0x561e1c5f73ff &lt;unknown&gt;
-#6 0x561e1c6064e0 &lt;unknown&gt;
-#7 0x561e1c6203e7 &lt;unknown&gt;
-#8 0x561e1c627c5b &lt;unknown&gt;
-#9 0x561e1c5f7b59 &lt;unknown&gt;
-</t>
-        </is>
-      </c>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -6083,33 +5217,26 @@
           <t>https://www.amazon.in/dp/B0FCFY6QN6</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr"/>
-      <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr"/>
-      <c r="F172" t="inlineStr"/>
+      <c r="C172" t="n">
+        <v>10279</v>
+      </c>
+      <c r="D172" t="n">
+        <v>1</v>
+      </c>
+      <c r="E172" t="n">
+        <v>1</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Only 2 left in stock.</t>
+        </is>
+      </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
-  (Session info: chrome=150.0.7871.114)
-Stacktrace:
-#0 0x561e1cc3941a &lt;unknown&gt;
-#1 0x561e1c611689 &lt;unknown&gt;
-#2 0x561e1c5f921a &lt;unknown&gt;
-#3 0x561e1c5f8e96 &lt;unknown&gt;
-#4 0x561e1c5f6a7e &lt;unknown&gt;
-#5 0x561e1c5f73ff &lt;unknown&gt;
-#6 0x561e1c6064e0 &lt;unknown&gt;
-#7 0x561e1c6203e7 &lt;unknown&gt;
-#8 0x561e1c627c5b &lt;unknown&gt;
-#9 0x561e1c5f7b59 &lt;unknown&gt;
-</t>
-        </is>
-      </c>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -6123,32 +5250,27 @@
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
-      <c r="D173" t="inlineStr"/>
-      <c r="E173" t="inlineStr"/>
-      <c r="F173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
-  (Session info: chrome=150.0.7871.114)
-Stacktrace:
-#0 0x561e1cc3941a &lt;unknown&gt;
-#1 0x561e1c611689 &lt;unknown&gt;
-#2 0x561e1c5f921a &lt;unknown&gt;
-#3 0x561e1c5f8e96 &lt;unknown&gt;
-#4 0x561e1c5f6a7e &lt;unknown&gt;
-#5 0x561e1c5f73ff &lt;unknown&gt;
-#6 0x561e1c6064e0 &lt;unknown&gt;
-#7 0x561e1c6203e7 &lt;unknown&gt;
-#8 0x561e1c627c5b &lt;unknown&gt;
-#9 0x561e1c5f7b59 &lt;unknown&gt;
-</t>
-        </is>
-      </c>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -6162,32 +5284,27 @@
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
-      <c r="D174" t="inlineStr"/>
-      <c r="E174" t="inlineStr"/>
-      <c r="F174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
-  (Session info: chrome=150.0.7871.114)
-Stacktrace:
-#0 0x561e1cc3941a &lt;unknown&gt;
-#1 0x561e1c611689 &lt;unknown&gt;
-#2 0x561e1c5f921a &lt;unknown&gt;
-#3 0x561e1c5f8e96 &lt;unknown&gt;
-#4 0x561e1c5f6a7e &lt;unknown&gt;
-#5 0x561e1c5f73ff &lt;unknown&gt;
-#6 0x561e1c6064e0 &lt;unknown&gt;
-#7 0x561e1c6203e7 &lt;unknown&gt;
-#8 0x561e1c627c5b &lt;unknown&gt;
-#9 0x561e1c5f7b59 &lt;unknown&gt;
-</t>
-        </is>
-      </c>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6201,32 +5318,27 @@
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
-      <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
-  (Session info: chrome=150.0.7871.114)
-Stacktrace:
-#0 0x561e1cc3941a &lt;unknown&gt;
-#1 0x561e1c611689 &lt;unknown&gt;
-#2 0x561e1c5f921a &lt;unknown&gt;
-#3 0x561e1c5f8e96 &lt;unknown&gt;
-#4 0x561e1c5f6a7e &lt;unknown&gt;
-#5 0x561e1c5f73ff &lt;unknown&gt;
-#6 0x561e1c6064e0 &lt;unknown&gt;
-#7 0x561e1c6203e7 &lt;unknown&gt;
-#8 0x561e1c627c5b &lt;unknown&gt;
-#9 0x561e1c5f7b59 &lt;unknown&gt;
-</t>
-        </is>
-      </c>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6240,32 +5352,27 @@
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
-      <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
-  (Session info: chrome=150.0.7871.114)
-Stacktrace:
-#0 0x561e1cc3941a &lt;unknown&gt;
-#1 0x561e1c611689 &lt;unknown&gt;
-#2 0x561e1c5f921a &lt;unknown&gt;
-#3 0x561e1c5f8e96 &lt;unknown&gt;
-#4 0x561e1c5f6a7e &lt;unknown&gt;
-#5 0x561e1c5f73ff &lt;unknown&gt;
-#6 0x561e1c6064e0 &lt;unknown&gt;
-#7 0x561e1c6203e7 &lt;unknown&gt;
-#8 0x561e1c627c5b &lt;unknown&gt;
-#9 0x561e1c5f7b59 &lt;unknown&gt;
-</t>
-        </is>
-      </c>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6279,32 +5386,27 @@
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
-      <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr"/>
-      <c r="F177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
-  (Session info: chrome=150.0.7871.114)
-Stacktrace:
-#0 0x561e1cc3941a &lt;unknown&gt;
-#1 0x561e1c611689 &lt;unknown&gt;
-#2 0x561e1c5f921a &lt;unknown&gt;
-#3 0x561e1c5f8e96 &lt;unknown&gt;
-#4 0x561e1c5f6a7e &lt;unknown&gt;
-#5 0x561e1c5f73ff &lt;unknown&gt;
-#6 0x561e1c6064e0 &lt;unknown&gt;
-#7 0x561e1c6203e7 &lt;unknown&gt;
-#8 0x561e1c627c5b &lt;unknown&gt;
-#9 0x561e1c5f7b59 &lt;unknown&gt;
-</t>
-        </is>
-      </c>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6318,10 +5420,26 @@
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
-      <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr"/>
-      <c r="F178" t="inlineStr"/>
-      <c r="G178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H178" t="inlineStr"/>
     </row>
     <row r="179">
@@ -6336,10 +5454,26 @@
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
-      <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr"/>
-      <c r="G179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H179" t="inlineStr"/>
     </row>
     <row r="180">
@@ -6354,10 +5488,26 @@
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
-      <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr"/>
-      <c r="G180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H180" t="inlineStr"/>
     </row>
     <row r="181">
@@ -6371,11 +5521,25 @@
           <t>https://www.amazon.in/dp/B0FCFY1STZ</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr"/>
-      <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr"/>
-      <c r="G181" t="inlineStr"/>
+      <c r="C181" t="n">
+        <v>10279</v>
+      </c>
+      <c r="D181" t="n">
+        <v>1</v>
+      </c>
+      <c r="E181" t="n">
+        <v>1</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H181" t="inlineStr"/>
     </row>
     <row r="182">
@@ -6389,11 +5553,25 @@
           <t>https://www.amazon.in/dp/B0FCFY7Q8J</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr"/>
-      <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr"/>
-      <c r="G182" t="inlineStr"/>
+      <c r="C182" t="n">
+        <v>17129</v>
+      </c>
+      <c r="D182" t="n">
+        <v>1</v>
+      </c>
+      <c r="E182" t="n">
+        <v>1</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H182" t="inlineStr"/>
     </row>
     <row r="183">
@@ -6407,11 +5585,25 @@
           <t>https://www.amazon.in/dp/B0FCFZN9J3</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr"/>
-      <c r="D183" t="inlineStr"/>
-      <c r="E183" t="inlineStr"/>
-      <c r="F183" t="inlineStr"/>
-      <c r="G183" t="inlineStr"/>
+      <c r="C183" t="n">
+        <v>17129</v>
+      </c>
+      <c r="D183" t="n">
+        <v>1</v>
+      </c>
+      <c r="E183" t="n">
+        <v>1</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H183" t="inlineStr"/>
     </row>
     <row r="184">
@@ -6425,11 +5617,25 @@
           <t>https://www.amazon.in/dp/B0FCFW299G</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr"/>
-      <c r="D184" t="inlineStr"/>
-      <c r="E184" t="inlineStr"/>
-      <c r="F184" t="inlineStr"/>
-      <c r="G184" t="inlineStr"/>
+      <c r="C184" t="n">
+        <v>10789</v>
+      </c>
+      <c r="D184" t="n">
+        <v>1</v>
+      </c>
+      <c r="E184" t="n">
+        <v>1</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H184" t="inlineStr"/>
     </row>
     <row r="185">
@@ -6443,11 +5649,25 @@
           <t>https://www.amazon.in/dp/B0FCFW9MXD</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr"/>
-      <c r="D185" t="inlineStr"/>
-      <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr"/>
-      <c r="G185" t="inlineStr"/>
+      <c r="C185" t="n">
+        <v>17129</v>
+      </c>
+      <c r="D185" t="n">
+        <v>1</v>
+      </c>
+      <c r="E185" t="n">
+        <v>1</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H185" t="inlineStr"/>
     </row>
     <row r="186">
@@ -6461,11 +5681,25 @@
           <t>https://www.amazon.in/dp/B0FCG1KFLZ</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr"/>
-      <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
-      <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr"/>
+      <c r="C186" t="n">
+        <v>17129</v>
+      </c>
+      <c r="D186" t="n">
+        <v>1</v>
+      </c>
+      <c r="E186" t="n">
+        <v>1</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Only 2 left in stock.</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H186" t="inlineStr"/>
     </row>
     <row r="187">
@@ -6479,11 +5713,25 @@
           <t>https://www.amazon.in/dp/B0FCFW9FBP</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr"/>
-      <c r="D187" t="inlineStr"/>
-      <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr"/>
-      <c r="G187" t="inlineStr"/>
+      <c r="C187" t="n">
+        <v>10279</v>
+      </c>
+      <c r="D187" t="n">
+        <v>1</v>
+      </c>
+      <c r="E187" t="n">
+        <v>1</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H187" t="inlineStr"/>
     </row>
     <row r="188">
@@ -6497,11 +5745,25 @@
           <t>https://www.amazon.in/dp/B0FCFYS96X</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr"/>
-      <c r="D188" t="inlineStr"/>
-      <c r="E188" t="inlineStr"/>
-      <c r="F188" t="inlineStr"/>
-      <c r="G188" t="inlineStr"/>
+      <c r="C188" t="n">
+        <v>10279</v>
+      </c>
+      <c r="D188" t="n">
+        <v>1</v>
+      </c>
+      <c r="E188" t="n">
+        <v>1</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H188" t="inlineStr"/>
     </row>
     <row r="189">
@@ -6515,11 +5777,25 @@
           <t>https://www.amazon.in/dp/B0FCFW9C1N</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr"/>
-      <c r="D189" t="inlineStr"/>
-      <c r="E189" t="inlineStr"/>
-      <c r="F189" t="inlineStr"/>
-      <c r="G189" t="inlineStr"/>
+      <c r="C189" t="n">
+        <v>10789</v>
+      </c>
+      <c r="D189" t="n">
+        <v>1</v>
+      </c>
+      <c r="E189" t="n">
+        <v>1</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H189" t="inlineStr"/>
     </row>
     <row r="190">
@@ -6533,11 +5809,25 @@
           <t>https://www.amazon.in/dp/B0FCFZDS8Q</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr"/>
-      <c r="D190" t="inlineStr"/>
-      <c r="E190" t="inlineStr"/>
-      <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr"/>
+      <c r="C190" t="n">
+        <v>10789</v>
+      </c>
+      <c r="D190" t="n">
+        <v>1</v>
+      </c>
+      <c r="E190" t="n">
+        <v>1</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H190" t="inlineStr"/>
     </row>
     <row r="191">
@@ -6551,11 +5841,25 @@
           <t>https://www.amazon.in/dp/B0FCFW7CSJ</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr"/>
-      <c r="D191" t="inlineStr"/>
-      <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr"/>
-      <c r="G191" t="inlineStr"/>
+      <c r="C191" t="n">
+        <v>10789</v>
+      </c>
+      <c r="D191" t="n">
+        <v>1</v>
+      </c>
+      <c r="E191" t="n">
+        <v>1</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H191" t="inlineStr"/>
     </row>
     <row r="192">
@@ -6569,11 +5873,25 @@
           <t>https://www.amazon.in/dp/B0DH86V5RG</t>
         </is>
       </c>
-      <c r="C192" t="inlineStr"/>
-      <c r="D192" t="inlineStr"/>
-      <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr"/>
+      <c r="C192" t="n">
+        <v>4499</v>
+      </c>
+      <c r="D192" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E192" t="n">
+        <v>6</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H192" t="inlineStr"/>
     </row>
     <row r="193">
@@ -6587,11 +5905,25 @@
           <t>https://www.amazon.in/dp/B0DH83V742</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr"/>
-      <c r="D193" t="inlineStr"/>
-      <c r="E193" t="inlineStr"/>
-      <c r="F193" t="inlineStr"/>
-      <c r="G193" t="inlineStr"/>
+      <c r="C193" t="n">
+        <v>5779</v>
+      </c>
+      <c r="D193" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E193" t="n">
+        <v>6</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H193" t="inlineStr"/>
     </row>
     <row r="194">
@@ -6605,11 +5937,25 @@
           <t>https://www.amazon.in/dp/B0DH83RPZY</t>
         </is>
       </c>
-      <c r="C194" t="inlineStr"/>
-      <c r="D194" t="inlineStr"/>
-      <c r="E194" t="inlineStr"/>
-      <c r="F194" t="inlineStr"/>
-      <c r="G194" t="inlineStr"/>
+      <c r="C194" t="n">
+        <v>4499</v>
+      </c>
+      <c r="D194" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E194" t="n">
+        <v>6</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Only 2 left in stock.</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H194" t="inlineStr"/>
     </row>
     <row r="195">
@@ -6623,11 +5969,25 @@
           <t>https://www.amazon.in/dp/B0DH84RSQW</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr"/>
-      <c r="D195" t="inlineStr"/>
-      <c r="E195" t="inlineStr"/>
-      <c r="F195" t="inlineStr"/>
-      <c r="G195" t="inlineStr"/>
+      <c r="C195" t="n">
+        <v>5779</v>
+      </c>
+      <c r="D195" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E195" t="n">
+        <v>6</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H195" t="inlineStr"/>
     </row>
     <row r="196">
@@ -6641,11 +6001,25 @@
           <t>https://www.amazon.in/dp/B0DH84HPS3</t>
         </is>
       </c>
-      <c r="C196" t="inlineStr"/>
-      <c r="D196" t="inlineStr"/>
-      <c r="E196" t="inlineStr"/>
-      <c r="F196" t="inlineStr"/>
-      <c r="G196" t="inlineStr"/>
+      <c r="C196" t="n">
+        <v>5779</v>
+      </c>
+      <c r="D196" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E196" t="n">
+        <v>6</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H196" t="inlineStr"/>
     </row>
     <row r="197">
@@ -6659,11 +6033,25 @@
           <t>https://www.amazon.in/dp/B0DH7RFK8H</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr"/>
-      <c r="D197" t="inlineStr"/>
-      <c r="E197" t="inlineStr"/>
-      <c r="F197" t="inlineStr"/>
-      <c r="G197" t="inlineStr"/>
+      <c r="C197" t="n">
+        <v>6849</v>
+      </c>
+      <c r="D197" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E197" t="n">
+        <v>6</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H197" t="inlineStr"/>
     </row>
     <row r="198">
@@ -6677,11 +6065,25 @@
           <t>https://www.amazon.in/dp/B0DH7V4W2R</t>
         </is>
       </c>
-      <c r="C198" t="inlineStr"/>
-      <c r="D198" t="inlineStr"/>
-      <c r="E198" t="inlineStr"/>
-      <c r="F198" t="inlineStr"/>
-      <c r="G198" t="inlineStr"/>
+      <c r="C198" t="n">
+        <v>4499</v>
+      </c>
+      <c r="D198" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E198" t="n">
+        <v>6</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H198" t="inlineStr"/>
     </row>
     <row r="199">
@@ -6695,11 +6097,25 @@
           <t>https://www.amazon.in/dp/B0DH7YMGNW</t>
         </is>
       </c>
-      <c r="C199" t="inlineStr"/>
-      <c r="D199" t="inlineStr"/>
-      <c r="E199" t="inlineStr"/>
-      <c r="F199" t="inlineStr"/>
-      <c r="G199" t="inlineStr"/>
+      <c r="C199" t="n">
+        <v>6849</v>
+      </c>
+      <c r="D199" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E199" t="n">
+        <v>6</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H199" t="inlineStr"/>
     </row>
     <row r="200">
@@ -6713,11 +6129,25 @@
           <t>https://www.amazon.in/dp/B0DH7NG1NF</t>
         </is>
       </c>
-      <c r="C200" t="inlineStr"/>
-      <c r="D200" t="inlineStr"/>
-      <c r="E200" t="inlineStr"/>
-      <c r="F200" t="inlineStr"/>
-      <c r="G200" t="inlineStr"/>
+      <c r="C200" t="n">
+        <v>2589</v>
+      </c>
+      <c r="D200" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E200" t="n">
+        <v>6</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>See all buying options</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H200" t="inlineStr"/>
     </row>
     <row r="201">
@@ -6731,11 +6161,25 @@
           <t>https://www.amazon.in/dp/B0DH84B3NS</t>
         </is>
       </c>
-      <c r="C201" t="inlineStr"/>
-      <c r="D201" t="inlineStr"/>
-      <c r="E201" t="inlineStr"/>
-      <c r="F201" t="inlineStr"/>
-      <c r="G201" t="inlineStr"/>
+      <c r="C201" t="n">
+        <v>6849</v>
+      </c>
+      <c r="D201" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E201" t="n">
+        <v>6</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H201" t="inlineStr"/>
     </row>
     <row r="202">
@@ -6750,10 +6194,26 @@
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
-      <c r="D202" t="inlineStr"/>
-      <c r="E202" t="inlineStr"/>
-      <c r="F202" t="inlineStr"/>
-      <c r="G202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H202" t="inlineStr"/>
     </row>
     <row r="203">
@@ -6767,11 +6227,29 @@
           <t>https://www.amazon.in/dp/B0CMTX7X47</t>
         </is>
       </c>
-      <c r="C203" t="inlineStr"/>
-      <c r="D203" t="inlineStr"/>
-      <c r="E203" t="inlineStr"/>
-      <c r="F203" t="inlineStr"/>
-      <c r="G203" t="inlineStr"/>
+      <c r="C203" t="n">
+        <v>949</v>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H203" t="inlineStr"/>
     </row>
     <row r="204">
@@ -6786,10 +6264,26 @@
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
-      <c r="D204" t="inlineStr"/>
-      <c r="E204" t="inlineStr"/>
-      <c r="F204" t="inlineStr"/>
-      <c r="G204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H204" t="inlineStr"/>
     </row>
     <row r="205">
@@ -6803,11 +6297,29 @@
           <t>https://www.amazon.in/dp/B0F384N4H1</t>
         </is>
       </c>
-      <c r="C205" t="inlineStr"/>
-      <c r="D205" t="inlineStr"/>
-      <c r="E205" t="inlineStr"/>
-      <c r="F205" t="inlineStr"/>
-      <c r="G205" t="inlineStr"/>
+      <c r="C205" t="n">
+        <v>749</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H205" t="inlineStr"/>
     </row>
     <row r="206">
@@ -6822,10 +6334,26 @@
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
-      <c r="D206" t="inlineStr"/>
-      <c r="E206" t="inlineStr"/>
-      <c r="F206" t="inlineStr"/>
-      <c r="G206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H206" t="inlineStr"/>
     </row>
     <row r="207">
@@ -6840,10 +6368,26 @@
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
-      <c r="D207" t="inlineStr"/>
-      <c r="E207" t="inlineStr"/>
-      <c r="F207" t="inlineStr"/>
-      <c r="G207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H207" t="inlineStr"/>
     </row>
     <row r="208">
@@ -6857,11 +6401,29 @@
           <t>https://www.amazon.in/dp/B0CN3DPQ4J</t>
         </is>
       </c>
-      <c r="C208" t="inlineStr"/>
-      <c r="D208" t="inlineStr"/>
-      <c r="E208" t="inlineStr"/>
-      <c r="F208" t="inlineStr"/>
-      <c r="G208" t="inlineStr"/>
+      <c r="C208" t="n">
+        <v>3899</v>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H208" t="inlineStr"/>
     </row>
     <row r="209">
@@ -6875,11 +6437,25 @@
           <t>https://www.amazon.in/dp/B0CQHNM17K</t>
         </is>
       </c>
-      <c r="C209" t="inlineStr"/>
-      <c r="D209" t="inlineStr"/>
-      <c r="E209" t="inlineStr"/>
-      <c r="F209" t="inlineStr"/>
-      <c r="G209" t="inlineStr"/>
+      <c r="C209" t="n">
+        <v>3859</v>
+      </c>
+      <c r="D209" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E209" t="n">
+        <v>237</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H209" t="inlineStr"/>
     </row>
     <row r="210">
@@ -6893,11 +6469,25 @@
           <t>https://www.amazon.in/dp/B0CQHQG61G</t>
         </is>
       </c>
-      <c r="C210" t="inlineStr"/>
-      <c r="D210" t="inlineStr"/>
-      <c r="E210" t="inlineStr"/>
-      <c r="F210" t="inlineStr"/>
-      <c r="G210" t="inlineStr"/>
+      <c r="C210" t="n">
+        <v>3859</v>
+      </c>
+      <c r="D210" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E210" t="n">
+        <v>237</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H210" t="inlineStr"/>
     </row>
     <row r="211">
@@ -6911,11 +6501,25 @@
           <t>https://www.amazon.in/dp/B0D7S5R7CW</t>
         </is>
       </c>
-      <c r="C211" t="inlineStr"/>
-      <c r="D211" t="inlineStr"/>
-      <c r="E211" t="inlineStr"/>
-      <c r="F211" t="inlineStr"/>
-      <c r="G211" t="inlineStr"/>
+      <c r="C211" t="n">
+        <v>3879</v>
+      </c>
+      <c r="D211" t="n">
+        <v>1</v>
+      </c>
+      <c r="E211" t="n">
+        <v>1</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Only 3 left in stock.</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H211" t="inlineStr"/>
     </row>
     <row r="212">
@@ -6929,11 +6533,25 @@
           <t>https://www.amazon.in/dp/B015EAM39Q</t>
         </is>
       </c>
-      <c r="C212" t="inlineStr"/>
-      <c r="D212" t="inlineStr"/>
-      <c r="E212" t="inlineStr"/>
-      <c r="F212" t="inlineStr"/>
-      <c r="G212" t="inlineStr"/>
+      <c r="C212" t="n">
+        <v>619</v>
+      </c>
+      <c r="D212" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E212" t="n">
+        <v>16</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H212" t="inlineStr"/>
     </row>
     <row r="213">
@@ -6947,11 +6565,25 @@
           <t>https://www.amazon.in/dp/B015EAM8MS</t>
         </is>
       </c>
-      <c r="C213" t="inlineStr"/>
-      <c r="D213" t="inlineStr"/>
-      <c r="E213" t="inlineStr"/>
-      <c r="F213" t="inlineStr"/>
-      <c r="G213" t="inlineStr"/>
+      <c r="C213" t="n">
+        <v>619</v>
+      </c>
+      <c r="D213" t="n">
+        <v>4</v>
+      </c>
+      <c r="E213" t="n">
+        <v>55</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H213" t="inlineStr"/>
     </row>
     <row r="214">
@@ -6965,11 +6597,25 @@
           <t>https://www.amazon.in/dp/B015EAMCWO</t>
         </is>
       </c>
-      <c r="C214" t="inlineStr"/>
-      <c r="D214" t="inlineStr"/>
-      <c r="E214" t="inlineStr"/>
-      <c r="F214" t="inlineStr"/>
-      <c r="G214" t="inlineStr"/>
+      <c r="C214" t="n">
+        <v>519</v>
+      </c>
+      <c r="D214" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E214" t="n">
+        <v>25</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H214" t="inlineStr"/>
     </row>
     <row r="215">
@@ -6984,10 +6630,26 @@
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
-      <c r="D215" t="inlineStr"/>
-      <c r="E215" t="inlineStr"/>
-      <c r="F215" t="inlineStr"/>
-      <c r="G215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H215" t="inlineStr"/>
     </row>
     <row r="216">
@@ -7002,10 +6664,26 @@
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
-      <c r="D216" t="inlineStr"/>
-      <c r="E216" t="inlineStr"/>
-      <c r="F216" t="inlineStr"/>
-      <c r="G216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H216" t="inlineStr"/>
     </row>
     <row r="217">
@@ -7019,11 +6697,25 @@
           <t>https://www.amazon.in/dp/B0F9T5C8CD</t>
         </is>
       </c>
-      <c r="C217" t="inlineStr"/>
-      <c r="D217" t="inlineStr"/>
-      <c r="E217" t="inlineStr"/>
-      <c r="F217" t="inlineStr"/>
-      <c r="G217" t="inlineStr"/>
+      <c r="C217" t="n">
+        <v>1479</v>
+      </c>
+      <c r="D217" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E217" t="n">
+        <v>47</v>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H217" t="inlineStr"/>
     </row>
     <row r="218">
@@ -7037,11 +6729,25 @@
           <t>https://www.amazon.in/dp/B0F7XRT6BB</t>
         </is>
       </c>
-      <c r="C218" t="inlineStr"/>
-      <c r="D218" t="inlineStr"/>
-      <c r="E218" t="inlineStr"/>
-      <c r="F218" t="inlineStr"/>
-      <c r="G218" t="inlineStr"/>
+      <c r="C218" t="n">
+        <v>2479</v>
+      </c>
+      <c r="D218" t="n">
+        <v>1</v>
+      </c>
+      <c r="E218" t="n">
+        <v>1</v>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H218" t="inlineStr"/>
     </row>
     <row r="219">
@@ -7056,10 +6762,26 @@
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
-      <c r="D219" t="inlineStr"/>
-      <c r="E219" t="inlineStr"/>
-      <c r="F219" t="inlineStr"/>
-      <c r="G219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H219" t="inlineStr"/>
     </row>
     <row r="220">
@@ -7073,11 +6795,25 @@
           <t>https://www.amazon.in/dp/B0F7RRS6C2</t>
         </is>
       </c>
-      <c r="C220" t="inlineStr"/>
-      <c r="D220" t="inlineStr"/>
-      <c r="E220" t="inlineStr"/>
-      <c r="F220" t="inlineStr"/>
-      <c r="G220" t="inlineStr"/>
+      <c r="C220" t="n">
+        <v>3529</v>
+      </c>
+      <c r="D220" t="n">
+        <v>4</v>
+      </c>
+      <c r="E220" t="n">
+        <v>8</v>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Only 2 left</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H220" t="inlineStr"/>
     </row>
     <row r="221">
@@ -7091,11 +6827,25 @@
           <t>https://www.amazon.in/dp/B0F66M9NNX</t>
         </is>
       </c>
-      <c r="C221" t="inlineStr"/>
-      <c r="D221" t="inlineStr"/>
-      <c r="E221" t="inlineStr"/>
-      <c r="F221" t="inlineStr"/>
-      <c r="G221" t="inlineStr"/>
+      <c r="C221" t="n">
+        <v>3529</v>
+      </c>
+      <c r="D221" t="n">
+        <v>4</v>
+      </c>
+      <c r="E221" t="n">
+        <v>8</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Only 2 left</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H221" t="inlineStr"/>
     </row>
     <row r="222">
@@ -7109,11 +6859,25 @@
           <t>https://www.amazon.in/dp/B0F6YJD7TK</t>
         </is>
       </c>
-      <c r="C222" t="inlineStr"/>
-      <c r="D222" t="inlineStr"/>
-      <c r="E222" t="inlineStr"/>
-      <c r="F222" t="inlineStr"/>
-      <c r="G222" t="inlineStr"/>
+      <c r="C222" t="n">
+        <v>3529</v>
+      </c>
+      <c r="D222" t="n">
+        <v>4</v>
+      </c>
+      <c r="E222" t="n">
+        <v>8</v>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Only 2 left</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H222" t="inlineStr"/>
     </row>
     <row r="223">
@@ -7127,11 +6891,25 @@
           <t>https://www.amazon.in/dp/B0F74FGS4P</t>
         </is>
       </c>
-      <c r="C223" t="inlineStr"/>
-      <c r="D223" t="inlineStr"/>
-      <c r="E223" t="inlineStr"/>
-      <c r="F223" t="inlineStr"/>
-      <c r="G223" t="inlineStr"/>
+      <c r="C223" t="n">
+        <v>4869</v>
+      </c>
+      <c r="D223" t="n">
+        <v>5</v>
+      </c>
+      <c r="E223" t="n">
+        <v>3</v>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H223" t="inlineStr"/>
     </row>
     <row r="224">
@@ -7145,11 +6923,25 @@
           <t>https://www.amazon.in/dp/B0F74HQLHK</t>
         </is>
       </c>
-      <c r="C224" t="inlineStr"/>
-      <c r="D224" t="inlineStr"/>
-      <c r="E224" t="inlineStr"/>
-      <c r="F224" t="inlineStr"/>
-      <c r="G224" t="inlineStr"/>
+      <c r="C224" t="n">
+        <v>4869</v>
+      </c>
+      <c r="D224" t="n">
+        <v>5</v>
+      </c>
+      <c r="E224" t="n">
+        <v>3</v>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H224" t="inlineStr"/>
     </row>
     <row r="225">
@@ -7163,11 +6955,25 @@
           <t>https://www.amazon.in/dp/B0F74DD2SD</t>
         </is>
       </c>
-      <c r="C225" t="inlineStr"/>
-      <c r="D225" t="inlineStr"/>
-      <c r="E225" t="inlineStr"/>
-      <c r="F225" t="inlineStr"/>
-      <c r="G225" t="inlineStr"/>
+      <c r="C225" t="n">
+        <v>4869</v>
+      </c>
+      <c r="D225" t="n">
+        <v>5</v>
+      </c>
+      <c r="E225" t="n">
+        <v>3</v>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H225" t="inlineStr"/>
     </row>
     <row r="226">
@@ -7181,11 +6987,25 @@
           <t>https://www.amazon.in/dp/B0F5QLVD15</t>
         </is>
       </c>
-      <c r="C226" t="inlineStr"/>
-      <c r="D226" t="inlineStr"/>
-      <c r="E226" t="inlineStr"/>
-      <c r="F226" t="inlineStr"/>
-      <c r="G226" t="inlineStr"/>
+      <c r="C226" t="n">
+        <v>1659</v>
+      </c>
+      <c r="D226" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E226" t="n">
+        <v>1655</v>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H226" t="inlineStr"/>
     </row>
     <row r="227">
@@ -7199,11 +7019,25 @@
           <t>https://www.amazon.in/dp/B0DPKFT27W</t>
         </is>
       </c>
-      <c r="C227" t="inlineStr"/>
-      <c r="D227" t="inlineStr"/>
-      <c r="E227" t="inlineStr"/>
-      <c r="F227" t="inlineStr"/>
-      <c r="G227" t="inlineStr"/>
+      <c r="C227" t="n">
+        <v>1659</v>
+      </c>
+      <c r="D227" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E227" t="n">
+        <v>1655</v>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H227" t="inlineStr"/>
     </row>
     <row r="228">
@@ -7217,11 +7051,25 @@
           <t>https://www.amazon.in/dp/B0D3FCZXVX</t>
         </is>
       </c>
-      <c r="C228" t="inlineStr"/>
-      <c r="D228" t="inlineStr"/>
-      <c r="E228" t="inlineStr"/>
-      <c r="F228" t="inlineStr"/>
-      <c r="G228" t="inlineStr"/>
+      <c r="C228" t="n">
+        <v>4369</v>
+      </c>
+      <c r="D228" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E228" t="n">
+        <v>30</v>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H228" t="inlineStr"/>
     </row>
     <row r="229">
@@ -7235,11 +7083,25 @@
           <t>https://www.amazon.in/dp/B0CKB9VZTM</t>
         </is>
       </c>
-      <c r="C229" t="inlineStr"/>
-      <c r="D229" t="inlineStr"/>
-      <c r="E229" t="inlineStr"/>
-      <c r="F229" t="inlineStr"/>
-      <c r="G229" t="inlineStr"/>
+      <c r="C229" t="n">
+        <v>1399</v>
+      </c>
+      <c r="D229" t="n">
+        <v>3</v>
+      </c>
+      <c r="E229" t="n">
+        <v>7</v>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H229" t="inlineStr"/>
     </row>
     <row r="230">
@@ -7254,10 +7116,26 @@
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
-      <c r="D230" t="inlineStr"/>
-      <c r="E230" t="inlineStr"/>
-      <c r="F230" t="inlineStr"/>
-      <c r="G230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H230" t="inlineStr"/>
     </row>
     <row r="231">
@@ -7271,11 +7149,25 @@
           <t>https://www.amazon.in/dp/B0F66L3FXF</t>
         </is>
       </c>
-      <c r="C231" t="inlineStr"/>
-      <c r="D231" t="inlineStr"/>
-      <c r="E231" t="inlineStr"/>
-      <c r="F231" t="inlineStr"/>
-      <c r="G231" t="inlineStr"/>
+      <c r="C231" t="n">
+        <v>10839</v>
+      </c>
+      <c r="D231" t="n">
+        <v>5</v>
+      </c>
+      <c r="E231" t="n">
+        <v>3</v>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Only 2 left in stock.</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H231" t="inlineStr"/>
     </row>
     <row r="232">
@@ -7289,11 +7181,25 @@
           <t>https://www.amazon.in/dp/B0F66H6N26</t>
         </is>
       </c>
-      <c r="C232" t="inlineStr"/>
-      <c r="D232" t="inlineStr"/>
-      <c r="E232" t="inlineStr"/>
-      <c r="F232" t="inlineStr"/>
-      <c r="G232" t="inlineStr"/>
+      <c r="C232" t="n">
+        <v>10839</v>
+      </c>
+      <c r="D232" t="n">
+        <v>5</v>
+      </c>
+      <c r="E232" t="n">
+        <v>3</v>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H232" t="inlineStr"/>
     </row>
     <row r="233">
@@ -7307,11 +7213,25 @@
           <t>https://www.amazon.in/dp/B0F66MD6B9</t>
         </is>
       </c>
-      <c r="C233" t="inlineStr"/>
-      <c r="D233" t="inlineStr"/>
-      <c r="E233" t="inlineStr"/>
-      <c r="F233" t="inlineStr"/>
-      <c r="G233" t="inlineStr"/>
+      <c r="C233" t="n">
+        <v>10839</v>
+      </c>
+      <c r="D233" t="n">
+        <v>5</v>
+      </c>
+      <c r="E233" t="n">
+        <v>3</v>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Only 2 left in stock.</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H233" t="inlineStr"/>
     </row>
     <row r="234">
@@ -7325,11 +7245,25 @@
           <t>https://www.amazon.in/dp/B0F66KBPSX</t>
         </is>
       </c>
-      <c r="C234" t="inlineStr"/>
-      <c r="D234" t="inlineStr"/>
-      <c r="E234" t="inlineStr"/>
-      <c r="F234" t="inlineStr"/>
-      <c r="G234" t="inlineStr"/>
+      <c r="C234" t="n">
+        <v>10839</v>
+      </c>
+      <c r="D234" t="n">
+        <v>5</v>
+      </c>
+      <c r="E234" t="n">
+        <v>3</v>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H234" t="inlineStr"/>
     </row>
     <row r="235">
@@ -7343,11 +7277,25 @@
           <t>https://www.amazon.in/dp/B0F66KFXDX</t>
         </is>
       </c>
-      <c r="C235" t="inlineStr"/>
-      <c r="D235" t="inlineStr"/>
-      <c r="E235" t="inlineStr"/>
-      <c r="F235" t="inlineStr"/>
-      <c r="G235" t="inlineStr"/>
+      <c r="C235" t="n">
+        <v>10839</v>
+      </c>
+      <c r="D235" t="n">
+        <v>5</v>
+      </c>
+      <c r="E235" t="n">
+        <v>3</v>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H235" t="inlineStr"/>
     </row>
     <row r="236">
@@ -7361,11 +7309,25 @@
           <t>https://www.amazon.in/dp/B0F66GTYTR</t>
         </is>
       </c>
-      <c r="C236" t="inlineStr"/>
-      <c r="D236" t="inlineStr"/>
-      <c r="E236" t="inlineStr"/>
-      <c r="F236" t="inlineStr"/>
-      <c r="G236" t="inlineStr"/>
+      <c r="C236" t="n">
+        <v>39129</v>
+      </c>
+      <c r="D236" t="n">
+        <v>5</v>
+      </c>
+      <c r="E236" t="n">
+        <v>3</v>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H236" t="inlineStr"/>
     </row>
     <row r="237">
@@ -7379,11 +7341,25 @@
           <t>https://www.amazon.in/dp/B0F66GD2BQ</t>
         </is>
       </c>
-      <c r="C237" t="inlineStr"/>
-      <c r="D237" t="inlineStr"/>
-      <c r="E237" t="inlineStr"/>
-      <c r="F237" t="inlineStr"/>
-      <c r="G237" t="inlineStr"/>
+      <c r="C237" t="n">
+        <v>39129</v>
+      </c>
+      <c r="D237" t="n">
+        <v>5</v>
+      </c>
+      <c r="E237" t="n">
+        <v>3</v>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H237" t="inlineStr"/>
     </row>
     <row r="238">
@@ -7397,11 +7373,25 @@
           <t>https://www.amazon.in/dp/B0F66MC7VX</t>
         </is>
       </c>
-      <c r="C238" t="inlineStr"/>
-      <c r="D238" t="inlineStr"/>
-      <c r="E238" t="inlineStr"/>
-      <c r="F238" t="inlineStr"/>
-      <c r="G238" t="inlineStr"/>
+      <c r="C238" t="n">
+        <v>39129</v>
+      </c>
+      <c r="D238" t="n">
+        <v>5</v>
+      </c>
+      <c r="E238" t="n">
+        <v>3</v>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H238" t="inlineStr"/>
     </row>
     <row r="239">
@@ -7415,11 +7405,25 @@
           <t>https://www.amazon.in/dp/B0F66GS3NN</t>
         </is>
       </c>
-      <c r="C239" t="inlineStr"/>
-      <c r="D239" t="inlineStr"/>
-      <c r="E239" t="inlineStr"/>
-      <c r="F239" t="inlineStr"/>
-      <c r="G239" t="inlineStr"/>
+      <c r="C239" t="n">
+        <v>39129</v>
+      </c>
+      <c r="D239" t="n">
+        <v>5</v>
+      </c>
+      <c r="E239" t="n">
+        <v>3</v>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H239" t="inlineStr"/>
     </row>
     <row r="240">
@@ -7433,11 +7437,25 @@
           <t>https://www.amazon.in/dp/B0F66DWDG1</t>
         </is>
       </c>
-      <c r="C240" t="inlineStr"/>
-      <c r="D240" t="inlineStr"/>
-      <c r="E240" t="inlineStr"/>
-      <c r="F240" t="inlineStr"/>
-      <c r="G240" t="inlineStr"/>
+      <c r="C240" t="n">
+        <v>39129</v>
+      </c>
+      <c r="D240" t="n">
+        <v>5</v>
+      </c>
+      <c r="E240" t="n">
+        <v>3</v>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H240" t="inlineStr"/>
     </row>
     <row r="241">
@@ -7451,11 +7469,25 @@
           <t>https://www.amazon.in/dp/B0F66LLZNZ</t>
         </is>
       </c>
-      <c r="C241" t="inlineStr"/>
-      <c r="D241" t="inlineStr"/>
-      <c r="E241" t="inlineStr"/>
-      <c r="F241" t="inlineStr"/>
-      <c r="G241" t="inlineStr"/>
+      <c r="C241" t="n">
+        <v>13249</v>
+      </c>
+      <c r="D241" t="n">
+        <v>5</v>
+      </c>
+      <c r="E241" t="n">
+        <v>3</v>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H241" t="inlineStr"/>
     </row>
     <row r="242">
@@ -7469,11 +7501,25 @@
           <t>https://www.amazon.in/dp/B0F66MMWS4</t>
         </is>
       </c>
-      <c r="C242" t="inlineStr"/>
-      <c r="D242" t="inlineStr"/>
-      <c r="E242" t="inlineStr"/>
-      <c r="F242" t="inlineStr"/>
-      <c r="G242" t="inlineStr"/>
+      <c r="C242" t="n">
+        <v>13249</v>
+      </c>
+      <c r="D242" t="n">
+        <v>5</v>
+      </c>
+      <c r="E242" t="n">
+        <v>3</v>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H242" t="inlineStr"/>
     </row>
     <row r="243">
@@ -7487,11 +7533,25 @@
           <t>https://www.amazon.in/dp/B0F66G97FD</t>
         </is>
       </c>
-      <c r="C243" t="inlineStr"/>
-      <c r="D243" t="inlineStr"/>
-      <c r="E243" t="inlineStr"/>
-      <c r="F243" t="inlineStr"/>
-      <c r="G243" t="inlineStr"/>
+      <c r="C243" t="n">
+        <v>13249</v>
+      </c>
+      <c r="D243" t="n">
+        <v>5</v>
+      </c>
+      <c r="E243" t="n">
+        <v>3</v>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H243" t="inlineStr"/>
     </row>
     <row r="244">
@@ -7505,11 +7565,25 @@
           <t>https://www.amazon.in/dp/B0F66KJHRY</t>
         </is>
       </c>
-      <c r="C244" t="inlineStr"/>
-      <c r="D244" t="inlineStr"/>
-      <c r="E244" t="inlineStr"/>
-      <c r="F244" t="inlineStr"/>
-      <c r="G244" t="inlineStr"/>
+      <c r="C244" t="n">
+        <v>13249</v>
+      </c>
+      <c r="D244" t="n">
+        <v>5</v>
+      </c>
+      <c r="E244" t="n">
+        <v>3</v>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H244" t="inlineStr"/>
     </row>
     <row r="245">
@@ -7523,11 +7597,25 @@
           <t>https://www.amazon.in/dp/B0F66G931N</t>
         </is>
       </c>
-      <c r="C245" t="inlineStr"/>
-      <c r="D245" t="inlineStr"/>
-      <c r="E245" t="inlineStr"/>
-      <c r="F245" t="inlineStr"/>
-      <c r="G245" t="inlineStr"/>
+      <c r="C245" t="n">
+        <v>13249</v>
+      </c>
+      <c r="D245" t="n">
+        <v>5</v>
+      </c>
+      <c r="E245" t="n">
+        <v>3</v>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H245" t="inlineStr"/>
     </row>
     <row r="246">
@@ -7541,11 +7629,25 @@
           <t>https://www.amazon.in/dp/B0F66LDLYW</t>
         </is>
       </c>
-      <c r="C246" t="inlineStr"/>
-      <c r="D246" t="inlineStr"/>
-      <c r="E246" t="inlineStr"/>
-      <c r="F246" t="inlineStr"/>
-      <c r="G246" t="inlineStr"/>
+      <c r="C246" t="n">
+        <v>15049</v>
+      </c>
+      <c r="D246" t="n">
+        <v>5</v>
+      </c>
+      <c r="E246" t="n">
+        <v>3</v>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H246" t="inlineStr"/>
     </row>
     <row r="247">
@@ -7559,11 +7661,25 @@
           <t>https://www.amazon.in/dp/B0F66PG7TF</t>
         </is>
       </c>
-      <c r="C247" t="inlineStr"/>
-      <c r="D247" t="inlineStr"/>
-      <c r="E247" t="inlineStr"/>
-      <c r="F247" t="inlineStr"/>
-      <c r="G247" t="inlineStr"/>
+      <c r="C247" t="n">
+        <v>15049</v>
+      </c>
+      <c r="D247" t="n">
+        <v>5</v>
+      </c>
+      <c r="E247" t="n">
+        <v>3</v>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H247" t="inlineStr"/>
     </row>
     <row r="248">
@@ -7577,11 +7693,25 @@
           <t>https://www.amazon.in/dp/B0F66FSY9Y</t>
         </is>
       </c>
-      <c r="C248" t="inlineStr"/>
-      <c r="D248" t="inlineStr"/>
-      <c r="E248" t="inlineStr"/>
-      <c r="F248" t="inlineStr"/>
-      <c r="G248" t="inlineStr"/>
+      <c r="C248" t="n">
+        <v>15049</v>
+      </c>
+      <c r="D248" t="n">
+        <v>5</v>
+      </c>
+      <c r="E248" t="n">
+        <v>3</v>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H248" t="inlineStr"/>
     </row>
     <row r="249">
@@ -7595,11 +7725,25 @@
           <t>https://www.amazon.in/dp/B0F66NFX4M</t>
         </is>
       </c>
-      <c r="C249" t="inlineStr"/>
-      <c r="D249" t="inlineStr"/>
-      <c r="E249" t="inlineStr"/>
-      <c r="F249" t="inlineStr"/>
-      <c r="G249" t="inlineStr"/>
+      <c r="C249" t="n">
+        <v>15049</v>
+      </c>
+      <c r="D249" t="n">
+        <v>5</v>
+      </c>
+      <c r="E249" t="n">
+        <v>3</v>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H249" t="inlineStr"/>
     </row>
     <row r="250">
@@ -7613,11 +7757,25 @@
           <t>https://www.amazon.in/dp/B0F66GXZ5W</t>
         </is>
       </c>
-      <c r="C250" t="inlineStr"/>
-      <c r="D250" t="inlineStr"/>
-      <c r="E250" t="inlineStr"/>
-      <c r="F250" t="inlineStr"/>
-      <c r="G250" t="inlineStr"/>
+      <c r="C250" t="n">
+        <v>15049</v>
+      </c>
+      <c r="D250" t="n">
+        <v>5</v>
+      </c>
+      <c r="E250" t="n">
+        <v>3</v>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H250" t="inlineStr"/>
     </row>
     <row r="251">
@@ -7631,11 +7789,25 @@
           <t>https://www.amazon.in/dp/B0C3MHG797</t>
         </is>
       </c>
-      <c r="C251" t="inlineStr"/>
-      <c r="D251" t="inlineStr"/>
-      <c r="E251" t="inlineStr"/>
-      <c r="F251" t="inlineStr"/>
-      <c r="G251" t="inlineStr"/>
+      <c r="C251" t="n">
+        <v>2369</v>
+      </c>
+      <c r="D251" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E251" t="n">
+        <v>594</v>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H251" t="inlineStr"/>
     </row>
     <row r="252">
@@ -7649,11 +7821,25 @@
           <t>https://www.amazon.in/dp/B0C3MH4NDY</t>
         </is>
       </c>
-      <c r="C252" t="inlineStr"/>
-      <c r="D252" t="inlineStr"/>
-      <c r="E252" t="inlineStr"/>
-      <c r="F252" t="inlineStr"/>
-      <c r="G252" t="inlineStr"/>
+      <c r="C252" t="n">
+        <v>3429</v>
+      </c>
+      <c r="D252" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E252" t="n">
+        <v>594</v>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H252" t="inlineStr"/>
     </row>
     <row r="253">
@@ -7667,11 +7853,25 @@
           <t>https://www.amazon.in/dp/B0C3MG4MJG</t>
         </is>
       </c>
-      <c r="C253" t="inlineStr"/>
-      <c r="D253" t="inlineStr"/>
-      <c r="E253" t="inlineStr"/>
-      <c r="F253" t="inlineStr"/>
-      <c r="G253" t="inlineStr"/>
+      <c r="C253" t="n">
+        <v>2369</v>
+      </c>
+      <c r="D253" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E253" t="n">
+        <v>594</v>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H253" t="inlineStr"/>
     </row>
     <row r="254">
@@ -7686,10 +7886,26 @@
         </is>
       </c>
       <c r="C254" t="inlineStr"/>
-      <c r="D254" t="inlineStr"/>
-      <c r="E254" t="inlineStr"/>
-      <c r="F254" t="inlineStr"/>
-      <c r="G254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H254" t="inlineStr"/>
     </row>
     <row r="255">
@@ -7703,11 +7919,25 @@
           <t>https://www.amazon.in/dp/B0F74JVKY9</t>
         </is>
       </c>
-      <c r="C255" t="inlineStr"/>
-      <c r="D255" t="inlineStr"/>
-      <c r="E255" t="inlineStr"/>
-      <c r="F255" t="inlineStr"/>
-      <c r="G255" t="inlineStr"/>
+      <c r="C255" t="n">
+        <v>4239</v>
+      </c>
+      <c r="D255" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E255" t="n">
+        <v>15</v>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H255" t="inlineStr"/>
     </row>
     <row r="256">
@@ -7721,11 +7951,25 @@
           <t>https://www.amazon.in/dp/B0CQ529M31</t>
         </is>
       </c>
-      <c r="C256" t="inlineStr"/>
-      <c r="D256" t="inlineStr"/>
-      <c r="E256" t="inlineStr"/>
-      <c r="F256" t="inlineStr"/>
-      <c r="G256" t="inlineStr"/>
+      <c r="C256" t="n">
+        <v>4239</v>
+      </c>
+      <c r="D256" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E256" t="n">
+        <v>15</v>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H256" t="inlineStr"/>
     </row>
     <row r="257">
@@ -7739,11 +7983,25 @@
           <t>https://www.amazon.in/dp/B0D3PQJRBJ</t>
         </is>
       </c>
-      <c r="C257" t="inlineStr"/>
-      <c r="D257" t="inlineStr"/>
-      <c r="E257" t="inlineStr"/>
-      <c r="F257" t="inlineStr"/>
-      <c r="G257" t="inlineStr"/>
+      <c r="C257" t="n">
+        <v>4639</v>
+      </c>
+      <c r="D257" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E257" t="n">
+        <v>14</v>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H257" t="inlineStr"/>
     </row>
     <row r="258">
@@ -7757,11 +8015,25 @@
           <t>https://www.amazon.in/dp/B0DH7R21BT</t>
         </is>
       </c>
-      <c r="C258" t="inlineStr"/>
-      <c r="D258" t="inlineStr"/>
-      <c r="E258" t="inlineStr"/>
-      <c r="F258" t="inlineStr"/>
-      <c r="G258" t="inlineStr"/>
+      <c r="C258" t="n">
+        <v>4999</v>
+      </c>
+      <c r="D258" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E258" t="n">
+        <v>5</v>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H258" t="inlineStr"/>
     </row>
     <row r="259">
@@ -7775,11 +8047,25 @@
           <t>https://www.amazon.in/dp/B0DH84WK81</t>
         </is>
       </c>
-      <c r="C259" t="inlineStr"/>
-      <c r="D259" t="inlineStr"/>
-      <c r="E259" t="inlineStr"/>
-      <c r="F259" t="inlineStr"/>
-      <c r="G259" t="inlineStr"/>
+      <c r="C259" t="n">
+        <v>4879</v>
+      </c>
+      <c r="D259" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E259" t="n">
+        <v>5</v>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H259" t="inlineStr"/>
     </row>
     <row r="260">
@@ -7793,11 +8079,25 @@
           <t>https://www.amazon.in/dp/B0DH7WH458</t>
         </is>
       </c>
-      <c r="C260" t="inlineStr"/>
-      <c r="D260" t="inlineStr"/>
-      <c r="E260" t="inlineStr"/>
-      <c r="F260" t="inlineStr"/>
-      <c r="G260" t="inlineStr"/>
+      <c r="C260" t="n">
+        <v>4879</v>
+      </c>
+      <c r="D260" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E260" t="n">
+        <v>5</v>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Only 2 left in stock.</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H260" t="inlineStr"/>
     </row>
     <row r="261">
@@ -7811,11 +8111,25 @@
           <t>https://www.amazon.in/dp/B0DH823YKC</t>
         </is>
       </c>
-      <c r="C261" t="inlineStr"/>
-      <c r="D261" t="inlineStr"/>
-      <c r="E261" t="inlineStr"/>
-      <c r="F261" t="inlineStr"/>
-      <c r="G261" t="inlineStr"/>
+      <c r="C261" t="n">
+        <v>4879</v>
+      </c>
+      <c r="D261" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E261" t="n">
+        <v>5</v>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H261" t="inlineStr"/>
     </row>
     <row r="262">
@@ -7829,11 +8143,25 @@
           <t>https://www.amazon.in/dp/B0DH83S3RF</t>
         </is>
       </c>
-      <c r="C262" t="inlineStr"/>
-      <c r="D262" t="inlineStr"/>
-      <c r="E262" t="inlineStr"/>
-      <c r="F262" t="inlineStr"/>
-      <c r="G262" t="inlineStr"/>
+      <c r="C262" t="n">
+        <v>4999</v>
+      </c>
+      <c r="D262" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E262" t="n">
+        <v>5</v>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H262" t="inlineStr"/>
     </row>
     <row r="263">
@@ -7847,11 +8175,25 @@
           <t>https://www.amazon.in/dp/B0DH7ZW8WT</t>
         </is>
       </c>
-      <c r="C263" t="inlineStr"/>
-      <c r="D263" t="inlineStr"/>
-      <c r="E263" t="inlineStr"/>
-      <c r="F263" t="inlineStr"/>
-      <c r="G263" t="inlineStr"/>
+      <c r="C263" t="n">
+        <v>5909</v>
+      </c>
+      <c r="D263" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E263" t="n">
+        <v>5</v>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H263" t="inlineStr"/>
     </row>
     <row r="264">
@@ -7865,11 +8207,25 @@
           <t>https://www.amazon.in/dp/B0DH8CVH7L</t>
         </is>
       </c>
-      <c r="C264" t="inlineStr"/>
-      <c r="D264" t="inlineStr"/>
-      <c r="E264" t="inlineStr"/>
-      <c r="F264" t="inlineStr"/>
-      <c r="G264" t="inlineStr"/>
+      <c r="C264" t="n">
+        <v>4879</v>
+      </c>
+      <c r="D264" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E264" t="n">
+        <v>5</v>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Only 2 left in stock.</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H264" t="inlineStr"/>
     </row>
     <row r="265">
@@ -7883,11 +8239,25 @@
           <t>https://www.amazon.in/dp/B0DH7HZHF2</t>
         </is>
       </c>
-      <c r="C265" t="inlineStr"/>
-      <c r="D265" t="inlineStr"/>
-      <c r="E265" t="inlineStr"/>
-      <c r="F265" t="inlineStr"/>
-      <c r="G265" t="inlineStr"/>
+      <c r="C265" t="n">
+        <v>4999</v>
+      </c>
+      <c r="D265" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E265" t="n">
+        <v>5</v>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H265" t="inlineStr"/>
     </row>
     <row r="266">
@@ -7901,11 +8271,25 @@
           <t>https://www.amazon.in/dp/B0DH7ZYQQX</t>
         </is>
       </c>
-      <c r="C266" t="inlineStr"/>
-      <c r="D266" t="inlineStr"/>
-      <c r="E266" t="inlineStr"/>
-      <c r="F266" t="inlineStr"/>
-      <c r="G266" t="inlineStr"/>
+      <c r="C266" t="n">
+        <v>4999</v>
+      </c>
+      <c r="D266" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E266" t="n">
+        <v>5</v>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H266" t="inlineStr"/>
     </row>
     <row r="267">
@@ -7919,11 +8303,25 @@
           <t>https://www.amazon.in/dp/B0DH7X28RP</t>
         </is>
       </c>
-      <c r="C267" t="inlineStr"/>
-      <c r="D267" t="inlineStr"/>
-      <c r="E267" t="inlineStr"/>
-      <c r="F267" t="inlineStr"/>
-      <c r="G267" t="inlineStr"/>
+      <c r="C267" t="n">
+        <v>4879</v>
+      </c>
+      <c r="D267" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E267" t="n">
+        <v>5</v>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H267" t="inlineStr"/>
     </row>
     <row r="268">
@@ -7937,11 +8335,25 @@
           <t>https://www.amazon.in/dp/B0DH86FNDS</t>
         </is>
       </c>
-      <c r="C268" t="inlineStr"/>
-      <c r="D268" t="inlineStr"/>
-      <c r="E268" t="inlineStr"/>
-      <c r="F268" t="inlineStr"/>
-      <c r="G268" t="inlineStr"/>
+      <c r="C268" t="n">
+        <v>6939</v>
+      </c>
+      <c r="D268" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E268" t="n">
+        <v>5</v>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H268" t="inlineStr"/>
     </row>
     <row r="269">
@@ -7955,11 +8367,25 @@
           <t>https://www.amazon.in/dp/B0DH7WBNPD</t>
         </is>
       </c>
-      <c r="C269" t="inlineStr"/>
-      <c r="D269" t="inlineStr"/>
-      <c r="E269" t="inlineStr"/>
-      <c r="F269" t="inlineStr"/>
-      <c r="G269" t="inlineStr"/>
+      <c r="C269" t="n">
+        <v>4879</v>
+      </c>
+      <c r="D269" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E269" t="n">
+        <v>5</v>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H269" t="inlineStr"/>
     </row>
     <row r="270">
@@ -7974,10 +8400,26 @@
         </is>
       </c>
       <c r="C270" t="inlineStr"/>
-      <c r="D270" t="inlineStr"/>
-      <c r="E270" t="inlineStr"/>
-      <c r="F270" t="inlineStr"/>
-      <c r="G270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H270" t="inlineStr"/>
     </row>
     <row r="271">
@@ -7991,11 +8433,25 @@
           <t>https://www.amazon.in/dp/B0C77BNM7P</t>
         </is>
       </c>
-      <c r="C271" t="inlineStr"/>
-      <c r="D271" t="inlineStr"/>
-      <c r="E271" t="inlineStr"/>
-      <c r="F271" t="inlineStr"/>
-      <c r="G271" t="inlineStr"/>
+      <c r="C271" t="n">
+        <v>649</v>
+      </c>
+      <c r="D271" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E271" t="n">
+        <v>2</v>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H271" t="inlineStr"/>
     </row>
     <row r="272">
@@ -8009,11 +8465,25 @@
           <t>https://www.amazon.in/dp/B0CMXT4X1V</t>
         </is>
       </c>
-      <c r="C272" t="inlineStr"/>
-      <c r="D272" t="inlineStr"/>
-      <c r="E272" t="inlineStr"/>
-      <c r="F272" t="inlineStr"/>
-      <c r="G272" t="inlineStr"/>
+      <c r="C272" t="n">
+        <v>999</v>
+      </c>
+      <c r="D272" t="n">
+        <v>1</v>
+      </c>
+      <c r="E272" t="n">
+        <v>6</v>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H272" t="inlineStr"/>
     </row>
     <row r="273">
@@ -8027,11 +8497,25 @@
           <t>https://www.amazon.in/dp/B0DXF7BTF2</t>
         </is>
       </c>
-      <c r="C273" t="inlineStr"/>
-      <c r="D273" t="inlineStr"/>
-      <c r="E273" t="inlineStr"/>
-      <c r="F273" t="inlineStr"/>
-      <c r="G273" t="inlineStr"/>
+      <c r="C273" t="n">
+        <v>3509</v>
+      </c>
+      <c r="D273" t="n">
+        <v>5</v>
+      </c>
+      <c r="E273" t="n">
+        <v>3</v>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H273" t="inlineStr"/>
     </row>
     <row r="274">
@@ -8046,10 +8530,26 @@
         </is>
       </c>
       <c r="C274" t="inlineStr"/>
-      <c r="D274" t="inlineStr"/>
-      <c r="E274" t="inlineStr"/>
-      <c r="F274" t="inlineStr"/>
-      <c r="G274" t="inlineStr"/>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H274" t="inlineStr"/>
     </row>
     <row r="275">
@@ -8064,10 +8564,26 @@
         </is>
       </c>
       <c r="C275" t="inlineStr"/>
-      <c r="D275" t="inlineStr"/>
-      <c r="E275" t="inlineStr"/>
-      <c r="F275" t="inlineStr"/>
-      <c r="G275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H275" t="inlineStr"/>
     </row>
     <row r="276">
@@ -8081,11 +8597,25 @@
           <t>https://www.amazon.in/dp/B0DXF84GZC</t>
         </is>
       </c>
-      <c r="C276" t="inlineStr"/>
-      <c r="D276" t="inlineStr"/>
-      <c r="E276" t="inlineStr"/>
-      <c r="F276" t="inlineStr"/>
-      <c r="G276" t="inlineStr"/>
+      <c r="C276" t="n">
+        <v>3509</v>
+      </c>
+      <c r="D276" t="n">
+        <v>5</v>
+      </c>
+      <c r="E276" t="n">
+        <v>3</v>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H276" t="inlineStr"/>
     </row>
     <row r="277">
@@ -8099,11 +8629,25 @@
           <t>https://www.amazon.in/dp/B0DXF6WJKS</t>
         </is>
       </c>
-      <c r="C277" t="inlineStr"/>
-      <c r="D277" t="inlineStr"/>
-      <c r="E277" t="inlineStr"/>
-      <c r="F277" t="inlineStr"/>
-      <c r="G277" t="inlineStr"/>
+      <c r="C277" t="n">
+        <v>3509</v>
+      </c>
+      <c r="D277" t="n">
+        <v>5</v>
+      </c>
+      <c r="E277" t="n">
+        <v>3</v>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H277" t="inlineStr"/>
     </row>
     <row r="278">
@@ -8117,11 +8661,25 @@
           <t>https://www.amazon.in/dp/B0DXF7DDFJ</t>
         </is>
       </c>
-      <c r="C278" t="inlineStr"/>
-      <c r="D278" t="inlineStr"/>
-      <c r="E278" t="inlineStr"/>
-      <c r="F278" t="inlineStr"/>
-      <c r="G278" t="inlineStr"/>
+      <c r="C278" t="n">
+        <v>3509</v>
+      </c>
+      <c r="D278" t="n">
+        <v>5</v>
+      </c>
+      <c r="E278" t="n">
+        <v>3</v>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H278" t="inlineStr"/>
     </row>
     <row r="279">
@@ -8135,11 +8693,25 @@
           <t>https://www.amazon.in/dp/B0DXF86WC6</t>
         </is>
       </c>
-      <c r="C279" t="inlineStr"/>
-      <c r="D279" t="inlineStr"/>
-      <c r="E279" t="inlineStr"/>
-      <c r="F279" t="inlineStr"/>
-      <c r="G279" t="inlineStr"/>
+      <c r="C279" t="n">
+        <v>3509</v>
+      </c>
+      <c r="D279" t="n">
+        <v>5</v>
+      </c>
+      <c r="E279" t="n">
+        <v>3</v>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H279" t="inlineStr"/>
     </row>
     <row r="280">
@@ -8153,11 +8725,25 @@
           <t>https://www.amazon.in/dp/B0DXF7JFDJ</t>
         </is>
       </c>
-      <c r="C280" t="inlineStr"/>
-      <c r="D280" t="inlineStr"/>
-      <c r="E280" t="inlineStr"/>
-      <c r="F280" t="inlineStr"/>
-      <c r="G280" t="inlineStr"/>
+      <c r="C280" t="n">
+        <v>3509</v>
+      </c>
+      <c r="D280" t="n">
+        <v>5</v>
+      </c>
+      <c r="E280" t="n">
+        <v>3</v>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H280" t="inlineStr"/>
     </row>
     <row r="281">
@@ -8171,11 +8757,25 @@
           <t>https://www.amazon.in/dp/B0DXF7NG2K</t>
         </is>
       </c>
-      <c r="C281" t="inlineStr"/>
-      <c r="D281" t="inlineStr"/>
-      <c r="E281" t="inlineStr"/>
-      <c r="F281" t="inlineStr"/>
-      <c r="G281" t="inlineStr"/>
+      <c r="C281" t="n">
+        <v>3509</v>
+      </c>
+      <c r="D281" t="n">
+        <v>5</v>
+      </c>
+      <c r="E281" t="n">
+        <v>3</v>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H281" t="inlineStr"/>
     </row>
     <row r="282">
@@ -8190,10 +8790,26 @@
         </is>
       </c>
       <c r="C282" t="inlineStr"/>
-      <c r="D282" t="inlineStr"/>
-      <c r="E282" t="inlineStr"/>
-      <c r="F282" t="inlineStr"/>
-      <c r="G282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H282" t="inlineStr"/>
     </row>
     <row r="283">
@@ -8208,10 +8824,26 @@
         </is>
       </c>
       <c r="C283" t="inlineStr"/>
-      <c r="D283" t="inlineStr"/>
-      <c r="E283" t="inlineStr"/>
-      <c r="F283" t="inlineStr"/>
-      <c r="G283" t="inlineStr"/>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H283" t="inlineStr"/>
     </row>
     <row r="284">
@@ -8226,10 +8858,26 @@
         </is>
       </c>
       <c r="C284" t="inlineStr"/>
-      <c r="D284" t="inlineStr"/>
-      <c r="E284" t="inlineStr"/>
-      <c r="F284" t="inlineStr"/>
-      <c r="G284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H284" t="inlineStr"/>
     </row>
     <row r="285">
@@ -8243,11 +8891,25 @@
           <t>https://www.amazon.in/dp/B0DCK89TKM</t>
         </is>
       </c>
-      <c r="C285" t="inlineStr"/>
-      <c r="D285" t="inlineStr"/>
-      <c r="E285" t="inlineStr"/>
-      <c r="F285" t="inlineStr"/>
-      <c r="G285" t="inlineStr"/>
+      <c r="C285" t="n">
+        <v>3919</v>
+      </c>
+      <c r="D285" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E285" t="n">
+        <v>3</v>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H285" t="inlineStr"/>
     </row>
     <row r="286">
@@ -8261,11 +8923,25 @@
           <t>https://www.amazon.in/dp/B09QKSHJFV</t>
         </is>
       </c>
-      <c r="C286" t="inlineStr"/>
-      <c r="D286" t="inlineStr"/>
-      <c r="E286" t="inlineStr"/>
-      <c r="F286" t="inlineStr"/>
-      <c r="G286" t="inlineStr"/>
+      <c r="C286" t="n">
+        <v>3219</v>
+      </c>
+      <c r="D286" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E286" t="n">
+        <v>9</v>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H286" t="inlineStr"/>
     </row>
     <row r="287">
@@ -8279,11 +8955,25 @@
           <t>https://www.amazon.in/dp/B09TP39RT1</t>
         </is>
       </c>
-      <c r="C287" t="inlineStr"/>
-      <c r="D287" t="inlineStr"/>
-      <c r="E287" t="inlineStr"/>
-      <c r="F287" t="inlineStr"/>
-      <c r="G287" t="inlineStr"/>
+      <c r="C287" t="n">
+        <v>4079</v>
+      </c>
+      <c r="D287" t="n">
+        <v>5</v>
+      </c>
+      <c r="E287" t="n">
+        <v>1</v>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H287" t="inlineStr"/>
     </row>
     <row r="288">
@@ -8297,11 +8987,29 @@
           <t>https://www.amazon.in/dp/B09TP3694L</t>
         </is>
       </c>
-      <c r="C288" t="inlineStr"/>
-      <c r="D288" t="inlineStr"/>
-      <c r="E288" t="inlineStr"/>
-      <c r="F288" t="inlineStr"/>
-      <c r="G288" t="inlineStr"/>
+      <c r="C288" t="n">
+        <v>4079</v>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H288" t="inlineStr"/>
     </row>
     <row r="289">
@@ -8315,11 +9023,29 @@
           <t>https://www.amazon.in/dp/B09ZBBBMG2</t>
         </is>
       </c>
-      <c r="C289" t="inlineStr"/>
-      <c r="D289" t="inlineStr"/>
-      <c r="E289" t="inlineStr"/>
-      <c r="F289" t="inlineStr"/>
-      <c r="G289" t="inlineStr"/>
+      <c r="C289" t="n">
+        <v>4079</v>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H289" t="inlineStr"/>
     </row>
     <row r="290">
@@ -8333,11 +9059,25 @@
           <t>https://www.amazon.in/dp/B0B4KFPWFV</t>
         </is>
       </c>
-      <c r="C290" t="inlineStr"/>
-      <c r="D290" t="inlineStr"/>
-      <c r="E290" t="inlineStr"/>
-      <c r="F290" t="inlineStr"/>
-      <c r="G290" t="inlineStr"/>
+      <c r="C290" t="n">
+        <v>3199</v>
+      </c>
+      <c r="D290" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E290" t="n">
+        <v>4</v>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H290" t="inlineStr"/>
     </row>
     <row r="291">
@@ -8351,11 +9091,25 @@
           <t>https://www.amazon.in/dp/B0B4KJ1FXC</t>
         </is>
       </c>
-      <c r="C291" t="inlineStr"/>
-      <c r="D291" t="inlineStr"/>
-      <c r="E291" t="inlineStr"/>
-      <c r="F291" t="inlineStr"/>
-      <c r="G291" t="inlineStr"/>
+      <c r="C291" t="n">
+        <v>5089</v>
+      </c>
+      <c r="D291" t="n">
+        <v>2</v>
+      </c>
+      <c r="E291" t="n">
+        <v>2</v>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H291" t="inlineStr"/>
     </row>
     <row r="292">
@@ -8369,11 +9123,25 @@
           <t>https://www.amazon.in/dp/B0BHZ4K32C</t>
         </is>
       </c>
-      <c r="C292" t="inlineStr"/>
-      <c r="D292" t="inlineStr"/>
-      <c r="E292" t="inlineStr"/>
-      <c r="F292" t="inlineStr"/>
-      <c r="G292" t="inlineStr"/>
+      <c r="C292" t="n">
+        <v>2589</v>
+      </c>
+      <c r="D292" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E292" t="n">
+        <v>34</v>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H292" t="inlineStr"/>
     </row>
     <row r="293">
@@ -8387,11 +9155,25 @@
           <t>https://www.amazon.in/dp/B0DF32V43Y</t>
         </is>
       </c>
-      <c r="C293" t="inlineStr"/>
-      <c r="D293" t="inlineStr"/>
-      <c r="E293" t="inlineStr"/>
-      <c r="F293" t="inlineStr"/>
-      <c r="G293" t="inlineStr"/>
+      <c r="C293" t="n">
+        <v>3239</v>
+      </c>
+      <c r="D293" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E293" t="n">
+        <v>16</v>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H293" t="inlineStr"/>
     </row>
     <row r="294">
@@ -8406,10 +9188,26 @@
         </is>
       </c>
       <c r="C294" t="inlineStr"/>
-      <c r="D294" t="inlineStr"/>
-      <c r="E294" t="inlineStr"/>
-      <c r="F294" t="inlineStr"/>
-      <c r="G294" t="inlineStr"/>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H294" t="inlineStr"/>
     </row>
     <row r="295">
@@ -8423,11 +9221,25 @@
           <t>https://www.amazon.in/dp/B0DF32HX8Q</t>
         </is>
       </c>
-      <c r="C295" t="inlineStr"/>
-      <c r="D295" t="inlineStr"/>
-      <c r="E295" t="inlineStr"/>
-      <c r="F295" t="inlineStr"/>
-      <c r="G295" t="inlineStr"/>
+      <c r="C295" t="n">
+        <v>3089</v>
+      </c>
+      <c r="D295" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E295" t="n">
+        <v>5</v>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H295" t="inlineStr"/>
     </row>
     <row r="296">
@@ -8441,11 +9253,25 @@
           <t>https://www.amazon.in/dp/B0DF327J2C</t>
         </is>
       </c>
-      <c r="C296" t="inlineStr"/>
-      <c r="D296" t="inlineStr"/>
-      <c r="E296" t="inlineStr"/>
-      <c r="F296" t="inlineStr"/>
-      <c r="G296" t="inlineStr"/>
+      <c r="C296" t="n">
+        <v>4039</v>
+      </c>
+      <c r="D296" t="n">
+        <v>1</v>
+      </c>
+      <c r="E296" t="n">
+        <v>1</v>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H296" t="inlineStr"/>
     </row>
     <row r="297">
@@ -8459,11 +9285,29 @@
           <t>https://www.amazon.in/dp/B0DF31X6Z2</t>
         </is>
       </c>
-      <c r="C297" t="inlineStr"/>
-      <c r="D297" t="inlineStr"/>
-      <c r="E297" t="inlineStr"/>
-      <c r="F297" t="inlineStr"/>
-      <c r="G297" t="inlineStr"/>
+      <c r="C297" t="n">
+        <v>3249</v>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H297" t="inlineStr"/>
     </row>
     <row r="298">
@@ -8478,10 +9322,26 @@
         </is>
       </c>
       <c r="C298" t="inlineStr"/>
-      <c r="D298" t="inlineStr"/>
-      <c r="E298" t="inlineStr"/>
-      <c r="F298" t="inlineStr"/>
-      <c r="G298" t="inlineStr"/>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H298" t="inlineStr"/>
     </row>
     <row r="299">
@@ -8496,10 +9356,26 @@
         </is>
       </c>
       <c r="C299" t="inlineStr"/>
-      <c r="D299" t="inlineStr"/>
-      <c r="E299" t="inlineStr"/>
-      <c r="F299" t="inlineStr"/>
-      <c r="G299" t="inlineStr"/>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H299" t="inlineStr"/>
     </row>
     <row r="300">
@@ -8513,11 +9389,25 @@
           <t>https://www.amazon.in/dp/B0F2MMMG7Y</t>
         </is>
       </c>
-      <c r="C300" t="inlineStr"/>
-      <c r="D300" t="inlineStr"/>
-      <c r="E300" t="inlineStr"/>
-      <c r="F300" t="inlineStr"/>
-      <c r="G300" t="inlineStr"/>
+      <c r="C300" t="n">
+        <v>1795</v>
+      </c>
+      <c r="D300" t="n">
+        <v>5</v>
+      </c>
+      <c r="E300" t="n">
+        <v>1</v>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H300" t="inlineStr"/>
     </row>
     <row r="301">
@@ -8531,11 +9421,25 @@
           <t>https://www.amazon.in/dp/B0F2MQ33XF</t>
         </is>
       </c>
-      <c r="C301" t="inlineStr"/>
-      <c r="D301" t="inlineStr"/>
-      <c r="E301" t="inlineStr"/>
-      <c r="F301" t="inlineStr"/>
-      <c r="G301" t="inlineStr"/>
+      <c r="C301" t="n">
+        <v>2245</v>
+      </c>
+      <c r="D301" t="n">
+        <v>5</v>
+      </c>
+      <c r="E301" t="n">
+        <v>1</v>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H301" t="inlineStr"/>
     </row>
     <row r="302">
@@ -8549,11 +9453,29 @@
           <t>https://www.amazon.in/dp/B0D7S35L45</t>
         </is>
       </c>
-      <c r="C302" t="inlineStr"/>
-      <c r="D302" t="inlineStr"/>
-      <c r="E302" t="inlineStr"/>
-      <c r="F302" t="inlineStr"/>
-      <c r="G302" t="inlineStr"/>
+      <c r="C302" t="n">
+        <v>1829</v>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H302" t="inlineStr"/>
     </row>
     <row r="303">
@@ -8567,11 +9489,29 @@
           <t>https://www.amazon.in/dp/B0D7Q7HXZR</t>
         </is>
       </c>
-      <c r="C303" t="inlineStr"/>
-      <c r="D303" t="inlineStr"/>
-      <c r="E303" t="inlineStr"/>
-      <c r="F303" t="inlineStr"/>
-      <c r="G303" t="inlineStr"/>
+      <c r="C303" t="n">
+        <v>1219</v>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H303" t="inlineStr"/>
     </row>
     <row r="304">
@@ -8585,11 +9525,25 @@
           <t>https://www.amazon.in/dp/B0DZ2P51H4</t>
         </is>
       </c>
-      <c r="C304" t="inlineStr"/>
-      <c r="D304" t="inlineStr"/>
-      <c r="E304" t="inlineStr"/>
-      <c r="F304" t="inlineStr"/>
-      <c r="G304" t="inlineStr"/>
+      <c r="C304" t="n">
+        <v>7200</v>
+      </c>
+      <c r="D304" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E304" t="n">
+        <v>7</v>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H304" t="inlineStr"/>
     </row>
     <row r="305">
@@ -8604,10 +9558,22 @@
         </is>
       </c>
       <c r="C305" t="inlineStr"/>
-      <c r="D305" t="inlineStr"/>
-      <c r="E305" t="inlineStr"/>
-      <c r="F305" t="inlineStr"/>
-      <c r="G305" t="inlineStr"/>
+      <c r="D305" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E305" t="n">
+        <v>4</v>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H305" t="inlineStr"/>
     </row>
     <row r="306">
@@ -8621,11 +9587,25 @@
           <t>https://www.amazon.in/dp/B0DZ2NVXJQ</t>
         </is>
       </c>
-      <c r="C306" t="inlineStr"/>
-      <c r="D306" t="inlineStr"/>
-      <c r="E306" t="inlineStr"/>
-      <c r="F306" t="inlineStr"/>
-      <c r="G306" t="inlineStr"/>
+      <c r="C306" t="n">
+        <v>7339</v>
+      </c>
+      <c r="D306" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E306" t="n">
+        <v>10</v>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H306" t="inlineStr"/>
     </row>
     <row r="307">
@@ -8639,11 +9619,25 @@
           <t>https://www.amazon.in/dp/B0DZ2NM1KG</t>
         </is>
       </c>
-      <c r="C307" t="inlineStr"/>
-      <c r="D307" t="inlineStr"/>
-      <c r="E307" t="inlineStr"/>
-      <c r="F307" t="inlineStr"/>
-      <c r="G307" t="inlineStr"/>
+      <c r="C307" t="n">
+        <v>19449</v>
+      </c>
+      <c r="D307" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E307" t="n">
+        <v>2</v>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H307" t="inlineStr"/>
     </row>
     <row r="308">
@@ -8657,11 +9651,25 @@
           <t>https://www.amazon.in/dp/B0DZ2N2RK6</t>
         </is>
       </c>
-      <c r="C308" t="inlineStr"/>
-      <c r="D308" t="inlineStr"/>
-      <c r="E308" t="inlineStr"/>
-      <c r="F308" t="inlineStr"/>
-      <c r="G308" t="inlineStr"/>
+      <c r="C308" t="n">
+        <v>7200</v>
+      </c>
+      <c r="D308" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E308" t="n">
+        <v>7</v>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H308" t="inlineStr"/>
     </row>
     <row r="309">
@@ -8675,11 +9683,25 @@
           <t>https://www.amazon.in/dp/B0DZ2RJ4KV</t>
         </is>
       </c>
-      <c r="C309" t="inlineStr"/>
-      <c r="D309" t="inlineStr"/>
-      <c r="E309" t="inlineStr"/>
-      <c r="F309" t="inlineStr"/>
-      <c r="G309" t="inlineStr"/>
+      <c r="C309" t="n">
+        <v>1679</v>
+      </c>
+      <c r="D309" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E309" t="n">
+        <v>4</v>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H309" t="inlineStr"/>
     </row>
     <row r="310">
@@ -8693,11 +9715,25 @@
           <t>https://www.amazon.in/dp/B0DZP54VZP</t>
         </is>
       </c>
-      <c r="C310" t="inlineStr"/>
-      <c r="D310" t="inlineStr"/>
-      <c r="E310" t="inlineStr"/>
-      <c r="F310" t="inlineStr"/>
-      <c r="G310" t="inlineStr"/>
+      <c r="C310" t="n">
+        <v>7339</v>
+      </c>
+      <c r="D310" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E310" t="n">
+        <v>10</v>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H310" t="inlineStr"/>
     </row>
     <row r="311">
@@ -8711,11 +9747,25 @@
           <t>https://www.amazon.in/dp/B0DZ2N9D78</t>
         </is>
       </c>
-      <c r="C311" t="inlineStr"/>
-      <c r="D311" t="inlineStr"/>
-      <c r="E311" t="inlineStr"/>
-      <c r="F311" t="inlineStr"/>
-      <c r="G311" t="inlineStr"/>
+      <c r="C311" t="n">
+        <v>7339</v>
+      </c>
+      <c r="D311" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E311" t="n">
+        <v>2</v>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H311" t="inlineStr"/>
     </row>
     <row r="312">
@@ -8729,11 +9779,25 @@
           <t>https://www.amazon.in/dp/B0DZ2PZ9X7</t>
         </is>
       </c>
-      <c r="C312" t="inlineStr"/>
-      <c r="D312" t="inlineStr"/>
-      <c r="E312" t="inlineStr"/>
-      <c r="F312" t="inlineStr"/>
-      <c r="G312" t="inlineStr"/>
+      <c r="C312" t="n">
+        <v>7200</v>
+      </c>
+      <c r="D312" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E312" t="n">
+        <v>7</v>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H312" t="inlineStr"/>
     </row>
     <row r="313">
@@ -8748,10 +9812,22 @@
         </is>
       </c>
       <c r="C313" t="inlineStr"/>
-      <c r="D313" t="inlineStr"/>
-      <c r="E313" t="inlineStr"/>
-      <c r="F313" t="inlineStr"/>
-      <c r="G313" t="inlineStr"/>
+      <c r="D313" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E313" t="n">
+        <v>4</v>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H313" t="inlineStr"/>
     </row>
     <row r="314">
@@ -8765,11 +9841,25 @@
           <t>https://www.amazon.in/dp/B0DZ2R84QJ</t>
         </is>
       </c>
-      <c r="C314" t="inlineStr"/>
-      <c r="D314" t="inlineStr"/>
-      <c r="E314" t="inlineStr"/>
-      <c r="F314" t="inlineStr"/>
-      <c r="G314" t="inlineStr"/>
+      <c r="C314" t="n">
+        <v>7339</v>
+      </c>
+      <c r="D314" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E314" t="n">
+        <v>10</v>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H314" t="inlineStr"/>
     </row>
     <row r="315">
@@ -8783,11 +9873,25 @@
           <t>https://www.amazon.in/dp/B0DZ2ND4D1</t>
         </is>
       </c>
-      <c r="C315" t="inlineStr"/>
-      <c r="D315" t="inlineStr"/>
-      <c r="E315" t="inlineStr"/>
-      <c r="F315" t="inlineStr"/>
-      <c r="G315" t="inlineStr"/>
+      <c r="C315" t="n">
+        <v>16389</v>
+      </c>
+      <c r="D315" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E315" t="n">
+        <v>2</v>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H315" t="inlineStr"/>
     </row>
     <row r="316">
@@ -8801,11 +9905,25 @@
           <t>https://www.amazon.in/dp/B0DZ2PQCHN</t>
         </is>
       </c>
-      <c r="C316" t="inlineStr"/>
-      <c r="D316" t="inlineStr"/>
-      <c r="E316" t="inlineStr"/>
-      <c r="F316" t="inlineStr"/>
-      <c r="G316" t="inlineStr"/>
+      <c r="C316" t="n">
+        <v>7200</v>
+      </c>
+      <c r="D316" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E316" t="n">
+        <v>7</v>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H316" t="inlineStr"/>
     </row>
     <row r="317">
@@ -8820,10 +9938,22 @@
         </is>
       </c>
       <c r="C317" t="inlineStr"/>
-      <c r="D317" t="inlineStr"/>
-      <c r="E317" t="inlineStr"/>
-      <c r="F317" t="inlineStr"/>
-      <c r="G317" t="inlineStr"/>
+      <c r="D317" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E317" t="n">
+        <v>4</v>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H317" t="inlineStr"/>
     </row>
     <row r="318">
@@ -8837,11 +9967,25 @@
           <t>https://www.amazon.in/dp/B0DZ2PFLXV</t>
         </is>
       </c>
-      <c r="C318" t="inlineStr"/>
-      <c r="D318" t="inlineStr"/>
-      <c r="E318" t="inlineStr"/>
-      <c r="F318" t="inlineStr"/>
-      <c r="G318" t="inlineStr"/>
+      <c r="C318" t="n">
+        <v>7339</v>
+      </c>
+      <c r="D318" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E318" t="n">
+        <v>10</v>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H318" t="inlineStr"/>
     </row>
     <row r="319">
@@ -8855,11 +9999,25 @@
           <t>https://www.amazon.in/dp/B0DZ2QPM6C</t>
         </is>
       </c>
-      <c r="C319" t="inlineStr"/>
-      <c r="D319" t="inlineStr"/>
-      <c r="E319" t="inlineStr"/>
-      <c r="F319" t="inlineStr"/>
-      <c r="G319" t="inlineStr"/>
+      <c r="C319" t="n">
+        <v>26789</v>
+      </c>
+      <c r="D319" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E319" t="n">
+        <v>2</v>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H319" t="inlineStr"/>
     </row>
     <row r="320">
@@ -8873,11 +10031,25 @@
           <t>https://www.amazon.in/dp/B0DZ2QP9JT</t>
         </is>
       </c>
-      <c r="C320" t="inlineStr"/>
-      <c r="D320" t="inlineStr"/>
-      <c r="E320" t="inlineStr"/>
-      <c r="F320" t="inlineStr"/>
-      <c r="G320" t="inlineStr"/>
+      <c r="C320" t="n">
+        <v>7200</v>
+      </c>
+      <c r="D320" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E320" t="n">
+        <v>7</v>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H320" t="inlineStr"/>
     </row>
     <row r="321">
@@ -8891,11 +10063,25 @@
           <t>https://www.amazon.in/dp/B0DZ2R4K1T</t>
         </is>
       </c>
-      <c r="C321" t="inlineStr"/>
-      <c r="D321" t="inlineStr"/>
-      <c r="E321" t="inlineStr"/>
-      <c r="F321" t="inlineStr"/>
-      <c r="G321" t="inlineStr"/>
+      <c r="C321" t="n">
+        <v>12938</v>
+      </c>
+      <c r="D321" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E321" t="n">
+        <v>4</v>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H321" t="inlineStr"/>
     </row>
     <row r="322">
@@ -8909,11 +10095,25 @@
           <t>https://www.amazon.in/dp/B0DZ2PSF5Y</t>
         </is>
       </c>
-      <c r="C322" t="inlineStr"/>
-      <c r="D322" t="inlineStr"/>
-      <c r="E322" t="inlineStr"/>
-      <c r="F322" t="inlineStr"/>
-      <c r="G322" t="inlineStr"/>
+      <c r="C322" t="n">
+        <v>7339</v>
+      </c>
+      <c r="D322" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E322" t="n">
+        <v>10</v>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H322" t="inlineStr"/>
     </row>
     <row r="323">
@@ -8927,11 +10127,25 @@
           <t>https://www.amazon.in/dp/B0DZ2N888B</t>
         </is>
       </c>
-      <c r="C323" t="inlineStr"/>
-      <c r="D323" t="inlineStr"/>
-      <c r="E323" t="inlineStr"/>
-      <c r="F323" t="inlineStr"/>
-      <c r="G323" t="inlineStr"/>
+      <c r="C323" t="n">
+        <v>17179</v>
+      </c>
+      <c r="D323" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E323" t="n">
+        <v>2</v>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H323" t="inlineStr"/>
     </row>
     <row r="324">
@@ -8945,11 +10159,25 @@
           <t>https://www.amazon.in/dp/B0DZ2RK2R9</t>
         </is>
       </c>
-      <c r="C324" t="inlineStr"/>
-      <c r="D324" t="inlineStr"/>
-      <c r="E324" t="inlineStr"/>
-      <c r="F324" t="inlineStr"/>
-      <c r="G324" t="inlineStr"/>
+      <c r="C324" t="n">
+        <v>7200</v>
+      </c>
+      <c r="D324" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E324" t="n">
+        <v>7</v>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H324" t="inlineStr"/>
     </row>
     <row r="325">
@@ -8963,11 +10191,25 @@
           <t>https://www.amazon.in/dp/B0DZ2PJXNV</t>
         </is>
       </c>
-      <c r="C325" t="inlineStr"/>
-      <c r="D325" t="inlineStr"/>
-      <c r="E325" t="inlineStr"/>
-      <c r="F325" t="inlineStr"/>
-      <c r="G325" t="inlineStr"/>
+      <c r="C325" t="n">
+        <v>2049</v>
+      </c>
+      <c r="D325" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E325" t="n">
+        <v>4</v>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H325" t="inlineStr"/>
     </row>
     <row r="326">
@@ -8981,11 +10223,25 @@
           <t>https://www.amazon.in/dp/B0DZP5DZBK</t>
         </is>
       </c>
-      <c r="C326" t="inlineStr"/>
-      <c r="D326" t="inlineStr"/>
-      <c r="E326" t="inlineStr"/>
-      <c r="F326" t="inlineStr"/>
-      <c r="G326" t="inlineStr"/>
+      <c r="C326" t="n">
+        <v>7339</v>
+      </c>
+      <c r="D326" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E326" t="n">
+        <v>10</v>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H326" t="inlineStr"/>
     </row>
     <row r="327">
@@ -8999,11 +10255,25 @@
           <t>https://www.amazon.in/dp/B0DZ2Q6CCP</t>
         </is>
       </c>
-      <c r="C327" t="inlineStr"/>
-      <c r="D327" t="inlineStr"/>
-      <c r="E327" t="inlineStr"/>
-      <c r="F327" t="inlineStr"/>
-      <c r="G327" t="inlineStr"/>
+      <c r="C327" t="n">
+        <v>9059</v>
+      </c>
+      <c r="D327" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E327" t="n">
+        <v>2</v>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H327" t="inlineStr"/>
     </row>
     <row r="328">
@@ -9017,11 +10287,25 @@
           <t>https://www.amazon.in/dp/B0DZ2NXL7T</t>
         </is>
       </c>
-      <c r="C328" t="inlineStr"/>
-      <c r="D328" t="inlineStr"/>
-      <c r="E328" t="inlineStr"/>
-      <c r="F328" t="inlineStr"/>
-      <c r="G328" t="inlineStr"/>
+      <c r="C328" t="n">
+        <v>7200</v>
+      </c>
+      <c r="D328" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E328" t="n">
+        <v>7</v>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H328" t="inlineStr"/>
     </row>
     <row r="329">
@@ -9035,11 +10319,25 @@
           <t>https://www.amazon.in/dp/B0DZ2L2F99</t>
         </is>
       </c>
-      <c r="C329" t="inlineStr"/>
-      <c r="D329" t="inlineStr"/>
-      <c r="E329" t="inlineStr"/>
-      <c r="F329" t="inlineStr"/>
-      <c r="G329" t="inlineStr"/>
+      <c r="C329" t="n">
+        <v>1679</v>
+      </c>
+      <c r="D329" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E329" t="n">
+        <v>4</v>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H329" t="inlineStr"/>
     </row>
     <row r="330">
@@ -9053,11 +10351,25 @@
           <t>https://www.amazon.in/dp/B0DZP67TYN</t>
         </is>
       </c>
-      <c r="C330" t="inlineStr"/>
-      <c r="D330" t="inlineStr"/>
-      <c r="E330" t="inlineStr"/>
-      <c r="F330" t="inlineStr"/>
-      <c r="G330" t="inlineStr"/>
+      <c r="C330" t="n">
+        <v>7339</v>
+      </c>
+      <c r="D330" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E330" t="n">
+        <v>10</v>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H330" t="inlineStr"/>
     </row>
     <row r="331">
@@ -9071,11 +10383,25 @@
           <t>https://www.amazon.in/dp/B0DZ2PJ55G</t>
         </is>
       </c>
-      <c r="C331" t="inlineStr"/>
-      <c r="D331" t="inlineStr"/>
-      <c r="E331" t="inlineStr"/>
-      <c r="F331" t="inlineStr"/>
-      <c r="G331" t="inlineStr"/>
+      <c r="C331" t="n">
+        <v>10399</v>
+      </c>
+      <c r="D331" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E331" t="n">
+        <v>2</v>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H331" t="inlineStr"/>
     </row>
     <row r="332">
@@ -9089,11 +10415,29 @@
           <t>https://www.amazon.in/dp/B0FC2G3P4M</t>
         </is>
       </c>
-      <c r="C332" t="inlineStr"/>
-      <c r="D332" t="inlineStr"/>
-      <c r="E332" t="inlineStr"/>
-      <c r="F332" t="inlineStr"/>
-      <c r="G332" t="inlineStr"/>
+      <c r="C332" t="n">
+        <v>4829</v>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H332" t="inlineStr"/>
     </row>
     <row r="333">
@@ -9107,11 +10451,25 @@
           <t>https://www.amazon.in/dp/B0CGNTXQG6</t>
         </is>
       </c>
-      <c r="C333" t="inlineStr"/>
-      <c r="D333" t="inlineStr"/>
-      <c r="E333" t="inlineStr"/>
-      <c r="F333" t="inlineStr"/>
-      <c r="G333" t="inlineStr"/>
+      <c r="C333" t="n">
+        <v>3419</v>
+      </c>
+      <c r="D333" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E333" t="n">
+        <v>5</v>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H333" t="inlineStr"/>
     </row>
     <row r="334">
@@ -9125,11 +10483,25 @@
           <t>https://www.amazon.in/dp/B0CGNV38JQ</t>
         </is>
       </c>
-      <c r="C334" t="inlineStr"/>
-      <c r="D334" t="inlineStr"/>
-      <c r="E334" t="inlineStr"/>
-      <c r="F334" t="inlineStr"/>
-      <c r="G334" t="inlineStr"/>
+      <c r="C334" t="n">
+        <v>4059</v>
+      </c>
+      <c r="D334" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E334" t="n">
+        <v>5</v>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H334" t="inlineStr"/>
     </row>
     <row r="335">
@@ -9143,11 +10515,25 @@
           <t>https://www.amazon.in/dp/B0CGNTYL2G</t>
         </is>
       </c>
-      <c r="C335" t="inlineStr"/>
-      <c r="D335" t="inlineStr"/>
-      <c r="E335" t="inlineStr"/>
-      <c r="F335" t="inlineStr"/>
-      <c r="G335" t="inlineStr"/>
+      <c r="C335" t="n">
+        <v>4499</v>
+      </c>
+      <c r="D335" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E335" t="n">
+        <v>5</v>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H335" t="inlineStr"/>
     </row>
     <row r="336">
@@ -9161,11 +10547,25 @@
           <t>https://www.amazon.in/dp/B0CGNXBKW5</t>
         </is>
       </c>
-      <c r="C336" t="inlineStr"/>
-      <c r="D336" t="inlineStr"/>
-      <c r="E336" t="inlineStr"/>
-      <c r="F336" t="inlineStr"/>
-      <c r="G336" t="inlineStr"/>
+      <c r="C336" t="n">
+        <v>3419</v>
+      </c>
+      <c r="D336" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E336" t="n">
+        <v>5</v>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H336" t="inlineStr"/>
     </row>
     <row r="337">
@@ -9180,10 +10580,26 @@
         </is>
       </c>
       <c r="C337" t="inlineStr"/>
-      <c r="D337" t="inlineStr"/>
-      <c r="E337" t="inlineStr"/>
-      <c r="F337" t="inlineStr"/>
-      <c r="G337" t="inlineStr"/>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H337" t="inlineStr"/>
     </row>
     <row r="338">
@@ -9197,11 +10613,25 @@
           <t>https://www.amazon.in/dp/B0CGNV8QGD</t>
         </is>
       </c>
-      <c r="C338" t="inlineStr"/>
-      <c r="D338" t="inlineStr"/>
-      <c r="E338" t="inlineStr"/>
-      <c r="F338" t="inlineStr"/>
-      <c r="G338" t="inlineStr"/>
+      <c r="C338" t="n">
+        <v>4499</v>
+      </c>
+      <c r="D338" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E338" t="n">
+        <v>5</v>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H338" t="inlineStr"/>
     </row>
     <row r="339">
@@ -9216,10 +10646,26 @@
         </is>
       </c>
       <c r="C339" t="inlineStr"/>
-      <c r="D339" t="inlineStr"/>
-      <c r="E339" t="inlineStr"/>
-      <c r="F339" t="inlineStr"/>
-      <c r="G339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H339" t="inlineStr"/>
     </row>
     <row r="340">
@@ -9234,10 +10680,26 @@
         </is>
       </c>
       <c r="C340" t="inlineStr"/>
-      <c r="D340" t="inlineStr"/>
-      <c r="E340" t="inlineStr"/>
-      <c r="F340" t="inlineStr"/>
-      <c r="G340" t="inlineStr"/>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H340" t="inlineStr"/>
     </row>
     <row r="341">
@@ -9252,10 +10714,26 @@
         </is>
       </c>
       <c r="C341" t="inlineStr"/>
-      <c r="D341" t="inlineStr"/>
-      <c r="E341" t="inlineStr"/>
-      <c r="F341" t="inlineStr"/>
-      <c r="G341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H341" t="inlineStr"/>
     </row>
     <row r="342">
@@ -9270,10 +10748,26 @@
         </is>
       </c>
       <c r="C342" t="inlineStr"/>
-      <c r="D342" t="inlineStr"/>
-      <c r="E342" t="inlineStr"/>
-      <c r="F342" t="inlineStr"/>
-      <c r="G342" t="inlineStr"/>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H342" t="inlineStr"/>
     </row>
     <row r="343">
@@ -9288,10 +10782,26 @@
         </is>
       </c>
       <c r="C343" t="inlineStr"/>
-      <c r="D343" t="inlineStr"/>
-      <c r="E343" t="inlineStr"/>
-      <c r="F343" t="inlineStr"/>
-      <c r="G343" t="inlineStr"/>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H343" t="inlineStr"/>
     </row>
     <row r="344">
@@ -9306,10 +10816,26 @@
         </is>
       </c>
       <c r="C344" t="inlineStr"/>
-      <c r="D344" t="inlineStr"/>
-      <c r="E344" t="inlineStr"/>
-      <c r="F344" t="inlineStr"/>
-      <c r="G344" t="inlineStr"/>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H344" t="inlineStr"/>
     </row>
     <row r="345">
@@ -9324,10 +10850,26 @@
         </is>
       </c>
       <c r="C345" t="inlineStr"/>
-      <c r="D345" t="inlineStr"/>
-      <c r="E345" t="inlineStr"/>
-      <c r="F345" t="inlineStr"/>
-      <c r="G345" t="inlineStr"/>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H345" t="inlineStr"/>
     </row>
     <row r="346">
@@ -9341,11 +10883,25 @@
           <t>https://www.amazon.in/dp/B0CRHJTP3D</t>
         </is>
       </c>
-      <c r="C346" t="inlineStr"/>
-      <c r="D346" t="inlineStr"/>
-      <c r="E346" t="inlineStr"/>
-      <c r="F346" t="inlineStr"/>
-      <c r="G346" t="inlineStr"/>
+      <c r="C346" t="n">
+        <v>5299</v>
+      </c>
+      <c r="D346" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E346" t="n">
+        <v>9</v>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>Only 2 left in stock.</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H346" t="inlineStr"/>
     </row>
     <row r="347">
@@ -9359,11 +10915,25 @@
           <t>https://www.amazon.in/dp/B0CRHJHT7T</t>
         </is>
       </c>
-      <c r="C347" t="inlineStr"/>
-      <c r="D347" t="inlineStr"/>
-      <c r="E347" t="inlineStr"/>
-      <c r="F347" t="inlineStr"/>
-      <c r="G347" t="inlineStr"/>
+      <c r="C347" t="n">
+        <v>5299</v>
+      </c>
+      <c r="D347" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E347" t="n">
+        <v>9</v>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>Only 2 left in stock.</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H347" t="inlineStr"/>
     </row>
     <row r="348">
@@ -9377,11 +10947,25 @@
           <t>https://www.amazon.in/dp/B0CRHHYWTX</t>
         </is>
       </c>
-      <c r="C348" t="inlineStr"/>
-      <c r="D348" t="inlineStr"/>
-      <c r="E348" t="inlineStr"/>
-      <c r="F348" t="inlineStr"/>
-      <c r="G348" t="inlineStr"/>
+      <c r="C348" t="n">
+        <v>5299</v>
+      </c>
+      <c r="D348" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E348" t="n">
+        <v>9</v>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>Only 2 left in stock.</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H348" t="inlineStr"/>
     </row>
     <row r="349">
@@ -9395,11 +10979,25 @@
           <t>https://www.amazon.in/dp/B0F32P8CW5</t>
         </is>
       </c>
-      <c r="C349" t="inlineStr"/>
-      <c r="D349" t="inlineStr"/>
-      <c r="E349" t="inlineStr"/>
-      <c r="F349" t="inlineStr"/>
-      <c r="G349" t="inlineStr"/>
+      <c r="C349" t="n">
+        <v>5299</v>
+      </c>
+      <c r="D349" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E349" t="n">
+        <v>9</v>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>Only 2 left in stock.</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H349" t="inlineStr"/>
     </row>
     <row r="350">
@@ -9413,11 +11011,25 @@
           <t>https://www.amazon.in/dp/B0DZXCNBKF</t>
         </is>
       </c>
-      <c r="C350" t="inlineStr"/>
-      <c r="D350" t="inlineStr"/>
-      <c r="E350" t="inlineStr"/>
-      <c r="F350" t="inlineStr"/>
-      <c r="G350" t="inlineStr"/>
+      <c r="C350" t="n">
+        <v>5299</v>
+      </c>
+      <c r="D350" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E350" t="n">
+        <v>9</v>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>Only 2 left in stock.</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H350" t="inlineStr"/>
     </row>
     <row r="351">
@@ -9431,11 +11043,25 @@
           <t>https://www.amazon.in/dp/B0DZXDKYSJ</t>
         </is>
       </c>
-      <c r="C351" t="inlineStr"/>
-      <c r="D351" t="inlineStr"/>
-      <c r="E351" t="inlineStr"/>
-      <c r="F351" t="inlineStr"/>
-      <c r="G351" t="inlineStr"/>
+      <c r="C351" t="n">
+        <v>5299</v>
+      </c>
+      <c r="D351" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E351" t="n">
+        <v>9</v>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>Only 2 left in stock.</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H351" t="inlineStr"/>
     </row>
     <row r="352">
@@ -9449,11 +11075,25 @@
           <t>https://www.amazon.in/dp/B0D37YPC3X</t>
         </is>
       </c>
-      <c r="C352" t="inlineStr"/>
-      <c r="D352" t="inlineStr"/>
-      <c r="E352" t="inlineStr"/>
-      <c r="F352" t="inlineStr"/>
-      <c r="G352" t="inlineStr"/>
+      <c r="C352" t="n">
+        <v>5299</v>
+      </c>
+      <c r="D352" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E352" t="n">
+        <v>9</v>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>Only 2 left in stock.</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H352" t="inlineStr"/>
     </row>
     <row r="353">
@@ -9467,11 +11107,25 @@
           <t>https://www.amazon.in/dp/B0D37Y3G5B</t>
         </is>
       </c>
-      <c r="C353" t="inlineStr"/>
-      <c r="D353" t="inlineStr"/>
-      <c r="E353" t="inlineStr"/>
-      <c r="F353" t="inlineStr"/>
-      <c r="G353" t="inlineStr"/>
+      <c r="C353" t="n">
+        <v>5299</v>
+      </c>
+      <c r="D353" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E353" t="n">
+        <v>9</v>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>Only 2 left in stock.</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H353" t="inlineStr"/>
     </row>
     <row r="354">
@@ -9485,11 +11139,25 @@
           <t>https://www.amazon.in/dp/B0D37XX7C2</t>
         </is>
       </c>
-      <c r="C354" t="inlineStr"/>
-      <c r="D354" t="inlineStr"/>
-      <c r="E354" t="inlineStr"/>
-      <c r="F354" t="inlineStr"/>
-      <c r="G354" t="inlineStr"/>
+      <c r="C354" t="n">
+        <v>5299</v>
+      </c>
+      <c r="D354" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E354" t="n">
+        <v>9</v>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>Only 2 left in stock.</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H354" t="inlineStr"/>
     </row>
     <row r="355">
@@ -9503,11 +11171,25 @@
           <t>https://www.amazon.in/dp/B0CRHK1GJS</t>
         </is>
       </c>
-      <c r="C355" t="inlineStr"/>
-      <c r="D355" t="inlineStr"/>
-      <c r="E355" t="inlineStr"/>
-      <c r="F355" t="inlineStr"/>
-      <c r="G355" t="inlineStr"/>
+      <c r="C355" t="n">
+        <v>6179</v>
+      </c>
+      <c r="D355" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E355" t="n">
+        <v>9</v>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>Only 2 left in stock.</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H355" t="inlineStr"/>
     </row>
     <row r="356">
@@ -9521,11 +11203,25 @@
           <t>https://www.amazon.in/dp/B0CRHKNF3V</t>
         </is>
       </c>
-      <c r="C356" t="inlineStr"/>
-      <c r="D356" t="inlineStr"/>
-      <c r="E356" t="inlineStr"/>
-      <c r="F356" t="inlineStr"/>
-      <c r="G356" t="inlineStr"/>
+      <c r="C356" t="n">
+        <v>6179</v>
+      </c>
+      <c r="D356" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E356" t="n">
+        <v>9</v>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>Only 2 left in stock.</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H356" t="inlineStr"/>
     </row>
     <row r="357">
@@ -9539,11 +11235,25 @@
           <t>https://www.amazon.in/dp/B0CRHK3JXN</t>
         </is>
       </c>
-      <c r="C357" t="inlineStr"/>
-      <c r="D357" t="inlineStr"/>
-      <c r="E357" t="inlineStr"/>
-      <c r="F357" t="inlineStr"/>
-      <c r="G357" t="inlineStr"/>
+      <c r="C357" t="n">
+        <v>6179</v>
+      </c>
+      <c r="D357" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E357" t="n">
+        <v>9</v>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H357" t="inlineStr"/>
     </row>
     <row r="358">
@@ -9557,11 +11267,25 @@
           <t>https://www.amazon.in/dp/B0CRHKBTZ1</t>
         </is>
       </c>
-      <c r="C358" t="inlineStr"/>
-      <c r="D358" t="inlineStr"/>
-      <c r="E358" t="inlineStr"/>
-      <c r="F358" t="inlineStr"/>
-      <c r="G358" t="inlineStr"/>
+      <c r="C358" t="n">
+        <v>7649</v>
+      </c>
+      <c r="D358" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E358" t="n">
+        <v>9</v>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H358" t="inlineStr"/>
     </row>
     <row r="359">
@@ -9575,11 +11299,25 @@
           <t>https://www.amazon.in/dp/B0CRHHLLXK</t>
         </is>
       </c>
-      <c r="C359" t="inlineStr"/>
-      <c r="D359" t="inlineStr"/>
-      <c r="E359" t="inlineStr"/>
-      <c r="F359" t="inlineStr"/>
-      <c r="G359" t="inlineStr"/>
+      <c r="C359" t="n">
+        <v>7649</v>
+      </c>
+      <c r="D359" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E359" t="n">
+        <v>9</v>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H359" t="inlineStr"/>
     </row>
     <row r="360">
@@ -9593,11 +11331,25 @@
           <t>https://www.amazon.in/dp/B0CRHJSBH8</t>
         </is>
       </c>
-      <c r="C360" t="inlineStr"/>
-      <c r="D360" t="inlineStr"/>
-      <c r="E360" t="inlineStr"/>
-      <c r="F360" t="inlineStr"/>
-      <c r="G360" t="inlineStr"/>
+      <c r="C360" t="n">
+        <v>7649</v>
+      </c>
+      <c r="D360" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E360" t="n">
+        <v>9</v>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H360" t="inlineStr"/>
     </row>
     <row r="361">
@@ -9615,8 +11367,29 @@
       <c r="D361" t="inlineStr"/>
       <c r="E361" t="inlineStr"/>
       <c r="F361" t="inlineStr"/>
-      <c r="G361" t="inlineStr"/>
-      <c r="H361" t="inlineStr"/>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
+  (Session info: chrome=150.0.7871.114)
+Stacktrace:
+#0 0x5586f4c7f41a &lt;unknown&gt;
+#1 0x5586f4657689 &lt;unknown&gt;
+#2 0x5586f463f21a &lt;unknown&gt;
+#3 0x5586f463ee96 &lt;unknown&gt;
+#4 0x5586f463ca7e &lt;unknown&gt;
+#5 0x5586f463d3ff &lt;unknown&gt;
+#6 0x5586f464c4e0 &lt;unknown&gt;
+#7 0x5586f46663e7 &lt;unknown&gt;
+#8 0x5586f466dc5b &lt;unknown&gt;
+#9 0x5586f463db59 &lt;unknown&gt;
+</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -9633,8 +11406,29 @@
       <c r="D362" t="inlineStr"/>
       <c r="E362" t="inlineStr"/>
       <c r="F362" t="inlineStr"/>
-      <c r="G362" t="inlineStr"/>
-      <c r="H362" t="inlineStr"/>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
+  (Session info: chrome=150.0.7871.114)
+Stacktrace:
+#0 0x5586f4c7f41a &lt;unknown&gt;
+#1 0x5586f4657689 &lt;unknown&gt;
+#2 0x5586f463f21a &lt;unknown&gt;
+#3 0x5586f463ee96 &lt;unknown&gt;
+#4 0x5586f463ca7e &lt;unknown&gt;
+#5 0x5586f463d3ff &lt;unknown&gt;
+#6 0x5586f464c4e0 &lt;unknown&gt;
+#7 0x5586f46663e7 &lt;unknown&gt;
+#8 0x5586f466dc5b &lt;unknown&gt;
+#9 0x5586f463db59 &lt;unknown&gt;
+</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -9651,8 +11445,29 @@
       <c r="D363" t="inlineStr"/>
       <c r="E363" t="inlineStr"/>
       <c r="F363" t="inlineStr"/>
-      <c r="G363" t="inlineStr"/>
-      <c r="H363" t="inlineStr"/>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
+  (Session info: chrome=150.0.7871.114)
+Stacktrace:
+#0 0x5586f4c7f41a &lt;unknown&gt;
+#1 0x5586f4657689 &lt;unknown&gt;
+#2 0x5586f463f21a &lt;unknown&gt;
+#3 0x5586f463ee96 &lt;unknown&gt;
+#4 0x5586f463ca7e &lt;unknown&gt;
+#5 0x5586f463d3ff &lt;unknown&gt;
+#6 0x5586f464c4e0 &lt;unknown&gt;
+#7 0x5586f46663e7 &lt;unknown&gt;
+#8 0x5586f466dc5b &lt;unknown&gt;
+#9 0x5586f463db59 &lt;unknown&gt;
+</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -9669,8 +11484,29 @@
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="inlineStr"/>
-      <c r="G364" t="inlineStr"/>
-      <c r="H364" t="inlineStr"/>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
+  (Session info: chrome=150.0.7871.114)
+Stacktrace:
+#0 0x5586f4c7f41a &lt;unknown&gt;
+#1 0x5586f4657689 &lt;unknown&gt;
+#2 0x5586f463f21a &lt;unknown&gt;
+#3 0x5586f463ee96 &lt;unknown&gt;
+#4 0x5586f463ca7e &lt;unknown&gt;
+#5 0x5586f463d3ff &lt;unknown&gt;
+#6 0x5586f464c4e0 &lt;unknown&gt;
+#7 0x5586f46663e7 &lt;unknown&gt;
+#8 0x5586f466dc5b &lt;unknown&gt;
+#9 0x5586f463db59 &lt;unknown&gt;
+</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -9687,8 +11523,29 @@
       <c r="D365" t="inlineStr"/>
       <c r="E365" t="inlineStr"/>
       <c r="F365" t="inlineStr"/>
-      <c r="G365" t="inlineStr"/>
-      <c r="H365" t="inlineStr"/>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
+  (Session info: chrome=150.0.7871.114)
+Stacktrace:
+#0 0x5586f4c7f41a &lt;unknown&gt;
+#1 0x5586f4657689 &lt;unknown&gt;
+#2 0x5586f463f21a &lt;unknown&gt;
+#3 0x5586f463ee96 &lt;unknown&gt;
+#4 0x5586f463ca7e &lt;unknown&gt;
+#5 0x5586f463d3ff &lt;unknown&gt;
+#6 0x5586f464c4e0 &lt;unknown&gt;
+#7 0x5586f46663e7 &lt;unknown&gt;
+#8 0x5586f466dc5b &lt;unknown&gt;
+#9 0x5586f463db59 &lt;unknown&gt;
+</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -9705,8 +11562,29 @@
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr"/>
       <c r="F366" t="inlineStr"/>
-      <c r="G366" t="inlineStr"/>
-      <c r="H366" t="inlineStr"/>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
+  (Session info: chrome=150.0.7871.114)
+Stacktrace:
+#0 0x5586f4c7f41a &lt;unknown&gt;
+#1 0x5586f4657689 &lt;unknown&gt;
+#2 0x5586f463f21a &lt;unknown&gt;
+#3 0x5586f463ee96 &lt;unknown&gt;
+#4 0x5586f463ca7e &lt;unknown&gt;
+#5 0x5586f463d3ff &lt;unknown&gt;
+#6 0x5586f464c4e0 &lt;unknown&gt;
+#7 0x5586f46663e7 &lt;unknown&gt;
+#8 0x5586f466dc5b &lt;unknown&gt;
+#9 0x5586f463db59 &lt;unknown&gt;
+</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -9723,8 +11601,29 @@
       <c r="D367" t="inlineStr"/>
       <c r="E367" t="inlineStr"/>
       <c r="F367" t="inlineStr"/>
-      <c r="G367" t="inlineStr"/>
-      <c r="H367" t="inlineStr"/>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
+  (Session info: chrome=150.0.7871.114)
+Stacktrace:
+#0 0x5586f4c7f41a &lt;unknown&gt;
+#1 0x5586f4657689 &lt;unknown&gt;
+#2 0x5586f463f21a &lt;unknown&gt;
+#3 0x5586f463ee96 &lt;unknown&gt;
+#4 0x5586f463ca7e &lt;unknown&gt;
+#5 0x5586f463d3ff &lt;unknown&gt;
+#6 0x5586f464c4e0 &lt;unknown&gt;
+#7 0x5586f46663e7 &lt;unknown&gt;
+#8 0x5586f466dc5b &lt;unknown&gt;
+#9 0x5586f463db59 &lt;unknown&gt;
+</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -9741,8 +11640,29 @@
       <c r="D368" t="inlineStr"/>
       <c r="E368" t="inlineStr"/>
       <c r="F368" t="inlineStr"/>
-      <c r="G368" t="inlineStr"/>
-      <c r="H368" t="inlineStr"/>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
+  (Session info: chrome=150.0.7871.114)
+Stacktrace:
+#0 0x5586f4c7f41a &lt;unknown&gt;
+#1 0x5586f4657689 &lt;unknown&gt;
+#2 0x5586f463f21a &lt;unknown&gt;
+#3 0x5586f463ee96 &lt;unknown&gt;
+#4 0x5586f463ca7e &lt;unknown&gt;
+#5 0x5586f463d3ff &lt;unknown&gt;
+#6 0x5586f464c4e0 &lt;unknown&gt;
+#7 0x5586f46663e7 &lt;unknown&gt;
+#8 0x5586f466dc5b &lt;unknown&gt;
+#9 0x5586f463db59 &lt;unknown&gt;
+</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -9759,8 +11679,29 @@
       <c r="D369" t="inlineStr"/>
       <c r="E369" t="inlineStr"/>
       <c r="F369" t="inlineStr"/>
-      <c r="G369" t="inlineStr"/>
-      <c r="H369" t="inlineStr"/>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
+  (Session info: chrome=150.0.7871.114)
+Stacktrace:
+#0 0x5586f4c7f41a &lt;unknown&gt;
+#1 0x5586f4657689 &lt;unknown&gt;
+#2 0x5586f463f21a &lt;unknown&gt;
+#3 0x5586f463ee96 &lt;unknown&gt;
+#4 0x5586f463ca7e &lt;unknown&gt;
+#5 0x5586f463d3ff &lt;unknown&gt;
+#6 0x5586f464c4e0 &lt;unknown&gt;
+#7 0x5586f46663e7 &lt;unknown&gt;
+#8 0x5586f466dc5b &lt;unknown&gt;
+#9 0x5586f463db59 &lt;unknown&gt;
+</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -9777,8 +11718,29 @@
       <c r="D370" t="inlineStr"/>
       <c r="E370" t="inlineStr"/>
       <c r="F370" t="inlineStr"/>
-      <c r="G370" t="inlineStr"/>
-      <c r="H370" t="inlineStr"/>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
+  (Session info: chrome=150.0.7871.114)
+Stacktrace:
+#0 0x5586f4c7f41a &lt;unknown&gt;
+#1 0x5586f4657689 &lt;unknown&gt;
+#2 0x5586f463f21a &lt;unknown&gt;
+#3 0x5586f463ee96 &lt;unknown&gt;
+#4 0x5586f463ca7e &lt;unknown&gt;
+#5 0x5586f463d3ff &lt;unknown&gt;
+#6 0x5586f464c4e0 &lt;unknown&gt;
+#7 0x5586f46663e7 &lt;unknown&gt;
+#8 0x5586f466dc5b &lt;unknown&gt;
+#9 0x5586f463db59 &lt;unknown&gt;
+</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -9795,8 +11757,29 @@
       <c r="D371" t="inlineStr"/>
       <c r="E371" t="inlineStr"/>
       <c r="F371" t="inlineStr"/>
-      <c r="G371" t="inlineStr"/>
-      <c r="H371" t="inlineStr"/>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
+  (Session info: chrome=150.0.7871.114)
+Stacktrace:
+#0 0x5586f4c7f41a &lt;unknown&gt;
+#1 0x5586f4657689 &lt;unknown&gt;
+#2 0x5586f463f21a &lt;unknown&gt;
+#3 0x5586f463ee96 &lt;unknown&gt;
+#4 0x5586f463ca7e &lt;unknown&gt;
+#5 0x5586f463d3ff &lt;unknown&gt;
+#6 0x5586f464c4e0 &lt;unknown&gt;
+#7 0x5586f46663e7 &lt;unknown&gt;
+#8 0x5586f466dc5b &lt;unknown&gt;
+#9 0x5586f463db59 &lt;unknown&gt;
+</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">

--- a/output.xlsx
+++ b/output.xlsx
@@ -5014,21 +5014,9 @@
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
       <c r="G166" t="inlineStr">
         <is>
           <t>OK</t>
@@ -5048,21 +5036,9 @@
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
       <c r="G167" t="inlineStr">
         <is>
           <t>OK</t>
@@ -5082,21 +5058,9 @@
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr">
         <is>
           <t>OK</t>
@@ -5116,21 +5080,9 @@
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr"/>
       <c r="G169" t="inlineStr">
         <is>
           <t>OK</t>
@@ -5150,21 +5102,9 @@
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
       <c r="G170" t="inlineStr">
         <is>
           <t>OK</t>
@@ -5184,21 +5124,9 @@
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
       <c r="G171" t="inlineStr">
         <is>
           <t>OK</t>
@@ -5250,21 +5178,9 @@
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr"/>
       <c r="G173" t="inlineStr">
         <is>
           <t>OK</t>
@@ -5284,21 +5200,9 @@
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr"/>
       <c r="G174" t="inlineStr">
         <is>
           <t>OK</t>
@@ -5318,21 +5222,9 @@
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr"/>
       <c r="G175" t="inlineStr">
         <is>
           <t>OK</t>
@@ -5352,21 +5244,9 @@
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
       <c r="G176" t="inlineStr">
         <is>
           <t>OK</t>
@@ -5386,21 +5266,9 @@
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr"/>
       <c r="G177" t="inlineStr">
         <is>
           <t>OK</t>
@@ -5420,21 +5288,9 @@
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr"/>
       <c r="G178" t="inlineStr">
         <is>
           <t>OK</t>
@@ -5454,21 +5310,9 @@
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr"/>
       <c r="G179" t="inlineStr">
         <is>
           <t>OK</t>
@@ -5488,21 +5332,9 @@
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr"/>
       <c r="G180" t="inlineStr">
         <is>
           <t>OK</t>
@@ -5914,11 +5746,7 @@
       <c r="E193" t="n">
         <v>6</v>
       </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr">
         <is>
           <t>OK</t>
@@ -6074,11 +5902,7 @@
       <c r="E198" t="n">
         <v>6</v>
       </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr">
         <is>
           <t>OK</t>
@@ -6106,11 +5930,7 @@
       <c r="E199" t="n">
         <v>6</v>
       </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr">
         <is>
           <t>OK</t>
@@ -6170,11 +5990,7 @@
       <c r="E201" t="n">
         <v>6</v>
       </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F201" t="inlineStr"/>
       <c r="G201" t="inlineStr">
         <is>
           <t>OK</t>
@@ -6194,21 +6010,9 @@
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr"/>
       <c r="G202" t="inlineStr">
         <is>
           <t>OK</t>
@@ -6230,16 +6034,8 @@
       <c r="C203" t="n">
         <v>949</v>
       </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
           <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
@@ -6264,21 +6060,9 @@
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr"/>
       <c r="G204" t="inlineStr">
         <is>
           <t>OK</t>
@@ -6300,16 +6084,8 @@
       <c r="C205" t="n">
         <v>749</v>
       </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr">
         <is>
           <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
@@ -6334,21 +6110,9 @@
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr"/>
       <c r="G206" t="inlineStr">
         <is>
           <t>OK</t>
@@ -6368,21 +6132,9 @@
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr"/>
       <c r="G207" t="inlineStr">
         <is>
           <t>OK</t>
@@ -6404,16 +6156,8 @@
       <c r="C208" t="n">
         <v>3899</v>
       </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
         <is>
           <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
@@ -6446,11 +6190,7 @@
       <c r="E209" t="n">
         <v>237</v>
       </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F209" t="inlineStr"/>
       <c r="G209" t="inlineStr">
         <is>
           <t>OK</t>
@@ -6478,11 +6218,7 @@
       <c r="E210" t="n">
         <v>237</v>
       </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F210" t="inlineStr"/>
       <c r="G210" t="inlineStr">
         <is>
           <t>OK</t>
@@ -6542,11 +6278,7 @@
       <c r="E212" t="n">
         <v>16</v>
       </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F212" t="inlineStr"/>
       <c r="G212" t="inlineStr">
         <is>
           <t>OK</t>
@@ -6574,11 +6306,7 @@
       <c r="E213" t="n">
         <v>55</v>
       </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F213" t="inlineStr"/>
       <c r="G213" t="inlineStr">
         <is>
           <t>OK</t>
@@ -6606,11 +6334,7 @@
       <c r="E214" t="n">
         <v>25</v>
       </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F214" t="inlineStr"/>
       <c r="G214" t="inlineStr">
         <is>
           <t>OK</t>
@@ -6630,21 +6354,9 @@
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr"/>
       <c r="G215" t="inlineStr">
         <is>
           <t>OK</t>
@@ -6664,21 +6376,9 @@
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" t="inlineStr"/>
+      <c r="F216" t="inlineStr"/>
       <c r="G216" t="inlineStr">
         <is>
           <t>OK</t>
@@ -6706,11 +6406,7 @@
       <c r="E217" t="n">
         <v>47</v>
       </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F217" t="inlineStr"/>
       <c r="G217" t="inlineStr">
         <is>
           <t>OK</t>
@@ -6738,11 +6434,7 @@
       <c r="E218" t="n">
         <v>1</v>
       </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F218" t="inlineStr"/>
       <c r="G218" t="inlineStr">
         <is>
           <t>OK</t>
@@ -6762,21 +6454,9 @@
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr"/>
       <c r="G219" t="inlineStr">
         <is>
           <t>OK</t>
@@ -6900,11 +6580,7 @@
       <c r="E223" t="n">
         <v>3</v>
       </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F223" t="inlineStr"/>
       <c r="G223" t="inlineStr">
         <is>
           <t>OK</t>
@@ -6932,11 +6608,7 @@
       <c r="E224" t="n">
         <v>3</v>
       </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F224" t="inlineStr"/>
       <c r="G224" t="inlineStr">
         <is>
           <t>OK</t>
@@ -6964,11 +6636,7 @@
       <c r="E225" t="n">
         <v>3</v>
       </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F225" t="inlineStr"/>
       <c r="G225" t="inlineStr">
         <is>
           <t>OK</t>
@@ -6996,11 +6664,7 @@
       <c r="E226" t="n">
         <v>1655</v>
       </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F226" t="inlineStr"/>
       <c r="G226" t="inlineStr">
         <is>
           <t>OK</t>
@@ -7028,11 +6692,7 @@
       <c r="E227" t="n">
         <v>1655</v>
       </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F227" t="inlineStr"/>
       <c r="G227" t="inlineStr">
         <is>
           <t>OK</t>
@@ -7060,11 +6720,7 @@
       <c r="E228" t="n">
         <v>30</v>
       </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F228" t="inlineStr"/>
       <c r="G228" t="inlineStr">
         <is>
           <t>OK</t>
@@ -7116,21 +6772,9 @@
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D230" t="inlineStr"/>
+      <c r="E230" t="inlineStr"/>
+      <c r="F230" t="inlineStr"/>
       <c r="G230" t="inlineStr">
         <is>
           <t>OK</t>
@@ -7798,11 +7442,7 @@
       <c r="E251" t="n">
         <v>594</v>
       </c>
-      <c r="F251" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F251" t="inlineStr"/>
       <c r="G251" t="inlineStr">
         <is>
           <t>OK</t>
@@ -7830,11 +7470,7 @@
       <c r="E252" t="n">
         <v>594</v>
       </c>
-      <c r="F252" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F252" t="inlineStr"/>
       <c r="G252" t="inlineStr">
         <is>
           <t>OK</t>
@@ -7862,11 +7498,7 @@
       <c r="E253" t="n">
         <v>594</v>
       </c>
-      <c r="F253" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F253" t="inlineStr"/>
       <c r="G253" t="inlineStr">
         <is>
           <t>OK</t>
@@ -7886,21 +7518,9 @@
         </is>
       </c>
       <c r="C254" t="inlineStr"/>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E254" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F254" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D254" t="inlineStr"/>
+      <c r="E254" t="inlineStr"/>
+      <c r="F254" t="inlineStr"/>
       <c r="G254" t="inlineStr">
         <is>
           <t>OK</t>
@@ -7928,11 +7548,7 @@
       <c r="E255" t="n">
         <v>15</v>
       </c>
-      <c r="F255" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F255" t="inlineStr"/>
       <c r="G255" t="inlineStr">
         <is>
           <t>OK</t>
@@ -7960,11 +7576,7 @@
       <c r="E256" t="n">
         <v>15</v>
       </c>
-      <c r="F256" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F256" t="inlineStr"/>
       <c r="G256" t="inlineStr">
         <is>
           <t>OK</t>
@@ -7992,11 +7604,7 @@
       <c r="E257" t="n">
         <v>14</v>
       </c>
-      <c r="F257" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F257" t="inlineStr"/>
       <c r="G257" t="inlineStr">
         <is>
           <t>OK</t>
@@ -8024,11 +7632,7 @@
       <c r="E258" t="n">
         <v>5</v>
       </c>
-      <c r="F258" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F258" t="inlineStr"/>
       <c r="G258" t="inlineStr">
         <is>
           <t>OK</t>
@@ -8120,11 +7724,7 @@
       <c r="E261" t="n">
         <v>5</v>
       </c>
-      <c r="F261" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F261" t="inlineStr"/>
       <c r="G261" t="inlineStr">
         <is>
           <t>OK</t>
@@ -8152,11 +7752,7 @@
       <c r="E262" t="n">
         <v>5</v>
       </c>
-      <c r="F262" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F262" t="inlineStr"/>
       <c r="G262" t="inlineStr">
         <is>
           <t>OK</t>
@@ -8248,11 +7844,7 @@
       <c r="E265" t="n">
         <v>5</v>
       </c>
-      <c r="F265" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F265" t="inlineStr"/>
       <c r="G265" t="inlineStr">
         <is>
           <t>OK</t>
@@ -8280,11 +7872,7 @@
       <c r="E266" t="n">
         <v>5</v>
       </c>
-      <c r="F266" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F266" t="inlineStr"/>
       <c r="G266" t="inlineStr">
         <is>
           <t>OK</t>
@@ -8376,11 +7964,7 @@
       <c r="E269" t="n">
         <v>5</v>
       </c>
-      <c r="F269" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F269" t="inlineStr"/>
       <c r="G269" t="inlineStr">
         <is>
           <t>OK</t>
@@ -8400,21 +7984,9 @@
         </is>
       </c>
       <c r="C270" t="inlineStr"/>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F270" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D270" t="inlineStr"/>
+      <c r="E270" t="inlineStr"/>
+      <c r="F270" t="inlineStr"/>
       <c r="G270" t="inlineStr">
         <is>
           <t>OK</t>
@@ -8506,11 +8078,7 @@
       <c r="E273" t="n">
         <v>3</v>
       </c>
-      <c r="F273" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F273" t="inlineStr"/>
       <c r="G273" t="inlineStr">
         <is>
           <t>OK</t>
@@ -8530,21 +8098,9 @@
         </is>
       </c>
       <c r="C274" t="inlineStr"/>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E274" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F274" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D274" t="inlineStr"/>
+      <c r="E274" t="inlineStr"/>
+      <c r="F274" t="inlineStr"/>
       <c r="G274" t="inlineStr">
         <is>
           <t>OK</t>
@@ -8564,21 +8120,9 @@
         </is>
       </c>
       <c r="C275" t="inlineStr"/>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E275" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F275" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D275" t="inlineStr"/>
+      <c r="E275" t="inlineStr"/>
+      <c r="F275" t="inlineStr"/>
       <c r="G275" t="inlineStr">
         <is>
           <t>OK</t>
@@ -8606,11 +8150,7 @@
       <c r="E276" t="n">
         <v>3</v>
       </c>
-      <c r="F276" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F276" t="inlineStr"/>
       <c r="G276" t="inlineStr">
         <is>
           <t>OK</t>
@@ -8638,11 +8178,7 @@
       <c r="E277" t="n">
         <v>3</v>
       </c>
-      <c r="F277" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F277" t="inlineStr"/>
       <c r="G277" t="inlineStr">
         <is>
           <t>OK</t>
@@ -8670,11 +8206,7 @@
       <c r="E278" t="n">
         <v>3</v>
       </c>
-      <c r="F278" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F278" t="inlineStr"/>
       <c r="G278" t="inlineStr">
         <is>
           <t>OK</t>
@@ -8702,11 +8234,7 @@
       <c r="E279" t="n">
         <v>3</v>
       </c>
-      <c r="F279" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F279" t="inlineStr"/>
       <c r="G279" t="inlineStr">
         <is>
           <t>OK</t>
@@ -8766,11 +8294,7 @@
       <c r="E281" t="n">
         <v>3</v>
       </c>
-      <c r="F281" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F281" t="inlineStr"/>
       <c r="G281" t="inlineStr">
         <is>
           <t>OK</t>
@@ -8790,21 +8314,9 @@
         </is>
       </c>
       <c r="C282" t="inlineStr"/>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E282" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F282" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D282" t="inlineStr"/>
+      <c r="E282" t="inlineStr"/>
+      <c r="F282" t="inlineStr"/>
       <c r="G282" t="inlineStr">
         <is>
           <t>OK</t>
@@ -8824,21 +8336,9 @@
         </is>
       </c>
       <c r="C283" t="inlineStr"/>
-      <c r="D283" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E283" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F283" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D283" t="inlineStr"/>
+      <c r="E283" t="inlineStr"/>
+      <c r="F283" t="inlineStr"/>
       <c r="G283" t="inlineStr">
         <is>
           <t>OK</t>
@@ -8858,21 +8358,9 @@
         </is>
       </c>
       <c r="C284" t="inlineStr"/>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E284" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F284" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D284" t="inlineStr"/>
+      <c r="E284" t="inlineStr"/>
+      <c r="F284" t="inlineStr"/>
       <c r="G284" t="inlineStr">
         <is>
           <t>OK</t>
@@ -8900,11 +8388,7 @@
       <c r="E285" t="n">
         <v>3</v>
       </c>
-      <c r="F285" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F285" t="inlineStr"/>
       <c r="G285" t="inlineStr">
         <is>
           <t>OK</t>
@@ -8990,16 +8474,8 @@
       <c r="C288" t="n">
         <v>4079</v>
       </c>
-      <c r="D288" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E288" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D288" t="inlineStr"/>
+      <c r="E288" t="inlineStr"/>
       <c r="F288" t="inlineStr">
         <is>
           <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
@@ -9026,16 +8502,8 @@
       <c r="C289" t="n">
         <v>4079</v>
       </c>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E289" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D289" t="inlineStr"/>
+      <c r="E289" t="inlineStr"/>
       <c r="F289" t="inlineStr">
         <is>
           <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
@@ -9068,11 +8536,7 @@
       <c r="E290" t="n">
         <v>4</v>
       </c>
-      <c r="F290" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F290" t="inlineStr"/>
       <c r="G290" t="inlineStr">
         <is>
           <t>OK</t>
@@ -9100,11 +8564,7 @@
       <c r="E291" t="n">
         <v>2</v>
       </c>
-      <c r="F291" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F291" t="inlineStr"/>
       <c r="G291" t="inlineStr">
         <is>
           <t>OK</t>
@@ -9132,11 +8592,7 @@
       <c r="E292" t="n">
         <v>34</v>
       </c>
-      <c r="F292" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F292" t="inlineStr"/>
       <c r="G292" t="inlineStr">
         <is>
           <t>OK</t>
@@ -9164,11 +8620,7 @@
       <c r="E293" t="n">
         <v>16</v>
       </c>
-      <c r="F293" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F293" t="inlineStr"/>
       <c r="G293" t="inlineStr">
         <is>
           <t>OK</t>
@@ -9188,21 +8640,9 @@
         </is>
       </c>
       <c r="C294" t="inlineStr"/>
-      <c r="D294" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E294" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F294" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D294" t="inlineStr"/>
+      <c r="E294" t="inlineStr"/>
+      <c r="F294" t="inlineStr"/>
       <c r="G294" t="inlineStr">
         <is>
           <t>OK</t>
@@ -9230,11 +8670,7 @@
       <c r="E295" t="n">
         <v>5</v>
       </c>
-      <c r="F295" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F295" t="inlineStr"/>
       <c r="G295" t="inlineStr">
         <is>
           <t>OK</t>
@@ -9262,11 +8698,7 @@
       <c r="E296" t="n">
         <v>1</v>
       </c>
-      <c r="F296" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F296" t="inlineStr"/>
       <c r="G296" t="inlineStr">
         <is>
           <t>OK</t>
@@ -9288,21 +8720,9 @@
       <c r="C297" t="n">
         <v>3249</v>
       </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E297" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F297" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D297" t="inlineStr"/>
+      <c r="E297" t="inlineStr"/>
+      <c r="F297" t="inlineStr"/>
       <c r="G297" t="inlineStr">
         <is>
           <t>OK</t>
@@ -9322,21 +8742,9 @@
         </is>
       </c>
       <c r="C298" t="inlineStr"/>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E298" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F298" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D298" t="inlineStr"/>
+      <c r="E298" t="inlineStr"/>
+      <c r="F298" t="inlineStr"/>
       <c r="G298" t="inlineStr">
         <is>
           <t>OK</t>
@@ -9356,21 +8764,9 @@
         </is>
       </c>
       <c r="C299" t="inlineStr"/>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E299" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F299" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D299" t="inlineStr"/>
+      <c r="E299" t="inlineStr"/>
+      <c r="F299" t="inlineStr"/>
       <c r="G299" t="inlineStr">
         <is>
           <t>OK</t>
@@ -9456,16 +8852,8 @@
       <c r="C302" t="n">
         <v>1829</v>
       </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E302" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D302" t="inlineStr"/>
+      <c r="E302" t="inlineStr"/>
       <c r="F302" t="inlineStr">
         <is>
           <t>Only 1 left in stock.</t>
@@ -9492,21 +8880,9 @@
       <c r="C303" t="n">
         <v>1219</v>
       </c>
-      <c r="D303" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E303" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F303" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D303" t="inlineStr"/>
+      <c r="E303" t="inlineStr"/>
+      <c r="F303" t="inlineStr"/>
       <c r="G303" t="inlineStr">
         <is>
           <t>OK</t>
@@ -9628,11 +9004,7 @@
       <c r="E307" t="n">
         <v>2</v>
       </c>
-      <c r="F307" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F307" t="inlineStr"/>
       <c r="G307" t="inlineStr">
         <is>
           <t>OK</t>
@@ -10008,11 +9380,7 @@
       <c r="E319" t="n">
         <v>2</v>
       </c>
-      <c r="F319" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F319" t="inlineStr"/>
       <c r="G319" t="inlineStr">
         <is>
           <t>OK</t>
@@ -10418,21 +9786,9 @@
       <c r="C332" t="n">
         <v>4829</v>
       </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E332" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F332" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D332" t="inlineStr"/>
+      <c r="E332" t="inlineStr"/>
+      <c r="F332" t="inlineStr"/>
       <c r="G332" t="inlineStr">
         <is>
           <t>OK</t>
@@ -10556,11 +9912,7 @@
       <c r="E336" t="n">
         <v>5</v>
       </c>
-      <c r="F336" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F336" t="inlineStr"/>
       <c r="G336" t="inlineStr">
         <is>
           <t>OK</t>
@@ -10580,21 +9932,9 @@
         </is>
       </c>
       <c r="C337" t="inlineStr"/>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E337" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F337" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D337" t="inlineStr"/>
+      <c r="E337" t="inlineStr"/>
+      <c r="F337" t="inlineStr"/>
       <c r="G337" t="inlineStr">
         <is>
           <t>OK</t>
@@ -10646,21 +9986,9 @@
         </is>
       </c>
       <c r="C339" t="inlineStr"/>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E339" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F339" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D339" t="inlineStr"/>
+      <c r="E339" t="inlineStr"/>
+      <c r="F339" t="inlineStr"/>
       <c r="G339" t="inlineStr">
         <is>
           <t>OK</t>
@@ -10680,21 +10008,9 @@
         </is>
       </c>
       <c r="C340" t="inlineStr"/>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E340" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F340" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D340" t="inlineStr"/>
+      <c r="E340" t="inlineStr"/>
+      <c r="F340" t="inlineStr"/>
       <c r="G340" t="inlineStr">
         <is>
           <t>OK</t>
@@ -10714,21 +10030,9 @@
         </is>
       </c>
       <c r="C341" t="inlineStr"/>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E341" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F341" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D341" t="inlineStr"/>
+      <c r="E341" t="inlineStr"/>
+      <c r="F341" t="inlineStr"/>
       <c r="G341" t="inlineStr">
         <is>
           <t>OK</t>
@@ -10748,21 +10052,9 @@
         </is>
       </c>
       <c r="C342" t="inlineStr"/>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E342" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F342" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D342" t="inlineStr"/>
+      <c r="E342" t="inlineStr"/>
+      <c r="F342" t="inlineStr"/>
       <c r="G342" t="inlineStr">
         <is>
           <t>OK</t>
@@ -10782,21 +10074,9 @@
         </is>
       </c>
       <c r="C343" t="inlineStr"/>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E343" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F343" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D343" t="inlineStr"/>
+      <c r="E343" t="inlineStr"/>
+      <c r="F343" t="inlineStr"/>
       <c r="G343" t="inlineStr">
         <is>
           <t>OK</t>
@@ -10816,21 +10096,9 @@
         </is>
       </c>
       <c r="C344" t="inlineStr"/>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E344" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F344" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D344" t="inlineStr"/>
+      <c r="E344" t="inlineStr"/>
+      <c r="F344" t="inlineStr"/>
       <c r="G344" t="inlineStr">
         <is>
           <t>OK</t>
@@ -10850,21 +10118,9 @@
         </is>
       </c>
       <c r="C345" t="inlineStr"/>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E345" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F345" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D345" t="inlineStr"/>
+      <c r="E345" t="inlineStr"/>
+      <c r="F345" t="inlineStr"/>
       <c r="G345" t="inlineStr">
         <is>
           <t>OK</t>
@@ -11364,32 +10620,27 @@
         </is>
       </c>
       <c r="C361" t="inlineStr"/>
-      <c r="D361" t="inlineStr"/>
-      <c r="E361" t="inlineStr"/>
-      <c r="F361" t="inlineStr"/>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="H361" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
-  (Session info: chrome=150.0.7871.114)
-Stacktrace:
-#0 0x5586f4c7f41a &lt;unknown&gt;
-#1 0x5586f4657689 &lt;unknown&gt;
-#2 0x5586f463f21a &lt;unknown&gt;
-#3 0x5586f463ee96 &lt;unknown&gt;
-#4 0x5586f463ca7e &lt;unknown&gt;
-#5 0x5586f463d3ff &lt;unknown&gt;
-#6 0x5586f464c4e0 &lt;unknown&gt;
-#7 0x5586f46663e7 &lt;unknown&gt;
-#8 0x5586f466dc5b &lt;unknown&gt;
-#9 0x5586f463db59 &lt;unknown&gt;
-</t>
-        </is>
-      </c>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -11403,32 +10654,27 @@
         </is>
       </c>
       <c r="C362" t="inlineStr"/>
-      <c r="D362" t="inlineStr"/>
-      <c r="E362" t="inlineStr"/>
-      <c r="F362" t="inlineStr"/>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="H362" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
-  (Session info: chrome=150.0.7871.114)
-Stacktrace:
-#0 0x5586f4c7f41a &lt;unknown&gt;
-#1 0x5586f4657689 &lt;unknown&gt;
-#2 0x5586f463f21a &lt;unknown&gt;
-#3 0x5586f463ee96 &lt;unknown&gt;
-#4 0x5586f463ca7e &lt;unknown&gt;
-#5 0x5586f463d3ff &lt;unknown&gt;
-#6 0x5586f464c4e0 &lt;unknown&gt;
-#7 0x5586f46663e7 &lt;unknown&gt;
-#8 0x5586f466dc5b &lt;unknown&gt;
-#9 0x5586f463db59 &lt;unknown&gt;
-</t>
-        </is>
-      </c>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -11441,33 +10687,26 @@
           <t>https://www.amazon.in/dp/B0FHBB49GS</t>
         </is>
       </c>
-      <c r="C363" t="inlineStr"/>
-      <c r="D363" t="inlineStr"/>
-      <c r="E363" t="inlineStr"/>
-      <c r="F363" t="inlineStr"/>
+      <c r="C363" t="n">
+        <v>10839</v>
+      </c>
+      <c r="D363" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E363" t="n">
+        <v>9</v>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="H363" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
-  (Session info: chrome=150.0.7871.114)
-Stacktrace:
-#0 0x5586f4c7f41a &lt;unknown&gt;
-#1 0x5586f4657689 &lt;unknown&gt;
-#2 0x5586f463f21a &lt;unknown&gt;
-#3 0x5586f463ee96 &lt;unknown&gt;
-#4 0x5586f463ca7e &lt;unknown&gt;
-#5 0x5586f463d3ff &lt;unknown&gt;
-#6 0x5586f464c4e0 &lt;unknown&gt;
-#7 0x5586f46663e7 &lt;unknown&gt;
-#8 0x5586f466dc5b &lt;unknown&gt;
-#9 0x5586f463db59 &lt;unknown&gt;
-</t>
-        </is>
-      </c>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -11480,33 +10719,26 @@
           <t>https://www.amazon.in/dp/B0FHB7XSFB</t>
         </is>
       </c>
-      <c r="C364" t="inlineStr"/>
-      <c r="D364" t="inlineStr"/>
-      <c r="E364" t="inlineStr"/>
-      <c r="F364" t="inlineStr"/>
+      <c r="C364" t="n">
+        <v>10839</v>
+      </c>
+      <c r="D364" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E364" t="n">
+        <v>9</v>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="H364" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
-  (Session info: chrome=150.0.7871.114)
-Stacktrace:
-#0 0x5586f4c7f41a &lt;unknown&gt;
-#1 0x5586f4657689 &lt;unknown&gt;
-#2 0x5586f463f21a &lt;unknown&gt;
-#3 0x5586f463ee96 &lt;unknown&gt;
-#4 0x5586f463ca7e &lt;unknown&gt;
-#5 0x5586f463d3ff &lt;unknown&gt;
-#6 0x5586f464c4e0 &lt;unknown&gt;
-#7 0x5586f46663e7 &lt;unknown&gt;
-#8 0x5586f466dc5b &lt;unknown&gt;
-#9 0x5586f463db59 &lt;unknown&gt;
-</t>
-        </is>
-      </c>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -11519,33 +10751,26 @@
           <t>https://www.amazon.in/dp/B0FHB5G82B</t>
         </is>
       </c>
-      <c r="C365" t="inlineStr"/>
-      <c r="D365" t="inlineStr"/>
-      <c r="E365" t="inlineStr"/>
-      <c r="F365" t="inlineStr"/>
+      <c r="C365" t="n">
+        <v>10839</v>
+      </c>
+      <c r="D365" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E365" t="n">
+        <v>9</v>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="H365" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
-  (Session info: chrome=150.0.7871.114)
-Stacktrace:
-#0 0x5586f4c7f41a &lt;unknown&gt;
-#1 0x5586f4657689 &lt;unknown&gt;
-#2 0x5586f463f21a &lt;unknown&gt;
-#3 0x5586f463ee96 &lt;unknown&gt;
-#4 0x5586f463ca7e &lt;unknown&gt;
-#5 0x5586f463d3ff &lt;unknown&gt;
-#6 0x5586f464c4e0 &lt;unknown&gt;
-#7 0x5586f46663e7 &lt;unknown&gt;
-#8 0x5586f466dc5b &lt;unknown&gt;
-#9 0x5586f463db59 &lt;unknown&gt;
-</t>
-        </is>
-      </c>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -11558,33 +10783,26 @@
           <t>https://www.amazon.in/dp/B0FC6QJ8TZ</t>
         </is>
       </c>
-      <c r="C366" t="inlineStr"/>
-      <c r="D366" t="inlineStr"/>
-      <c r="E366" t="inlineStr"/>
-      <c r="F366" t="inlineStr"/>
+      <c r="C366" t="n">
+        <v>37319</v>
+      </c>
+      <c r="D366" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E366" t="n">
+        <v>4</v>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="H366" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
-  (Session info: chrome=150.0.7871.114)
-Stacktrace:
-#0 0x5586f4c7f41a &lt;unknown&gt;
-#1 0x5586f4657689 &lt;unknown&gt;
-#2 0x5586f463f21a &lt;unknown&gt;
-#3 0x5586f463ee96 &lt;unknown&gt;
-#4 0x5586f463ca7e &lt;unknown&gt;
-#5 0x5586f463d3ff &lt;unknown&gt;
-#6 0x5586f464c4e0 &lt;unknown&gt;
-#7 0x5586f46663e7 &lt;unknown&gt;
-#8 0x5586f466dc5b &lt;unknown&gt;
-#9 0x5586f463db59 &lt;unknown&gt;
-</t>
-        </is>
-      </c>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -11597,33 +10815,26 @@
           <t>https://www.amazon.in/dp/B0FC6RTN1S</t>
         </is>
       </c>
-      <c r="C367" t="inlineStr"/>
-      <c r="D367" t="inlineStr"/>
-      <c r="E367" t="inlineStr"/>
-      <c r="F367" t="inlineStr"/>
+      <c r="C367" t="n">
+        <v>37319</v>
+      </c>
+      <c r="D367" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E367" t="n">
+        <v>4</v>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="H367" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
-  (Session info: chrome=150.0.7871.114)
-Stacktrace:
-#0 0x5586f4c7f41a &lt;unknown&gt;
-#1 0x5586f4657689 &lt;unknown&gt;
-#2 0x5586f463f21a &lt;unknown&gt;
-#3 0x5586f463ee96 &lt;unknown&gt;
-#4 0x5586f463ca7e &lt;unknown&gt;
-#5 0x5586f463d3ff &lt;unknown&gt;
-#6 0x5586f464c4e0 &lt;unknown&gt;
-#7 0x5586f46663e7 &lt;unknown&gt;
-#8 0x5586f466dc5b &lt;unknown&gt;
-#9 0x5586f463db59 &lt;unknown&gt;
-</t>
-        </is>
-      </c>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -11636,33 +10847,26 @@
           <t>https://www.amazon.in/dp/B0D37YQ1BX</t>
         </is>
       </c>
-      <c r="C368" t="inlineStr"/>
-      <c r="D368" t="inlineStr"/>
-      <c r="E368" t="inlineStr"/>
-      <c r="F368" t="inlineStr"/>
+      <c r="C368" t="n">
+        <v>37319</v>
+      </c>
+      <c r="D368" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E368" t="n">
+        <v>4</v>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="H368" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
-  (Session info: chrome=150.0.7871.114)
-Stacktrace:
-#0 0x5586f4c7f41a &lt;unknown&gt;
-#1 0x5586f4657689 &lt;unknown&gt;
-#2 0x5586f463f21a &lt;unknown&gt;
-#3 0x5586f463ee96 &lt;unknown&gt;
-#4 0x5586f463ca7e &lt;unknown&gt;
-#5 0x5586f463d3ff &lt;unknown&gt;
-#6 0x5586f464c4e0 &lt;unknown&gt;
-#7 0x5586f46663e7 &lt;unknown&gt;
-#8 0x5586f466dc5b &lt;unknown&gt;
-#9 0x5586f463db59 &lt;unknown&gt;
-</t>
-        </is>
-      </c>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -11675,33 +10879,26 @@
           <t>https://www.amazon.in/dp/B0D37WV1DN</t>
         </is>
       </c>
-      <c r="C369" t="inlineStr"/>
-      <c r="D369" t="inlineStr"/>
-      <c r="E369" t="inlineStr"/>
-      <c r="F369" t="inlineStr"/>
+      <c r="C369" t="n">
+        <v>37319</v>
+      </c>
+      <c r="D369" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E369" t="n">
+        <v>4</v>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="H369" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
-  (Session info: chrome=150.0.7871.114)
-Stacktrace:
-#0 0x5586f4c7f41a &lt;unknown&gt;
-#1 0x5586f4657689 &lt;unknown&gt;
-#2 0x5586f463f21a &lt;unknown&gt;
-#3 0x5586f463ee96 &lt;unknown&gt;
-#4 0x5586f463ca7e &lt;unknown&gt;
-#5 0x5586f463d3ff &lt;unknown&gt;
-#6 0x5586f464c4e0 &lt;unknown&gt;
-#7 0x5586f46663e7 &lt;unknown&gt;
-#8 0x5586f466dc5b &lt;unknown&gt;
-#9 0x5586f463db59 &lt;unknown&gt;
-</t>
-        </is>
-      </c>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -11714,33 +10911,26 @@
           <t>https://www.amazon.in/dp/B0D37YDPPH</t>
         </is>
       </c>
-      <c r="C370" t="inlineStr"/>
-      <c r="D370" t="inlineStr"/>
-      <c r="E370" t="inlineStr"/>
-      <c r="F370" t="inlineStr"/>
+      <c r="C370" t="n">
+        <v>37319</v>
+      </c>
+      <c r="D370" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E370" t="n">
+        <v>4</v>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="H370" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
-  (Session info: chrome=150.0.7871.114)
-Stacktrace:
-#0 0x5586f4c7f41a &lt;unknown&gt;
-#1 0x5586f4657689 &lt;unknown&gt;
-#2 0x5586f463f21a &lt;unknown&gt;
-#3 0x5586f463ee96 &lt;unknown&gt;
-#4 0x5586f463ca7e &lt;unknown&gt;
-#5 0x5586f463d3ff &lt;unknown&gt;
-#6 0x5586f464c4e0 &lt;unknown&gt;
-#7 0x5586f46663e7 &lt;unknown&gt;
-#8 0x5586f466dc5b &lt;unknown&gt;
-#9 0x5586f463db59 &lt;unknown&gt;
-</t>
-        </is>
-      </c>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -11753,33 +10943,26 @@
           <t>https://www.amazon.in/dp/B0DNF9MTXC</t>
         </is>
       </c>
-      <c r="C371" t="inlineStr"/>
-      <c r="D371" t="inlineStr"/>
-      <c r="E371" t="inlineStr"/>
-      <c r="F371" t="inlineStr"/>
+      <c r="C371" t="n">
+        <v>37319</v>
+      </c>
+      <c r="D371" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E371" t="n">
+        <v>4</v>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="H371" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
-  (Session info: chrome=150.0.7871.114)
-Stacktrace:
-#0 0x5586f4c7f41a &lt;unknown&gt;
-#1 0x5586f4657689 &lt;unknown&gt;
-#2 0x5586f463f21a &lt;unknown&gt;
-#3 0x5586f463ee96 &lt;unknown&gt;
-#4 0x5586f463ca7e &lt;unknown&gt;
-#5 0x5586f463d3ff &lt;unknown&gt;
-#6 0x5586f464c4e0 &lt;unknown&gt;
-#7 0x5586f46663e7 &lt;unknown&gt;
-#8 0x5586f466dc5b &lt;unknown&gt;
-#9 0x5586f463db59 &lt;unknown&gt;
-</t>
-        </is>
-      </c>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -11792,11 +10975,25 @@
           <t>https://www.amazon.in/dp/B0FHB77B51</t>
         </is>
       </c>
-      <c r="C372" t="inlineStr"/>
-      <c r="D372" t="inlineStr"/>
-      <c r="E372" t="inlineStr"/>
-      <c r="F372" t="inlineStr"/>
-      <c r="G372" t="inlineStr"/>
+      <c r="C372" t="n">
+        <v>10839</v>
+      </c>
+      <c r="D372" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E372" t="n">
+        <v>9</v>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H372" t="inlineStr"/>
     </row>
     <row r="373">
@@ -11810,11 +11007,25 @@
           <t>https://www.amazon.in/dp/B0FHB6PMBC</t>
         </is>
       </c>
-      <c r="C373" t="inlineStr"/>
-      <c r="D373" t="inlineStr"/>
-      <c r="E373" t="inlineStr"/>
-      <c r="F373" t="inlineStr"/>
-      <c r="G373" t="inlineStr"/>
+      <c r="C373" t="n">
+        <v>10839</v>
+      </c>
+      <c r="D373" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E373" t="n">
+        <v>9</v>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H373" t="inlineStr"/>
     </row>
     <row r="374">
@@ -11828,11 +11039,25 @@
           <t>https://www.amazon.in/dp/B0FC6QN3YX</t>
         </is>
       </c>
-      <c r="C374" t="inlineStr"/>
-      <c r="D374" t="inlineStr"/>
-      <c r="E374" t="inlineStr"/>
-      <c r="F374" t="inlineStr"/>
-      <c r="G374" t="inlineStr"/>
+      <c r="C374" t="n">
+        <v>37319</v>
+      </c>
+      <c r="D374" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E374" t="n">
+        <v>4</v>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H374" t="inlineStr"/>
     </row>
     <row r="375">
@@ -11846,11 +11071,25 @@
           <t>https://www.amazon.in/dp/B0FC6PG1FH</t>
         </is>
       </c>
-      <c r="C375" t="inlineStr"/>
-      <c r="D375" t="inlineStr"/>
-      <c r="E375" t="inlineStr"/>
-      <c r="F375" t="inlineStr"/>
-      <c r="G375" t="inlineStr"/>
+      <c r="C375" t="n">
+        <v>37319</v>
+      </c>
+      <c r="D375" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E375" t="n">
+        <v>4</v>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H375" t="inlineStr"/>
     </row>
     <row r="376">
@@ -11864,11 +11103,25 @@
           <t>https://www.amazon.in/dp/B0FHB794S2</t>
         </is>
       </c>
-      <c r="C376" t="inlineStr"/>
-      <c r="D376" t="inlineStr"/>
-      <c r="E376" t="inlineStr"/>
-      <c r="F376" t="inlineStr"/>
-      <c r="G376" t="inlineStr"/>
+      <c r="C376" t="n">
+        <v>10839</v>
+      </c>
+      <c r="D376" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E376" t="n">
+        <v>9</v>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H376" t="inlineStr"/>
     </row>
     <row r="377">
@@ -11882,11 +11135,25 @@
           <t>https://www.amazon.in/dp/B0FHB5YGT9</t>
         </is>
       </c>
-      <c r="C377" t="inlineStr"/>
-      <c r="D377" t="inlineStr"/>
-      <c r="E377" t="inlineStr"/>
-      <c r="F377" t="inlineStr"/>
-      <c r="G377" t="inlineStr"/>
+      <c r="C377" t="n">
+        <v>10839</v>
+      </c>
+      <c r="D377" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E377" t="n">
+        <v>9</v>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H377" t="inlineStr"/>
     </row>
     <row r="378">
@@ -11900,11 +11167,25 @@
           <t>https://www.amazon.in/dp/B0FHB635KH</t>
         </is>
       </c>
-      <c r="C378" t="inlineStr"/>
-      <c r="D378" t="inlineStr"/>
-      <c r="E378" t="inlineStr"/>
-      <c r="F378" t="inlineStr"/>
-      <c r="G378" t="inlineStr"/>
+      <c r="C378" t="n">
+        <v>10839</v>
+      </c>
+      <c r="D378" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E378" t="n">
+        <v>9</v>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H378" t="inlineStr"/>
     </row>
     <row r="379">
@@ -11918,11 +11199,29 @@
           <t>https://www.amazon.in/dp/B0F74D5JTF</t>
         </is>
       </c>
-      <c r="C379" t="inlineStr"/>
-      <c r="D379" t="inlineStr"/>
-      <c r="E379" t="inlineStr"/>
-      <c r="F379" t="inlineStr"/>
-      <c r="G379" t="inlineStr"/>
+      <c r="C379" t="n">
+        <v>4119</v>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H379" t="inlineStr"/>
     </row>
     <row r="380">
@@ -11936,11 +11235,29 @@
           <t>https://www.amazon.in/dp/B0F74K2HYH</t>
         </is>
       </c>
-      <c r="C380" t="inlineStr"/>
-      <c r="D380" t="inlineStr"/>
-      <c r="E380" t="inlineStr"/>
-      <c r="F380" t="inlineStr"/>
-      <c r="G380" t="inlineStr"/>
+      <c r="C380" t="n">
+        <v>4119</v>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H380" t="inlineStr"/>
     </row>
     <row r="381">
@@ -11954,11 +11271,29 @@
           <t>https://www.amazon.in/dp/B0F74F3K6Z</t>
         </is>
       </c>
-      <c r="C381" t="inlineStr"/>
-      <c r="D381" t="inlineStr"/>
-      <c r="E381" t="inlineStr"/>
-      <c r="F381" t="inlineStr"/>
-      <c r="G381" t="inlineStr"/>
+      <c r="C381" t="n">
+        <v>4119</v>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H381" t="inlineStr"/>
     </row>
     <row r="382">
@@ -11973,10 +11308,26 @@
         </is>
       </c>
       <c r="C382" t="inlineStr"/>
-      <c r="D382" t="inlineStr"/>
-      <c r="E382" t="inlineStr"/>
-      <c r="F382" t="inlineStr"/>
-      <c r="G382" t="inlineStr"/>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H382" t="inlineStr"/>
     </row>
     <row r="383">
@@ -11990,11 +11341,25 @@
           <t>https://www.amazon.in/dp/B09M8QW4GN</t>
         </is>
       </c>
-      <c r="C383" t="inlineStr"/>
-      <c r="D383" t="inlineStr"/>
-      <c r="E383" t="inlineStr"/>
-      <c r="F383" t="inlineStr"/>
-      <c r="G383" t="inlineStr"/>
+      <c r="C383" t="n">
+        <v>569</v>
+      </c>
+      <c r="D383" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E383" t="n">
+        <v>3</v>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>Only 2 left in stock.</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H383" t="inlineStr"/>
     </row>
     <row r="384">
@@ -12008,11 +11373,25 @@
           <t>https://www.amazon.in/dp/B0BTYVQZ99</t>
         </is>
       </c>
-      <c r="C384" t="inlineStr"/>
-      <c r="D384" t="inlineStr"/>
-      <c r="E384" t="inlineStr"/>
-      <c r="F384" t="inlineStr"/>
-      <c r="G384" t="inlineStr"/>
+      <c r="C384" t="n">
+        <v>1389</v>
+      </c>
+      <c r="D384" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E384" t="n">
+        <v>121</v>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H384" t="inlineStr"/>
     </row>
     <row r="385">
@@ -12026,11 +11405,25 @@
           <t>https://www.amazon.in/dp/B0BCQJNFP6</t>
         </is>
       </c>
-      <c r="C385" t="inlineStr"/>
-      <c r="D385" t="inlineStr"/>
-      <c r="E385" t="inlineStr"/>
-      <c r="F385" t="inlineStr"/>
-      <c r="G385" t="inlineStr"/>
+      <c r="C385" t="n">
+        <v>1829</v>
+      </c>
+      <c r="D385" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E385" t="n">
+        <v>41</v>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H385" t="inlineStr"/>
     </row>
     <row r="386">
@@ -12044,11 +11437,25 @@
           <t>https://www.amazon.in/dp/B07RTCXJYZ</t>
         </is>
       </c>
-      <c r="C386" t="inlineStr"/>
-      <c r="D386" t="inlineStr"/>
-      <c r="E386" t="inlineStr"/>
-      <c r="F386" t="inlineStr"/>
-      <c r="G386" t="inlineStr"/>
+      <c r="C386" t="n">
+        <v>1859</v>
+      </c>
+      <c r="D386" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E386" t="n">
+        <v>12</v>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H386" t="inlineStr"/>
     </row>
     <row r="387">
@@ -12062,11 +11469,25 @@
           <t>https://www.amazon.in/dp/B07Z8C892Z</t>
         </is>
       </c>
-      <c r="C387" t="inlineStr"/>
-      <c r="D387" t="inlineStr"/>
-      <c r="E387" t="inlineStr"/>
-      <c r="F387" t="inlineStr"/>
-      <c r="G387" t="inlineStr"/>
+      <c r="C387" t="n">
+        <v>2369</v>
+      </c>
+      <c r="D387" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E387" t="n">
+        <v>49</v>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H387" t="inlineStr"/>
     </row>
     <row r="388">
@@ -12080,11 +11501,25 @@
           <t>https://www.amazon.in/dp/B01MSJU2PM</t>
         </is>
       </c>
-      <c r="C388" t="inlineStr"/>
-      <c r="D388" t="inlineStr"/>
-      <c r="E388" t="inlineStr"/>
-      <c r="F388" t="inlineStr"/>
-      <c r="G388" t="inlineStr"/>
+      <c r="C388" t="n">
+        <v>1369</v>
+      </c>
+      <c r="D388" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E388" t="n">
+        <v>105</v>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>Only 3 left in stock.</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H388" t="inlineStr"/>
     </row>
     <row r="389">
@@ -12098,11 +11533,25 @@
           <t>https://www.amazon.in/dp/B071K21S2Z</t>
         </is>
       </c>
-      <c r="C389" t="inlineStr"/>
-      <c r="D389" t="inlineStr"/>
-      <c r="E389" t="inlineStr"/>
-      <c r="F389" t="inlineStr"/>
-      <c r="G389" t="inlineStr"/>
+      <c r="C389" t="n">
+        <v>1439</v>
+      </c>
+      <c r="D389" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E389" t="n">
+        <v>115</v>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H389" t="inlineStr"/>
     </row>
     <row r="390">
@@ -12116,11 +11565,25 @@
           <t>https://www.amazon.in/dp/B092JGK3T3</t>
         </is>
       </c>
-      <c r="C390" t="inlineStr"/>
-      <c r="D390" t="inlineStr"/>
-      <c r="E390" t="inlineStr"/>
-      <c r="F390" t="inlineStr"/>
-      <c r="G390" t="inlineStr"/>
+      <c r="C390" t="n">
+        <v>1659</v>
+      </c>
+      <c r="D390" t="n">
+        <v>5</v>
+      </c>
+      <c r="E390" t="n">
+        <v>1</v>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H390" t="inlineStr"/>
     </row>
     <row r="391">
@@ -12134,11 +11597,25 @@
           <t>https://www.amazon.in/dp/B092JH19NL</t>
         </is>
       </c>
-      <c r="C391" t="inlineStr"/>
-      <c r="D391" t="inlineStr"/>
-      <c r="E391" t="inlineStr"/>
-      <c r="F391" t="inlineStr"/>
-      <c r="G391" t="inlineStr"/>
+      <c r="C391" t="n">
+        <v>2069</v>
+      </c>
+      <c r="D391" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E391" t="n">
+        <v>12</v>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H391" t="inlineStr"/>
     </row>
     <row r="392">
@@ -12152,11 +11629,29 @@
           <t>https://www.amazon.in/dp/B092JG2HYM</t>
         </is>
       </c>
-      <c r="C392" t="inlineStr"/>
-      <c r="D392" t="inlineStr"/>
-      <c r="E392" t="inlineStr"/>
-      <c r="F392" t="inlineStr"/>
-      <c r="G392" t="inlineStr"/>
+      <c r="C392" t="n">
+        <v>1869</v>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H392" t="inlineStr"/>
     </row>
     <row r="393">
@@ -12170,11 +11665,29 @@
           <t>https://www.amazon.in/dp/B09T9KQYJ7</t>
         </is>
       </c>
-      <c r="C393" t="inlineStr"/>
-      <c r="D393" t="inlineStr"/>
-      <c r="E393" t="inlineStr"/>
-      <c r="F393" t="inlineStr"/>
-      <c r="G393" t="inlineStr"/>
+      <c r="C393" t="n">
+        <v>2649</v>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H393" t="inlineStr"/>
     </row>
     <row r="394">
@@ -12189,10 +11702,26 @@
         </is>
       </c>
       <c r="C394" t="inlineStr"/>
-      <c r="D394" t="inlineStr"/>
-      <c r="E394" t="inlineStr"/>
-      <c r="F394" t="inlineStr"/>
-      <c r="G394" t="inlineStr"/>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H394" t="inlineStr"/>
     </row>
     <row r="395">
@@ -12206,11 +11735,25 @@
           <t>https://www.amazon.in/dp/B07PPNLML1</t>
         </is>
       </c>
-      <c r="C395" t="inlineStr"/>
-      <c r="D395" t="inlineStr"/>
-      <c r="E395" t="inlineStr"/>
-      <c r="F395" t="inlineStr"/>
-      <c r="G395" t="inlineStr"/>
+      <c r="C395" t="n">
+        <v>1439</v>
+      </c>
+      <c r="D395" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E395" t="n">
+        <v>3</v>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H395" t="inlineStr"/>
     </row>
     <row r="396">
@@ -12225,10 +11768,26 @@
         </is>
       </c>
       <c r="C396" t="inlineStr"/>
-      <c r="D396" t="inlineStr"/>
-      <c r="E396" t="inlineStr"/>
-      <c r="F396" t="inlineStr"/>
-      <c r="G396" t="inlineStr"/>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H396" t="inlineStr"/>
     </row>
     <row r="397">
@@ -12242,11 +11801,25 @@
           <t>https://www.amazon.in/dp/B092JFYGDR</t>
         </is>
       </c>
-      <c r="C397" t="inlineStr"/>
-      <c r="D397" t="inlineStr"/>
-      <c r="E397" t="inlineStr"/>
-      <c r="F397" t="inlineStr"/>
-      <c r="G397" t="inlineStr"/>
+      <c r="C397" t="n">
+        <v>2499</v>
+      </c>
+      <c r="D397" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E397" t="n">
+        <v>25</v>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H397" t="inlineStr"/>
     </row>
     <row r="398">
@@ -12260,11 +11833,25 @@
           <t>https://www.amazon.in/dp/B092JG5H44</t>
         </is>
       </c>
-      <c r="C398" t="inlineStr"/>
-      <c r="D398" t="inlineStr"/>
-      <c r="E398" t="inlineStr"/>
-      <c r="F398" t="inlineStr"/>
-      <c r="G398" t="inlineStr"/>
+      <c r="C398" t="n">
+        <v>3149</v>
+      </c>
+      <c r="D398" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E398" t="n">
+        <v>45</v>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H398" t="inlineStr"/>
     </row>
     <row r="399">
@@ -12278,11 +11865,25 @@
           <t>https://www.amazon.in/dp/B07Y916W4P</t>
         </is>
       </c>
-      <c r="C399" t="inlineStr"/>
-      <c r="D399" t="inlineStr"/>
-      <c r="E399" t="inlineStr"/>
-      <c r="F399" t="inlineStr"/>
-      <c r="G399" t="inlineStr"/>
+      <c r="C399" t="n">
+        <v>2509</v>
+      </c>
+      <c r="D399" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E399" t="n">
+        <v>738</v>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H399" t="inlineStr"/>
     </row>
     <row r="400">
@@ -12296,11 +11897,25 @@
           <t>https://www.amazon.in/dp/B092JG312H</t>
         </is>
       </c>
-      <c r="C400" t="inlineStr"/>
-      <c r="D400" t="inlineStr"/>
-      <c r="E400" t="inlineStr"/>
-      <c r="F400" t="inlineStr"/>
-      <c r="G400" t="inlineStr"/>
+      <c r="C400" t="n">
+        <v>2939</v>
+      </c>
+      <c r="D400" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E400" t="n">
+        <v>2</v>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H400" t="inlineStr"/>
     </row>
     <row r="401">
@@ -12314,11 +11929,25 @@
           <t>https://www.amazon.in/dp/B092JH52SY</t>
         </is>
       </c>
-      <c r="C401" t="inlineStr"/>
-      <c r="D401" t="inlineStr"/>
-      <c r="E401" t="inlineStr"/>
-      <c r="F401" t="inlineStr"/>
-      <c r="G401" t="inlineStr"/>
+      <c r="C401" t="n">
+        <v>2939</v>
+      </c>
+      <c r="D401" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E401" t="n">
+        <v>10</v>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H401" t="inlineStr"/>
     </row>
     <row r="402">
@@ -12332,11 +11961,25 @@
           <t>https://www.amazon.in/dp/B09T9KP767</t>
         </is>
       </c>
-      <c r="C402" t="inlineStr"/>
-      <c r="D402" t="inlineStr"/>
-      <c r="E402" t="inlineStr"/>
-      <c r="F402" t="inlineStr"/>
-      <c r="G402" t="inlineStr"/>
+      <c r="C402" t="n">
+        <v>2499</v>
+      </c>
+      <c r="D402" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E402" t="n">
+        <v>42</v>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H402" t="inlineStr"/>
     </row>
     <row r="403">
@@ -12350,11 +11993,25 @@
           <t>https://www.amazon.in/dp/B09T9KZ47J</t>
         </is>
       </c>
-      <c r="C403" t="inlineStr"/>
-      <c r="D403" t="inlineStr"/>
-      <c r="E403" t="inlineStr"/>
-      <c r="F403" t="inlineStr"/>
-      <c r="G403" t="inlineStr"/>
+      <c r="C403" t="n">
+        <v>1969</v>
+      </c>
+      <c r="D403" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E403" t="n">
+        <v>67</v>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H403" t="inlineStr"/>
     </row>
     <row r="404">
@@ -12368,11 +12025,25 @@
           <t>https://www.amazon.in/dp/B09T9L19P9</t>
         </is>
       </c>
-      <c r="C404" t="inlineStr"/>
-      <c r="D404" t="inlineStr"/>
-      <c r="E404" t="inlineStr"/>
-      <c r="F404" t="inlineStr"/>
-      <c r="G404" t="inlineStr"/>
+      <c r="C404" t="n">
+        <v>3129</v>
+      </c>
+      <c r="D404" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E404" t="n">
+        <v>26</v>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H404" t="inlineStr"/>
     </row>
     <row r="405">
@@ -12386,11 +12057,25 @@
           <t>https://www.amazon.in/dp/B0BBQT5YY5</t>
         </is>
       </c>
-      <c r="C405" t="inlineStr"/>
-      <c r="D405" t="inlineStr"/>
-      <c r="E405" t="inlineStr"/>
-      <c r="F405" t="inlineStr"/>
-      <c r="G405" t="inlineStr"/>
+      <c r="C405" t="n">
+        <v>2499</v>
+      </c>
+      <c r="D405" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E405" t="n">
+        <v>42</v>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H405" t="inlineStr"/>
     </row>
     <row r="406">
@@ -12404,11 +12089,29 @@
           <t>https://www.amazon.in/dp/B0DF32G1S1</t>
         </is>
       </c>
-      <c r="C406" t="inlineStr"/>
-      <c r="D406" t="inlineStr"/>
-      <c r="E406" t="inlineStr"/>
-      <c r="F406" t="inlineStr"/>
-      <c r="G406" t="inlineStr"/>
+      <c r="C406" t="n">
+        <v>3119</v>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H406" t="inlineStr"/>
     </row>
     <row r="407">
@@ -12422,11 +12125,29 @@
           <t>https://www.amazon.in/dp/B0DF35F628</t>
         </is>
       </c>
-      <c r="C407" t="inlineStr"/>
-      <c r="D407" t="inlineStr"/>
-      <c r="E407" t="inlineStr"/>
-      <c r="F407" t="inlineStr"/>
-      <c r="G407" t="inlineStr"/>
+      <c r="C407" t="n">
+        <v>3069</v>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H407" t="inlineStr"/>
     </row>
     <row r="408">
@@ -12440,11 +12161,25 @@
           <t>https://www.amazon.in/dp/B07Y916W4T</t>
         </is>
       </c>
-      <c r="C408" t="inlineStr"/>
-      <c r="D408" t="inlineStr"/>
-      <c r="E408" t="inlineStr"/>
-      <c r="F408" t="inlineStr"/>
-      <c r="G408" t="inlineStr"/>
+      <c r="C408" t="n">
+        <v>2509</v>
+      </c>
+      <c r="D408" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E408" t="n">
+        <v>296</v>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H408" t="inlineStr"/>
     </row>
     <row r="409">
@@ -12458,11 +12193,25 @@
           <t>https://www.amazon.in/dp/B092JHDRDX</t>
         </is>
       </c>
-      <c r="C409" t="inlineStr"/>
-      <c r="D409" t="inlineStr"/>
-      <c r="E409" t="inlineStr"/>
-      <c r="F409" t="inlineStr"/>
-      <c r="G409" t="inlineStr"/>
+      <c r="C409" t="n">
+        <v>1659</v>
+      </c>
+      <c r="D409" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E409" t="n">
+        <v>5</v>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H409" t="inlineStr"/>
     </row>
     <row r="410">
@@ -12476,11 +12225,25 @@
           <t>https://www.amazon.in/dp/B092JG7DLH</t>
         </is>
       </c>
-      <c r="C410" t="inlineStr"/>
-      <c r="D410" t="inlineStr"/>
-      <c r="E410" t="inlineStr"/>
-      <c r="F410" t="inlineStr"/>
-      <c r="G410" t="inlineStr"/>
+      <c r="C410" t="n">
+        <v>3149</v>
+      </c>
+      <c r="D410" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E410" t="n">
+        <v>25</v>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H410" t="inlineStr"/>
     </row>
     <row r="411">
@@ -12494,11 +12257,25 @@
           <t>https://www.amazon.in/dp/B09T9GRLHC</t>
         </is>
       </c>
-      <c r="C411" t="inlineStr"/>
-      <c r="D411" t="inlineStr"/>
-      <c r="E411" t="inlineStr"/>
-      <c r="F411" t="inlineStr"/>
-      <c r="G411" t="inlineStr"/>
+      <c r="C411" t="n">
+        <v>2499</v>
+      </c>
+      <c r="D411" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E411" t="n">
+        <v>14</v>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H411" t="inlineStr"/>
     </row>
     <row r="412">
@@ -12512,11 +12289,25 @@
           <t>https://www.amazon.in/dp/B092JGQ1XG</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
-      <c r="G412" t="inlineStr"/>
+      <c r="C412" t="n">
+        <v>2939</v>
+      </c>
+      <c r="D412" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E412" t="n">
+        <v>2</v>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H412" t="inlineStr"/>
     </row>
     <row r="413">
@@ -12530,11 +12321,25 @@
           <t>https://www.amazon.in/dp/B09T9K17GK</t>
         </is>
       </c>
-      <c r="C413" t="inlineStr"/>
-      <c r="D413" t="inlineStr"/>
-      <c r="E413" t="inlineStr"/>
-      <c r="F413" t="inlineStr"/>
-      <c r="G413" t="inlineStr"/>
+      <c r="C413" t="n">
+        <v>3699</v>
+      </c>
+      <c r="D413" t="n">
+        <v>5</v>
+      </c>
+      <c r="E413" t="n">
+        <v>1</v>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H413" t="inlineStr"/>
     </row>
     <row r="414">
@@ -12549,10 +12354,26 @@
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
-      <c r="D414" t="inlineStr"/>
-      <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
-      <c r="G414" t="inlineStr"/>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H414" t="inlineStr"/>
     </row>
     <row r="415">
@@ -12566,11 +12387,25 @@
           <t>https://www.amazon.in/dp/B09T9N4RH3</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
-      <c r="D415" t="inlineStr"/>
-      <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
-      <c r="G415" t="inlineStr"/>
+      <c r="C415" t="n">
+        <v>3129</v>
+      </c>
+      <c r="D415" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E415" t="n">
+        <v>6</v>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H415" t="inlineStr"/>
     </row>
     <row r="416">
@@ -12584,11 +12419,25 @@
           <t>https://www.amazon.in/dp/B0BBRJ7WJR</t>
         </is>
       </c>
-      <c r="C416" t="inlineStr"/>
-      <c r="D416" t="inlineStr"/>
-      <c r="E416" t="inlineStr"/>
-      <c r="F416" t="inlineStr"/>
-      <c r="G416" t="inlineStr"/>
+      <c r="C416" t="n">
+        <v>2499</v>
+      </c>
+      <c r="D416" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E416" t="n">
+        <v>27</v>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H416" t="inlineStr"/>
     </row>
     <row r="417">
@@ -12602,11 +12451,29 @@
           <t>https://www.amazon.in/dp/B0DF32TZR3</t>
         </is>
       </c>
-      <c r="C417" t="inlineStr"/>
-      <c r="D417" t="inlineStr"/>
-      <c r="E417" t="inlineStr"/>
-      <c r="F417" t="inlineStr"/>
-      <c r="G417" t="inlineStr"/>
+      <c r="C417" t="n">
+        <v>3149</v>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H417" t="inlineStr"/>
     </row>
     <row r="418">
@@ -12620,11 +12487,25 @@
           <t>https://www.amazon.in/dp/B0DF2ZY74J</t>
         </is>
       </c>
-      <c r="C418" t="inlineStr"/>
-      <c r="D418" t="inlineStr"/>
-      <c r="E418" t="inlineStr"/>
-      <c r="F418" t="inlineStr"/>
-      <c r="G418" t="inlineStr"/>
+      <c r="C418" t="n">
+        <v>3109</v>
+      </c>
+      <c r="D418" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E418" t="n">
+        <v>7</v>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H418" t="inlineStr"/>
     </row>
     <row r="419">
@@ -12638,11 +12519,25 @@
           <t>https://www.amazon.in/dp/B0974KHG7W</t>
         </is>
       </c>
-      <c r="C419" t="inlineStr"/>
-      <c r="D419" t="inlineStr"/>
-      <c r="E419" t="inlineStr"/>
-      <c r="F419" t="inlineStr"/>
-      <c r="G419" t="inlineStr"/>
+      <c r="C419" t="n">
+        <v>909</v>
+      </c>
+      <c r="D419" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E419" t="n">
+        <v>12</v>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H419" t="inlineStr"/>
     </row>
     <row r="420">
@@ -12656,11 +12551,25 @@
           <t>https://www.amazon.in/dp/B09C8KHM9P</t>
         </is>
       </c>
-      <c r="C420" t="inlineStr"/>
-      <c r="D420" t="inlineStr"/>
-      <c r="E420" t="inlineStr"/>
-      <c r="F420" t="inlineStr"/>
-      <c r="G420" t="inlineStr"/>
+      <c r="C420" t="n">
+        <v>1449</v>
+      </c>
+      <c r="D420" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E420" t="n">
+        <v>37</v>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H420" t="inlineStr"/>
     </row>
     <row r="421">
@@ -12674,11 +12583,25 @@
           <t>https://www.amazon.in/dp/B09C8KZTKZ</t>
         </is>
       </c>
-      <c r="C421" t="inlineStr"/>
-      <c r="D421" t="inlineStr"/>
-      <c r="E421" t="inlineStr"/>
-      <c r="F421" t="inlineStr"/>
-      <c r="G421" t="inlineStr"/>
+      <c r="C421" t="n">
+        <v>1679</v>
+      </c>
+      <c r="D421" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E421" t="n">
+        <v>267</v>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H421" t="inlineStr"/>
     </row>
     <row r="422">
@@ -12692,11 +12615,25 @@
           <t>https://www.amazon.in/dp/B09T9NS7SB</t>
         </is>
       </c>
-      <c r="C422" t="inlineStr"/>
-      <c r="D422" t="inlineStr"/>
-      <c r="E422" t="inlineStr"/>
-      <c r="F422" t="inlineStr"/>
-      <c r="G422" t="inlineStr"/>
+      <c r="C422" t="n">
+        <v>1659</v>
+      </c>
+      <c r="D422" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E422" t="n">
+        <v>12</v>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H422" t="inlineStr"/>
     </row>
     <row r="423">
@@ -12710,11 +12647,25 @@
           <t>https://www.amazon.in/dp/B09T9VW7GF</t>
         </is>
       </c>
-      <c r="C423" t="inlineStr"/>
-      <c r="D423" t="inlineStr"/>
-      <c r="E423" t="inlineStr"/>
-      <c r="F423" t="inlineStr"/>
-      <c r="G423" t="inlineStr"/>
+      <c r="C423" t="n">
+        <v>2889</v>
+      </c>
+      <c r="D423" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E423" t="n">
+        <v>3</v>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H423" t="inlineStr"/>
     </row>
     <row r="424">
@@ -12728,11 +12679,25 @@
           <t>https://www.amazon.in/dp/B09T9JQQCB</t>
         </is>
       </c>
-      <c r="C424" t="inlineStr"/>
-      <c r="D424" t="inlineStr"/>
-      <c r="E424" t="inlineStr"/>
-      <c r="F424" t="inlineStr"/>
-      <c r="G424" t="inlineStr"/>
+      <c r="C424" t="n">
+        <v>1659</v>
+      </c>
+      <c r="D424" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E424" t="n">
+        <v>60</v>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H424" t="inlineStr"/>
     </row>
     <row r="425">
@@ -12746,11 +12711,25 @@
           <t>https://www.amazon.in/dp/B0DF34Z83C</t>
         </is>
       </c>
-      <c r="C425" t="inlineStr"/>
-      <c r="D425" t="inlineStr"/>
-      <c r="E425" t="inlineStr"/>
-      <c r="F425" t="inlineStr"/>
-      <c r="G425" t="inlineStr"/>
+      <c r="C425" t="n">
+        <v>2329</v>
+      </c>
+      <c r="D425" t="n">
+        <v>5</v>
+      </c>
+      <c r="E425" t="n">
+        <v>1</v>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H425" t="inlineStr"/>
     </row>
     <row r="426">
@@ -12764,11 +12743,29 @@
           <t>https://www.amazon.in/dp/B0DF32ZBZ7</t>
         </is>
       </c>
-      <c r="C426" t="inlineStr"/>
-      <c r="D426" t="inlineStr"/>
-      <c r="E426" t="inlineStr"/>
-      <c r="F426" t="inlineStr"/>
-      <c r="G426" t="inlineStr"/>
+      <c r="C426" t="n">
+        <v>2319</v>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H426" t="inlineStr"/>
     </row>
     <row r="427">
@@ -12782,11 +12779,29 @@
           <t>https://www.amazon.in/dp/B0DF3686NR</t>
         </is>
       </c>
-      <c r="C427" t="inlineStr"/>
-      <c r="D427" t="inlineStr"/>
-      <c r="E427" t="inlineStr"/>
-      <c r="F427" t="inlineStr"/>
-      <c r="G427" t="inlineStr"/>
+      <c r="C427" t="n">
+        <v>2269</v>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H427" t="inlineStr"/>
     </row>
     <row r="428">
@@ -12800,11 +12815,25 @@
           <t>https://www.amazon.in/dp/B09C8LCV9X</t>
         </is>
       </c>
-      <c r="C428" t="inlineStr"/>
-      <c r="D428" t="inlineStr"/>
-      <c r="E428" t="inlineStr"/>
-      <c r="F428" t="inlineStr"/>
-      <c r="G428" t="inlineStr"/>
+      <c r="C428" t="n">
+        <v>1679</v>
+      </c>
+      <c r="D428" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E428" t="n">
+        <v>267</v>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H428" t="inlineStr"/>
     </row>
     <row r="429">
@@ -12818,11 +12847,25 @@
           <t>https://www.amazon.in/dp/B09T9K6S4Y</t>
         </is>
       </c>
-      <c r="C429" t="inlineStr"/>
-      <c r="D429" t="inlineStr"/>
-      <c r="E429" t="inlineStr"/>
-      <c r="F429" t="inlineStr"/>
-      <c r="G429" t="inlineStr"/>
+      <c r="C429" t="n">
+        <v>1679</v>
+      </c>
+      <c r="D429" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E429" t="n">
+        <v>3</v>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H429" t="inlineStr"/>
     </row>
     <row r="430">
@@ -12836,11 +12879,25 @@
           <t>https://www.amazon.in/dp/B09T9LFMYH</t>
         </is>
       </c>
-      <c r="C430" t="inlineStr"/>
-      <c r="D430" t="inlineStr"/>
-      <c r="E430" t="inlineStr"/>
-      <c r="F430" t="inlineStr"/>
-      <c r="G430" t="inlineStr"/>
+      <c r="C430" t="n">
+        <v>2889</v>
+      </c>
+      <c r="D430" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E430" t="n">
+        <v>2</v>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H430" t="inlineStr"/>
     </row>
     <row r="431">
@@ -12854,11 +12911,25 @@
           <t>https://www.amazon.in/dp/B09T9S7RZ9</t>
         </is>
       </c>
-      <c r="C431" t="inlineStr"/>
-      <c r="D431" t="inlineStr"/>
-      <c r="E431" t="inlineStr"/>
-      <c r="F431" t="inlineStr"/>
-      <c r="G431" t="inlineStr"/>
+      <c r="C431" t="n">
+        <v>2369</v>
+      </c>
+      <c r="D431" t="n">
+        <v>4</v>
+      </c>
+      <c r="E431" t="n">
+        <v>19</v>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H431" t="inlineStr"/>
     </row>
     <row r="432">
@@ -12872,11 +12943,29 @@
           <t>https://www.amazon.in/dp/B0DF353Y8J</t>
         </is>
       </c>
-      <c r="C432" t="inlineStr"/>
-      <c r="D432" t="inlineStr"/>
-      <c r="E432" t="inlineStr"/>
-      <c r="F432" t="inlineStr"/>
-      <c r="G432" t="inlineStr"/>
+      <c r="C432" t="n">
+        <v>2329</v>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H432" t="inlineStr"/>
     </row>
     <row r="433">
@@ -12890,11 +12979,29 @@
           <t>https://www.amazon.in/dp/B0DF35DMJ6</t>
         </is>
       </c>
-      <c r="C433" t="inlineStr"/>
-      <c r="D433" t="inlineStr"/>
-      <c r="E433" t="inlineStr"/>
-      <c r="F433" t="inlineStr"/>
-      <c r="G433" t="inlineStr"/>
+      <c r="C433" t="n">
+        <v>2319</v>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H433" t="inlineStr"/>
     </row>
     <row r="434">
@@ -12908,11 +13015,29 @@
           <t>https://www.amazon.in/dp/B0DF35SSG6</t>
         </is>
       </c>
-      <c r="C434" t="inlineStr"/>
-      <c r="D434" t="inlineStr"/>
-      <c r="E434" t="inlineStr"/>
-      <c r="F434" t="inlineStr"/>
-      <c r="G434" t="inlineStr"/>
+      <c r="C434" t="n">
+        <v>2269</v>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H434" t="inlineStr"/>
     </row>
     <row r="435">
@@ -12926,11 +13051,25 @@
           <t>https://www.amazon.in/dp/B0BMGCJ4Z7</t>
         </is>
       </c>
-      <c r="C435" t="inlineStr"/>
-      <c r="D435" t="inlineStr"/>
-      <c r="E435" t="inlineStr"/>
-      <c r="F435" t="inlineStr"/>
-      <c r="G435" t="inlineStr"/>
+      <c r="C435" t="n">
+        <v>1859</v>
+      </c>
+      <c r="D435" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E435" t="n">
+        <v>87</v>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H435" t="inlineStr"/>
     </row>
     <row r="436">
@@ -12945,10 +13084,26 @@
         </is>
       </c>
       <c r="C436" t="inlineStr"/>
-      <c r="D436" t="inlineStr"/>
-      <c r="E436" t="inlineStr"/>
-      <c r="F436" t="inlineStr"/>
-      <c r="G436" t="inlineStr"/>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H436" t="inlineStr"/>
     </row>
     <row r="437">
@@ -12963,10 +13118,26 @@
         </is>
       </c>
       <c r="C437" t="inlineStr"/>
-      <c r="D437" t="inlineStr"/>
-      <c r="E437" t="inlineStr"/>
-      <c r="F437" t="inlineStr"/>
-      <c r="G437" t="inlineStr"/>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H437" t="inlineStr"/>
     </row>
     <row r="438">
@@ -12981,10 +13152,26 @@
         </is>
       </c>
       <c r="C438" t="inlineStr"/>
-      <c r="D438" t="inlineStr"/>
-      <c r="E438" t="inlineStr"/>
-      <c r="F438" t="inlineStr"/>
-      <c r="G438" t="inlineStr"/>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H438" t="inlineStr"/>
     </row>
     <row r="439">
@@ -12999,10 +13186,26 @@
         </is>
       </c>
       <c r="C439" t="inlineStr"/>
-      <c r="D439" t="inlineStr"/>
-      <c r="E439" t="inlineStr"/>
-      <c r="F439" t="inlineStr"/>
-      <c r="G439" t="inlineStr"/>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H439" t="inlineStr"/>
     </row>
     <row r="440">
@@ -13017,10 +13220,26 @@
         </is>
       </c>
       <c r="C440" t="inlineStr"/>
-      <c r="D440" t="inlineStr"/>
-      <c r="E440" t="inlineStr"/>
-      <c r="F440" t="inlineStr"/>
-      <c r="G440" t="inlineStr"/>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H440" t="inlineStr"/>
     </row>
     <row r="441">
@@ -13034,11 +13253,25 @@
           <t>https://www.amazon.in/dp/B0BBLZ2KT8</t>
         </is>
       </c>
-      <c r="C441" t="inlineStr"/>
-      <c r="D441" t="inlineStr"/>
-      <c r="E441" t="inlineStr"/>
-      <c r="F441" t="inlineStr"/>
-      <c r="G441" t="inlineStr"/>
+      <c r="C441" t="n">
+        <v>1249</v>
+      </c>
+      <c r="D441" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E441" t="n">
+        <v>30</v>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H441" t="inlineStr"/>
     </row>
     <row r="442">
@@ -13053,10 +13286,26 @@
         </is>
       </c>
       <c r="C442" t="inlineStr"/>
-      <c r="D442" t="inlineStr"/>
-      <c r="E442" t="inlineStr"/>
-      <c r="F442" t="inlineStr"/>
-      <c r="G442" t="inlineStr"/>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H442" t="inlineStr"/>
     </row>
     <row r="443">
@@ -13071,10 +13320,26 @@
         </is>
       </c>
       <c r="C443" t="inlineStr"/>
-      <c r="D443" t="inlineStr"/>
-      <c r="E443" t="inlineStr"/>
-      <c r="F443" t="inlineStr"/>
-      <c r="G443" t="inlineStr"/>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H443" t="inlineStr"/>
     </row>
     <row r="444">
@@ -13089,10 +13354,26 @@
         </is>
       </c>
       <c r="C444" t="inlineStr"/>
-      <c r="D444" t="inlineStr"/>
-      <c r="E444" t="inlineStr"/>
-      <c r="F444" t="inlineStr"/>
-      <c r="G444" t="inlineStr"/>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H444" t="inlineStr"/>
     </row>
     <row r="445">
@@ -13106,11 +13387,25 @@
           <t>https://www.amazon.in/dp/B0BQBQKMS8</t>
         </is>
       </c>
-      <c r="C445" t="inlineStr"/>
-      <c r="D445" t="inlineStr"/>
-      <c r="E445" t="inlineStr"/>
-      <c r="F445" t="inlineStr"/>
-      <c r="G445" t="inlineStr"/>
+      <c r="C445" t="n">
+        <v>1919</v>
+      </c>
+      <c r="D445" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E445" t="n">
+        <v>12</v>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H445" t="inlineStr"/>
     </row>
     <row r="446">
@@ -13124,11 +13419,25 @@
           <t>https://www.amazon.in/dp/B08GSQCSQX</t>
         </is>
       </c>
-      <c r="C446" t="inlineStr"/>
-      <c r="D446" t="inlineStr"/>
-      <c r="E446" t="inlineStr"/>
-      <c r="F446" t="inlineStr"/>
-      <c r="G446" t="inlineStr"/>
+      <c r="C446" t="n">
+        <v>1999</v>
+      </c>
+      <c r="D446" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E446" t="n">
+        <v>221</v>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H446" t="inlineStr"/>
     </row>
     <row r="447">
@@ -13142,11 +13451,29 @@
           <t>https://www.amazon.in/dp/B09MB163J9</t>
         </is>
       </c>
-      <c r="C447" t="inlineStr"/>
-      <c r="D447" t="inlineStr"/>
-      <c r="E447" t="inlineStr"/>
-      <c r="F447" t="inlineStr"/>
-      <c r="G447" t="inlineStr"/>
+      <c r="C447" t="n">
+        <v>3369</v>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H447" t="inlineStr"/>
     </row>
     <row r="448">
@@ -13160,11 +13487,25 @@
           <t>https://www.amazon.in/dp/B09VT5TDTW</t>
         </is>
       </c>
-      <c r="C448" t="inlineStr"/>
-      <c r="D448" t="inlineStr"/>
-      <c r="E448" t="inlineStr"/>
-      <c r="F448" t="inlineStr"/>
-      <c r="G448" t="inlineStr"/>
+      <c r="C448" t="n">
+        <v>399</v>
+      </c>
+      <c r="D448" t="n">
+        <v>4</v>
+      </c>
+      <c r="E448" t="n">
+        <v>1</v>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H448" t="inlineStr"/>
     </row>
     <row r="449">
@@ -13178,11 +13519,25 @@
           <t>https://www.amazon.in/dp/B09VT6372M</t>
         </is>
       </c>
-      <c r="C449" t="inlineStr"/>
-      <c r="D449" t="inlineStr"/>
-      <c r="E449" t="inlineStr"/>
-      <c r="F449" t="inlineStr"/>
-      <c r="G449" t="inlineStr"/>
+      <c r="C449" t="n">
+        <v>1799</v>
+      </c>
+      <c r="D449" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E449" t="n">
+        <v>3</v>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H449" t="inlineStr"/>
     </row>
     <row r="450">
@@ -13196,11 +13551,25 @@
           <t>https://www.amazon.in/dp/B09C83F7LD</t>
         </is>
       </c>
-      <c r="C450" t="inlineStr"/>
-      <c r="D450" t="inlineStr"/>
-      <c r="E450" t="inlineStr"/>
-      <c r="F450" t="inlineStr"/>
-      <c r="G450" t="inlineStr"/>
+      <c r="C450" t="n">
+        <v>389</v>
+      </c>
+      <c r="D450" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E450" t="n">
+        <v>11</v>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H450" t="inlineStr"/>
     </row>
     <row r="451">
@@ -13215,10 +13584,26 @@
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
-      <c r="D451" t="inlineStr"/>
-      <c r="E451" t="inlineStr"/>
-      <c r="F451" t="inlineStr"/>
-      <c r="G451" t="inlineStr"/>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H451" t="inlineStr"/>
     </row>
     <row r="452">
@@ -13233,10 +13618,26 @@
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
-      <c r="D452" t="inlineStr"/>
-      <c r="E452" t="inlineStr"/>
-      <c r="F452" t="inlineStr"/>
-      <c r="G452" t="inlineStr"/>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H452" t="inlineStr"/>
     </row>
     <row r="453">
@@ -13250,11 +13651,29 @@
           <t>https://www.amazon.in/dp/B0D7S1JQ85</t>
         </is>
       </c>
-      <c r="C453" t="inlineStr"/>
-      <c r="D453" t="inlineStr"/>
-      <c r="E453" t="inlineStr"/>
-      <c r="F453" t="inlineStr"/>
-      <c r="G453" t="inlineStr"/>
+      <c r="C453" t="n">
+        <v>3369</v>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H453" t="inlineStr"/>
     </row>
     <row r="454">
@@ -13268,11 +13687,25 @@
           <t>https://www.amazon.in/dp/B0F7HVLKG7</t>
         </is>
       </c>
-      <c r="C454" t="inlineStr"/>
-      <c r="D454" t="inlineStr"/>
-      <c r="E454" t="inlineStr"/>
-      <c r="F454" t="inlineStr"/>
-      <c r="G454" t="inlineStr"/>
+      <c r="C454" t="n">
+        <v>9729</v>
+      </c>
+      <c r="D454" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E454" t="n">
+        <v>4</v>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H454" t="inlineStr"/>
     </row>
     <row r="455">
@@ -13286,11 +13719,25 @@
           <t>https://www.amazon.in/dp/B0F7HVCXG3</t>
         </is>
       </c>
-      <c r="C455" t="inlineStr"/>
-      <c r="D455" t="inlineStr"/>
-      <c r="E455" t="inlineStr"/>
-      <c r="F455" t="inlineStr"/>
-      <c r="G455" t="inlineStr"/>
+      <c r="C455" t="n">
+        <v>9729</v>
+      </c>
+      <c r="D455" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E455" t="n">
+        <v>4</v>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H455" t="inlineStr"/>
     </row>
     <row r="456">
@@ -13304,11 +13751,25 @@
           <t>https://www.amazon.in/dp/B0F7HVB78G</t>
         </is>
       </c>
-      <c r="C456" t="inlineStr"/>
-      <c r="D456" t="inlineStr"/>
-      <c r="E456" t="inlineStr"/>
-      <c r="F456" t="inlineStr"/>
-      <c r="G456" t="inlineStr"/>
+      <c r="C456" t="n">
+        <v>9729</v>
+      </c>
+      <c r="D456" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E456" t="n">
+        <v>4</v>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H456" t="inlineStr"/>
     </row>
     <row r="457">
@@ -13322,11 +13783,25 @@
           <t>https://www.amazon.in/dp/B0F7HTG26Y</t>
         </is>
       </c>
-      <c r="C457" t="inlineStr"/>
-      <c r="D457" t="inlineStr"/>
-      <c r="E457" t="inlineStr"/>
-      <c r="F457" t="inlineStr"/>
-      <c r="G457" t="inlineStr"/>
+      <c r="C457" t="n">
+        <v>20419</v>
+      </c>
+      <c r="D457" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E457" t="n">
+        <v>4</v>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H457" t="inlineStr"/>
     </row>
     <row r="458">
@@ -13340,11 +13815,25 @@
           <t>https://www.amazon.in/dp/B0F7HW5CNM</t>
         </is>
       </c>
-      <c r="C458" t="inlineStr"/>
-      <c r="D458" t="inlineStr"/>
-      <c r="E458" t="inlineStr"/>
-      <c r="F458" t="inlineStr"/>
-      <c r="G458" t="inlineStr"/>
+      <c r="C458" t="n">
+        <v>20419</v>
+      </c>
+      <c r="D458" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E458" t="n">
+        <v>4</v>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H458" t="inlineStr"/>
     </row>
     <row r="459">
@@ -13358,11 +13847,25 @@
           <t>https://www.amazon.in/dp/B0F7HV6QBV</t>
         </is>
       </c>
-      <c r="C459" t="inlineStr"/>
-      <c r="D459" t="inlineStr"/>
-      <c r="E459" t="inlineStr"/>
-      <c r="F459" t="inlineStr"/>
-      <c r="G459" t="inlineStr"/>
+      <c r="C459" t="n">
+        <v>20419</v>
+      </c>
+      <c r="D459" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E459" t="n">
+        <v>4</v>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H459" t="inlineStr"/>
     </row>
     <row r="460">
@@ -13376,11 +13879,25 @@
           <t>https://www.amazon.in/dp/B0F7HQQPK8</t>
         </is>
       </c>
-      <c r="C460" t="inlineStr"/>
-      <c r="D460" t="inlineStr"/>
-      <c r="E460" t="inlineStr"/>
-      <c r="F460" t="inlineStr"/>
-      <c r="G460" t="inlineStr"/>
+      <c r="C460" t="n">
+        <v>31999</v>
+      </c>
+      <c r="D460" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E460" t="n">
+        <v>4</v>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H460" t="inlineStr"/>
     </row>
     <row r="461">
@@ -13394,11 +13911,25 @@
           <t>https://www.amazon.in/dp/B0F7HVW8Q1</t>
         </is>
       </c>
-      <c r="C461" t="inlineStr"/>
-      <c r="D461" t="inlineStr"/>
-      <c r="E461" t="inlineStr"/>
-      <c r="F461" t="inlineStr"/>
-      <c r="G461" t="inlineStr"/>
+      <c r="C461" t="n">
+        <v>22500</v>
+      </c>
+      <c r="D461" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E461" t="n">
+        <v>4</v>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H461" t="inlineStr"/>
     </row>
     <row r="462">
@@ -13412,11 +13943,25 @@
           <t>https://www.amazon.in/dp/B0F7HWH9VP</t>
         </is>
       </c>
-      <c r="C462" t="inlineStr"/>
-      <c r="D462" t="inlineStr"/>
-      <c r="E462" t="inlineStr"/>
-      <c r="F462" t="inlineStr"/>
-      <c r="G462" t="inlineStr"/>
+      <c r="C462" t="n">
+        <v>34909</v>
+      </c>
+      <c r="D462" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E462" t="n">
+        <v>4</v>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H462" t="inlineStr"/>
     </row>
     <row r="463">
@@ -13430,11 +13975,25 @@
           <t>https://www.amazon.in/dp/B0F7HVBHTZ</t>
         </is>
       </c>
-      <c r="C463" t="inlineStr"/>
-      <c r="D463" t="inlineStr"/>
-      <c r="E463" t="inlineStr"/>
-      <c r="F463" t="inlineStr"/>
-      <c r="G463" t="inlineStr"/>
+      <c r="C463" t="n">
+        <v>21479</v>
+      </c>
+      <c r="D463" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E463" t="n">
+        <v>4</v>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H463" t="inlineStr"/>
     </row>
     <row r="464">
@@ -13448,11 +14007,25 @@
           <t>https://www.amazon.in/dp/B0F7HSM2TY</t>
         </is>
       </c>
-      <c r="C464" t="inlineStr"/>
-      <c r="D464" t="inlineStr"/>
-      <c r="E464" t="inlineStr"/>
-      <c r="F464" t="inlineStr"/>
-      <c r="G464" t="inlineStr"/>
+      <c r="C464" t="n">
+        <v>21479</v>
+      </c>
+      <c r="D464" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E464" t="n">
+        <v>4</v>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H464" t="inlineStr"/>
     </row>
     <row r="465">
@@ -13466,11 +14039,25 @@
           <t>https://www.amazon.in/dp/B0F7HV1FM9</t>
         </is>
       </c>
-      <c r="C465" t="inlineStr"/>
-      <c r="D465" t="inlineStr"/>
-      <c r="E465" t="inlineStr"/>
-      <c r="F465" t="inlineStr"/>
-      <c r="G465" t="inlineStr"/>
+      <c r="C465" t="n">
+        <v>21479</v>
+      </c>
+      <c r="D465" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E465" t="n">
+        <v>4</v>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H465" t="inlineStr"/>
     </row>
     <row r="466">
@@ -13484,11 +14071,25 @@
           <t>https://www.amazon.in/dp/B0F7HSL6WV</t>
         </is>
       </c>
-      <c r="C466" t="inlineStr"/>
-      <c r="D466" t="inlineStr"/>
-      <c r="E466" t="inlineStr"/>
-      <c r="F466" t="inlineStr"/>
-      <c r="G466" t="inlineStr"/>
+      <c r="C466" t="n">
+        <v>11769</v>
+      </c>
+      <c r="D466" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E466" t="n">
+        <v>4</v>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H466" t="inlineStr"/>
     </row>
     <row r="467">
@@ -13502,11 +14103,25 @@
           <t>https://www.amazon.in/dp/B0F7HV5KPF</t>
         </is>
       </c>
-      <c r="C467" t="inlineStr"/>
-      <c r="D467" t="inlineStr"/>
-      <c r="E467" t="inlineStr"/>
-      <c r="F467" t="inlineStr"/>
-      <c r="G467" t="inlineStr"/>
+      <c r="C467" t="n">
+        <v>11769</v>
+      </c>
+      <c r="D467" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E467" t="n">
+        <v>4</v>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H467" t="inlineStr"/>
     </row>
     <row r="468">
@@ -13520,11 +14135,25 @@
           <t>https://www.amazon.in/dp/B0F7HXKDHN</t>
         </is>
       </c>
-      <c r="C468" t="inlineStr"/>
-      <c r="D468" t="inlineStr"/>
-      <c r="E468" t="inlineStr"/>
-      <c r="F468" t="inlineStr"/>
-      <c r="G468" t="inlineStr"/>
+      <c r="C468" t="n">
+        <v>10700</v>
+      </c>
+      <c r="D468" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E468" t="n">
+        <v>4</v>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>Only 2 left in stock.</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H468" t="inlineStr"/>
     </row>
     <row r="469">
@@ -13538,11 +14167,25 @@
           <t>https://www.amazon.in/dp/B0F7HTLSBP</t>
         </is>
       </c>
-      <c r="C469" t="inlineStr"/>
-      <c r="D469" t="inlineStr"/>
-      <c r="E469" t="inlineStr"/>
-      <c r="F469" t="inlineStr"/>
-      <c r="G469" t="inlineStr"/>
+      <c r="C469" t="n">
+        <v>23059</v>
+      </c>
+      <c r="D469" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E469" t="n">
+        <v>4</v>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H469" t="inlineStr"/>
     </row>
     <row r="470">
@@ -13556,11 +14199,25 @@
           <t>https://www.amazon.in/dp/B0F7HSYKQZ</t>
         </is>
       </c>
-      <c r="C470" t="inlineStr"/>
-      <c r="D470" t="inlineStr"/>
-      <c r="E470" t="inlineStr"/>
-      <c r="F470" t="inlineStr"/>
-      <c r="G470" t="inlineStr"/>
+      <c r="C470" t="n">
+        <v>21479</v>
+      </c>
+      <c r="D470" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E470" t="n">
+        <v>4</v>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H470" t="inlineStr"/>
     </row>
     <row r="471">
@@ -13574,11 +14231,25 @@
           <t>https://www.amazon.in/dp/B0F7HT5S3T</t>
         </is>
       </c>
-      <c r="C471" t="inlineStr"/>
-      <c r="D471" t="inlineStr"/>
-      <c r="E471" t="inlineStr"/>
-      <c r="F471" t="inlineStr"/>
-      <c r="G471" t="inlineStr"/>
+      <c r="C471" t="n">
+        <v>23059</v>
+      </c>
+      <c r="D471" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E471" t="n">
+        <v>4</v>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H471" t="inlineStr"/>
     </row>
     <row r="472">
@@ -13592,11 +14263,25 @@
           <t>https://www.amazon.in/dp/B0F7HVJMXS</t>
         </is>
       </c>
-      <c r="C472" t="inlineStr"/>
-      <c r="D472" t="inlineStr"/>
-      <c r="E472" t="inlineStr"/>
-      <c r="F472" t="inlineStr"/>
-      <c r="G472" t="inlineStr"/>
+      <c r="C472" t="n">
+        <v>12300</v>
+      </c>
+      <c r="D472" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E472" t="n">
+        <v>4</v>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H472" t="inlineStr"/>
     </row>
     <row r="473">
@@ -13610,11 +14295,25 @@
           <t>https://www.amazon.in/dp/B0F7HX1BR3</t>
         </is>
       </c>
-      <c r="C473" t="inlineStr"/>
-      <c r="D473" t="inlineStr"/>
-      <c r="E473" t="inlineStr"/>
-      <c r="F473" t="inlineStr"/>
-      <c r="G473" t="inlineStr"/>
+      <c r="C473" t="n">
+        <v>12340</v>
+      </c>
+      <c r="D473" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E473" t="n">
+        <v>4</v>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H473" t="inlineStr"/>
     </row>
     <row r="474">
@@ -13628,11 +14327,25 @@
           <t>https://www.amazon.in/dp/B0F7HTQSCZ</t>
         </is>
       </c>
-      <c r="C474" t="inlineStr"/>
-      <c r="D474" t="inlineStr"/>
-      <c r="E474" t="inlineStr"/>
-      <c r="F474" t="inlineStr"/>
-      <c r="G474" t="inlineStr"/>
+      <c r="C474" t="n">
+        <v>11229</v>
+      </c>
+      <c r="D474" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E474" t="n">
+        <v>4</v>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>Only 2 left in stock.</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H474" t="inlineStr"/>
     </row>
     <row r="475">
@@ -13646,11 +14359,25 @@
           <t>https://www.amazon.in/dp/B0D7S7WXYS</t>
         </is>
       </c>
-      <c r="C475" t="inlineStr"/>
-      <c r="D475" t="inlineStr"/>
-      <c r="E475" t="inlineStr"/>
-      <c r="F475" t="inlineStr"/>
-      <c r="G475" t="inlineStr"/>
+      <c r="C475" t="n">
+        <v>2339</v>
+      </c>
+      <c r="D475" t="n">
+        <v>1</v>
+      </c>
+      <c r="E475" t="n">
+        <v>1</v>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H475" t="inlineStr"/>
     </row>
     <row r="476">
@@ -13664,11 +14391,25 @@
           <t>https://www.amazon.in/dp/B07RS7HMGC</t>
         </is>
       </c>
-      <c r="C476" t="inlineStr"/>
-      <c r="D476" t="inlineStr"/>
-      <c r="E476" t="inlineStr"/>
-      <c r="F476" t="inlineStr"/>
-      <c r="G476" t="inlineStr"/>
+      <c r="C476" t="n">
+        <v>399</v>
+      </c>
+      <c r="D476" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E476" t="n">
+        <v>14</v>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H476" t="inlineStr"/>
     </row>
     <row r="477">
@@ -13682,11 +14423,25 @@
           <t>https://www.amazon.in/dp/B0CKWCB1XS</t>
         </is>
       </c>
-      <c r="C477" t="inlineStr"/>
-      <c r="D477" t="inlineStr"/>
-      <c r="E477" t="inlineStr"/>
-      <c r="F477" t="inlineStr"/>
-      <c r="G477" t="inlineStr"/>
+      <c r="C477" t="n">
+        <v>4079</v>
+      </c>
+      <c r="D477" t="n">
+        <v>4</v>
+      </c>
+      <c r="E477" t="n">
+        <v>83</v>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H477" t="inlineStr"/>
     </row>
     <row r="478">
@@ -13700,11 +14455,25 @@
           <t>https://www.amazon.in/dp/B0CKW993KL</t>
         </is>
       </c>
-      <c r="C478" t="inlineStr"/>
-      <c r="D478" t="inlineStr"/>
-      <c r="E478" t="inlineStr"/>
-      <c r="F478" t="inlineStr"/>
-      <c r="G478" t="inlineStr"/>
+      <c r="C478" t="n">
+        <v>3349</v>
+      </c>
+      <c r="D478" t="n">
+        <v>4</v>
+      </c>
+      <c r="E478" t="n">
+        <v>83</v>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H478" t="inlineStr"/>
     </row>
     <row r="479">
@@ -13719,10 +14488,26 @@
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
-      <c r="D479" t="inlineStr"/>
-      <c r="E479" t="inlineStr"/>
-      <c r="F479" t="inlineStr"/>
-      <c r="G479" t="inlineStr"/>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H479" t="inlineStr"/>
     </row>
     <row r="480">
@@ -13736,11 +14521,25 @@
           <t>https://www.amazon.in/dp/B0CKWBY51K</t>
         </is>
       </c>
-      <c r="C480" t="inlineStr"/>
-      <c r="D480" t="inlineStr"/>
-      <c r="E480" t="inlineStr"/>
-      <c r="F480" t="inlineStr"/>
-      <c r="G480" t="inlineStr"/>
+      <c r="C480" t="n">
+        <v>3219</v>
+      </c>
+      <c r="D480" t="n">
+        <v>4</v>
+      </c>
+      <c r="E480" t="n">
+        <v>83</v>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H480" t="inlineStr"/>
     </row>
     <row r="481">
@@ -13755,10 +14554,26 @@
         </is>
       </c>
       <c r="C481" t="inlineStr"/>
-      <c r="D481" t="inlineStr"/>
-      <c r="E481" t="inlineStr"/>
-      <c r="F481" t="inlineStr"/>
-      <c r="G481" t="inlineStr"/>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H481" t="inlineStr"/>
     </row>
     <row r="482">
@@ -13772,11 +14587,25 @@
           <t>https://www.amazon.in/dp/B0CKW9S55C</t>
         </is>
       </c>
-      <c r="C482" t="inlineStr"/>
-      <c r="D482" t="inlineStr"/>
-      <c r="E482" t="inlineStr"/>
-      <c r="F482" t="inlineStr"/>
-      <c r="G482" t="inlineStr"/>
+      <c r="C482" t="n">
+        <v>3219</v>
+      </c>
+      <c r="D482" t="n">
+        <v>4</v>
+      </c>
+      <c r="E482" t="n">
+        <v>112</v>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H482" t="inlineStr"/>
     </row>
     <row r="483">
@@ -13790,11 +14619,25 @@
           <t>https://www.amazon.in/dp/B0CKW732B9</t>
         </is>
       </c>
-      <c r="C483" t="inlineStr"/>
-      <c r="D483" t="inlineStr"/>
-      <c r="E483" t="inlineStr"/>
-      <c r="F483" t="inlineStr"/>
-      <c r="G483" t="inlineStr"/>
+      <c r="C483" t="n">
+        <v>3419</v>
+      </c>
+      <c r="D483" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E483" t="n">
+        <v>119</v>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H483" t="inlineStr"/>
     </row>
     <row r="484">
@@ -13808,11 +14651,25 @@
           <t>https://www.amazon.in/dp/B077VL6SHH</t>
         </is>
       </c>
-      <c r="C484" t="inlineStr"/>
-      <c r="D484" t="inlineStr"/>
-      <c r="E484" t="inlineStr"/>
-      <c r="F484" t="inlineStr"/>
-      <c r="G484" t="inlineStr"/>
+      <c r="C484" t="n">
+        <v>899</v>
+      </c>
+      <c r="D484" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E484" t="n">
+        <v>218</v>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H484" t="inlineStr"/>
     </row>
     <row r="485">
@@ -13826,11 +14683,25 @@
           <t>https://www.amazon.in/dp/B08Z3SZGKD</t>
         </is>
       </c>
-      <c r="C485" t="inlineStr"/>
-      <c r="D485" t="inlineStr"/>
-      <c r="E485" t="inlineStr"/>
-      <c r="F485" t="inlineStr"/>
-      <c r="G485" t="inlineStr"/>
+      <c r="C485" t="n">
+        <v>2399</v>
+      </c>
+      <c r="D485" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E485" t="n">
+        <v>26</v>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H485" t="inlineStr"/>
     </row>
     <row r="486">
@@ -13844,11 +14715,25 @@
           <t>https://www.amazon.in/dp/B09TL4H17K</t>
         </is>
       </c>
-      <c r="C486" t="inlineStr"/>
-      <c r="D486" t="inlineStr"/>
-      <c r="E486" t="inlineStr"/>
-      <c r="F486" t="inlineStr"/>
-      <c r="G486" t="inlineStr"/>
+      <c r="C486" t="n">
+        <v>3759</v>
+      </c>
+      <c r="D486" t="n">
+        <v>1</v>
+      </c>
+      <c r="E486" t="n">
+        <v>1</v>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H486" t="inlineStr"/>
     </row>
     <row r="487">
@@ -13862,11 +14747,25 @@
           <t>https://www.amazon.in/dp/B09TL6JR53</t>
         </is>
       </c>
-      <c r="C487" t="inlineStr"/>
-      <c r="D487" t="inlineStr"/>
-      <c r="E487" t="inlineStr"/>
-      <c r="F487" t="inlineStr"/>
-      <c r="G487" t="inlineStr"/>
+      <c r="C487" t="n">
+        <v>1859</v>
+      </c>
+      <c r="D487" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E487" t="n">
+        <v>14</v>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H487" t="inlineStr"/>
     </row>
     <row r="488">
@@ -13880,11 +14779,25 @@
           <t>https://www.amazon.in/dp/B09TL3JFPY</t>
         </is>
       </c>
-      <c r="C488" t="inlineStr"/>
-      <c r="D488" t="inlineStr"/>
-      <c r="E488" t="inlineStr"/>
-      <c r="F488" t="inlineStr"/>
-      <c r="G488" t="inlineStr"/>
+      <c r="C488" t="n">
+        <v>3419</v>
+      </c>
+      <c r="D488" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E488" t="n">
+        <v>22</v>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H488" t="inlineStr"/>
     </row>
     <row r="489">
@@ -13899,10 +14812,26 @@
         </is>
       </c>
       <c r="C489" t="inlineStr"/>
-      <c r="D489" t="inlineStr"/>
-      <c r="E489" t="inlineStr"/>
-      <c r="F489" t="inlineStr"/>
-      <c r="G489" t="inlineStr"/>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H489" t="inlineStr"/>
     </row>
     <row r="490">
@@ -13916,11 +14845,25 @@
           <t>https://www.amazon.in/dp/B07DVTBSQM</t>
         </is>
       </c>
-      <c r="C490" t="inlineStr"/>
-      <c r="D490" t="inlineStr"/>
-      <c r="E490" t="inlineStr"/>
-      <c r="F490" t="inlineStr"/>
-      <c r="G490" t="inlineStr"/>
+      <c r="C490" t="n">
+        <v>3999</v>
+      </c>
+      <c r="D490" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E490" t="n">
+        <v>77</v>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H490" t="inlineStr"/>
     </row>
     <row r="491">
@@ -13934,11 +14877,25 @@
           <t>https://www.amazon.in/dp/B09TL5BF1H</t>
         </is>
       </c>
-      <c r="C491" t="inlineStr"/>
-      <c r="D491" t="inlineStr"/>
-      <c r="E491" t="inlineStr"/>
-      <c r="F491" t="inlineStr"/>
-      <c r="G491" t="inlineStr"/>
+      <c r="C491" t="n">
+        <v>3999</v>
+      </c>
+      <c r="D491" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E491" t="n">
+        <v>4</v>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H491" t="inlineStr"/>
     </row>
     <row r="492">
@@ -13952,11 +14909,25 @@
           <t>https://www.amazon.in/dp/B09TL4H4G6</t>
         </is>
       </c>
-      <c r="C492" t="inlineStr"/>
-      <c r="D492" t="inlineStr"/>
-      <c r="E492" t="inlineStr"/>
-      <c r="F492" t="inlineStr"/>
-      <c r="G492" t="inlineStr"/>
+      <c r="C492" t="n">
+        <v>4369</v>
+      </c>
+      <c r="D492" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E492" t="n">
+        <v>13</v>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H492" t="inlineStr"/>
     </row>
     <row r="493">
@@ -13970,11 +14941,25 @@
           <t>https://www.amazon.in/dp/B09TL3B57Y</t>
         </is>
       </c>
-      <c r="C493" t="inlineStr"/>
-      <c r="D493" t="inlineStr"/>
-      <c r="E493" t="inlineStr"/>
-      <c r="F493" t="inlineStr"/>
-      <c r="G493" t="inlineStr"/>
+      <c r="C493" t="n">
+        <v>3999</v>
+      </c>
+      <c r="D493" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E493" t="n">
+        <v>14</v>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H493" t="inlineStr"/>
     </row>
     <row r="494">
@@ -13988,11 +14973,25 @@
           <t>https://www.amazon.in/dp/B0BHJ9WMZK</t>
         </is>
       </c>
-      <c r="C494" t="inlineStr"/>
-      <c r="D494" t="inlineStr"/>
-      <c r="E494" t="inlineStr"/>
-      <c r="F494" t="inlineStr"/>
-      <c r="G494" t="inlineStr"/>
+      <c r="C494" t="n">
+        <v>3999</v>
+      </c>
+      <c r="D494" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E494" t="n">
+        <v>84</v>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H494" t="inlineStr"/>
     </row>
     <row r="495">
@@ -14010,8 +15009,29 @@
       <c r="D495" t="inlineStr"/>
       <c r="E495" t="inlineStr"/>
       <c r="F495" t="inlineStr"/>
-      <c r="G495" t="inlineStr"/>
-      <c r="H495" t="inlineStr"/>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
+  (Session info: chrome=150.0.7871.114)
+Stacktrace:
+#0 0x55e3b9a1c41a &lt;unknown&gt;
+#1 0x55e3b93f4689 &lt;unknown&gt;
+#2 0x55e3b93dc21a &lt;unknown&gt;
+#3 0x55e3b93dbe96 &lt;unknown&gt;
+#4 0x55e3b93d9a7e &lt;unknown&gt;
+#5 0x55e3b93da3ff &lt;unknown&gt;
+#6 0x55e3b93e94e0 &lt;unknown&gt;
+#7 0x55e3b94033e7 &lt;unknown&gt;
+#8 0x55e3b940ac5b &lt;unknown&gt;
+#9 0x55e3b93dab59 &lt;unknown&gt;
+</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -14028,8 +15048,29 @@
       <c r="D496" t="inlineStr"/>
       <c r="E496" t="inlineStr"/>
       <c r="F496" t="inlineStr"/>
-      <c r="G496" t="inlineStr"/>
-      <c r="H496" t="inlineStr"/>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
+  (Session info: chrome=150.0.7871.114)
+Stacktrace:
+#0 0x55e3b9a1c41a &lt;unknown&gt;
+#1 0x55e3b93f4689 &lt;unknown&gt;
+#2 0x55e3b93dc21a &lt;unknown&gt;
+#3 0x55e3b93dbe96 &lt;unknown&gt;
+#4 0x55e3b93d9a7e &lt;unknown&gt;
+#5 0x55e3b93da3ff &lt;unknown&gt;
+#6 0x55e3b93e94e0 &lt;unknown&gt;
+#7 0x55e3b94033e7 &lt;unknown&gt;
+#8 0x55e3b940ac5b &lt;unknown&gt;
+#9 0x55e3b93dab59 &lt;unknown&gt;
+</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -14046,8 +15087,29 @@
       <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr"/>
       <c r="F497" t="inlineStr"/>
-      <c r="G497" t="inlineStr"/>
-      <c r="H497" t="inlineStr"/>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
+  (Session info: chrome=150.0.7871.114)
+Stacktrace:
+#0 0x55e3b9a1c41a &lt;unknown&gt;
+#1 0x55e3b93f4689 &lt;unknown&gt;
+#2 0x55e3b93dc21a &lt;unknown&gt;
+#3 0x55e3b93dbe96 &lt;unknown&gt;
+#4 0x55e3b93d9a7e &lt;unknown&gt;
+#5 0x55e3b93da3ff &lt;unknown&gt;
+#6 0x55e3b93e94e0 &lt;unknown&gt;
+#7 0x55e3b94033e7 &lt;unknown&gt;
+#8 0x55e3b940ac5b &lt;unknown&gt;
+#9 0x55e3b93dab59 &lt;unknown&gt;
+</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -14064,8 +15126,29 @@
       <c r="D498" t="inlineStr"/>
       <c r="E498" t="inlineStr"/>
       <c r="F498" t="inlineStr"/>
-      <c r="G498" t="inlineStr"/>
-      <c r="H498" t="inlineStr"/>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
+  (Session info: chrome=150.0.7871.114)
+Stacktrace:
+#0 0x55e3b9a1c41a &lt;unknown&gt;
+#1 0x55e3b93f4689 &lt;unknown&gt;
+#2 0x55e3b93dc21a &lt;unknown&gt;
+#3 0x55e3b93dbe96 &lt;unknown&gt;
+#4 0x55e3b93d9a7e &lt;unknown&gt;
+#5 0x55e3b93da3ff &lt;unknown&gt;
+#6 0x55e3b93e94e0 &lt;unknown&gt;
+#7 0x55e3b94033e7 &lt;unknown&gt;
+#8 0x55e3b940ac5b &lt;unknown&gt;
+#9 0x55e3b93dab59 &lt;unknown&gt;
+</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -14082,8 +15165,29 @@
       <c r="D499" t="inlineStr"/>
       <c r="E499" t="inlineStr"/>
       <c r="F499" t="inlineStr"/>
-      <c r="G499" t="inlineStr"/>
-      <c r="H499" t="inlineStr"/>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
+  (Session info: chrome=150.0.7871.114)
+Stacktrace:
+#0 0x55e3b9a1c41a &lt;unknown&gt;
+#1 0x55e3b93f4689 &lt;unknown&gt;
+#2 0x55e3b93dc21a &lt;unknown&gt;
+#3 0x55e3b93dbe96 &lt;unknown&gt;
+#4 0x55e3b93d9a7e &lt;unknown&gt;
+#5 0x55e3b93da3ff &lt;unknown&gt;
+#6 0x55e3b93e94e0 &lt;unknown&gt;
+#7 0x55e3b94033e7 &lt;unknown&gt;
+#8 0x55e3b940ac5b &lt;unknown&gt;
+#9 0x55e3b93dab59 &lt;unknown&gt;
+</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -14100,8 +15204,29 @@
       <c r="D500" t="inlineStr"/>
       <c r="E500" t="inlineStr"/>
       <c r="F500" t="inlineStr"/>
-      <c r="G500" t="inlineStr"/>
-      <c r="H500" t="inlineStr"/>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
+  (Session info: chrome=150.0.7871.114)
+Stacktrace:
+#0 0x55e3b9a1c41a &lt;unknown&gt;
+#1 0x55e3b93f4689 &lt;unknown&gt;
+#2 0x55e3b93dc21a &lt;unknown&gt;
+#3 0x55e3b93dbe96 &lt;unknown&gt;
+#4 0x55e3b93d9a7e &lt;unknown&gt;
+#5 0x55e3b93da3ff &lt;unknown&gt;
+#6 0x55e3b93e94e0 &lt;unknown&gt;
+#7 0x55e3b94033e7 &lt;unknown&gt;
+#8 0x55e3b940ac5b &lt;unknown&gt;
+#9 0x55e3b93dab59 &lt;unknown&gt;
+</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -14118,8 +15243,29 @@
       <c r="D501" t="inlineStr"/>
       <c r="E501" t="inlineStr"/>
       <c r="F501" t="inlineStr"/>
-      <c r="G501" t="inlineStr"/>
-      <c r="H501" t="inlineStr"/>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
+  (Session info: chrome=150.0.7871.114)
+Stacktrace:
+#0 0x55e3b9a1c41a &lt;unknown&gt;
+#1 0x55e3b93f4689 &lt;unknown&gt;
+#2 0x55e3b93dc21a &lt;unknown&gt;
+#3 0x55e3b93dbe96 &lt;unknown&gt;
+#4 0x55e3b93d9a7e &lt;unknown&gt;
+#5 0x55e3b93da3ff &lt;unknown&gt;
+#6 0x55e3b93e94e0 &lt;unknown&gt;
+#7 0x55e3b94033e7 &lt;unknown&gt;
+#8 0x55e3b940ac5b &lt;unknown&gt;
+#9 0x55e3b93dab59 &lt;unknown&gt;
+</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -14136,8 +15282,29 @@
       <c r="D502" t="inlineStr"/>
       <c r="E502" t="inlineStr"/>
       <c r="F502" t="inlineStr"/>
-      <c r="G502" t="inlineStr"/>
-      <c r="H502" t="inlineStr"/>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
+  (Session info: chrome=150.0.7871.114)
+Stacktrace:
+#0 0x55e3b9a1c41a &lt;unknown&gt;
+#1 0x55e3b93f4689 &lt;unknown&gt;
+#2 0x55e3b93dc21a &lt;unknown&gt;
+#3 0x55e3b93dbe96 &lt;unknown&gt;
+#4 0x55e3b93d9a7e &lt;unknown&gt;
+#5 0x55e3b93da3ff &lt;unknown&gt;
+#6 0x55e3b93e94e0 &lt;unknown&gt;
+#7 0x55e3b94033e7 &lt;unknown&gt;
+#8 0x55e3b940ac5b &lt;unknown&gt;
+#9 0x55e3b93dab59 &lt;unknown&gt;
+</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -14154,8 +15321,29 @@
       <c r="D503" t="inlineStr"/>
       <c r="E503" t="inlineStr"/>
       <c r="F503" t="inlineStr"/>
-      <c r="G503" t="inlineStr"/>
-      <c r="H503" t="inlineStr"/>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
+  (Session info: chrome=150.0.7871.114)
+Stacktrace:
+#0 0x55e3b9a1c41a &lt;unknown&gt;
+#1 0x55e3b93f4689 &lt;unknown&gt;
+#2 0x55e3b93dc21a &lt;unknown&gt;
+#3 0x55e3b93dbe96 &lt;unknown&gt;
+#4 0x55e3b93d9a7e &lt;unknown&gt;
+#5 0x55e3b93da3ff &lt;unknown&gt;
+#6 0x55e3b93e94e0 &lt;unknown&gt;
+#7 0x55e3b94033e7 &lt;unknown&gt;
+#8 0x55e3b940ac5b &lt;unknown&gt;
+#9 0x55e3b93dab59 &lt;unknown&gt;
+</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -14172,8 +15360,29 @@
       <c r="D504" t="inlineStr"/>
       <c r="E504" t="inlineStr"/>
       <c r="F504" t="inlineStr"/>
-      <c r="G504" t="inlineStr"/>
-      <c r="H504" t="inlineStr"/>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
+  (Session info: chrome=150.0.7871.114)
+Stacktrace:
+#0 0x55e3b9a1c41a &lt;unknown&gt;
+#1 0x55e3b93f4689 &lt;unknown&gt;
+#2 0x55e3b93dc21a &lt;unknown&gt;
+#3 0x55e3b93dbe96 &lt;unknown&gt;
+#4 0x55e3b93d9a7e &lt;unknown&gt;
+#5 0x55e3b93da3ff &lt;unknown&gt;
+#6 0x55e3b93e94e0 &lt;unknown&gt;
+#7 0x55e3b94033e7 &lt;unknown&gt;
+#8 0x55e3b940ac5b &lt;unknown&gt;
+#9 0x55e3b93dab59 &lt;unknown&gt;
+</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -14190,8 +15399,29 @@
       <c r="D505" t="inlineStr"/>
       <c r="E505" t="inlineStr"/>
       <c r="F505" t="inlineStr"/>
-      <c r="G505" t="inlineStr"/>
-      <c r="H505" t="inlineStr"/>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
+  (Session info: chrome=150.0.7871.114)
+Stacktrace:
+#0 0x55e3b9a1c41a &lt;unknown&gt;
+#1 0x55e3b93f4689 &lt;unknown&gt;
+#2 0x55e3b93dc21a &lt;unknown&gt;
+#3 0x55e3b93dbe96 &lt;unknown&gt;
+#4 0x55e3b93d9a7e &lt;unknown&gt;
+#5 0x55e3b93da3ff &lt;unknown&gt;
+#6 0x55e3b93e94e0 &lt;unknown&gt;
+#7 0x55e3b94033e7 &lt;unknown&gt;
+#8 0x55e3b940ac5b &lt;unknown&gt;
+#9 0x55e3b93dab59 &lt;unknown&gt;
+</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -14208,8 +15438,29 @@
       <c r="D506" t="inlineStr"/>
       <c r="E506" t="inlineStr"/>
       <c r="F506" t="inlineStr"/>
-      <c r="G506" t="inlineStr"/>
-      <c r="H506" t="inlineStr"/>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
+  (Session info: chrome=150.0.7871.114)
+Stacktrace:
+#0 0x55e3b9a1c41a &lt;unknown&gt;
+#1 0x55e3b93f4689 &lt;unknown&gt;
+#2 0x55e3b93dc21a &lt;unknown&gt;
+#3 0x55e3b93dbe96 &lt;unknown&gt;
+#4 0x55e3b93d9a7e &lt;unknown&gt;
+#5 0x55e3b93da3ff &lt;unknown&gt;
+#6 0x55e3b93e94e0 &lt;unknown&gt;
+#7 0x55e3b94033e7 &lt;unknown&gt;
+#8 0x55e3b940ac5b &lt;unknown&gt;
+#9 0x55e3b93dab59 &lt;unknown&gt;
+</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -14226,8 +15477,29 @@
       <c r="D507" t="inlineStr"/>
       <c r="E507" t="inlineStr"/>
       <c r="F507" t="inlineStr"/>
-      <c r="G507" t="inlineStr"/>
-      <c r="H507" t="inlineStr"/>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
+  (Session info: chrome=150.0.7871.114)
+Stacktrace:
+#0 0x55e3b9a1c41a &lt;unknown&gt;
+#1 0x55e3b93f4689 &lt;unknown&gt;
+#2 0x55e3b93dc21a &lt;unknown&gt;
+#3 0x55e3b93dbe96 &lt;unknown&gt;
+#4 0x55e3b93d9a7e &lt;unknown&gt;
+#5 0x55e3b93da3ff &lt;unknown&gt;
+#6 0x55e3b93e94e0 &lt;unknown&gt;
+#7 0x55e3b94033e7 &lt;unknown&gt;
+#8 0x55e3b940ac5b &lt;unknown&gt;
+#9 0x55e3b93dab59 &lt;unknown&gt;
+</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">

--- a/output.xlsx
+++ b/output.xlsx
@@ -10620,21 +10620,9 @@
         </is>
       </c>
       <c r="C361" t="inlineStr"/>
-      <c r="D361" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E361" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F361" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D361" t="inlineStr"/>
+      <c r="E361" t="inlineStr"/>
+      <c r="F361" t="inlineStr"/>
       <c r="G361" t="inlineStr">
         <is>
           <t>OK</t>
@@ -10654,21 +10642,9 @@
         </is>
       </c>
       <c r="C362" t="inlineStr"/>
-      <c r="D362" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E362" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F362" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D362" t="inlineStr"/>
+      <c r="E362" t="inlineStr"/>
+      <c r="F362" t="inlineStr"/>
       <c r="G362" t="inlineStr">
         <is>
           <t>OK</t>
@@ -11202,21 +11178,9 @@
       <c r="C379" t="n">
         <v>4119</v>
       </c>
-      <c r="D379" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E379" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F379" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D379" t="inlineStr"/>
+      <c r="E379" t="inlineStr"/>
+      <c r="F379" t="inlineStr"/>
       <c r="G379" t="inlineStr">
         <is>
           <t>OK</t>
@@ -11238,21 +11202,9 @@
       <c r="C380" t="n">
         <v>4119</v>
       </c>
-      <c r="D380" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E380" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F380" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D380" t="inlineStr"/>
+      <c r="E380" t="inlineStr"/>
+      <c r="F380" t="inlineStr"/>
       <c r="G380" t="inlineStr">
         <is>
           <t>OK</t>
@@ -11274,21 +11226,9 @@
       <c r="C381" t="n">
         <v>4119</v>
       </c>
-      <c r="D381" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E381" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F381" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D381" t="inlineStr"/>
+      <c r="E381" t="inlineStr"/>
+      <c r="F381" t="inlineStr"/>
       <c r="G381" t="inlineStr">
         <is>
           <t>OK</t>
@@ -11308,21 +11248,9 @@
         </is>
       </c>
       <c r="C382" t="inlineStr"/>
-      <c r="D382" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E382" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F382" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D382" t="inlineStr"/>
+      <c r="E382" t="inlineStr"/>
+      <c r="F382" t="inlineStr"/>
       <c r="G382" t="inlineStr">
         <is>
           <t>OK</t>
@@ -11382,11 +11310,7 @@
       <c r="E384" t="n">
         <v>121</v>
       </c>
-      <c r="F384" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F384" t="inlineStr"/>
       <c r="G384" t="inlineStr">
         <is>
           <t>OK</t>
@@ -11414,11 +11338,7 @@
       <c r="E385" t="n">
         <v>41</v>
       </c>
-      <c r="F385" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F385" t="inlineStr"/>
       <c r="G385" t="inlineStr">
         <is>
           <t>OK</t>
@@ -11542,11 +11462,7 @@
       <c r="E389" t="n">
         <v>115</v>
       </c>
-      <c r="F389" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F389" t="inlineStr"/>
       <c r="G389" t="inlineStr">
         <is>
           <t>OK</t>
@@ -11606,11 +11522,7 @@
       <c r="E391" t="n">
         <v>12</v>
       </c>
-      <c r="F391" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F391" t="inlineStr"/>
       <c r="G391" t="inlineStr">
         <is>
           <t>OK</t>
@@ -11632,21 +11544,9 @@
       <c r="C392" t="n">
         <v>1869</v>
       </c>
-      <c r="D392" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E392" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F392" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D392" t="inlineStr"/>
+      <c r="E392" t="inlineStr"/>
+      <c r="F392" t="inlineStr"/>
       <c r="G392" t="inlineStr">
         <is>
           <t>OK</t>
@@ -11668,21 +11568,9 @@
       <c r="C393" t="n">
         <v>2649</v>
       </c>
-      <c r="D393" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E393" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F393" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D393" t="inlineStr"/>
+      <c r="E393" t="inlineStr"/>
+      <c r="F393" t="inlineStr"/>
       <c r="G393" t="inlineStr">
         <is>
           <t>OK</t>
@@ -11702,21 +11590,9 @@
         </is>
       </c>
       <c r="C394" t="inlineStr"/>
-      <c r="D394" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E394" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F394" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D394" t="inlineStr"/>
+      <c r="E394" t="inlineStr"/>
+      <c r="F394" t="inlineStr"/>
       <c r="G394" t="inlineStr">
         <is>
           <t>OK</t>
@@ -11744,11 +11620,7 @@
       <c r="E395" t="n">
         <v>3</v>
       </c>
-      <c r="F395" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F395" t="inlineStr"/>
       <c r="G395" t="inlineStr">
         <is>
           <t>OK</t>
@@ -11768,21 +11640,9 @@
         </is>
       </c>
       <c r="C396" t="inlineStr"/>
-      <c r="D396" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E396" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F396" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D396" t="inlineStr"/>
+      <c r="E396" t="inlineStr"/>
+      <c r="F396" t="inlineStr"/>
       <c r="G396" t="inlineStr">
         <is>
           <t>OK</t>
@@ -11842,11 +11702,7 @@
       <c r="E398" t="n">
         <v>45</v>
       </c>
-      <c r="F398" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F398" t="inlineStr"/>
       <c r="G398" t="inlineStr">
         <is>
           <t>OK</t>
@@ -11874,11 +11730,7 @@
       <c r="E399" t="n">
         <v>738</v>
       </c>
-      <c r="F399" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F399" t="inlineStr"/>
       <c r="G399" t="inlineStr">
         <is>
           <t>OK</t>
@@ -11906,11 +11758,7 @@
       <c r="E400" t="n">
         <v>2</v>
       </c>
-      <c r="F400" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F400" t="inlineStr"/>
       <c r="G400" t="inlineStr">
         <is>
           <t>OK</t>
@@ -11938,11 +11786,7 @@
       <c r="E401" t="n">
         <v>10</v>
       </c>
-      <c r="F401" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F401" t="inlineStr"/>
       <c r="G401" t="inlineStr">
         <is>
           <t>OK</t>
@@ -11970,11 +11814,7 @@
       <c r="E402" t="n">
         <v>42</v>
       </c>
-      <c r="F402" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F402" t="inlineStr"/>
       <c r="G402" t="inlineStr">
         <is>
           <t>OK</t>
@@ -12034,11 +11874,7 @@
       <c r="E404" t="n">
         <v>26</v>
       </c>
-      <c r="F404" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F404" t="inlineStr"/>
       <c r="G404" t="inlineStr">
         <is>
           <t>OK</t>
@@ -12066,11 +11902,7 @@
       <c r="E405" t="n">
         <v>42</v>
       </c>
-      <c r="F405" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F405" t="inlineStr"/>
       <c r="G405" t="inlineStr">
         <is>
           <t>OK</t>
@@ -12092,21 +11924,9 @@
       <c r="C406" t="n">
         <v>3119</v>
       </c>
-      <c r="D406" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E406" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F406" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D406" t="inlineStr"/>
+      <c r="E406" t="inlineStr"/>
+      <c r="F406" t="inlineStr"/>
       <c r="G406" t="inlineStr">
         <is>
           <t>OK</t>
@@ -12128,21 +11948,9 @@
       <c r="C407" t="n">
         <v>3069</v>
       </c>
-      <c r="D407" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E407" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F407" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D407" t="inlineStr"/>
+      <c r="E407" t="inlineStr"/>
+      <c r="F407" t="inlineStr"/>
       <c r="G407" t="inlineStr">
         <is>
           <t>OK</t>
@@ -12170,11 +11978,7 @@
       <c r="E408" t="n">
         <v>296</v>
       </c>
-      <c r="F408" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F408" t="inlineStr"/>
       <c r="G408" t="inlineStr">
         <is>
           <t>OK</t>
@@ -12234,11 +12038,7 @@
       <c r="E410" t="n">
         <v>25</v>
       </c>
-      <c r="F410" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F410" t="inlineStr"/>
       <c r="G410" t="inlineStr">
         <is>
           <t>OK</t>
@@ -12298,11 +12098,7 @@
       <c r="E412" t="n">
         <v>2</v>
       </c>
-      <c r="F412" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F412" t="inlineStr"/>
       <c r="G412" t="inlineStr">
         <is>
           <t>OK</t>
@@ -12330,11 +12126,7 @@
       <c r="E413" t="n">
         <v>1</v>
       </c>
-      <c r="F413" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F413" t="inlineStr"/>
       <c r="G413" t="inlineStr">
         <is>
           <t>OK</t>
@@ -12354,21 +12146,9 @@
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
-      <c r="D414" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E414" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F414" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D414" t="inlineStr"/>
+      <c r="E414" t="inlineStr"/>
+      <c r="F414" t="inlineStr"/>
       <c r="G414" t="inlineStr">
         <is>
           <t>OK</t>
@@ -12396,11 +12176,7 @@
       <c r="E415" t="n">
         <v>6</v>
       </c>
-      <c r="F415" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F415" t="inlineStr"/>
       <c r="G415" t="inlineStr">
         <is>
           <t>OK</t>
@@ -12428,11 +12204,7 @@
       <c r="E416" t="n">
         <v>27</v>
       </c>
-      <c r="F416" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F416" t="inlineStr"/>
       <c r="G416" t="inlineStr">
         <is>
           <t>OK</t>
@@ -12454,21 +12226,9 @@
       <c r="C417" t="n">
         <v>3149</v>
       </c>
-      <c r="D417" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E417" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F417" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D417" t="inlineStr"/>
+      <c r="E417" t="inlineStr"/>
+      <c r="F417" t="inlineStr"/>
       <c r="G417" t="inlineStr">
         <is>
           <t>OK</t>
@@ -12496,11 +12256,7 @@
       <c r="E418" t="n">
         <v>7</v>
       </c>
-      <c r="F418" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F418" t="inlineStr"/>
       <c r="G418" t="inlineStr">
         <is>
           <t>OK</t>
@@ -12528,11 +12284,7 @@
       <c r="E419" t="n">
         <v>12</v>
       </c>
-      <c r="F419" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F419" t="inlineStr"/>
       <c r="G419" t="inlineStr">
         <is>
           <t>OK</t>
@@ -12560,11 +12312,7 @@
       <c r="E420" t="n">
         <v>37</v>
       </c>
-      <c r="F420" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F420" t="inlineStr"/>
       <c r="G420" t="inlineStr">
         <is>
           <t>OK</t>
@@ -12592,11 +12340,7 @@
       <c r="E421" t="n">
         <v>267</v>
       </c>
-      <c r="F421" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F421" t="inlineStr"/>
       <c r="G421" t="inlineStr">
         <is>
           <t>OK</t>
@@ -12656,11 +12400,7 @@
       <c r="E423" t="n">
         <v>3</v>
       </c>
-      <c r="F423" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F423" t="inlineStr"/>
       <c r="G423" t="inlineStr">
         <is>
           <t>OK</t>
@@ -12720,11 +12460,7 @@
       <c r="E425" t="n">
         <v>1</v>
       </c>
-      <c r="F425" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F425" t="inlineStr"/>
       <c r="G425" t="inlineStr">
         <is>
           <t>OK</t>
@@ -12746,21 +12482,9 @@
       <c r="C426" t="n">
         <v>2319</v>
       </c>
-      <c r="D426" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E426" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F426" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D426" t="inlineStr"/>
+      <c r="E426" t="inlineStr"/>
+      <c r="F426" t="inlineStr"/>
       <c r="G426" t="inlineStr">
         <is>
           <t>OK</t>
@@ -12782,21 +12506,9 @@
       <c r="C427" t="n">
         <v>2269</v>
       </c>
-      <c r="D427" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E427" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F427" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D427" t="inlineStr"/>
+      <c r="E427" t="inlineStr"/>
+      <c r="F427" t="inlineStr"/>
       <c r="G427" t="inlineStr">
         <is>
           <t>OK</t>
@@ -12824,11 +12536,7 @@
       <c r="E428" t="n">
         <v>267</v>
       </c>
-      <c r="F428" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F428" t="inlineStr"/>
       <c r="G428" t="inlineStr">
         <is>
           <t>OK</t>
@@ -12888,11 +12596,7 @@
       <c r="E430" t="n">
         <v>2</v>
       </c>
-      <c r="F430" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F430" t="inlineStr"/>
       <c r="G430" t="inlineStr">
         <is>
           <t>OK</t>
@@ -12946,21 +12650,9 @@
       <c r="C432" t="n">
         <v>2329</v>
       </c>
-      <c r="D432" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E432" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F432" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D432" t="inlineStr"/>
+      <c r="E432" t="inlineStr"/>
+      <c r="F432" t="inlineStr"/>
       <c r="G432" t="inlineStr">
         <is>
           <t>OK</t>
@@ -12982,21 +12674,9 @@
       <c r="C433" t="n">
         <v>2319</v>
       </c>
-      <c r="D433" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E433" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F433" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D433" t="inlineStr"/>
+      <c r="E433" t="inlineStr"/>
+      <c r="F433" t="inlineStr"/>
       <c r="G433" t="inlineStr">
         <is>
           <t>OK</t>
@@ -13018,21 +12698,9 @@
       <c r="C434" t="n">
         <v>2269</v>
       </c>
-      <c r="D434" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E434" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F434" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D434" t="inlineStr"/>
+      <c r="E434" t="inlineStr"/>
+      <c r="F434" t="inlineStr"/>
       <c r="G434" t="inlineStr">
         <is>
           <t>OK</t>
@@ -13060,11 +12728,7 @@
       <c r="E435" t="n">
         <v>87</v>
       </c>
-      <c r="F435" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F435" t="inlineStr"/>
       <c r="G435" t="inlineStr">
         <is>
           <t>OK</t>
@@ -13084,21 +12748,9 @@
         </is>
       </c>
       <c r="C436" t="inlineStr"/>
-      <c r="D436" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E436" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F436" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D436" t="inlineStr"/>
+      <c r="E436" t="inlineStr"/>
+      <c r="F436" t="inlineStr"/>
       <c r="G436" t="inlineStr">
         <is>
           <t>OK</t>
@@ -13118,21 +12770,9 @@
         </is>
       </c>
       <c r="C437" t="inlineStr"/>
-      <c r="D437" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E437" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F437" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D437" t="inlineStr"/>
+      <c r="E437" t="inlineStr"/>
+      <c r="F437" t="inlineStr"/>
       <c r="G437" t="inlineStr">
         <is>
           <t>OK</t>
@@ -13152,21 +12792,9 @@
         </is>
       </c>
       <c r="C438" t="inlineStr"/>
-      <c r="D438" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E438" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F438" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D438" t="inlineStr"/>
+      <c r="E438" t="inlineStr"/>
+      <c r="F438" t="inlineStr"/>
       <c r="G438" t="inlineStr">
         <is>
           <t>OK</t>
@@ -13186,21 +12814,9 @@
         </is>
       </c>
       <c r="C439" t="inlineStr"/>
-      <c r="D439" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E439" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F439" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D439" t="inlineStr"/>
+      <c r="E439" t="inlineStr"/>
+      <c r="F439" t="inlineStr"/>
       <c r="G439" t="inlineStr">
         <is>
           <t>OK</t>
@@ -13220,21 +12836,9 @@
         </is>
       </c>
       <c r="C440" t="inlineStr"/>
-      <c r="D440" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E440" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F440" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D440" t="inlineStr"/>
+      <c r="E440" t="inlineStr"/>
+      <c r="F440" t="inlineStr"/>
       <c r="G440" t="inlineStr">
         <is>
           <t>OK</t>
@@ -13286,21 +12890,9 @@
         </is>
       </c>
       <c r="C442" t="inlineStr"/>
-      <c r="D442" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E442" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F442" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D442" t="inlineStr"/>
+      <c r="E442" t="inlineStr"/>
+      <c r="F442" t="inlineStr"/>
       <c r="G442" t="inlineStr">
         <is>
           <t>OK</t>
@@ -13320,21 +12912,9 @@
         </is>
       </c>
       <c r="C443" t="inlineStr"/>
-      <c r="D443" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E443" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F443" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D443" t="inlineStr"/>
+      <c r="E443" t="inlineStr"/>
+      <c r="F443" t="inlineStr"/>
       <c r="G443" t="inlineStr">
         <is>
           <t>OK</t>
@@ -13354,21 +12934,9 @@
         </is>
       </c>
       <c r="C444" t="inlineStr"/>
-      <c r="D444" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E444" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F444" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D444" t="inlineStr"/>
+      <c r="E444" t="inlineStr"/>
+      <c r="F444" t="inlineStr"/>
       <c r="G444" t="inlineStr">
         <is>
           <t>OK</t>
@@ -13396,11 +12964,7 @@
       <c r="E445" t="n">
         <v>12</v>
       </c>
-      <c r="F445" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F445" t="inlineStr"/>
       <c r="G445" t="inlineStr">
         <is>
           <t>OK</t>
@@ -13454,16 +13018,8 @@
       <c r="C447" t="n">
         <v>3369</v>
       </c>
-      <c r="D447" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E447" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D447" t="inlineStr"/>
+      <c r="E447" t="inlineStr"/>
       <c r="F447" t="inlineStr">
         <is>
           <t>Only 1 left</t>
@@ -13584,21 +13140,9 @@
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
-      <c r="D451" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E451" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F451" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D451" t="inlineStr"/>
+      <c r="E451" t="inlineStr"/>
+      <c r="F451" t="inlineStr"/>
       <c r="G451" t="inlineStr">
         <is>
           <t>OK</t>
@@ -13618,21 +13162,9 @@
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
-      <c r="D452" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E452" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F452" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D452" t="inlineStr"/>
+      <c r="E452" t="inlineStr"/>
+      <c r="F452" t="inlineStr"/>
       <c r="G452" t="inlineStr">
         <is>
           <t>OK</t>
@@ -13654,21 +13186,9 @@
       <c r="C453" t="n">
         <v>3369</v>
       </c>
-      <c r="D453" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E453" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F453" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D453" t="inlineStr"/>
+      <c r="E453" t="inlineStr"/>
+      <c r="F453" t="inlineStr"/>
       <c r="G453" t="inlineStr">
         <is>
           <t>OK</t>
@@ -13760,11 +13280,7 @@
       <c r="E456" t="n">
         <v>4</v>
       </c>
-      <c r="F456" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F456" t="inlineStr"/>
       <c r="G456" t="inlineStr">
         <is>
           <t>OK</t>
@@ -13952,11 +13468,7 @@
       <c r="E462" t="n">
         <v>4</v>
       </c>
-      <c r="F462" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F462" t="inlineStr"/>
       <c r="G462" t="inlineStr">
         <is>
           <t>OK</t>
@@ -14240,11 +13752,7 @@
       <c r="E471" t="n">
         <v>4</v>
       </c>
-      <c r="F471" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F471" t="inlineStr"/>
       <c r="G471" t="inlineStr">
         <is>
           <t>OK</t>
@@ -14368,11 +13876,7 @@
       <c r="E475" t="n">
         <v>1</v>
       </c>
-      <c r="F475" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F475" t="inlineStr"/>
       <c r="G475" t="inlineStr">
         <is>
           <t>OK</t>
@@ -14488,21 +13992,9 @@
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
-      <c r="D479" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E479" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F479" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D479" t="inlineStr"/>
+      <c r="E479" t="inlineStr"/>
+      <c r="F479" t="inlineStr"/>
       <c r="G479" t="inlineStr">
         <is>
           <t>OK</t>
@@ -14554,21 +14046,9 @@
         </is>
       </c>
       <c r="C481" t="inlineStr"/>
-      <c r="D481" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E481" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F481" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D481" t="inlineStr"/>
+      <c r="E481" t="inlineStr"/>
+      <c r="F481" t="inlineStr"/>
       <c r="G481" t="inlineStr">
         <is>
           <t>OK</t>
@@ -14596,11 +14076,7 @@
       <c r="E482" t="n">
         <v>112</v>
       </c>
-      <c r="F482" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F482" t="inlineStr"/>
       <c r="G482" t="inlineStr">
         <is>
           <t>OK</t>
@@ -14628,11 +14104,7 @@
       <c r="E483" t="n">
         <v>119</v>
       </c>
-      <c r="F483" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F483" t="inlineStr"/>
       <c r="G483" t="inlineStr">
         <is>
           <t>OK</t>
@@ -14812,21 +14284,9 @@
         </is>
       </c>
       <c r="C489" t="inlineStr"/>
-      <c r="D489" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E489" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F489" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D489" t="inlineStr"/>
+      <c r="E489" t="inlineStr"/>
+      <c r="F489" t="inlineStr"/>
       <c r="G489" t="inlineStr">
         <is>
           <t>OK</t>
@@ -15006,32 +14466,27 @@
         </is>
       </c>
       <c r="C495" t="inlineStr"/>
-      <c r="D495" t="inlineStr"/>
-      <c r="E495" t="inlineStr"/>
-      <c r="F495" t="inlineStr"/>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="H495" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
-  (Session info: chrome=150.0.7871.114)
-Stacktrace:
-#0 0x55e3b9a1c41a &lt;unknown&gt;
-#1 0x55e3b93f4689 &lt;unknown&gt;
-#2 0x55e3b93dc21a &lt;unknown&gt;
-#3 0x55e3b93dbe96 &lt;unknown&gt;
-#4 0x55e3b93d9a7e &lt;unknown&gt;
-#5 0x55e3b93da3ff &lt;unknown&gt;
-#6 0x55e3b93e94e0 &lt;unknown&gt;
-#7 0x55e3b94033e7 &lt;unknown&gt;
-#8 0x55e3b940ac5b &lt;unknown&gt;
-#9 0x55e3b93dab59 &lt;unknown&gt;
-</t>
-        </is>
-      </c>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -15045,32 +14500,27 @@
         </is>
       </c>
       <c r="C496" t="inlineStr"/>
-      <c r="D496" t="inlineStr"/>
-      <c r="E496" t="inlineStr"/>
-      <c r="F496" t="inlineStr"/>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="H496" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
-  (Session info: chrome=150.0.7871.114)
-Stacktrace:
-#0 0x55e3b9a1c41a &lt;unknown&gt;
-#1 0x55e3b93f4689 &lt;unknown&gt;
-#2 0x55e3b93dc21a &lt;unknown&gt;
-#3 0x55e3b93dbe96 &lt;unknown&gt;
-#4 0x55e3b93d9a7e &lt;unknown&gt;
-#5 0x55e3b93da3ff &lt;unknown&gt;
-#6 0x55e3b93e94e0 &lt;unknown&gt;
-#7 0x55e3b94033e7 &lt;unknown&gt;
-#8 0x55e3b940ac5b &lt;unknown&gt;
-#9 0x55e3b93dab59 &lt;unknown&gt;
-</t>
-        </is>
-      </c>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -15084,32 +14534,27 @@
         </is>
       </c>
       <c r="C497" t="inlineStr"/>
-      <c r="D497" t="inlineStr"/>
-      <c r="E497" t="inlineStr"/>
-      <c r="F497" t="inlineStr"/>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="H497" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
-  (Session info: chrome=150.0.7871.114)
-Stacktrace:
-#0 0x55e3b9a1c41a &lt;unknown&gt;
-#1 0x55e3b93f4689 &lt;unknown&gt;
-#2 0x55e3b93dc21a &lt;unknown&gt;
-#3 0x55e3b93dbe96 &lt;unknown&gt;
-#4 0x55e3b93d9a7e &lt;unknown&gt;
-#5 0x55e3b93da3ff &lt;unknown&gt;
-#6 0x55e3b93e94e0 &lt;unknown&gt;
-#7 0x55e3b94033e7 &lt;unknown&gt;
-#8 0x55e3b940ac5b &lt;unknown&gt;
-#9 0x55e3b93dab59 &lt;unknown&gt;
-</t>
-        </is>
-      </c>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -15123,32 +14568,27 @@
         </is>
       </c>
       <c r="C498" t="inlineStr"/>
-      <c r="D498" t="inlineStr"/>
-      <c r="E498" t="inlineStr"/>
-      <c r="F498" t="inlineStr"/>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="H498" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
-  (Session info: chrome=150.0.7871.114)
-Stacktrace:
-#0 0x55e3b9a1c41a &lt;unknown&gt;
-#1 0x55e3b93f4689 &lt;unknown&gt;
-#2 0x55e3b93dc21a &lt;unknown&gt;
-#3 0x55e3b93dbe96 &lt;unknown&gt;
-#4 0x55e3b93d9a7e &lt;unknown&gt;
-#5 0x55e3b93da3ff &lt;unknown&gt;
-#6 0x55e3b93e94e0 &lt;unknown&gt;
-#7 0x55e3b94033e7 &lt;unknown&gt;
-#8 0x55e3b940ac5b &lt;unknown&gt;
-#9 0x55e3b93dab59 &lt;unknown&gt;
-</t>
-        </is>
-      </c>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -15162,32 +14602,27 @@
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
-      <c r="D499" t="inlineStr"/>
-      <c r="E499" t="inlineStr"/>
-      <c r="F499" t="inlineStr"/>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="H499" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
-  (Session info: chrome=150.0.7871.114)
-Stacktrace:
-#0 0x55e3b9a1c41a &lt;unknown&gt;
-#1 0x55e3b93f4689 &lt;unknown&gt;
-#2 0x55e3b93dc21a &lt;unknown&gt;
-#3 0x55e3b93dbe96 &lt;unknown&gt;
-#4 0x55e3b93d9a7e &lt;unknown&gt;
-#5 0x55e3b93da3ff &lt;unknown&gt;
-#6 0x55e3b93e94e0 &lt;unknown&gt;
-#7 0x55e3b94033e7 &lt;unknown&gt;
-#8 0x55e3b940ac5b &lt;unknown&gt;
-#9 0x55e3b93dab59 &lt;unknown&gt;
-</t>
-        </is>
-      </c>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -15201,32 +14636,27 @@
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
-      <c r="D500" t="inlineStr"/>
-      <c r="E500" t="inlineStr"/>
-      <c r="F500" t="inlineStr"/>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="H500" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
-  (Session info: chrome=150.0.7871.114)
-Stacktrace:
-#0 0x55e3b9a1c41a &lt;unknown&gt;
-#1 0x55e3b93f4689 &lt;unknown&gt;
-#2 0x55e3b93dc21a &lt;unknown&gt;
-#3 0x55e3b93dbe96 &lt;unknown&gt;
-#4 0x55e3b93d9a7e &lt;unknown&gt;
-#5 0x55e3b93da3ff &lt;unknown&gt;
-#6 0x55e3b93e94e0 &lt;unknown&gt;
-#7 0x55e3b94033e7 &lt;unknown&gt;
-#8 0x55e3b940ac5b &lt;unknown&gt;
-#9 0x55e3b93dab59 &lt;unknown&gt;
-</t>
-        </is>
-      </c>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -15240,32 +14670,27 @@
         </is>
       </c>
       <c r="C501" t="inlineStr"/>
-      <c r="D501" t="inlineStr"/>
-      <c r="E501" t="inlineStr"/>
-      <c r="F501" t="inlineStr"/>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="H501" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
-  (Session info: chrome=150.0.7871.114)
-Stacktrace:
-#0 0x55e3b9a1c41a &lt;unknown&gt;
-#1 0x55e3b93f4689 &lt;unknown&gt;
-#2 0x55e3b93dc21a &lt;unknown&gt;
-#3 0x55e3b93dbe96 &lt;unknown&gt;
-#4 0x55e3b93d9a7e &lt;unknown&gt;
-#5 0x55e3b93da3ff &lt;unknown&gt;
-#6 0x55e3b93e94e0 &lt;unknown&gt;
-#7 0x55e3b94033e7 &lt;unknown&gt;
-#8 0x55e3b940ac5b &lt;unknown&gt;
-#9 0x55e3b93dab59 &lt;unknown&gt;
-</t>
-        </is>
-      </c>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -15279,32 +14704,27 @@
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
-      <c r="D502" t="inlineStr"/>
-      <c r="E502" t="inlineStr"/>
-      <c r="F502" t="inlineStr"/>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="H502" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
-  (Session info: chrome=150.0.7871.114)
-Stacktrace:
-#0 0x55e3b9a1c41a &lt;unknown&gt;
-#1 0x55e3b93f4689 &lt;unknown&gt;
-#2 0x55e3b93dc21a &lt;unknown&gt;
-#3 0x55e3b93dbe96 &lt;unknown&gt;
-#4 0x55e3b93d9a7e &lt;unknown&gt;
-#5 0x55e3b93da3ff &lt;unknown&gt;
-#6 0x55e3b93e94e0 &lt;unknown&gt;
-#7 0x55e3b94033e7 &lt;unknown&gt;
-#8 0x55e3b940ac5b &lt;unknown&gt;
-#9 0x55e3b93dab59 &lt;unknown&gt;
-</t>
-        </is>
-      </c>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -15318,32 +14738,27 @@
         </is>
       </c>
       <c r="C503" t="inlineStr"/>
-      <c r="D503" t="inlineStr"/>
-      <c r="E503" t="inlineStr"/>
-      <c r="F503" t="inlineStr"/>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="H503" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
-  (Session info: chrome=150.0.7871.114)
-Stacktrace:
-#0 0x55e3b9a1c41a &lt;unknown&gt;
-#1 0x55e3b93f4689 &lt;unknown&gt;
-#2 0x55e3b93dc21a &lt;unknown&gt;
-#3 0x55e3b93dbe96 &lt;unknown&gt;
-#4 0x55e3b93d9a7e &lt;unknown&gt;
-#5 0x55e3b93da3ff &lt;unknown&gt;
-#6 0x55e3b93e94e0 &lt;unknown&gt;
-#7 0x55e3b94033e7 &lt;unknown&gt;
-#8 0x55e3b940ac5b &lt;unknown&gt;
-#9 0x55e3b93dab59 &lt;unknown&gt;
-</t>
-        </is>
-      </c>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -15357,32 +14772,27 @@
         </is>
       </c>
       <c r="C504" t="inlineStr"/>
-      <c r="D504" t="inlineStr"/>
-      <c r="E504" t="inlineStr"/>
-      <c r="F504" t="inlineStr"/>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="H504" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
-  (Session info: chrome=150.0.7871.114)
-Stacktrace:
-#0 0x55e3b9a1c41a &lt;unknown&gt;
-#1 0x55e3b93f4689 &lt;unknown&gt;
-#2 0x55e3b93dc21a &lt;unknown&gt;
-#3 0x55e3b93dbe96 &lt;unknown&gt;
-#4 0x55e3b93d9a7e &lt;unknown&gt;
-#5 0x55e3b93da3ff &lt;unknown&gt;
-#6 0x55e3b93e94e0 &lt;unknown&gt;
-#7 0x55e3b94033e7 &lt;unknown&gt;
-#8 0x55e3b940ac5b &lt;unknown&gt;
-#9 0x55e3b93dab59 &lt;unknown&gt;
-</t>
-        </is>
-      </c>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -15396,32 +14806,27 @@
         </is>
       </c>
       <c r="C505" t="inlineStr"/>
-      <c r="D505" t="inlineStr"/>
-      <c r="E505" t="inlineStr"/>
-      <c r="F505" t="inlineStr"/>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="H505" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
-  (Session info: chrome=150.0.7871.114)
-Stacktrace:
-#0 0x55e3b9a1c41a &lt;unknown&gt;
-#1 0x55e3b93f4689 &lt;unknown&gt;
-#2 0x55e3b93dc21a &lt;unknown&gt;
-#3 0x55e3b93dbe96 &lt;unknown&gt;
-#4 0x55e3b93d9a7e &lt;unknown&gt;
-#5 0x55e3b93da3ff &lt;unknown&gt;
-#6 0x55e3b93e94e0 &lt;unknown&gt;
-#7 0x55e3b94033e7 &lt;unknown&gt;
-#8 0x55e3b940ac5b &lt;unknown&gt;
-#9 0x55e3b93dab59 &lt;unknown&gt;
-</t>
-        </is>
-      </c>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -15435,32 +14840,27 @@
         </is>
       </c>
       <c r="C506" t="inlineStr"/>
-      <c r="D506" t="inlineStr"/>
-      <c r="E506" t="inlineStr"/>
-      <c r="F506" t="inlineStr"/>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="H506" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
-  (Session info: chrome=150.0.7871.114)
-Stacktrace:
-#0 0x55e3b9a1c41a &lt;unknown&gt;
-#1 0x55e3b93f4689 &lt;unknown&gt;
-#2 0x55e3b93dc21a &lt;unknown&gt;
-#3 0x55e3b93dbe96 &lt;unknown&gt;
-#4 0x55e3b93d9a7e &lt;unknown&gt;
-#5 0x55e3b93da3ff &lt;unknown&gt;
-#6 0x55e3b93e94e0 &lt;unknown&gt;
-#7 0x55e3b94033e7 &lt;unknown&gt;
-#8 0x55e3b940ac5b &lt;unknown&gt;
-#9 0x55e3b93dab59 &lt;unknown&gt;
-</t>
-        </is>
-      </c>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -15474,32 +14874,27 @@
         </is>
       </c>
       <c r="C507" t="inlineStr"/>
-      <c r="D507" t="inlineStr"/>
-      <c r="E507" t="inlineStr"/>
-      <c r="F507" t="inlineStr"/>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="H507" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
-  (Session info: chrome=150.0.7871.114)
-Stacktrace:
-#0 0x55e3b9a1c41a &lt;unknown&gt;
-#1 0x55e3b93f4689 &lt;unknown&gt;
-#2 0x55e3b93dc21a &lt;unknown&gt;
-#3 0x55e3b93dbe96 &lt;unknown&gt;
-#4 0x55e3b93d9a7e &lt;unknown&gt;
-#5 0x55e3b93da3ff &lt;unknown&gt;
-#6 0x55e3b93e94e0 &lt;unknown&gt;
-#7 0x55e3b94033e7 &lt;unknown&gt;
-#8 0x55e3b940ac5b &lt;unknown&gt;
-#9 0x55e3b93dab59 &lt;unknown&gt;
-</t>
-        </is>
-      </c>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -15513,10 +14908,26 @@
         </is>
       </c>
       <c r="C508" t="inlineStr"/>
-      <c r="D508" t="inlineStr"/>
-      <c r="E508" t="inlineStr"/>
-      <c r="F508" t="inlineStr"/>
-      <c r="G508" t="inlineStr"/>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H508" t="inlineStr"/>
     </row>
     <row r="509">
@@ -15531,10 +14942,26 @@
         </is>
       </c>
       <c r="C509" t="inlineStr"/>
-      <c r="D509" t="inlineStr"/>
-      <c r="E509" t="inlineStr"/>
-      <c r="F509" t="inlineStr"/>
-      <c r="G509" t="inlineStr"/>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H509" t="inlineStr"/>
     </row>
     <row r="510">
@@ -15549,10 +14976,26 @@
         </is>
       </c>
       <c r="C510" t="inlineStr"/>
-      <c r="D510" t="inlineStr"/>
-      <c r="E510" t="inlineStr"/>
-      <c r="F510" t="inlineStr"/>
-      <c r="G510" t="inlineStr"/>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H510" t="inlineStr"/>
     </row>
     <row r="511">
@@ -15567,10 +15010,26 @@
         </is>
       </c>
       <c r="C511" t="inlineStr"/>
-      <c r="D511" t="inlineStr"/>
-      <c r="E511" t="inlineStr"/>
-      <c r="F511" t="inlineStr"/>
-      <c r="G511" t="inlineStr"/>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H511" t="inlineStr"/>
     </row>
     <row r="512">
@@ -15585,10 +15044,26 @@
         </is>
       </c>
       <c r="C512" t="inlineStr"/>
-      <c r="D512" t="inlineStr"/>
-      <c r="E512" t="inlineStr"/>
-      <c r="F512" t="inlineStr"/>
-      <c r="G512" t="inlineStr"/>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H512" t="inlineStr"/>
     </row>
     <row r="513">
@@ -15603,10 +15078,26 @@
         </is>
       </c>
       <c r="C513" t="inlineStr"/>
-      <c r="D513" t="inlineStr"/>
-      <c r="E513" t="inlineStr"/>
-      <c r="F513" t="inlineStr"/>
-      <c r="G513" t="inlineStr"/>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H513" t="inlineStr"/>
     </row>
     <row r="514">
@@ -15621,10 +15112,26 @@
         </is>
       </c>
       <c r="C514" t="inlineStr"/>
-      <c r="D514" t="inlineStr"/>
-      <c r="E514" t="inlineStr"/>
-      <c r="F514" t="inlineStr"/>
-      <c r="G514" t="inlineStr"/>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H514" t="inlineStr"/>
     </row>
     <row r="515">
@@ -15639,10 +15146,26 @@
         </is>
       </c>
       <c r="C515" t="inlineStr"/>
-      <c r="D515" t="inlineStr"/>
-      <c r="E515" t="inlineStr"/>
-      <c r="F515" t="inlineStr"/>
-      <c r="G515" t="inlineStr"/>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H515" t="inlineStr"/>
     </row>
     <row r="516">
@@ -15657,10 +15180,26 @@
         </is>
       </c>
       <c r="C516" t="inlineStr"/>
-      <c r="D516" t="inlineStr"/>
-      <c r="E516" t="inlineStr"/>
-      <c r="F516" t="inlineStr"/>
-      <c r="G516" t="inlineStr"/>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H516" t="inlineStr"/>
     </row>
     <row r="517">
@@ -15675,10 +15214,26 @@
         </is>
       </c>
       <c r="C517" t="inlineStr"/>
-      <c r="D517" t="inlineStr"/>
-      <c r="E517" t="inlineStr"/>
-      <c r="F517" t="inlineStr"/>
-      <c r="G517" t="inlineStr"/>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H517" t="inlineStr"/>
     </row>
     <row r="518">
@@ -15693,10 +15248,26 @@
         </is>
       </c>
       <c r="C518" t="inlineStr"/>
-      <c r="D518" t="inlineStr"/>
-      <c r="E518" t="inlineStr"/>
-      <c r="F518" t="inlineStr"/>
-      <c r="G518" t="inlineStr"/>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H518" t="inlineStr"/>
     </row>
     <row r="519">
@@ -15711,10 +15282,26 @@
         </is>
       </c>
       <c r="C519" t="inlineStr"/>
-      <c r="D519" t="inlineStr"/>
-      <c r="E519" t="inlineStr"/>
-      <c r="F519" t="inlineStr"/>
-      <c r="G519" t="inlineStr"/>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H519" t="inlineStr"/>
     </row>
     <row r="520">
@@ -15729,10 +15316,26 @@
         </is>
       </c>
       <c r="C520" t="inlineStr"/>
-      <c r="D520" t="inlineStr"/>
-      <c r="E520" t="inlineStr"/>
-      <c r="F520" t="inlineStr"/>
-      <c r="G520" t="inlineStr"/>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H520" t="inlineStr"/>
     </row>
     <row r="521">
@@ -15747,10 +15350,26 @@
         </is>
       </c>
       <c r="C521" t="inlineStr"/>
-      <c r="D521" t="inlineStr"/>
-      <c r="E521" t="inlineStr"/>
-      <c r="F521" t="inlineStr"/>
-      <c r="G521" t="inlineStr"/>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H521" t="inlineStr"/>
     </row>
     <row r="522">
@@ -15765,10 +15384,26 @@
         </is>
       </c>
       <c r="C522" t="inlineStr"/>
-      <c r="D522" t="inlineStr"/>
-      <c r="E522" t="inlineStr"/>
-      <c r="F522" t="inlineStr"/>
-      <c r="G522" t="inlineStr"/>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H522" t="inlineStr"/>
     </row>
     <row r="523">
@@ -15783,10 +15418,26 @@
         </is>
       </c>
       <c r="C523" t="inlineStr"/>
-      <c r="D523" t="inlineStr"/>
-      <c r="E523" t="inlineStr"/>
-      <c r="F523" t="inlineStr"/>
-      <c r="G523" t="inlineStr"/>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H523" t="inlineStr"/>
     </row>
     <row r="524">
@@ -15801,10 +15452,26 @@
         </is>
       </c>
       <c r="C524" t="inlineStr"/>
-      <c r="D524" t="inlineStr"/>
-      <c r="E524" t="inlineStr"/>
-      <c r="F524" t="inlineStr"/>
-      <c r="G524" t="inlineStr"/>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H524" t="inlineStr"/>
     </row>
     <row r="525">
@@ -15819,10 +15486,26 @@
         </is>
       </c>
       <c r="C525" t="inlineStr"/>
-      <c r="D525" t="inlineStr"/>
-      <c r="E525" t="inlineStr"/>
-      <c r="F525" t="inlineStr"/>
-      <c r="G525" t="inlineStr"/>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H525" t="inlineStr"/>
     </row>
     <row r="526">
@@ -15837,10 +15520,26 @@
         </is>
       </c>
       <c r="C526" t="inlineStr"/>
-      <c r="D526" t="inlineStr"/>
-      <c r="E526" t="inlineStr"/>
-      <c r="F526" t="inlineStr"/>
-      <c r="G526" t="inlineStr"/>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H526" t="inlineStr"/>
     </row>
     <row r="527">
@@ -15855,10 +15554,26 @@
         </is>
       </c>
       <c r="C527" t="inlineStr"/>
-      <c r="D527" t="inlineStr"/>
-      <c r="E527" t="inlineStr"/>
-      <c r="F527" t="inlineStr"/>
-      <c r="G527" t="inlineStr"/>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H527" t="inlineStr"/>
     </row>
     <row r="528">
@@ -15873,10 +15588,26 @@
         </is>
       </c>
       <c r="C528" t="inlineStr"/>
-      <c r="D528" t="inlineStr"/>
-      <c r="E528" t="inlineStr"/>
-      <c r="F528" t="inlineStr"/>
-      <c r="G528" t="inlineStr"/>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H528" t="inlineStr"/>
     </row>
     <row r="529">
@@ -15891,10 +15622,26 @@
         </is>
       </c>
       <c r="C529" t="inlineStr"/>
-      <c r="D529" t="inlineStr"/>
-      <c r="E529" t="inlineStr"/>
-      <c r="F529" t="inlineStr"/>
-      <c r="G529" t="inlineStr"/>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H529" t="inlineStr"/>
     </row>
     <row r="530">
@@ -15909,10 +15656,26 @@
         </is>
       </c>
       <c r="C530" t="inlineStr"/>
-      <c r="D530" t="inlineStr"/>
-      <c r="E530" t="inlineStr"/>
-      <c r="F530" t="inlineStr"/>
-      <c r="G530" t="inlineStr"/>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H530" t="inlineStr"/>
     </row>
     <row r="531">
@@ -15927,10 +15690,26 @@
         </is>
       </c>
       <c r="C531" t="inlineStr"/>
-      <c r="D531" t="inlineStr"/>
-      <c r="E531" t="inlineStr"/>
-      <c r="F531" t="inlineStr"/>
-      <c r="G531" t="inlineStr"/>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H531" t="inlineStr"/>
     </row>
     <row r="532">
@@ -15945,10 +15724,26 @@
         </is>
       </c>
       <c r="C532" t="inlineStr"/>
-      <c r="D532" t="inlineStr"/>
-      <c r="E532" t="inlineStr"/>
-      <c r="F532" t="inlineStr"/>
-      <c r="G532" t="inlineStr"/>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H532" t="inlineStr"/>
     </row>
     <row r="533">
@@ -15963,10 +15758,26 @@
         </is>
       </c>
       <c r="C533" t="inlineStr"/>
-      <c r="D533" t="inlineStr"/>
-      <c r="E533" t="inlineStr"/>
-      <c r="F533" t="inlineStr"/>
-      <c r="G533" t="inlineStr"/>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H533" t="inlineStr"/>
     </row>
     <row r="534">
@@ -15981,10 +15792,26 @@
         </is>
       </c>
       <c r="C534" t="inlineStr"/>
-      <c r="D534" t="inlineStr"/>
-      <c r="E534" t="inlineStr"/>
-      <c r="F534" t="inlineStr"/>
-      <c r="G534" t="inlineStr"/>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H534" t="inlineStr"/>
     </row>
     <row r="535">
@@ -15999,10 +15826,26 @@
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
-      <c r="D535" t="inlineStr"/>
-      <c r="E535" t="inlineStr"/>
-      <c r="F535" t="inlineStr"/>
-      <c r="G535" t="inlineStr"/>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H535" t="inlineStr"/>
     </row>
     <row r="536">
@@ -16017,10 +15860,26 @@
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
-      <c r="D536" t="inlineStr"/>
-      <c r="E536" t="inlineStr"/>
-      <c r="F536" t="inlineStr"/>
-      <c r="G536" t="inlineStr"/>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H536" t="inlineStr"/>
     </row>
     <row r="537">
@@ -16035,10 +15894,26 @@
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
-      <c r="D537" t="inlineStr"/>
-      <c r="E537" t="inlineStr"/>
-      <c r="F537" t="inlineStr"/>
-      <c r="G537" t="inlineStr"/>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H537" t="inlineStr"/>
     </row>
     <row r="538">
@@ -16053,10 +15928,26 @@
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
-      <c r="D538" t="inlineStr"/>
-      <c r="E538" t="inlineStr"/>
-      <c r="F538" t="inlineStr"/>
-      <c r="G538" t="inlineStr"/>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H538" t="inlineStr"/>
     </row>
     <row r="539">
@@ -16071,10 +15962,26 @@
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
-      <c r="D539" t="inlineStr"/>
-      <c r="E539" t="inlineStr"/>
-      <c r="F539" t="inlineStr"/>
-      <c r="G539" t="inlineStr"/>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H539" t="inlineStr"/>
     </row>
     <row r="540">
@@ -16089,10 +15996,26 @@
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
-      <c r="D540" t="inlineStr"/>
-      <c r="E540" t="inlineStr"/>
-      <c r="F540" t="inlineStr"/>
-      <c r="G540" t="inlineStr"/>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H540" t="inlineStr"/>
     </row>
     <row r="541">
@@ -16107,10 +16030,26 @@
         </is>
       </c>
       <c r="C541" t="inlineStr"/>
-      <c r="D541" t="inlineStr"/>
-      <c r="E541" t="inlineStr"/>
-      <c r="F541" t="inlineStr"/>
-      <c r="G541" t="inlineStr"/>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H541" t="inlineStr"/>
     </row>
     <row r="542">
@@ -16125,10 +16064,26 @@
         </is>
       </c>
       <c r="C542" t="inlineStr"/>
-      <c r="D542" t="inlineStr"/>
-      <c r="E542" t="inlineStr"/>
-      <c r="F542" t="inlineStr"/>
-      <c r="G542" t="inlineStr"/>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H542" t="inlineStr"/>
     </row>
     <row r="543">
@@ -16143,10 +16098,26 @@
         </is>
       </c>
       <c r="C543" t="inlineStr"/>
-      <c r="D543" t="inlineStr"/>
-      <c r="E543" t="inlineStr"/>
-      <c r="F543" t="inlineStr"/>
-      <c r="G543" t="inlineStr"/>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H543" t="inlineStr"/>
     </row>
     <row r="544">
@@ -16161,10 +16132,26 @@
         </is>
       </c>
       <c r="C544" t="inlineStr"/>
-      <c r="D544" t="inlineStr"/>
-      <c r="E544" t="inlineStr"/>
-      <c r="F544" t="inlineStr"/>
-      <c r="G544" t="inlineStr"/>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H544" t="inlineStr"/>
     </row>
     <row r="545">
@@ -16179,10 +16166,26 @@
         </is>
       </c>
       <c r="C545" t="inlineStr"/>
-      <c r="D545" t="inlineStr"/>
-      <c r="E545" t="inlineStr"/>
-      <c r="F545" t="inlineStr"/>
-      <c r="G545" t="inlineStr"/>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H545" t="inlineStr"/>
     </row>
     <row r="546">
@@ -16197,10 +16200,26 @@
         </is>
       </c>
       <c r="C546" t="inlineStr"/>
-      <c r="D546" t="inlineStr"/>
-      <c r="E546" t="inlineStr"/>
-      <c r="F546" t="inlineStr"/>
-      <c r="G546" t="inlineStr"/>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H546" t="inlineStr"/>
     </row>
     <row r="547">
@@ -16215,10 +16234,26 @@
         </is>
       </c>
       <c r="C547" t="inlineStr"/>
-      <c r="D547" t="inlineStr"/>
-      <c r="E547" t="inlineStr"/>
-      <c r="F547" t="inlineStr"/>
-      <c r="G547" t="inlineStr"/>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H547" t="inlineStr"/>
     </row>
     <row r="548">
@@ -16233,10 +16268,26 @@
         </is>
       </c>
       <c r="C548" t="inlineStr"/>
-      <c r="D548" t="inlineStr"/>
-      <c r="E548" t="inlineStr"/>
-      <c r="F548" t="inlineStr"/>
-      <c r="G548" t="inlineStr"/>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H548" t="inlineStr"/>
     </row>
     <row r="549">
@@ -16251,10 +16302,26 @@
         </is>
       </c>
       <c r="C549" t="inlineStr"/>
-      <c r="D549" t="inlineStr"/>
-      <c r="E549" t="inlineStr"/>
-      <c r="F549" t="inlineStr"/>
-      <c r="G549" t="inlineStr"/>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H549" t="inlineStr"/>
     </row>
     <row r="550">
@@ -16269,10 +16336,26 @@
         </is>
       </c>
       <c r="C550" t="inlineStr"/>
-      <c r="D550" t="inlineStr"/>
-      <c r="E550" t="inlineStr"/>
-      <c r="F550" t="inlineStr"/>
-      <c r="G550" t="inlineStr"/>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H550" t="inlineStr"/>
     </row>
     <row r="551">
@@ -16287,10 +16370,26 @@
         </is>
       </c>
       <c r="C551" t="inlineStr"/>
-      <c r="D551" t="inlineStr"/>
-      <c r="E551" t="inlineStr"/>
-      <c r="F551" t="inlineStr"/>
-      <c r="G551" t="inlineStr"/>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H551" t="inlineStr"/>
     </row>
     <row r="552">
@@ -16305,10 +16404,26 @@
         </is>
       </c>
       <c r="C552" t="inlineStr"/>
-      <c r="D552" t="inlineStr"/>
-      <c r="E552" t="inlineStr"/>
-      <c r="F552" t="inlineStr"/>
-      <c r="G552" t="inlineStr"/>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H552" t="inlineStr"/>
     </row>
     <row r="553">
@@ -16323,10 +16438,26 @@
         </is>
       </c>
       <c r="C553" t="inlineStr"/>
-      <c r="D553" t="inlineStr"/>
-      <c r="E553" t="inlineStr"/>
-      <c r="F553" t="inlineStr"/>
-      <c r="G553" t="inlineStr"/>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H553" t="inlineStr"/>
     </row>
     <row r="554">
@@ -16341,10 +16472,26 @@
         </is>
       </c>
       <c r="C554" t="inlineStr"/>
-      <c r="D554" t="inlineStr"/>
-      <c r="E554" t="inlineStr"/>
-      <c r="F554" t="inlineStr"/>
-      <c r="G554" t="inlineStr"/>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H554" t="inlineStr"/>
     </row>
     <row r="555">
@@ -16359,10 +16506,26 @@
         </is>
       </c>
       <c r="C555" t="inlineStr"/>
-      <c r="D555" t="inlineStr"/>
-      <c r="E555" t="inlineStr"/>
-      <c r="F555" t="inlineStr"/>
-      <c r="G555" t="inlineStr"/>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H555" t="inlineStr"/>
     </row>
     <row r="556">
@@ -16376,11 +16539,25 @@
           <t>https://www.amazon.in/dp/B0D8442XWC</t>
         </is>
       </c>
-      <c r="C556" t="inlineStr"/>
-      <c r="D556" t="inlineStr"/>
-      <c r="E556" t="inlineStr"/>
-      <c r="F556" t="inlineStr"/>
-      <c r="G556" t="inlineStr"/>
+      <c r="C556" t="n">
+        <v>4559</v>
+      </c>
+      <c r="D556" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E556" t="n">
+        <v>10</v>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H556" t="inlineStr"/>
     </row>
     <row r="557">
@@ -16394,11 +16571,25 @@
           <t>https://www.amazon.in/dp/B0D83ZSCJF</t>
         </is>
       </c>
-      <c r="C557" t="inlineStr"/>
-      <c r="D557" t="inlineStr"/>
-      <c r="E557" t="inlineStr"/>
-      <c r="F557" t="inlineStr"/>
-      <c r="G557" t="inlineStr"/>
+      <c r="C557" t="n">
+        <v>4559</v>
+      </c>
+      <c r="D557" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E557" t="n">
+        <v>10</v>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H557" t="inlineStr"/>
     </row>
     <row r="558">
@@ -16412,11 +16603,25 @@
           <t>https://www.amazon.in/dp/B0F2HKCHMX</t>
         </is>
       </c>
-      <c r="C558" t="inlineStr"/>
-      <c r="D558" t="inlineStr"/>
-      <c r="E558" t="inlineStr"/>
-      <c r="F558" t="inlineStr"/>
-      <c r="G558" t="inlineStr"/>
+      <c r="C558" t="n">
+        <v>4559</v>
+      </c>
+      <c r="D558" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E558" t="n">
+        <v>10</v>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H558" t="inlineStr"/>
     </row>
     <row r="559">
@@ -16430,11 +16635,25 @@
           <t>https://www.amazon.in/dp/B0F5WZ23CL</t>
         </is>
       </c>
-      <c r="C559" t="inlineStr"/>
-      <c r="D559" t="inlineStr"/>
-      <c r="E559" t="inlineStr"/>
-      <c r="F559" t="inlineStr"/>
-      <c r="G559" t="inlineStr"/>
+      <c r="C559" t="n">
+        <v>4559</v>
+      </c>
+      <c r="D559" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E559" t="n">
+        <v>10</v>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H559" t="inlineStr"/>
     </row>
     <row r="560">
@@ -16448,11 +16667,25 @@
           <t>https://www.amazon.in/dp/B0D842S3YP</t>
         </is>
       </c>
-      <c r="C560" t="inlineStr"/>
-      <c r="D560" t="inlineStr"/>
-      <c r="E560" t="inlineStr"/>
-      <c r="F560" t="inlineStr"/>
-      <c r="G560" t="inlineStr"/>
+      <c r="C560" t="n">
+        <v>4559</v>
+      </c>
+      <c r="D560" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E560" t="n">
+        <v>10</v>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H560" t="inlineStr"/>
     </row>
     <row r="561">
@@ -16466,11 +16699,25 @@
           <t>https://www.amazon.in/dp/B0F5WYCD5N</t>
         </is>
       </c>
-      <c r="C561" t="inlineStr"/>
-      <c r="D561" t="inlineStr"/>
-      <c r="E561" t="inlineStr"/>
-      <c r="F561" t="inlineStr"/>
-      <c r="G561" t="inlineStr"/>
+      <c r="C561" t="n">
+        <v>4559</v>
+      </c>
+      <c r="D561" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E561" t="n">
+        <v>10</v>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H561" t="inlineStr"/>
     </row>
     <row r="562">
@@ -16484,11 +16731,25 @@
           <t>https://www.amazon.in/dp/B0F2HM5RVC</t>
         </is>
       </c>
-      <c r="C562" t="inlineStr"/>
-      <c r="D562" t="inlineStr"/>
-      <c r="E562" t="inlineStr"/>
-      <c r="F562" t="inlineStr"/>
-      <c r="G562" t="inlineStr"/>
+      <c r="C562" t="n">
+        <v>4559</v>
+      </c>
+      <c r="D562" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E562" t="n">
+        <v>10</v>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H562" t="inlineStr"/>
     </row>
     <row r="563">
@@ -16502,11 +16763,25 @@
           <t>https://www.amazon.in/dp/B0FC6SLML5</t>
         </is>
       </c>
-      <c r="C563" t="inlineStr"/>
-      <c r="D563" t="inlineStr"/>
-      <c r="E563" t="inlineStr"/>
-      <c r="F563" t="inlineStr"/>
-      <c r="G563" t="inlineStr"/>
+      <c r="C563" t="n">
+        <v>10019</v>
+      </c>
+      <c r="D563" t="n">
+        <v>2</v>
+      </c>
+      <c r="E563" t="n">
+        <v>2</v>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H563" t="inlineStr"/>
     </row>
     <row r="564">
@@ -16520,11 +16795,25 @@
           <t>https://www.amazon.in/dp/B0FC6W6MCW</t>
         </is>
       </c>
-      <c r="C564" t="inlineStr"/>
-      <c r="D564" t="inlineStr"/>
-      <c r="E564" t="inlineStr"/>
-      <c r="F564" t="inlineStr"/>
-      <c r="G564" t="inlineStr"/>
+      <c r="C564" t="n">
+        <v>10019</v>
+      </c>
+      <c r="D564" t="n">
+        <v>2</v>
+      </c>
+      <c r="E564" t="n">
+        <v>2</v>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H564" t="inlineStr"/>
     </row>
     <row r="565">
@@ -16538,11 +16827,25 @@
           <t>https://www.amazon.in/dp/B0FC6Q89HX</t>
         </is>
       </c>
-      <c r="C565" t="inlineStr"/>
-      <c r="D565" t="inlineStr"/>
-      <c r="E565" t="inlineStr"/>
-      <c r="F565" t="inlineStr"/>
-      <c r="G565" t="inlineStr"/>
+      <c r="C565" t="n">
+        <v>10019</v>
+      </c>
+      <c r="D565" t="n">
+        <v>2</v>
+      </c>
+      <c r="E565" t="n">
+        <v>2</v>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H565" t="inlineStr"/>
     </row>
     <row r="566">
@@ -16556,11 +16859,25 @@
           <t>https://www.amazon.in/dp/B0FC6SL547</t>
         </is>
       </c>
-      <c r="C566" t="inlineStr"/>
-      <c r="D566" t="inlineStr"/>
-      <c r="E566" t="inlineStr"/>
-      <c r="F566" t="inlineStr"/>
-      <c r="G566" t="inlineStr"/>
+      <c r="C566" t="n">
+        <v>10019</v>
+      </c>
+      <c r="D566" t="n">
+        <v>2</v>
+      </c>
+      <c r="E566" t="n">
+        <v>2</v>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H566" t="inlineStr"/>
     </row>
     <row r="567">
@@ -16574,11 +16891,25 @@
           <t>https://www.amazon.in/dp/B0FC6TWK9Z</t>
         </is>
       </c>
-      <c r="C567" t="inlineStr"/>
-      <c r="D567" t="inlineStr"/>
-      <c r="E567" t="inlineStr"/>
-      <c r="F567" t="inlineStr"/>
-      <c r="G567" t="inlineStr"/>
+      <c r="C567" t="n">
+        <v>10019</v>
+      </c>
+      <c r="D567" t="n">
+        <v>2</v>
+      </c>
+      <c r="E567" t="n">
+        <v>2</v>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H567" t="inlineStr"/>
     </row>
     <row r="568">
@@ -16592,11 +16923,25 @@
           <t>https://www.amazon.in/dp/B0FC6W25SW</t>
         </is>
       </c>
-      <c r="C568" t="inlineStr"/>
-      <c r="D568" t="inlineStr"/>
-      <c r="E568" t="inlineStr"/>
-      <c r="F568" t="inlineStr"/>
-      <c r="G568" t="inlineStr"/>
+      <c r="C568" t="n">
+        <v>10019</v>
+      </c>
+      <c r="D568" t="n">
+        <v>2</v>
+      </c>
+      <c r="E568" t="n">
+        <v>2</v>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H568" t="inlineStr"/>
     </row>
     <row r="569">
@@ -16610,11 +16955,25 @@
           <t>https://www.amazon.in/dp/B0FC6VMX81</t>
         </is>
       </c>
-      <c r="C569" t="inlineStr"/>
-      <c r="D569" t="inlineStr"/>
-      <c r="E569" t="inlineStr"/>
-      <c r="F569" t="inlineStr"/>
-      <c r="G569" t="inlineStr"/>
+      <c r="C569" t="n">
+        <v>16569</v>
+      </c>
+      <c r="D569" t="n">
+        <v>2</v>
+      </c>
+      <c r="E569" t="n">
+        <v>2</v>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H569" t="inlineStr"/>
     </row>
     <row r="570">
@@ -16628,11 +16987,25 @@
           <t>https://www.amazon.in/dp/B0FC6TR4RZ</t>
         </is>
       </c>
-      <c r="C570" t="inlineStr"/>
-      <c r="D570" t="inlineStr"/>
-      <c r="E570" t="inlineStr"/>
-      <c r="F570" t="inlineStr"/>
-      <c r="G570" t="inlineStr"/>
+      <c r="C570" t="n">
+        <v>16569</v>
+      </c>
+      <c r="D570" t="n">
+        <v>2</v>
+      </c>
+      <c r="E570" t="n">
+        <v>2</v>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H570" t="inlineStr"/>
     </row>
     <row r="571">
@@ -16646,11 +17019,25 @@
           <t>https://www.amazon.in/dp/B0FC6VBTRL</t>
         </is>
       </c>
-      <c r="C571" t="inlineStr"/>
-      <c r="D571" t="inlineStr"/>
-      <c r="E571" t="inlineStr"/>
-      <c r="F571" t="inlineStr"/>
-      <c r="G571" t="inlineStr"/>
+      <c r="C571" t="n">
+        <v>16569</v>
+      </c>
+      <c r="D571" t="n">
+        <v>2</v>
+      </c>
+      <c r="E571" t="n">
+        <v>2</v>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H571" t="inlineStr"/>
     </row>
     <row r="572">
@@ -16664,11 +17051,25 @@
           <t>https://www.amazon.in/dp/B0FC6VMX83</t>
         </is>
       </c>
-      <c r="C572" t="inlineStr"/>
-      <c r="D572" t="inlineStr"/>
-      <c r="E572" t="inlineStr"/>
-      <c r="F572" t="inlineStr"/>
-      <c r="G572" t="inlineStr"/>
+      <c r="C572" t="n">
+        <v>16569</v>
+      </c>
+      <c r="D572" t="n">
+        <v>2</v>
+      </c>
+      <c r="E572" t="n">
+        <v>2</v>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H572" t="inlineStr"/>
     </row>
     <row r="573">
@@ -16682,11 +17083,25 @@
           <t>https://www.amazon.in/dp/B0FC6RT4YW</t>
         </is>
       </c>
-      <c r="C573" t="inlineStr"/>
-      <c r="D573" t="inlineStr"/>
-      <c r="E573" t="inlineStr"/>
-      <c r="F573" t="inlineStr"/>
-      <c r="G573" t="inlineStr"/>
+      <c r="C573" t="n">
+        <v>16569</v>
+      </c>
+      <c r="D573" t="n">
+        <v>2</v>
+      </c>
+      <c r="E573" t="n">
+        <v>2</v>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H573" t="inlineStr"/>
     </row>
     <row r="574">
@@ -16700,11 +17115,25 @@
           <t>https://www.amazon.in/dp/B0FC6TTM3Z</t>
         </is>
       </c>
-      <c r="C574" t="inlineStr"/>
-      <c r="D574" t="inlineStr"/>
-      <c r="E574" t="inlineStr"/>
-      <c r="F574" t="inlineStr"/>
-      <c r="G574" t="inlineStr"/>
+      <c r="C574" t="n">
+        <v>16569</v>
+      </c>
+      <c r="D574" t="n">
+        <v>2</v>
+      </c>
+      <c r="E574" t="n">
+        <v>2</v>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H574" t="inlineStr"/>
     </row>
     <row r="575">
@@ -16718,11 +17147,25 @@
           <t>https://www.amazon.in/dp/B0D83YQR3J</t>
         </is>
       </c>
-      <c r="C575" t="inlineStr"/>
-      <c r="D575" t="inlineStr"/>
-      <c r="E575" t="inlineStr"/>
-      <c r="F575" t="inlineStr"/>
-      <c r="G575" t="inlineStr"/>
+      <c r="C575" t="n">
+        <v>5459</v>
+      </c>
+      <c r="D575" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E575" t="n">
+        <v>10</v>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H575" t="inlineStr"/>
     </row>
     <row r="576">
@@ -16736,11 +17179,25 @@
           <t>https://www.amazon.in/dp/B0D841LYMP</t>
         </is>
       </c>
-      <c r="C576" t="inlineStr"/>
-      <c r="D576" t="inlineStr"/>
-      <c r="E576" t="inlineStr"/>
-      <c r="F576" t="inlineStr"/>
-      <c r="G576" t="inlineStr"/>
+      <c r="C576" t="n">
+        <v>5459</v>
+      </c>
+      <c r="D576" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E576" t="n">
+        <v>10</v>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H576" t="inlineStr"/>
     </row>
     <row r="577">
@@ -16754,11 +17211,25 @@
           <t>https://www.amazon.in/dp/B0F2HHCGNH</t>
         </is>
       </c>
-      <c r="C577" t="inlineStr"/>
-      <c r="D577" t="inlineStr"/>
-      <c r="E577" t="inlineStr"/>
-      <c r="F577" t="inlineStr"/>
-      <c r="G577" t="inlineStr"/>
+      <c r="C577" t="n">
+        <v>5459</v>
+      </c>
+      <c r="D577" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E577" t="n">
+        <v>10</v>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H577" t="inlineStr"/>
     </row>
     <row r="578">
@@ -16772,11 +17243,25 @@
           <t>https://www.amazon.in/dp/B0F5X2DT96</t>
         </is>
       </c>
-      <c r="C578" t="inlineStr"/>
-      <c r="D578" t="inlineStr"/>
-      <c r="E578" t="inlineStr"/>
-      <c r="F578" t="inlineStr"/>
-      <c r="G578" t="inlineStr"/>
+      <c r="C578" t="n">
+        <v>5459</v>
+      </c>
+      <c r="D578" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E578" t="n">
+        <v>10</v>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H578" t="inlineStr"/>
     </row>
     <row r="579">
@@ -16790,11 +17275,25 @@
           <t>https://www.amazon.in/dp/B0D83YQGJV</t>
         </is>
       </c>
-      <c r="C579" t="inlineStr"/>
-      <c r="D579" t="inlineStr"/>
-      <c r="E579" t="inlineStr"/>
-      <c r="F579" t="inlineStr"/>
-      <c r="G579" t="inlineStr"/>
+      <c r="C579" t="n">
+        <v>5459</v>
+      </c>
+      <c r="D579" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E579" t="n">
+        <v>10</v>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H579" t="inlineStr"/>
     </row>
     <row r="580">
@@ -16808,11 +17307,25 @@
           <t>https://www.amazon.in/dp/B0F5WZ6T12</t>
         </is>
       </c>
-      <c r="C580" t="inlineStr"/>
-      <c r="D580" t="inlineStr"/>
-      <c r="E580" t="inlineStr"/>
-      <c r="F580" t="inlineStr"/>
-      <c r="G580" t="inlineStr"/>
+      <c r="C580" t="n">
+        <v>5459</v>
+      </c>
+      <c r="D580" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E580" t="n">
+        <v>10</v>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H580" t="inlineStr"/>
     </row>
     <row r="581">
@@ -16826,11 +17339,25 @@
           <t>https://www.amazon.in/dp/B0F2HL6DCT</t>
         </is>
       </c>
-      <c r="C581" t="inlineStr"/>
-      <c r="D581" t="inlineStr"/>
-      <c r="E581" t="inlineStr"/>
-      <c r="F581" t="inlineStr"/>
-      <c r="G581" t="inlineStr"/>
+      <c r="C581" t="n">
+        <v>5459</v>
+      </c>
+      <c r="D581" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E581" t="n">
+        <v>10</v>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H581" t="inlineStr"/>
     </row>
     <row r="582">
@@ -16844,11 +17371,25 @@
           <t>https://www.amazon.in/dp/B0D8426WKC</t>
         </is>
       </c>
-      <c r="C582" t="inlineStr"/>
-      <c r="D582" t="inlineStr"/>
-      <c r="E582" t="inlineStr"/>
-      <c r="F582" t="inlineStr"/>
-      <c r="G582" t="inlineStr"/>
+      <c r="C582" t="n">
+        <v>6549</v>
+      </c>
+      <c r="D582" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E582" t="n">
+        <v>10</v>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H582" t="inlineStr"/>
     </row>
     <row r="583">
@@ -16862,11 +17403,25 @@
           <t>https://www.amazon.in/dp/B0D49Q8LTK</t>
         </is>
       </c>
-      <c r="C583" t="inlineStr"/>
-      <c r="D583" t="inlineStr"/>
-      <c r="E583" t="inlineStr"/>
-      <c r="F583" t="inlineStr"/>
-      <c r="G583" t="inlineStr"/>
+      <c r="C583" t="n">
+        <v>6549</v>
+      </c>
+      <c r="D583" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E583" t="n">
+        <v>10</v>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H583" t="inlineStr"/>
     </row>
     <row r="584">
@@ -16880,11 +17435,25 @@
           <t>https://www.amazon.in/dp/B0F2HJPJJ8</t>
         </is>
       </c>
-      <c r="C584" t="inlineStr"/>
-      <c r="D584" t="inlineStr"/>
-      <c r="E584" t="inlineStr"/>
-      <c r="F584" t="inlineStr"/>
-      <c r="G584" t="inlineStr"/>
+      <c r="C584" t="n">
+        <v>6549</v>
+      </c>
+      <c r="D584" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E584" t="n">
+        <v>10</v>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H584" t="inlineStr"/>
     </row>
     <row r="585">
@@ -16898,11 +17467,25 @@
           <t>https://www.amazon.in/dp/B0F5WYGDMC</t>
         </is>
       </c>
-      <c r="C585" t="inlineStr"/>
-      <c r="D585" t="inlineStr"/>
-      <c r="E585" t="inlineStr"/>
-      <c r="F585" t="inlineStr"/>
-      <c r="G585" t="inlineStr"/>
+      <c r="C585" t="n">
+        <v>6549</v>
+      </c>
+      <c r="D585" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E585" t="n">
+        <v>10</v>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H585" t="inlineStr"/>
     </row>
     <row r="586">
@@ -16916,11 +17499,25 @@
           <t>https://www.amazon.in/dp/B0D83ZZZGC</t>
         </is>
       </c>
-      <c r="C586" t="inlineStr"/>
-      <c r="D586" t="inlineStr"/>
-      <c r="E586" t="inlineStr"/>
-      <c r="F586" t="inlineStr"/>
-      <c r="G586" t="inlineStr"/>
+      <c r="C586" t="n">
+        <v>6549</v>
+      </c>
+      <c r="D586" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E586" t="n">
+        <v>10</v>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H586" t="inlineStr"/>
     </row>
     <row r="587">
@@ -16934,11 +17531,25 @@
           <t>https://www.amazon.in/dp/B0F5WVGCLY</t>
         </is>
       </c>
-      <c r="C587" t="inlineStr"/>
-      <c r="D587" t="inlineStr"/>
-      <c r="E587" t="inlineStr"/>
-      <c r="F587" t="inlineStr"/>
-      <c r="G587" t="inlineStr"/>
+      <c r="C587" t="n">
+        <v>6549</v>
+      </c>
+      <c r="D587" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E587" t="n">
+        <v>10</v>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H587" t="inlineStr"/>
     </row>
     <row r="588">
@@ -16952,11 +17563,25 @@
           <t>https://www.amazon.in/dp/B0F2HJK84B</t>
         </is>
       </c>
-      <c r="C588" t="inlineStr"/>
-      <c r="D588" t="inlineStr"/>
-      <c r="E588" t="inlineStr"/>
-      <c r="F588" t="inlineStr"/>
-      <c r="G588" t="inlineStr"/>
+      <c r="C588" t="n">
+        <v>6549</v>
+      </c>
+      <c r="D588" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E588" t="n">
+        <v>10</v>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H588" t="inlineStr"/>
     </row>
     <row r="589">
@@ -16971,10 +17596,26 @@
         </is>
       </c>
       <c r="C589" t="inlineStr"/>
-      <c r="D589" t="inlineStr"/>
-      <c r="E589" t="inlineStr"/>
-      <c r="F589" t="inlineStr"/>
-      <c r="G589" t="inlineStr"/>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H589" t="inlineStr"/>
     </row>
     <row r="590">
@@ -16989,10 +17630,26 @@
         </is>
       </c>
       <c r="C590" t="inlineStr"/>
-      <c r="D590" t="inlineStr"/>
-      <c r="E590" t="inlineStr"/>
-      <c r="F590" t="inlineStr"/>
-      <c r="G590" t="inlineStr"/>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H590" t="inlineStr"/>
     </row>
     <row r="591">
@@ -17007,10 +17664,26 @@
         </is>
       </c>
       <c r="C591" t="inlineStr"/>
-      <c r="D591" t="inlineStr"/>
-      <c r="E591" t="inlineStr"/>
-      <c r="F591" t="inlineStr"/>
-      <c r="G591" t="inlineStr"/>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H591" t="inlineStr"/>
     </row>
     <row r="592">
@@ -17024,11 +17697,25 @@
           <t>https://www.amazon.in/dp/B0F32P56NW</t>
         </is>
       </c>
-      <c r="C592" t="inlineStr"/>
-      <c r="D592" t="inlineStr"/>
-      <c r="E592" t="inlineStr"/>
-      <c r="F592" t="inlineStr"/>
-      <c r="G592" t="inlineStr"/>
+      <c r="C592" t="n">
+        <v>2999</v>
+      </c>
+      <c r="D592" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E592" t="n">
+        <v>2</v>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>See all buying options</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H592" t="inlineStr"/>
     </row>
     <row r="593">
@@ -17042,11 +17729,25 @@
           <t>https://www.amazon.in/dp/B0D9S32K3F</t>
         </is>
       </c>
-      <c r="C593" t="inlineStr"/>
-      <c r="D593" t="inlineStr"/>
-      <c r="E593" t="inlineStr"/>
-      <c r="F593" t="inlineStr"/>
-      <c r="G593" t="inlineStr"/>
+      <c r="C593" t="n">
+        <v>5459</v>
+      </c>
+      <c r="D593" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E593" t="n">
+        <v>6</v>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H593" t="inlineStr"/>
     </row>
     <row r="594">
@@ -17060,11 +17761,25 @@
           <t>https://www.amazon.in/dp/B0FC6518JC</t>
         </is>
       </c>
-      <c r="C594" t="inlineStr"/>
-      <c r="D594" t="inlineStr"/>
-      <c r="E594" t="inlineStr"/>
-      <c r="F594" t="inlineStr"/>
-      <c r="G594" t="inlineStr"/>
+      <c r="C594" t="n">
+        <v>11879</v>
+      </c>
+      <c r="D594" t="n">
+        <v>5</v>
+      </c>
+      <c r="E594" t="n">
+        <v>1</v>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H594" t="inlineStr"/>
     </row>
     <row r="595">
@@ -17078,11 +17793,29 @@
           <t>https://www.amazon.in/dp/B0FC62MSYH</t>
         </is>
       </c>
-      <c r="C595" t="inlineStr"/>
-      <c r="D595" t="inlineStr"/>
-      <c r="E595" t="inlineStr"/>
-      <c r="F595" t="inlineStr"/>
-      <c r="G595" t="inlineStr"/>
+      <c r="C595" t="n">
+        <v>4499</v>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H595" t="inlineStr"/>
     </row>
     <row r="596">
@@ -17096,11 +17829,29 @@
           <t>https://www.amazon.in/dp/B0FC62NWYJ</t>
         </is>
       </c>
-      <c r="C596" t="inlineStr"/>
-      <c r="D596" t="inlineStr"/>
-      <c r="E596" t="inlineStr"/>
-      <c r="F596" t="inlineStr"/>
-      <c r="G596" t="inlineStr"/>
+      <c r="C596" t="n">
+        <v>11879</v>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H596" t="inlineStr"/>
     </row>
     <row r="597">
@@ -17114,11 +17865,25 @@
           <t>https://www.amazon.in/dp/B0D37WWZX8</t>
         </is>
       </c>
-      <c r="C597" t="inlineStr"/>
-      <c r="D597" t="inlineStr"/>
-      <c r="E597" t="inlineStr"/>
-      <c r="F597" t="inlineStr"/>
-      <c r="G597" t="inlineStr"/>
+      <c r="C597" t="n">
+        <v>19269</v>
+      </c>
+      <c r="D597" t="n">
+        <v>3</v>
+      </c>
+      <c r="E597" t="n">
+        <v>1</v>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H597" t="inlineStr"/>
     </row>
     <row r="598">
@@ -17132,11 +17897,25 @@
           <t>https://www.amazon.in/dp/B0D37Z96QL</t>
         </is>
       </c>
-      <c r="C598" t="inlineStr"/>
-      <c r="D598" t="inlineStr"/>
-      <c r="E598" t="inlineStr"/>
-      <c r="F598" t="inlineStr"/>
-      <c r="G598" t="inlineStr"/>
+      <c r="C598" t="n">
+        <v>19269</v>
+      </c>
+      <c r="D598" t="n">
+        <v>3</v>
+      </c>
+      <c r="E598" t="n">
+        <v>1</v>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H598" t="inlineStr"/>
     </row>
     <row r="599">
@@ -17150,11 +17929,25 @@
           <t>https://www.amazon.in/dp/B0D37ZL3RL</t>
         </is>
       </c>
-      <c r="C599" t="inlineStr"/>
-      <c r="D599" t="inlineStr"/>
-      <c r="E599" t="inlineStr"/>
-      <c r="F599" t="inlineStr"/>
-      <c r="G599" t="inlineStr"/>
+      <c r="C599" t="n">
+        <v>19269</v>
+      </c>
+      <c r="D599" t="n">
+        <v>3</v>
+      </c>
+      <c r="E599" t="n">
+        <v>1</v>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H599" t="inlineStr"/>
     </row>
     <row r="600">
@@ -17168,11 +17961,25 @@
           <t>https://www.amazon.in/dp/B0D3HH3GPF</t>
         </is>
       </c>
-      <c r="C600" t="inlineStr"/>
-      <c r="D600" t="inlineStr"/>
-      <c r="E600" t="inlineStr"/>
-      <c r="F600" t="inlineStr"/>
-      <c r="G600" t="inlineStr"/>
+      <c r="C600" t="n">
+        <v>5459</v>
+      </c>
+      <c r="D600" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E600" t="n">
+        <v>6</v>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>Only 3 left</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H600" t="inlineStr"/>
     </row>
     <row r="601">
@@ -17186,11 +17993,25 @@
           <t>https://www.amazon.in/dp/B0D9S1MN69</t>
         </is>
       </c>
-      <c r="C601" t="inlineStr"/>
-      <c r="D601" t="inlineStr"/>
-      <c r="E601" t="inlineStr"/>
-      <c r="F601" t="inlineStr"/>
-      <c r="G601" t="inlineStr"/>
+      <c r="C601" t="n">
+        <v>6429</v>
+      </c>
+      <c r="D601" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E601" t="n">
+        <v>6</v>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H601" t="inlineStr"/>
     </row>
     <row r="602">
@@ -17204,11 +18025,25 @@
           <t>https://www.amazon.in/dp/B0D9S2MND1</t>
         </is>
       </c>
-      <c r="C602" t="inlineStr"/>
-      <c r="D602" t="inlineStr"/>
-      <c r="E602" t="inlineStr"/>
-      <c r="F602" t="inlineStr"/>
-      <c r="G602" t="inlineStr"/>
+      <c r="C602" t="n">
+        <v>5459</v>
+      </c>
+      <c r="D602" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E602" t="n">
+        <v>6</v>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H602" t="inlineStr"/>
     </row>
     <row r="603">
@@ -17222,11 +18057,25 @@
           <t>https://www.amazon.in/dp/B0D9S2S3SV</t>
         </is>
       </c>
-      <c r="C603" t="inlineStr"/>
-      <c r="D603" t="inlineStr"/>
-      <c r="E603" t="inlineStr"/>
-      <c r="F603" t="inlineStr"/>
-      <c r="G603" t="inlineStr"/>
+      <c r="C603" t="n">
+        <v>5459</v>
+      </c>
+      <c r="D603" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E603" t="n">
+        <v>6</v>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H603" t="inlineStr"/>
     </row>
     <row r="604">
@@ -17240,11 +18089,25 @@
           <t>https://www.amazon.in/dp/B0D3HD94L2</t>
         </is>
       </c>
-      <c r="C604" t="inlineStr"/>
-      <c r="D604" t="inlineStr"/>
-      <c r="E604" t="inlineStr"/>
-      <c r="F604" t="inlineStr"/>
-      <c r="G604" t="inlineStr"/>
+      <c r="C604" t="n">
+        <v>5459</v>
+      </c>
+      <c r="D604" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E604" t="n">
+        <v>6</v>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H604" t="inlineStr"/>
     </row>
     <row r="605">
@@ -17258,11 +18121,25 @@
           <t>https://www.amazon.in/dp/B0D3HFHNFQ</t>
         </is>
       </c>
-      <c r="C605" t="inlineStr"/>
-      <c r="D605" t="inlineStr"/>
-      <c r="E605" t="inlineStr"/>
-      <c r="F605" t="inlineStr"/>
-      <c r="G605" t="inlineStr"/>
+      <c r="C605" t="n">
+        <v>6429</v>
+      </c>
+      <c r="D605" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E605" t="n">
+        <v>6</v>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H605" t="inlineStr"/>
     </row>
     <row r="606">
@@ -17276,11 +18153,25 @@
           <t>https://www.amazon.in/dp/B0D9S3BBV1</t>
         </is>
       </c>
-      <c r="C606" t="inlineStr"/>
-      <c r="D606" t="inlineStr"/>
-      <c r="E606" t="inlineStr"/>
-      <c r="F606" t="inlineStr"/>
-      <c r="G606" t="inlineStr"/>
+      <c r="C606" t="n">
+        <v>7389</v>
+      </c>
+      <c r="D606" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E606" t="n">
+        <v>6</v>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H606" t="inlineStr"/>
     </row>
     <row r="607">
@@ -17294,11 +18185,25 @@
           <t>https://www.amazon.in/dp/B0F7RNZL52</t>
         </is>
       </c>
-      <c r="C607" t="inlineStr"/>
-      <c r="D607" t="inlineStr"/>
-      <c r="E607" t="inlineStr"/>
-      <c r="F607" t="inlineStr"/>
-      <c r="G607" t="inlineStr"/>
+      <c r="C607" t="n">
+        <v>3559</v>
+      </c>
+      <c r="D607" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E607" t="n">
+        <v>2</v>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H607" t="inlineStr"/>
     </row>
     <row r="608">
@@ -17312,11 +18217,25 @@
           <t>https://www.amazon.in/dp/B0F7RLLNBS</t>
         </is>
       </c>
-      <c r="C608" t="inlineStr"/>
-      <c r="D608" t="inlineStr"/>
-      <c r="E608" t="inlineStr"/>
-      <c r="F608" t="inlineStr"/>
-      <c r="G608" t="inlineStr"/>
+      <c r="C608" t="n">
+        <v>3559</v>
+      </c>
+      <c r="D608" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E608" t="n">
+        <v>2</v>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H608" t="inlineStr"/>
     </row>
     <row r="609">
@@ -17330,11 +18249,25 @@
           <t>https://www.amazon.in/dp/B0F7RHMSSF</t>
         </is>
       </c>
-      <c r="C609" t="inlineStr"/>
-      <c r="D609" t="inlineStr"/>
-      <c r="E609" t="inlineStr"/>
-      <c r="F609" t="inlineStr"/>
-      <c r="G609" t="inlineStr"/>
+      <c r="C609" t="n">
+        <v>3559</v>
+      </c>
+      <c r="D609" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E609" t="n">
+        <v>2</v>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H609" t="inlineStr"/>
     </row>
     <row r="610">
@@ -17348,11 +18281,25 @@
           <t>https://www.amazon.in/dp/B0F7RNLDTP</t>
         </is>
       </c>
-      <c r="C610" t="inlineStr"/>
-      <c r="D610" t="inlineStr"/>
-      <c r="E610" t="inlineStr"/>
-      <c r="F610" t="inlineStr"/>
-      <c r="G610" t="inlineStr"/>
+      <c r="C610" t="n">
+        <v>3559</v>
+      </c>
+      <c r="D610" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E610" t="n">
+        <v>2</v>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H610" t="inlineStr"/>
     </row>
     <row r="611">
@@ -17366,11 +18313,25 @@
           <t>https://www.amazon.in/dp/B0F7RT5F4W</t>
         </is>
       </c>
-      <c r="C611" t="inlineStr"/>
-      <c r="D611" t="inlineStr"/>
-      <c r="E611" t="inlineStr"/>
-      <c r="F611" t="inlineStr"/>
-      <c r="G611" t="inlineStr"/>
+      <c r="C611" t="n">
+        <v>13579</v>
+      </c>
+      <c r="D611" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E611" t="n">
+        <v>2</v>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H611" t="inlineStr"/>
     </row>
     <row r="612">
@@ -17384,11 +18345,25 @@
           <t>https://www.amazon.in/dp/B0F7RQ5JKB</t>
         </is>
       </c>
-      <c r="C612" t="inlineStr"/>
-      <c r="D612" t="inlineStr"/>
-      <c r="E612" t="inlineStr"/>
-      <c r="F612" t="inlineStr"/>
-      <c r="G612" t="inlineStr"/>
+      <c r="C612" t="n">
+        <v>13579</v>
+      </c>
+      <c r="D612" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E612" t="n">
+        <v>2</v>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H612" t="inlineStr"/>
     </row>
     <row r="613">
@@ -17402,11 +18377,25 @@
           <t>https://www.amazon.in/dp/B0F7RQKT51</t>
         </is>
       </c>
-      <c r="C613" t="inlineStr"/>
-      <c r="D613" t="inlineStr"/>
-      <c r="E613" t="inlineStr"/>
-      <c r="F613" t="inlineStr"/>
-      <c r="G613" t="inlineStr"/>
+      <c r="C613" t="n">
+        <v>3559</v>
+      </c>
+      <c r="D613" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E613" t="n">
+        <v>2</v>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H613" t="inlineStr"/>
     </row>
     <row r="614">
@@ -17420,11 +18409,25 @@
           <t>https://www.amazon.in/dp/B0F7RRSKH7</t>
         </is>
       </c>
-      <c r="C614" t="inlineStr"/>
-      <c r="D614" t="inlineStr"/>
-      <c r="E614" t="inlineStr"/>
-      <c r="F614" t="inlineStr"/>
-      <c r="G614" t="inlineStr"/>
+      <c r="C614" t="n">
+        <v>13579</v>
+      </c>
+      <c r="D614" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E614" t="n">
+        <v>2</v>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H614" t="inlineStr"/>
     </row>
     <row r="615">
@@ -17438,11 +18441,25 @@
           <t>https://www.amazon.in/dp/B0F7RKJMG8</t>
         </is>
       </c>
-      <c r="C615" t="inlineStr"/>
-      <c r="D615" t="inlineStr"/>
-      <c r="E615" t="inlineStr"/>
-      <c r="F615" t="inlineStr"/>
-      <c r="G615" t="inlineStr"/>
+      <c r="C615" t="n">
+        <v>4369</v>
+      </c>
+      <c r="D615" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E615" t="n">
+        <v>2</v>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H615" t="inlineStr"/>
     </row>
     <row r="616">
@@ -17456,11 +18473,25 @@
           <t>https://www.amazon.in/dp/B0F7RM7W3Z</t>
         </is>
       </c>
-      <c r="C616" t="inlineStr"/>
-      <c r="D616" t="inlineStr"/>
-      <c r="E616" t="inlineStr"/>
-      <c r="F616" t="inlineStr"/>
-      <c r="G616" t="inlineStr"/>
+      <c r="C616" t="n">
+        <v>4369</v>
+      </c>
+      <c r="D616" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E616" t="n">
+        <v>2</v>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H616" t="inlineStr"/>
     </row>
     <row r="617">
@@ -17474,11 +18505,25 @@
           <t>https://www.amazon.in/dp/B0F7RKVC46</t>
         </is>
       </c>
-      <c r="C617" t="inlineStr"/>
-      <c r="D617" t="inlineStr"/>
-      <c r="E617" t="inlineStr"/>
-      <c r="F617" t="inlineStr"/>
-      <c r="G617" t="inlineStr"/>
+      <c r="C617" t="n">
+        <v>4369</v>
+      </c>
+      <c r="D617" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E617" t="n">
+        <v>2</v>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H617" t="inlineStr"/>
     </row>
     <row r="618">
@@ -17492,11 +18537,25 @@
           <t>https://www.amazon.in/dp/B0F7RN37TG</t>
         </is>
       </c>
-      <c r="C618" t="inlineStr"/>
-      <c r="D618" t="inlineStr"/>
-      <c r="E618" t="inlineStr"/>
-      <c r="F618" t="inlineStr"/>
-      <c r="G618" t="inlineStr"/>
+      <c r="C618" t="n">
+        <v>3559</v>
+      </c>
+      <c r="D618" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E618" t="n">
+        <v>2</v>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H618" t="inlineStr"/>
     </row>
     <row r="619">
@@ -17510,11 +18569,25 @@
           <t>https://www.amazon.in/dp/B0F7RMZB1N</t>
         </is>
       </c>
-      <c r="C619" t="inlineStr"/>
-      <c r="D619" t="inlineStr"/>
-      <c r="E619" t="inlineStr"/>
-      <c r="F619" t="inlineStr"/>
-      <c r="G619" t="inlineStr"/>
+      <c r="C619" t="n">
+        <v>5669</v>
+      </c>
+      <c r="D619" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E619" t="n">
+        <v>2</v>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H619" t="inlineStr"/>
     </row>
     <row r="620">
@@ -17528,11 +18601,25 @@
           <t>https://www.amazon.in/dp/B0F7RKP9XP</t>
         </is>
       </c>
-      <c r="C620" t="inlineStr"/>
-      <c r="D620" t="inlineStr"/>
-      <c r="E620" t="inlineStr"/>
-      <c r="F620" t="inlineStr"/>
-      <c r="G620" t="inlineStr"/>
+      <c r="C620" t="n">
+        <v>5669</v>
+      </c>
+      <c r="D620" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E620" t="n">
+        <v>2</v>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H620" t="inlineStr"/>
     </row>
     <row r="621">
@@ -17546,11 +18633,25 @@
           <t>https://www.amazon.in/dp/B0F7RKD25Z</t>
         </is>
       </c>
-      <c r="C621" t="inlineStr"/>
-      <c r="D621" t="inlineStr"/>
-      <c r="E621" t="inlineStr"/>
-      <c r="F621" t="inlineStr"/>
-      <c r="G621" t="inlineStr"/>
+      <c r="C621" t="n">
+        <v>5669</v>
+      </c>
+      <c r="D621" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E621" t="n">
+        <v>2</v>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H621" t="inlineStr"/>
     </row>
     <row r="622">
@@ -17564,11 +18665,25 @@
           <t>https://www.amazon.in/dp/B0F7RMVP4S</t>
         </is>
       </c>
-      <c r="C622" t="inlineStr"/>
-      <c r="D622" t="inlineStr"/>
-      <c r="E622" t="inlineStr"/>
-      <c r="F622" t="inlineStr"/>
-      <c r="G622" t="inlineStr"/>
+      <c r="C622" t="n">
+        <v>5669</v>
+      </c>
+      <c r="D622" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E622" t="n">
+        <v>2</v>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>Only 2 left in stock.</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H622" t="inlineStr"/>
     </row>
     <row r="623">
@@ -17583,10 +18698,26 @@
         </is>
       </c>
       <c r="C623" t="inlineStr"/>
-      <c r="D623" t="inlineStr"/>
-      <c r="E623" t="inlineStr"/>
-      <c r="F623" t="inlineStr"/>
-      <c r="G623" t="inlineStr"/>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H623" t="inlineStr"/>
     </row>
     <row r="624">
@@ -17601,10 +18732,26 @@
         </is>
       </c>
       <c r="C624" t="inlineStr"/>
-      <c r="D624" t="inlineStr"/>
-      <c r="E624" t="inlineStr"/>
-      <c r="F624" t="inlineStr"/>
-      <c r="G624" t="inlineStr"/>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H624" t="inlineStr"/>
     </row>
     <row r="625">
@@ -17619,10 +18766,26 @@
         </is>
       </c>
       <c r="C625" t="inlineStr"/>
-      <c r="D625" t="inlineStr"/>
-      <c r="E625" t="inlineStr"/>
-      <c r="F625" t="inlineStr"/>
-      <c r="G625" t="inlineStr"/>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H625" t="inlineStr"/>
     </row>
     <row r="626">
@@ -17637,10 +18800,26 @@
         </is>
       </c>
       <c r="C626" t="inlineStr"/>
-      <c r="D626" t="inlineStr"/>
-      <c r="E626" t="inlineStr"/>
-      <c r="F626" t="inlineStr"/>
-      <c r="G626" t="inlineStr"/>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H626" t="inlineStr"/>
     </row>
     <row r="627">
@@ -17654,11 +18833,25 @@
           <t>https://www.amazon.in/dp/B0CL9SVH6Z</t>
         </is>
       </c>
-      <c r="C627" t="inlineStr"/>
-      <c r="D627" t="inlineStr"/>
-      <c r="E627" t="inlineStr"/>
-      <c r="F627" t="inlineStr"/>
-      <c r="G627" t="inlineStr"/>
+      <c r="C627" t="n">
+        <v>3269</v>
+      </c>
+      <c r="D627" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E627" t="n">
+        <v>8</v>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H627" t="inlineStr"/>
     </row>
     <row r="628">
@@ -17672,11 +18865,25 @@
           <t>https://www.amazon.in/dp/B0CKHJ21JP</t>
         </is>
       </c>
-      <c r="C628" t="inlineStr"/>
-      <c r="D628" t="inlineStr"/>
-      <c r="E628" t="inlineStr"/>
-      <c r="F628" t="inlineStr"/>
-      <c r="G628" t="inlineStr"/>
+      <c r="C628" t="n">
+        <v>3269</v>
+      </c>
+      <c r="D628" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E628" t="n">
+        <v>8</v>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H628" t="inlineStr"/>
     </row>
     <row r="629">
@@ -17691,10 +18898,26 @@
         </is>
       </c>
       <c r="C629" t="inlineStr"/>
-      <c r="D629" t="inlineStr"/>
-      <c r="E629" t="inlineStr"/>
-      <c r="F629" t="inlineStr"/>
-      <c r="G629" t="inlineStr"/>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H629" t="inlineStr"/>
     </row>
     <row r="630">
@@ -17708,11 +18931,29 @@
           <t>https://www.amazon.in/dp/B0F32TDYX4</t>
         </is>
       </c>
-      <c r="C630" t="inlineStr"/>
-      <c r="D630" t="inlineStr"/>
-      <c r="E630" t="inlineStr"/>
-      <c r="F630" t="inlineStr"/>
-      <c r="G630" t="inlineStr"/>
+      <c r="C630" t="n">
+        <v>3509</v>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>See all buying options</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H630" t="inlineStr"/>
     </row>
     <row r="631">
@@ -17727,10 +18968,26 @@
         </is>
       </c>
       <c r="C631" t="inlineStr"/>
-      <c r="D631" t="inlineStr"/>
-      <c r="E631" t="inlineStr"/>
-      <c r="F631" t="inlineStr"/>
-      <c r="G631" t="inlineStr"/>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H631" t="inlineStr"/>
     </row>
     <row r="632">
@@ -17745,10 +19002,26 @@
         </is>
       </c>
       <c r="C632" t="inlineStr"/>
-      <c r="D632" t="inlineStr"/>
-      <c r="E632" t="inlineStr"/>
-      <c r="F632" t="inlineStr"/>
-      <c r="G632" t="inlineStr"/>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H632" t="inlineStr"/>
     </row>
     <row r="633">
@@ -17762,11 +19035,25 @@
           <t>https://www.amazon.in/dp/B0CQK2VDPT</t>
         </is>
       </c>
-      <c r="C633" t="inlineStr"/>
-      <c r="D633" t="inlineStr"/>
-      <c r="E633" t="inlineStr"/>
-      <c r="F633" t="inlineStr"/>
-      <c r="G633" t="inlineStr"/>
+      <c r="C633" t="n">
+        <v>1229</v>
+      </c>
+      <c r="D633" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E633" t="n">
+        <v>3</v>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H633" t="inlineStr"/>
     </row>
     <row r="634">
@@ -17780,11 +19067,25 @@
           <t>https://www.amazon.in/dp/B0CVMXZT64</t>
         </is>
       </c>
-      <c r="C634" t="inlineStr"/>
-      <c r="D634" t="inlineStr"/>
-      <c r="E634" t="inlineStr"/>
-      <c r="F634" t="inlineStr"/>
-      <c r="G634" t="inlineStr"/>
+      <c r="C634" t="n">
+        <v>1659</v>
+      </c>
+      <c r="D634" t="n">
+        <v>5</v>
+      </c>
+      <c r="E634" t="n">
+        <v>1</v>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H634" t="inlineStr"/>
     </row>
     <row r="635">
@@ -17798,11 +19099,25 @@
           <t>https://www.amazon.in/dp/B0CTMTDR6D</t>
         </is>
       </c>
-      <c r="C635" t="inlineStr"/>
-      <c r="D635" t="inlineStr"/>
-      <c r="E635" t="inlineStr"/>
-      <c r="F635" t="inlineStr"/>
-      <c r="G635" t="inlineStr"/>
+      <c r="C635" t="n">
+        <v>1659</v>
+      </c>
+      <c r="D635" t="n">
+        <v>5</v>
+      </c>
+      <c r="E635" t="n">
+        <v>1</v>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H635" t="inlineStr"/>
     </row>
     <row r="636">
@@ -17816,11 +19131,25 @@
           <t>https://www.amazon.in/dp/B0CGM3ZZL9</t>
         </is>
       </c>
-      <c r="C636" t="inlineStr"/>
-      <c r="D636" t="inlineStr"/>
-      <c r="E636" t="inlineStr"/>
-      <c r="F636" t="inlineStr"/>
-      <c r="G636" t="inlineStr"/>
+      <c r="C636" t="n">
+        <v>1899</v>
+      </c>
+      <c r="D636" t="n">
+        <v>5</v>
+      </c>
+      <c r="E636" t="n">
+        <v>2</v>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H636" t="inlineStr"/>
     </row>
     <row r="637">
@@ -17834,11 +19163,29 @@
           <t>https://www.amazon.in/dp/B0CGM43L21</t>
         </is>
       </c>
-      <c r="C637" t="inlineStr"/>
-      <c r="D637" t="inlineStr"/>
-      <c r="E637" t="inlineStr"/>
-      <c r="F637" t="inlineStr"/>
-      <c r="G637" t="inlineStr"/>
+      <c r="C637" t="n">
+        <v>2049</v>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H637" t="inlineStr"/>
     </row>
     <row r="638">
@@ -17852,11 +19199,25 @@
           <t>https://www.amazon.in/dp/B0CLVLXR1S</t>
         </is>
       </c>
-      <c r="C638" t="inlineStr"/>
-      <c r="D638" t="inlineStr"/>
-      <c r="E638" t="inlineStr"/>
-      <c r="F638" t="inlineStr"/>
-      <c r="G638" t="inlineStr"/>
+      <c r="C638" t="n">
+        <v>3529</v>
+      </c>
+      <c r="D638" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E638" t="n">
+        <v>4</v>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H638" t="inlineStr"/>
     </row>
     <row r="639">
@@ -17871,10 +19232,26 @@
         </is>
       </c>
       <c r="C639" t="inlineStr"/>
-      <c r="D639" t="inlineStr"/>
-      <c r="E639" t="inlineStr"/>
-      <c r="F639" t="inlineStr"/>
-      <c r="G639" t="inlineStr"/>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H639" t="inlineStr"/>
     </row>
     <row r="640">
@@ -17889,10 +19266,26 @@
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
-      <c r="D640" t="inlineStr"/>
-      <c r="E640" t="inlineStr"/>
-      <c r="F640" t="inlineStr"/>
-      <c r="G640" t="inlineStr"/>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H640" t="inlineStr"/>
     </row>
     <row r="641">
@@ -17906,11 +19299,25 @@
           <t>https://www.amazon.in/dp/B0CLVMSCZ9</t>
         </is>
       </c>
-      <c r="C641" t="inlineStr"/>
-      <c r="D641" t="inlineStr"/>
-      <c r="E641" t="inlineStr"/>
-      <c r="F641" t="inlineStr"/>
-      <c r="G641" t="inlineStr"/>
+      <c r="C641" t="n">
+        <v>3529</v>
+      </c>
+      <c r="D641" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E641" t="n">
+        <v>4</v>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H641" t="inlineStr"/>
     </row>
     <row r="642">
@@ -17925,10 +19332,26 @@
         </is>
       </c>
       <c r="C642" t="inlineStr"/>
-      <c r="D642" t="inlineStr"/>
-      <c r="E642" t="inlineStr"/>
-      <c r="F642" t="inlineStr"/>
-      <c r="G642" t="inlineStr"/>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H642" t="inlineStr"/>
     </row>
     <row r="643">
@@ -17943,10 +19366,26 @@
         </is>
       </c>
       <c r="C643" t="inlineStr"/>
-      <c r="D643" t="inlineStr"/>
-      <c r="E643" t="inlineStr"/>
-      <c r="F643" t="inlineStr"/>
-      <c r="G643" t="inlineStr"/>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H643" t="inlineStr"/>
     </row>
     <row r="644">
@@ -17960,11 +19399,25 @@
           <t>https://www.amazon.in/dp/B0CLVNN9FL</t>
         </is>
       </c>
-      <c r="C644" t="inlineStr"/>
-      <c r="D644" t="inlineStr"/>
-      <c r="E644" t="inlineStr"/>
-      <c r="F644" t="inlineStr"/>
-      <c r="G644" t="inlineStr"/>
+      <c r="C644" t="n">
+        <v>3529</v>
+      </c>
+      <c r="D644" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E644" t="n">
+        <v>4</v>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>Only 2 left in stock.</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H644" t="inlineStr"/>
     </row>
     <row r="645">
@@ -17979,10 +19432,26 @@
         </is>
       </c>
       <c r="C645" t="inlineStr"/>
-      <c r="D645" t="inlineStr"/>
-      <c r="E645" t="inlineStr"/>
-      <c r="F645" t="inlineStr"/>
-      <c r="G645" t="inlineStr"/>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H645" t="inlineStr"/>
     </row>
     <row r="646">
@@ -17997,10 +19466,26 @@
         </is>
       </c>
       <c r="C646" t="inlineStr"/>
-      <c r="D646" t="inlineStr"/>
-      <c r="E646" t="inlineStr"/>
-      <c r="F646" t="inlineStr"/>
-      <c r="G646" t="inlineStr"/>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H646" t="inlineStr"/>
     </row>
     <row r="647">
@@ -18015,10 +19500,26 @@
         </is>
       </c>
       <c r="C647" t="inlineStr"/>
-      <c r="D647" t="inlineStr"/>
-      <c r="E647" t="inlineStr"/>
-      <c r="F647" t="inlineStr"/>
-      <c r="G647" t="inlineStr"/>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H647" t="inlineStr"/>
     </row>
     <row r="648">
@@ -18033,10 +19534,26 @@
         </is>
       </c>
       <c r="C648" t="inlineStr"/>
-      <c r="D648" t="inlineStr"/>
-      <c r="E648" t="inlineStr"/>
-      <c r="F648" t="inlineStr"/>
-      <c r="G648" t="inlineStr"/>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H648" t="inlineStr"/>
     </row>
     <row r="649">
@@ -18051,10 +19568,26 @@
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
-      <c r="D649" t="inlineStr"/>
-      <c r="E649" t="inlineStr"/>
-      <c r="F649" t="inlineStr"/>
-      <c r="G649" t="inlineStr"/>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H649" t="inlineStr"/>
     </row>
     <row r="650">
@@ -18069,10 +19602,26 @@
         </is>
       </c>
       <c r="C650" t="inlineStr"/>
-      <c r="D650" t="inlineStr"/>
-      <c r="E650" t="inlineStr"/>
-      <c r="F650" t="inlineStr"/>
-      <c r="G650" t="inlineStr"/>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H650" t="inlineStr"/>
     </row>
     <row r="651">
@@ -18087,10 +19636,26 @@
         </is>
       </c>
       <c r="C651" t="inlineStr"/>
-      <c r="D651" t="inlineStr"/>
-      <c r="E651" t="inlineStr"/>
-      <c r="F651" t="inlineStr"/>
-      <c r="G651" t="inlineStr"/>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H651" t="inlineStr"/>
     </row>
     <row r="652">
@@ -18105,10 +19670,26 @@
         </is>
       </c>
       <c r="C652" t="inlineStr"/>
-      <c r="D652" t="inlineStr"/>
-      <c r="E652" t="inlineStr"/>
-      <c r="F652" t="inlineStr"/>
-      <c r="G652" t="inlineStr"/>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H652" t="inlineStr"/>
     </row>
     <row r="653">
@@ -18123,10 +19704,26 @@
         </is>
       </c>
       <c r="C653" t="inlineStr"/>
-      <c r="D653" t="inlineStr"/>
-      <c r="E653" t="inlineStr"/>
-      <c r="F653" t="inlineStr"/>
-      <c r="G653" t="inlineStr"/>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H653" t="inlineStr"/>
     </row>
     <row r="654">
@@ -18140,11 +19737,29 @@
           <t>https://www.amazon.in/dp/B0F6N46HJ7</t>
         </is>
       </c>
-      <c r="C654" t="inlineStr"/>
-      <c r="D654" t="inlineStr"/>
-      <c r="E654" t="inlineStr"/>
-      <c r="F654" t="inlineStr"/>
-      <c r="G654" t="inlineStr"/>
+      <c r="C654" t="n">
+        <v>3479</v>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H654" t="inlineStr"/>
     </row>
     <row r="655">
@@ -18158,11 +19773,29 @@
           <t>https://www.amazon.in/dp/B0F6MYLDXR</t>
         </is>
       </c>
-      <c r="C655" t="inlineStr"/>
-      <c r="D655" t="inlineStr"/>
-      <c r="E655" t="inlineStr"/>
-      <c r="F655" t="inlineStr"/>
-      <c r="G655" t="inlineStr"/>
+      <c r="C655" t="n">
+        <v>3479</v>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H655" t="inlineStr"/>
     </row>
     <row r="656">
@@ -18176,11 +19809,29 @@
           <t>https://www.amazon.in/dp/B0F7RMZKQX</t>
         </is>
       </c>
-      <c r="C656" t="inlineStr"/>
-      <c r="D656" t="inlineStr"/>
-      <c r="E656" t="inlineStr"/>
-      <c r="F656" t="inlineStr"/>
-      <c r="G656" t="inlineStr"/>
+      <c r="C656" t="n">
+        <v>3479</v>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H656" t="inlineStr"/>
     </row>
     <row r="657">
@@ -18194,11 +19845,25 @@
           <t>https://www.amazon.in/dp/B0DRD24VF7</t>
         </is>
       </c>
-      <c r="C657" t="inlineStr"/>
-      <c r="D657" t="inlineStr"/>
-      <c r="E657" t="inlineStr"/>
-      <c r="F657" t="inlineStr"/>
-      <c r="G657" t="inlineStr"/>
+      <c r="C657" t="n">
+        <v>1449</v>
+      </c>
+      <c r="D657" t="n">
+        <v>5</v>
+      </c>
+      <c r="E657" t="n">
+        <v>3</v>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H657" t="inlineStr"/>
     </row>
     <row r="658">
@@ -18212,11 +19877,25 @@
           <t>https://www.amazon.in/dp/B0DRD1PZQW</t>
         </is>
       </c>
-      <c r="C658" t="inlineStr"/>
-      <c r="D658" t="inlineStr"/>
-      <c r="E658" t="inlineStr"/>
-      <c r="F658" t="inlineStr"/>
-      <c r="G658" t="inlineStr"/>
+      <c r="C658" t="n">
+        <v>1449</v>
+      </c>
+      <c r="D658" t="n">
+        <v>5</v>
+      </c>
+      <c r="E658" t="n">
+        <v>3</v>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H658" t="inlineStr"/>
     </row>
     <row r="659">
@@ -18230,11 +19909,25 @@
           <t>https://www.amazon.in/dp/B0DRD44TFZ</t>
         </is>
       </c>
-      <c r="C659" t="inlineStr"/>
-      <c r="D659" t="inlineStr"/>
-      <c r="E659" t="inlineStr"/>
-      <c r="F659" t="inlineStr"/>
-      <c r="G659" t="inlineStr"/>
+      <c r="C659" t="n">
+        <v>1449</v>
+      </c>
+      <c r="D659" t="n">
+        <v>5</v>
+      </c>
+      <c r="E659" t="n">
+        <v>3</v>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H659" t="inlineStr"/>
     </row>
     <row r="660">
@@ -18249,10 +19942,26 @@
         </is>
       </c>
       <c r="C660" t="inlineStr"/>
-      <c r="D660" t="inlineStr"/>
-      <c r="E660" t="inlineStr"/>
-      <c r="F660" t="inlineStr"/>
-      <c r="G660" t="inlineStr"/>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H660" t="inlineStr"/>
     </row>
     <row r="661">
@@ -18266,11 +19975,29 @@
           <t>https://www.amazon.in/dp/B0F844QW9G</t>
         </is>
       </c>
-      <c r="C661" t="inlineStr"/>
-      <c r="D661" t="inlineStr"/>
-      <c r="E661" t="inlineStr"/>
-      <c r="F661" t="inlineStr"/>
-      <c r="G661" t="inlineStr"/>
+      <c r="C661" t="n">
+        <v>1292</v>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H661" t="inlineStr"/>
     </row>
     <row r="662">
@@ -18284,11 +20011,25 @@
           <t>https://www.amazon.in/dp/B0C77RVYLV</t>
         </is>
       </c>
-      <c r="C662" t="inlineStr"/>
-      <c r="D662" t="inlineStr"/>
-      <c r="E662" t="inlineStr"/>
-      <c r="F662" t="inlineStr"/>
-      <c r="G662" t="inlineStr"/>
+      <c r="C662" t="n">
+        <v>1799</v>
+      </c>
+      <c r="D662" t="n">
+        <v>3</v>
+      </c>
+      <c r="E662" t="n">
+        <v>4</v>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H662" t="inlineStr"/>
     </row>
     <row r="663">
@@ -18302,11 +20043,29 @@
           <t>https://www.amazon.in/dp/B0FH2KCSXF</t>
         </is>
       </c>
-      <c r="C663" t="inlineStr"/>
-      <c r="D663" t="inlineStr"/>
-      <c r="E663" t="inlineStr"/>
-      <c r="F663" t="inlineStr"/>
-      <c r="G663" t="inlineStr"/>
+      <c r="C663" t="n">
+        <v>4379</v>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H663" t="inlineStr"/>
     </row>
     <row r="664">
@@ -18320,11 +20079,29 @@
           <t>https://www.amazon.in/dp/B0FH2PM3JD</t>
         </is>
       </c>
-      <c r="C664" t="inlineStr"/>
-      <c r="D664" t="inlineStr"/>
-      <c r="E664" t="inlineStr"/>
-      <c r="F664" t="inlineStr"/>
-      <c r="G664" t="inlineStr"/>
+      <c r="C664" t="n">
+        <v>4379</v>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H664" t="inlineStr"/>
     </row>
     <row r="665">
@@ -18338,11 +20115,25 @@
           <t>https://www.amazon.in/dp/B0D7C89CW5</t>
         </is>
       </c>
-      <c r="C665" t="inlineStr"/>
-      <c r="D665" t="inlineStr"/>
-      <c r="E665" t="inlineStr"/>
-      <c r="F665" t="inlineStr"/>
-      <c r="G665" t="inlineStr"/>
+      <c r="C665" t="n">
+        <v>390</v>
+      </c>
+      <c r="D665" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E665" t="n">
+        <v>10</v>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H665" t="inlineStr"/>
     </row>
     <row r="666">
@@ -18356,11 +20147,25 @@
           <t>https://www.amazon.in/dp/B0CL4SKZMV</t>
         </is>
       </c>
-      <c r="C666" t="inlineStr"/>
-      <c r="D666" t="inlineStr"/>
-      <c r="E666" t="inlineStr"/>
-      <c r="F666" t="inlineStr"/>
-      <c r="G666" t="inlineStr"/>
+      <c r="C666" t="n">
+        <v>3418</v>
+      </c>
+      <c r="D666" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E666" t="n">
+        <v>11</v>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H666" t="inlineStr"/>
     </row>
     <row r="667">
@@ -18375,10 +20180,26 @@
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
-      <c r="D667" t="inlineStr"/>
-      <c r="E667" t="inlineStr"/>
-      <c r="F667" t="inlineStr"/>
-      <c r="G667" t="inlineStr"/>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H667" t="inlineStr"/>
     </row>
     <row r="668">
@@ -18392,11 +20213,25 @@
           <t>https://www.amazon.in/dp/B0DY7WCF9N</t>
         </is>
       </c>
-      <c r="C668" t="inlineStr"/>
-      <c r="D668" t="inlineStr"/>
-      <c r="E668" t="inlineStr"/>
-      <c r="F668" t="inlineStr"/>
-      <c r="G668" t="inlineStr"/>
+      <c r="C668" t="n">
+        <v>2609</v>
+      </c>
+      <c r="D668" t="n">
+        <v>4</v>
+      </c>
+      <c r="E668" t="n">
+        <v>31</v>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H668" t="inlineStr"/>
     </row>
     <row r="669">
@@ -18411,10 +20246,26 @@
         </is>
       </c>
       <c r="C669" t="inlineStr"/>
-      <c r="D669" t="inlineStr"/>
-      <c r="E669" t="inlineStr"/>
-      <c r="F669" t="inlineStr"/>
-      <c r="G669" t="inlineStr"/>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H669" t="inlineStr"/>
     </row>
     <row r="670">
@@ -18429,10 +20280,26 @@
         </is>
       </c>
       <c r="C670" t="inlineStr"/>
-      <c r="D670" t="inlineStr"/>
-      <c r="E670" t="inlineStr"/>
-      <c r="F670" t="inlineStr"/>
-      <c r="G670" t="inlineStr"/>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H670" t="inlineStr"/>
     </row>
     <row r="671">
@@ -18447,10 +20314,26 @@
         </is>
       </c>
       <c r="C671" t="inlineStr"/>
-      <c r="D671" t="inlineStr"/>
-      <c r="E671" t="inlineStr"/>
-      <c r="F671" t="inlineStr"/>
-      <c r="G671" t="inlineStr"/>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H671" t="inlineStr"/>
     </row>
     <row r="672">
@@ -18464,11 +20347,25 @@
           <t>https://www.amazon.in/dp/B0CKQVMVLF</t>
         </is>
       </c>
-      <c r="C672" t="inlineStr"/>
-      <c r="D672" t="inlineStr"/>
-      <c r="E672" t="inlineStr"/>
-      <c r="F672" t="inlineStr"/>
-      <c r="G672" t="inlineStr"/>
+      <c r="C672" t="n">
+        <v>3769</v>
+      </c>
+      <c r="D672" t="n">
+        <v>4</v>
+      </c>
+      <c r="E672" t="n">
+        <v>1</v>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H672" t="inlineStr"/>
     </row>
     <row r="673">
@@ -18482,11 +20379,25 @@
           <t>https://www.amazon.in/dp/B0CKQTY4C2</t>
         </is>
       </c>
-      <c r="C673" t="inlineStr"/>
-      <c r="D673" t="inlineStr"/>
-      <c r="E673" t="inlineStr"/>
-      <c r="F673" t="inlineStr"/>
-      <c r="G673" t="inlineStr"/>
+      <c r="C673" t="n">
+        <v>4329</v>
+      </c>
+      <c r="D673" t="n">
+        <v>4</v>
+      </c>
+      <c r="E673" t="n">
+        <v>1</v>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H673" t="inlineStr"/>
     </row>
     <row r="674">
@@ -18500,11 +20411,25 @@
           <t>https://www.amazon.in/dp/B0CKQVPRHC</t>
         </is>
       </c>
-      <c r="C674" t="inlineStr"/>
-      <c r="D674" t="inlineStr"/>
-      <c r="E674" t="inlineStr"/>
-      <c r="F674" t="inlineStr"/>
-      <c r="G674" t="inlineStr"/>
+      <c r="C674" t="n">
+        <v>4999</v>
+      </c>
+      <c r="D674" t="n">
+        <v>4</v>
+      </c>
+      <c r="E674" t="n">
+        <v>1</v>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H674" t="inlineStr"/>
     </row>
     <row r="675">
@@ -18518,11 +20443,25 @@
           <t>https://www.amazon.in/dp/B0CKQWW3ZD</t>
         </is>
       </c>
-      <c r="C675" t="inlineStr"/>
-      <c r="D675" t="inlineStr"/>
-      <c r="E675" t="inlineStr"/>
-      <c r="F675" t="inlineStr"/>
-      <c r="G675" t="inlineStr"/>
+      <c r="C675" t="n">
+        <v>3769</v>
+      </c>
+      <c r="D675" t="n">
+        <v>4</v>
+      </c>
+      <c r="E675" t="n">
+        <v>1</v>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H675" t="inlineStr"/>
     </row>
     <row r="676">
@@ -18537,10 +20476,26 @@
         </is>
       </c>
       <c r="C676" t="inlineStr"/>
-      <c r="D676" t="inlineStr"/>
-      <c r="E676" t="inlineStr"/>
-      <c r="F676" t="inlineStr"/>
-      <c r="G676" t="inlineStr"/>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H676" t="inlineStr"/>
     </row>
     <row r="677">
@@ -18554,11 +20509,25 @@
           <t>https://www.amazon.in/dp/B0CKQX87HD</t>
         </is>
       </c>
-      <c r="C677" t="inlineStr"/>
-      <c r="D677" t="inlineStr"/>
-      <c r="E677" t="inlineStr"/>
-      <c r="F677" t="inlineStr"/>
-      <c r="G677" t="inlineStr"/>
+      <c r="C677" t="n">
+        <v>4999</v>
+      </c>
+      <c r="D677" t="n">
+        <v>4</v>
+      </c>
+      <c r="E677" t="n">
+        <v>1</v>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>Only 1 left in stock.</t>
+        </is>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H677" t="inlineStr"/>
     </row>
     <row r="678">
@@ -18573,10 +20542,26 @@
         </is>
       </c>
       <c r="C678" t="inlineStr"/>
-      <c r="D678" t="inlineStr"/>
-      <c r="E678" t="inlineStr"/>
-      <c r="F678" t="inlineStr"/>
-      <c r="G678" t="inlineStr"/>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H678" t="inlineStr"/>
     </row>
     <row r="679">
@@ -18590,11 +20575,25 @@
           <t>https://www.amazon.in/dp/B0DRNXW57B</t>
         </is>
       </c>
-      <c r="C679" t="inlineStr"/>
-      <c r="D679" t="inlineStr"/>
-      <c r="E679" t="inlineStr"/>
-      <c r="F679" t="inlineStr"/>
-      <c r="G679" t="inlineStr"/>
+      <c r="C679" t="n">
+        <v>3759</v>
+      </c>
+      <c r="D679" t="n">
+        <v>4</v>
+      </c>
+      <c r="E679" t="n">
+        <v>25</v>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H679" t="inlineStr"/>
     </row>
     <row r="680">
@@ -18609,10 +20608,26 @@
         </is>
       </c>
       <c r="C680" t="inlineStr"/>
-      <c r="D680" t="inlineStr"/>
-      <c r="E680" t="inlineStr"/>
-      <c r="F680" t="inlineStr"/>
-      <c r="G680" t="inlineStr"/>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H680" t="inlineStr"/>
     </row>
     <row r="681">
@@ -18627,10 +20642,26 @@
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
-      <c r="D681" t="inlineStr"/>
-      <c r="E681" t="inlineStr"/>
-      <c r="F681" t="inlineStr"/>
-      <c r="G681" t="inlineStr"/>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H681" t="inlineStr"/>
     </row>
     <row r="682">
@@ -18645,10 +20676,26 @@
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
-      <c r="D682" t="inlineStr"/>
-      <c r="E682" t="inlineStr"/>
-      <c r="F682" t="inlineStr"/>
-      <c r="G682" t="inlineStr"/>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H682" t="inlineStr"/>
     </row>
     <row r="683">
@@ -18663,10 +20710,26 @@
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
-      <c r="D683" t="inlineStr"/>
-      <c r="E683" t="inlineStr"/>
-      <c r="F683" t="inlineStr"/>
-      <c r="G683" t="inlineStr"/>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H683" t="inlineStr"/>
     </row>
     <row r="684">
@@ -18681,10 +20744,26 @@
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
-      <c r="D684" t="inlineStr"/>
-      <c r="E684" t="inlineStr"/>
-      <c r="F684" t="inlineStr"/>
-      <c r="G684" t="inlineStr"/>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H684" t="inlineStr"/>
     </row>
     <row r="685">
@@ -18699,10 +20778,26 @@
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
-      <c r="D685" t="inlineStr"/>
-      <c r="E685" t="inlineStr"/>
-      <c r="F685" t="inlineStr"/>
-      <c r="G685" t="inlineStr"/>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H685" t="inlineStr"/>
     </row>
     <row r="686">
@@ -18716,11 +20811,25 @@
           <t>https://www.amazon.in/dp/B0CLRZZ3BV</t>
         </is>
       </c>
-      <c r="C686" t="inlineStr"/>
-      <c r="D686" t="inlineStr"/>
-      <c r="E686" t="inlineStr"/>
-      <c r="F686" t="inlineStr"/>
-      <c r="G686" t="inlineStr"/>
+      <c r="C686" t="n">
+        <v>3729</v>
+      </c>
+      <c r="D686" t="n">
+        <v>5</v>
+      </c>
+      <c r="E686" t="n">
+        <v>2</v>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>Only 2 left</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H686" t="inlineStr"/>
     </row>
     <row r="687">
@@ -18735,10 +20844,26 @@
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
-      <c r="D687" t="inlineStr"/>
-      <c r="E687" t="inlineStr"/>
-      <c r="F687" t="inlineStr"/>
-      <c r="G687" t="inlineStr"/>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H687" t="inlineStr"/>
     </row>
     <row r="688">
@@ -18752,11 +20877,25 @@
           <t>https://www.amazon.in/dp/B0CLRY4K2R</t>
         </is>
       </c>
-      <c r="C688" t="inlineStr"/>
-      <c r="D688" t="inlineStr"/>
-      <c r="E688" t="inlineStr"/>
-      <c r="F688" t="inlineStr"/>
-      <c r="G688" t="inlineStr"/>
+      <c r="C688" t="n">
+        <v>4809</v>
+      </c>
+      <c r="D688" t="n">
+        <v>5</v>
+      </c>
+      <c r="E688" t="n">
+        <v>2</v>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H688" t="inlineStr"/>
     </row>
     <row r="689">
@@ -18771,10 +20910,26 @@
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
-      <c r="D689" t="inlineStr"/>
-      <c r="E689" t="inlineStr"/>
-      <c r="F689" t="inlineStr"/>
-      <c r="G689" t="inlineStr"/>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H689" t="inlineStr"/>
     </row>
     <row r="690">
@@ -18789,10 +20944,26 @@
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
-      <c r="D690" t="inlineStr"/>
-      <c r="E690" t="inlineStr"/>
-      <c r="F690" t="inlineStr"/>
-      <c r="G690" t="inlineStr"/>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H690" t="inlineStr"/>
     </row>
     <row r="691">
@@ -18807,10 +20978,26 @@
         </is>
       </c>
       <c r="C691" t="inlineStr"/>
-      <c r="D691" t="inlineStr"/>
-      <c r="E691" t="inlineStr"/>
-      <c r="F691" t="inlineStr"/>
-      <c r="G691" t="inlineStr"/>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H691" t="inlineStr"/>
     </row>
     <row r="692">
@@ -18824,11 +21011,25 @@
           <t>https://www.amazon.in/dp/B07HHYCWDF</t>
         </is>
       </c>
-      <c r="C692" t="inlineStr"/>
-      <c r="D692" t="inlineStr"/>
-      <c r="E692" t="inlineStr"/>
-      <c r="F692" t="inlineStr"/>
-      <c r="G692" t="inlineStr"/>
+      <c r="C692" t="n">
+        <v>1569</v>
+      </c>
+      <c r="D692" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E692" t="n">
+        <v>168</v>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H692" t="inlineStr"/>
     </row>
     <row r="693">
@@ -18842,11 +21043,25 @@
           <t>https://www.amazon.in/dp/B07RTCQRB2</t>
         </is>
       </c>
-      <c r="C693" t="inlineStr"/>
-      <c r="D693" t="inlineStr"/>
-      <c r="E693" t="inlineStr"/>
-      <c r="F693" t="inlineStr"/>
-      <c r="G693" t="inlineStr"/>
+      <c r="C693" t="n">
+        <v>1569</v>
+      </c>
+      <c r="D693" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E693" t="n">
+        <v>168</v>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H693" t="inlineStr"/>
     </row>
     <row r="694">
@@ -18860,11 +21075,25 @@
           <t>https://www.amazon.in/dp/B09TH5Y64Q</t>
         </is>
       </c>
-      <c r="C694" t="inlineStr"/>
-      <c r="D694" t="inlineStr"/>
-      <c r="E694" t="inlineStr"/>
-      <c r="F694" t="inlineStr"/>
-      <c r="G694" t="inlineStr"/>
+      <c r="C694" t="n">
+        <v>5999</v>
+      </c>
+      <c r="D694" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E694" t="n">
+        <v>4</v>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H694" t="inlineStr"/>
     </row>
     <row r="695">
@@ -18878,11 +21107,25 @@
           <t>https://www.amazon.in/dp/B07HHYNHCY</t>
         </is>
       </c>
-      <c r="C695" t="inlineStr"/>
-      <c r="D695" t="inlineStr"/>
-      <c r="E695" t="inlineStr"/>
-      <c r="F695" t="inlineStr"/>
-      <c r="G695" t="inlineStr"/>
+      <c r="C695" t="n">
+        <v>1569</v>
+      </c>
+      <c r="D695" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E695" t="n">
+        <v>60</v>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H695" t="inlineStr"/>
     </row>
     <row r="696">
@@ -18896,11 +21139,25 @@
           <t>https://www.amazon.in/dp/B07RR5MH4L</t>
         </is>
       </c>
-      <c r="C696" t="inlineStr"/>
-      <c r="D696" t="inlineStr"/>
-      <c r="E696" t="inlineStr"/>
-      <c r="F696" t="inlineStr"/>
-      <c r="G696" t="inlineStr"/>
+      <c r="C696" t="n">
+        <v>1569</v>
+      </c>
+      <c r="D696" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E696" t="n">
+        <v>168</v>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H696" t="inlineStr"/>
     </row>
     <row r="697">
@@ -18914,11 +21171,25 @@
           <t>https://www.amazon.in/dp/B09TH2LRMN</t>
         </is>
       </c>
-      <c r="C697" t="inlineStr"/>
-      <c r="D697" t="inlineStr"/>
-      <c r="E697" t="inlineStr"/>
-      <c r="F697" t="inlineStr"/>
-      <c r="G697" t="inlineStr"/>
+      <c r="C697" t="n">
+        <v>2141</v>
+      </c>
+      <c r="D697" t="n">
+        <v>5</v>
+      </c>
+      <c r="E697" t="n">
+        <v>5</v>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H697" t="inlineStr"/>
     </row>
     <row r="698">
@@ -18932,11 +21203,29 @@
           <t>https://www.amazon.in/dp/B09SHGLXV3</t>
         </is>
       </c>
-      <c r="C698" t="inlineStr"/>
-      <c r="D698" t="inlineStr"/>
-      <c r="E698" t="inlineStr"/>
-      <c r="F698" t="inlineStr"/>
-      <c r="G698" t="inlineStr"/>
+      <c r="C698" t="n">
+        <v>1589</v>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>Only 5 left in stock.</t>
+        </is>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H698" t="inlineStr"/>
     </row>
     <row r="699">
@@ -18950,11 +21239,25 @@
           <t>https://www.amazon.in/dp/B0BL3SQ6V4</t>
         </is>
       </c>
-      <c r="C699" t="inlineStr"/>
-      <c r="D699" t="inlineStr"/>
-      <c r="E699" t="inlineStr"/>
-      <c r="F699" t="inlineStr"/>
-      <c r="G699" t="inlineStr"/>
+      <c r="C699" t="n">
+        <v>929</v>
+      </c>
+      <c r="D699" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E699" t="n">
+        <v>31</v>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H699" t="inlineStr"/>
     </row>
     <row r="700">
@@ -18968,11 +21271,25 @@
           <t>https://www.amazon.in/dp/B0BHW171CS</t>
         </is>
       </c>
-      <c r="C700" t="inlineStr"/>
-      <c r="D700" t="inlineStr"/>
-      <c r="E700" t="inlineStr"/>
-      <c r="F700" t="inlineStr"/>
-      <c r="G700" t="inlineStr"/>
+      <c r="C700" t="n">
+        <v>1859</v>
+      </c>
+      <c r="D700" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E700" t="n">
+        <v>3</v>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H700" t="inlineStr"/>
     </row>
     <row r="701">
@@ -18986,11 +21303,25 @@
           <t>https://www.amazon.in/dp/B0CKQWVVCC</t>
         </is>
       </c>
-      <c r="C701" t="inlineStr"/>
-      <c r="D701" t="inlineStr"/>
-      <c r="E701" t="inlineStr"/>
-      <c r="F701" t="inlineStr"/>
-      <c r="G701" t="inlineStr"/>
+      <c r="C701" t="n">
+        <v>3769</v>
+      </c>
+      <c r="D701" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E701" t="n">
+        <v>5</v>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H701" t="inlineStr"/>
     </row>
     <row r="702">
@@ -19004,11 +21335,25 @@
           <t>https://www.amazon.in/dp/B0CKQWDG3W</t>
         </is>
       </c>
-      <c r="C702" t="inlineStr"/>
-      <c r="D702" t="inlineStr"/>
-      <c r="E702" t="inlineStr"/>
-      <c r="F702" t="inlineStr"/>
-      <c r="G702" t="inlineStr"/>
+      <c r="C702" t="n">
+        <v>4329</v>
+      </c>
+      <c r="D702" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E702" t="n">
+        <v>5</v>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H702" t="inlineStr"/>
     </row>
     <row r="703">
@@ -19022,11 +21367,25 @@
           <t>https://www.amazon.in/dp/B0CKQX1W9R</t>
         </is>
       </c>
-      <c r="C703" t="inlineStr"/>
-      <c r="D703" t="inlineStr"/>
-      <c r="E703" t="inlineStr"/>
-      <c r="F703" t="inlineStr"/>
-      <c r="G703" t="inlineStr"/>
+      <c r="C703" t="n">
+        <v>3769</v>
+      </c>
+      <c r="D703" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E703" t="n">
+        <v>5</v>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H703" t="inlineStr"/>
     </row>
     <row r="704">
@@ -19041,10 +21400,26 @@
         </is>
       </c>
       <c r="C704" t="inlineStr"/>
-      <c r="D704" t="inlineStr"/>
-      <c r="E704" t="inlineStr"/>
-      <c r="F704" t="inlineStr"/>
-      <c r="G704" t="inlineStr"/>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H704" t="inlineStr"/>
     </row>
     <row r="705">
@@ -19058,11 +21433,25 @@
           <t>https://www.amazon.in/dp/B0F6NQ1Q5H</t>
         </is>
       </c>
-      <c r="C705" t="inlineStr"/>
-      <c r="D705" t="inlineStr"/>
-      <c r="E705" t="inlineStr"/>
-      <c r="F705" t="inlineStr"/>
-      <c r="G705" t="inlineStr"/>
+      <c r="C705" t="n">
+        <v>1889</v>
+      </c>
+      <c r="D705" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E705" t="n">
+        <v>50</v>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H705" t="inlineStr"/>
     </row>
     <row r="706">
@@ -19076,11 +21465,25 @@
           <t>https://www.amazon.in/dp/B0F6NNKTKM</t>
         </is>
       </c>
-      <c r="C706" t="inlineStr"/>
-      <c r="D706" t="inlineStr"/>
-      <c r="E706" t="inlineStr"/>
-      <c r="F706" t="inlineStr"/>
-      <c r="G706" t="inlineStr"/>
+      <c r="C706" t="n">
+        <v>1889</v>
+      </c>
+      <c r="D706" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E706" t="n">
+        <v>50</v>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H706" t="inlineStr"/>
     </row>
     <row r="707">
@@ -19094,11 +21497,25 @@
           <t>https://www.amazon.in/dp/B0F6NMFVLJ</t>
         </is>
       </c>
-      <c r="C707" t="inlineStr"/>
-      <c r="D707" t="inlineStr"/>
-      <c r="E707" t="inlineStr"/>
-      <c r="F707" t="inlineStr"/>
-      <c r="G707" t="inlineStr"/>
+      <c r="C707" t="n">
+        <v>1889</v>
+      </c>
+      <c r="D707" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E707" t="n">
+        <v>50</v>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H707" t="inlineStr"/>
     </row>
     <row r="708">
@@ -19112,11 +21529,25 @@
           <t>https://www.amazon.in/dp/B0F29BDSQL</t>
         </is>
       </c>
-      <c r="C708" t="inlineStr"/>
-      <c r="D708" t="inlineStr"/>
-      <c r="E708" t="inlineStr"/>
-      <c r="F708" t="inlineStr"/>
-      <c r="G708" t="inlineStr"/>
+      <c r="C708" t="n">
+        <v>2549</v>
+      </c>
+      <c r="D708" t="n">
+        <v>4</v>
+      </c>
+      <c r="E708" t="n">
+        <v>1</v>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H708" t="inlineStr"/>
     </row>
     <row r="709">
@@ -19131,10 +21562,26 @@
         </is>
       </c>
       <c r="C709" t="inlineStr"/>
-      <c r="D709" t="inlineStr"/>
-      <c r="E709" t="inlineStr"/>
-      <c r="F709" t="inlineStr"/>
-      <c r="G709" t="inlineStr"/>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H709" t="inlineStr"/>
     </row>
     <row r="710">
@@ -19148,11 +21595,25 @@
           <t>https://www.amazon.in/dp/B0F298BVBF</t>
         </is>
       </c>
-      <c r="C710" t="inlineStr"/>
-      <c r="D710" t="inlineStr"/>
-      <c r="E710" t="inlineStr"/>
-      <c r="F710" t="inlineStr"/>
-      <c r="G710" t="inlineStr"/>
+      <c r="C710" t="n">
+        <v>2549</v>
+      </c>
+      <c r="D710" t="n">
+        <v>4</v>
+      </c>
+      <c r="E710" t="n">
+        <v>1</v>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>Only 2 left in stock.</t>
+        </is>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H710" t="inlineStr"/>
     </row>
     <row r="711">
@@ -19166,11 +21627,25 @@
           <t>https://www.amazon.in/dp/B0CSDN31GF</t>
         </is>
       </c>
-      <c r="C711" t="inlineStr"/>
-      <c r="D711" t="inlineStr"/>
-      <c r="E711" t="inlineStr"/>
-      <c r="F711" t="inlineStr"/>
-      <c r="G711" t="inlineStr"/>
+      <c r="C711" t="n">
+        <v>2049</v>
+      </c>
+      <c r="D711" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E711" t="n">
+        <v>12</v>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H711" t="inlineStr"/>
     </row>
     <row r="712">
@@ -19185,10 +21660,26 @@
         </is>
       </c>
       <c r="C712" t="inlineStr"/>
-      <c r="D712" t="inlineStr"/>
-      <c r="E712" t="inlineStr"/>
-      <c r="F712" t="inlineStr"/>
-      <c r="G712" t="inlineStr"/>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H712" t="inlineStr"/>
     </row>
     <row r="713">
@@ -19202,11 +21693,25 @@
           <t>https://www.amazon.in/dp/B0DZNBZVLV</t>
         </is>
       </c>
-      <c r="C713" t="inlineStr"/>
-      <c r="D713" t="inlineStr"/>
-      <c r="E713" t="inlineStr"/>
-      <c r="F713" t="inlineStr"/>
-      <c r="G713" t="inlineStr"/>
+      <c r="C713" t="n">
+        <v>4079</v>
+      </c>
+      <c r="D713" t="n">
+        <v>4</v>
+      </c>
+      <c r="E713" t="n">
+        <v>59</v>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H713" t="inlineStr"/>
     </row>
     <row r="714">
@@ -19221,10 +21726,26 @@
         </is>
       </c>
       <c r="C714" t="inlineStr"/>
-      <c r="D714" t="inlineStr"/>
-      <c r="E714" t="inlineStr"/>
-      <c r="F714" t="inlineStr"/>
-      <c r="G714" t="inlineStr"/>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H714" t="inlineStr"/>
     </row>
     <row r="715">
@@ -19238,11 +21759,25 @@
           <t>https://www.amazon.in/dp/B079XX7MRD</t>
         </is>
       </c>
-      <c r="C715" t="inlineStr"/>
-      <c r="D715" t="inlineStr"/>
-      <c r="E715" t="inlineStr"/>
-      <c r="F715" t="inlineStr"/>
-      <c r="G715" t="inlineStr"/>
+      <c r="C715" t="n">
+        <v>829</v>
+      </c>
+      <c r="D715" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E715" t="n">
+        <v>289</v>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H715" t="inlineStr"/>
     </row>
     <row r="716">
@@ -19256,11 +21791,25 @@
           <t>https://www.amazon.in/dp/B079Y5KSJR</t>
         </is>
       </c>
-      <c r="C716" t="inlineStr"/>
-      <c r="D716" t="inlineStr"/>
-      <c r="E716" t="inlineStr"/>
-      <c r="F716" t="inlineStr"/>
-      <c r="G716" t="inlineStr"/>
+      <c r="C716" t="n">
+        <v>829</v>
+      </c>
+      <c r="D716" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E716" t="n">
+        <v>681</v>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H716" t="inlineStr"/>
     </row>
     <row r="717">
@@ -19274,11 +21823,25 @@
           <t>https://www.amazon.in/dp/B0C6XR6SJD</t>
         </is>
       </c>
-      <c r="C717" t="inlineStr"/>
-      <c r="D717" t="inlineStr"/>
-      <c r="E717" t="inlineStr"/>
-      <c r="F717" t="inlineStr"/>
-      <c r="G717" t="inlineStr"/>
+      <c r="C717" t="n">
+        <v>1309</v>
+      </c>
+      <c r="D717" t="n">
+        <v>1</v>
+      </c>
+      <c r="E717" t="n">
+        <v>2</v>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H717" t="inlineStr"/>
     </row>
     <row r="718">
@@ -19293,10 +21856,26 @@
         </is>
       </c>
       <c r="C718" t="inlineStr"/>
-      <c r="D718" t="inlineStr"/>
-      <c r="E718" t="inlineStr"/>
-      <c r="F718" t="inlineStr"/>
-      <c r="G718" t="inlineStr"/>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H718" t="inlineStr"/>
     </row>
     <row r="719">
@@ -19310,11 +21889,29 @@
           <t>https://www.amazon.in/dp/B0D7S7RX14</t>
         </is>
       </c>
-      <c r="C719" t="inlineStr"/>
-      <c r="D719" t="inlineStr"/>
-      <c r="E719" t="inlineStr"/>
-      <c r="F719" t="inlineStr"/>
-      <c r="G719" t="inlineStr"/>
+      <c r="C719" t="n">
+        <v>2379</v>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H719" t="inlineStr"/>
     </row>
     <row r="720">
@@ -19328,11 +21925,25 @@
           <t>https://www.amazon.in/dp/B0DD36LQDF</t>
         </is>
       </c>
-      <c r="C720" t="inlineStr"/>
-      <c r="D720" t="inlineStr"/>
-      <c r="E720" t="inlineStr"/>
-      <c r="F720" t="inlineStr"/>
-      <c r="G720" t="inlineStr"/>
+      <c r="C720" t="n">
+        <v>2879</v>
+      </c>
+      <c r="D720" t="n">
+        <v>4</v>
+      </c>
+      <c r="E720" t="n">
+        <v>107</v>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H720" t="inlineStr"/>
     </row>
     <row r="721">
@@ -19346,11 +21957,25 @@
           <t>https://www.amazon.in/dp/B0D9QLVN6W</t>
         </is>
       </c>
-      <c r="C721" t="inlineStr"/>
-      <c r="D721" t="inlineStr"/>
-      <c r="E721" t="inlineStr"/>
-      <c r="F721" t="inlineStr"/>
-      <c r="G721" t="inlineStr"/>
+      <c r="C721" t="n">
+        <v>2879</v>
+      </c>
+      <c r="D721" t="n">
+        <v>4</v>
+      </c>
+      <c r="E721" t="n">
+        <v>107</v>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H721" t="inlineStr"/>
     </row>
     <row r="722">
@@ -19364,11 +21989,25 @@
           <t>https://www.amazon.in/dp/B0D9QM33FW</t>
         </is>
       </c>
-      <c r="C722" t="inlineStr"/>
-      <c r="D722" t="inlineStr"/>
-      <c r="E722" t="inlineStr"/>
-      <c r="F722" t="inlineStr"/>
-      <c r="G722" t="inlineStr"/>
+      <c r="C722" t="n">
+        <v>2879</v>
+      </c>
+      <c r="D722" t="n">
+        <v>4</v>
+      </c>
+      <c r="E722" t="n">
+        <v>107</v>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H722" t="inlineStr"/>
     </row>
     <row r="723">
@@ -19382,11 +22021,25 @@
           <t>https://www.amazon.in/dp/B0DD3DCFLR</t>
         </is>
       </c>
-      <c r="C723" t="inlineStr"/>
-      <c r="D723" t="inlineStr"/>
-      <c r="E723" t="inlineStr"/>
-      <c r="F723" t="inlineStr"/>
-      <c r="G723" t="inlineStr"/>
+      <c r="C723" t="n">
+        <v>2879</v>
+      </c>
+      <c r="D723" t="n">
+        <v>4</v>
+      </c>
+      <c r="E723" t="n">
+        <v>107</v>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H723" t="inlineStr"/>
     </row>
     <row r="724">
@@ -19400,11 +22053,25 @@
           <t>https://www.amazon.in/dp/B0DD3F37JB</t>
         </is>
       </c>
-      <c r="C724" t="inlineStr"/>
-      <c r="D724" t="inlineStr"/>
-      <c r="E724" t="inlineStr"/>
-      <c r="F724" t="inlineStr"/>
-      <c r="G724" t="inlineStr"/>
+      <c r="C724" t="n">
+        <v>2879</v>
+      </c>
+      <c r="D724" t="n">
+        <v>4</v>
+      </c>
+      <c r="E724" t="n">
+        <v>107</v>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H724" t="inlineStr"/>
     </row>
     <row r="725">
@@ -19418,11 +22085,25 @@
           <t>https://www.amazon.in/dp/B0DD38FWFG</t>
         </is>
       </c>
-      <c r="C725" t="inlineStr"/>
-      <c r="D725" t="inlineStr"/>
-      <c r="E725" t="inlineStr"/>
-      <c r="F725" t="inlineStr"/>
-      <c r="G725" t="inlineStr"/>
+      <c r="C725" t="n">
+        <v>2879</v>
+      </c>
+      <c r="D725" t="n">
+        <v>4</v>
+      </c>
+      <c r="E725" t="n">
+        <v>107</v>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H725" t="inlineStr"/>
     </row>
     <row r="726">
@@ -19436,11 +22117,25 @@
           <t>https://www.amazon.in/dp/B0DR5DLKJK</t>
         </is>
       </c>
-      <c r="C726" t="inlineStr"/>
-      <c r="D726" t="inlineStr"/>
-      <c r="E726" t="inlineStr"/>
-      <c r="F726" t="inlineStr"/>
-      <c r="G726" t="inlineStr"/>
+      <c r="C726" t="n">
+        <v>2879</v>
+      </c>
+      <c r="D726" t="n">
+        <v>4</v>
+      </c>
+      <c r="E726" t="n">
+        <v>107</v>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H726" t="inlineStr"/>
     </row>
     <row r="727">
@@ -19454,11 +22149,25 @@
           <t>https://www.amazon.in/dp/B0DB1ST8RH</t>
         </is>
       </c>
-      <c r="C727" t="inlineStr"/>
-      <c r="D727" t="inlineStr"/>
-      <c r="E727" t="inlineStr"/>
-      <c r="F727" t="inlineStr"/>
-      <c r="G727" t="inlineStr"/>
+      <c r="C727" t="n">
+        <v>3369</v>
+      </c>
+      <c r="D727" t="n">
+        <v>1</v>
+      </c>
+      <c r="E727" t="n">
+        <v>1</v>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H727" t="inlineStr"/>
     </row>
     <row r="728">
@@ -19472,11 +22181,29 @@
           <t>https://www.amazon.in/dp/B0DHH33GW3</t>
         </is>
       </c>
-      <c r="C728" t="inlineStr"/>
-      <c r="D728" t="inlineStr"/>
-      <c r="E728" t="inlineStr"/>
-      <c r="F728" t="inlineStr"/>
-      <c r="G728" t="inlineStr"/>
+      <c r="C728" t="n">
+        <v>6729</v>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H728" t="inlineStr"/>
     </row>
     <row r="729">
@@ -19490,11 +22217,29 @@
           <t>https://www.amazon.in/dp/B0FC68MDW9</t>
         </is>
       </c>
-      <c r="C729" t="inlineStr"/>
-      <c r="D729" t="inlineStr"/>
-      <c r="E729" t="inlineStr"/>
-      <c r="F729" t="inlineStr"/>
-      <c r="G729" t="inlineStr"/>
+      <c r="C729" t="n">
+        <v>6729</v>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H729" t="inlineStr"/>
     </row>
     <row r="730">
@@ -19508,11 +22253,29 @@
           <t>https://www.amazon.in/dp/B0DHH5LBQ5</t>
         </is>
       </c>
-      <c r="C730" t="inlineStr"/>
-      <c r="D730" t="inlineStr"/>
-      <c r="E730" t="inlineStr"/>
-      <c r="F730" t="inlineStr"/>
-      <c r="G730" t="inlineStr"/>
+      <c r="C730" t="n">
+        <v>6729</v>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H730" t="inlineStr"/>
     </row>
     <row r="731">
@@ -19526,11 +22289,29 @@
           <t>https://www.amazon.in/dp/B0FC68C1SQ</t>
         </is>
       </c>
-      <c r="C731" t="inlineStr"/>
-      <c r="D731" t="inlineStr"/>
-      <c r="E731" t="inlineStr"/>
-      <c r="F731" t="inlineStr"/>
-      <c r="G731" t="inlineStr"/>
+      <c r="C731" t="n">
+        <v>14679</v>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>Only 2 left in stock.</t>
+        </is>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H731" t="inlineStr"/>
     </row>
     <row r="732">
@@ -19544,11 +22325,29 @@
           <t>https://www.amazon.in/dp/B0FC6BGWHJ</t>
         </is>
       </c>
-      <c r="C732" t="inlineStr"/>
-      <c r="D732" t="inlineStr"/>
-      <c r="E732" t="inlineStr"/>
-      <c r="F732" t="inlineStr"/>
-      <c r="G732" t="inlineStr"/>
+      <c r="C732" t="n">
+        <v>14679</v>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H732" t="inlineStr"/>
     </row>
     <row r="733">
@@ -19562,11 +22361,29 @@
           <t>https://www.amazon.in/dp/B0FC69P1YH</t>
         </is>
       </c>
-      <c r="C733" t="inlineStr"/>
-      <c r="D733" t="inlineStr"/>
-      <c r="E733" t="inlineStr"/>
-      <c r="F733" t="inlineStr"/>
-      <c r="G733" t="inlineStr"/>
+      <c r="C733" t="n">
+        <v>14679</v>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H733" t="inlineStr"/>
     </row>
     <row r="734">
@@ -19580,11 +22397,29 @@
           <t>https://www.amazon.in/dp/B0DHH52PMR</t>
         </is>
       </c>
-      <c r="C734" t="inlineStr"/>
-      <c r="D734" t="inlineStr"/>
-      <c r="E734" t="inlineStr"/>
-      <c r="F734" t="inlineStr"/>
-      <c r="G734" t="inlineStr"/>
+      <c r="C734" t="n">
+        <v>14679</v>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>Only 2 left in stock.</t>
+        </is>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H734" t="inlineStr"/>
     </row>
     <row r="735">
@@ -19598,11 +22433,29 @@
           <t>https://www.amazon.in/dp/B0FC68YBNM</t>
         </is>
       </c>
-      <c r="C735" t="inlineStr"/>
-      <c r="D735" t="inlineStr"/>
-      <c r="E735" t="inlineStr"/>
-      <c r="F735" t="inlineStr"/>
-      <c r="G735" t="inlineStr"/>
+      <c r="C735" t="n">
+        <v>23849</v>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H735" t="inlineStr"/>
     </row>
     <row r="736">
@@ -19616,11 +22469,29 @@
           <t>https://www.amazon.in/dp/B0DHH4BK2B</t>
         </is>
       </c>
-      <c r="C736" t="inlineStr"/>
-      <c r="D736" t="inlineStr"/>
-      <c r="E736" t="inlineStr"/>
-      <c r="F736" t="inlineStr"/>
-      <c r="G736" t="inlineStr"/>
+      <c r="C736" t="n">
+        <v>23849</v>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H736" t="inlineStr"/>
     </row>
     <row r="737">
@@ -19634,11 +22505,29 @@
           <t>https://www.amazon.in/dp/B0DHGYLBKF</t>
         </is>
       </c>
-      <c r="C737" t="inlineStr"/>
-      <c r="D737" t="inlineStr"/>
-      <c r="E737" t="inlineStr"/>
-      <c r="F737" t="inlineStr"/>
-      <c r="G737" t="inlineStr"/>
+      <c r="C737" t="n">
+        <v>7949</v>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>Only 2 left in stock.</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H737" t="inlineStr"/>
     </row>
     <row r="738">
@@ -19652,11 +22541,29 @@
           <t>https://www.amazon.in/dp/B0FC6DXL2H</t>
         </is>
       </c>
-      <c r="C738" t="inlineStr"/>
-      <c r="D738" t="inlineStr"/>
-      <c r="E738" t="inlineStr"/>
-      <c r="F738" t="inlineStr"/>
-      <c r="G738" t="inlineStr"/>
+      <c r="C738" t="n">
+        <v>7949</v>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H738" t="inlineStr"/>
     </row>
     <row r="739">
@@ -19670,11 +22577,29 @@
           <t>https://www.amazon.in/dp/B0DHH3P2WZ</t>
         </is>
       </c>
-      <c r="C739" t="inlineStr"/>
-      <c r="D739" t="inlineStr"/>
-      <c r="E739" t="inlineStr"/>
-      <c r="F739" t="inlineStr"/>
-      <c r="G739" t="inlineStr"/>
+      <c r="C739" t="n">
+        <v>7949</v>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H739" t="inlineStr"/>
     </row>
     <row r="740">
@@ -19688,11 +22613,29 @@
           <t>https://www.amazon.in/dp/B0DHH2HWVB</t>
         </is>
       </c>
-      <c r="C740" t="inlineStr"/>
-      <c r="D740" t="inlineStr"/>
-      <c r="E740" t="inlineStr"/>
-      <c r="F740" t="inlineStr"/>
-      <c r="G740" t="inlineStr"/>
+      <c r="C740" t="n">
+        <v>14679</v>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>Only 2 left in stock.</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H740" t="inlineStr"/>
     </row>
     <row r="741">
@@ -19706,11 +22649,29 @@
           <t>https://www.amazon.in/dp/B0FC6D146L</t>
         </is>
       </c>
-      <c r="C741" t="inlineStr"/>
-      <c r="D741" t="inlineStr"/>
-      <c r="E741" t="inlineStr"/>
-      <c r="F741" t="inlineStr"/>
-      <c r="G741" t="inlineStr"/>
+      <c r="C741" t="n">
+        <v>9179</v>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H741" t="inlineStr"/>
     </row>
     <row r="742">
@@ -19724,11 +22685,29 @@
           <t>https://www.amazon.in/dp/B0DHH3J9PG</t>
         </is>
       </c>
-      <c r="C742" t="inlineStr"/>
-      <c r="D742" t="inlineStr"/>
-      <c r="E742" t="inlineStr"/>
-      <c r="F742" t="inlineStr"/>
-      <c r="G742" t="inlineStr"/>
+      <c r="C742" t="n">
+        <v>9179</v>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>Only 1 left</t>
+        </is>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H742" t="inlineStr"/>
     </row>
     <row r="743">
@@ -19742,11 +22721,29 @@
           <t>https://www.amazon.in/dp/B0D7S5XF9G</t>
         </is>
       </c>
-      <c r="C743" t="inlineStr"/>
-      <c r="D743" t="inlineStr"/>
-      <c r="E743" t="inlineStr"/>
-      <c r="F743" t="inlineStr"/>
-      <c r="G743" t="inlineStr"/>
+      <c r="C743" t="n">
+        <v>3369</v>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H743" t="inlineStr"/>
     </row>
     <row r="744">
@@ -19761,10 +22758,26 @@
         </is>
       </c>
       <c r="C744" t="inlineStr"/>
-      <c r="D744" t="inlineStr"/>
-      <c r="E744" t="inlineStr"/>
-      <c r="F744" t="inlineStr"/>
-      <c r="G744" t="inlineStr"/>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H744" t="inlineStr"/>
     </row>
     <row r="745">
@@ -19778,11 +22791,25 @@
           <t>https://www.amazon.in/dp/B0974HWD4J</t>
         </is>
       </c>
-      <c r="C745" t="inlineStr"/>
-      <c r="D745" t="inlineStr"/>
-      <c r="E745" t="inlineStr"/>
-      <c r="F745" t="inlineStr"/>
-      <c r="G745" t="inlineStr"/>
+      <c r="C745" t="n">
+        <v>899</v>
+      </c>
+      <c r="D745" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E745" t="n">
+        <v>41</v>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H745" t="inlineStr"/>
     </row>
     <row r="746">
@@ -19796,11 +22823,25 @@
           <t>https://www.amazon.in/dp/B09D3NWQ74</t>
         </is>
       </c>
-      <c r="C746" t="inlineStr"/>
-      <c r="D746" t="inlineStr"/>
-      <c r="E746" t="inlineStr"/>
-      <c r="F746" t="inlineStr"/>
-      <c r="G746" t="inlineStr"/>
+      <c r="C746" t="n">
+        <v>600</v>
+      </c>
+      <c r="D746" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E746" t="n">
+        <v>11</v>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H746" t="inlineStr"/>
     </row>
     <row r="747">
@@ -19814,11 +22855,25 @@
           <t>https://www.amazon.in/dp/B0BD5MM9ZC</t>
         </is>
       </c>
-      <c r="C747" t="inlineStr"/>
-      <c r="D747" t="inlineStr"/>
-      <c r="E747" t="inlineStr"/>
-      <c r="F747" t="inlineStr"/>
-      <c r="G747" t="inlineStr"/>
+      <c r="C747" t="n">
+        <v>500</v>
+      </c>
+      <c r="D747" t="n">
+        <v>5</v>
+      </c>
+      <c r="E747" t="n">
+        <v>1</v>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H747" t="inlineStr"/>
     </row>
     <row r="748">
@@ -19832,11 +22887,25 @@
           <t>https://www.amazon.in/dp/B0BD5DXDJD</t>
         </is>
       </c>
-      <c r="C748" t="inlineStr"/>
-      <c r="D748" t="inlineStr"/>
-      <c r="E748" t="inlineStr"/>
-      <c r="F748" t="inlineStr"/>
-      <c r="G748" t="inlineStr"/>
+      <c r="C748" t="n">
+        <v>1309</v>
+      </c>
+      <c r="D748" t="n">
+        <v>2</v>
+      </c>
+      <c r="E748" t="n">
+        <v>2</v>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="H748" t="inlineStr"/>
     </row>
     <row r="749">
@@ -19854,8 +22923,29 @@
       <c r="D749" t="inlineStr"/>
       <c r="E749" t="inlineStr"/>
       <c r="F749" t="inlineStr"/>
-      <c r="G749" t="inlineStr"/>
-      <c r="H749" t="inlineStr"/>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="H749" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
+  (Session info: chrome=150.0.7871.114)
+Stacktrace:
+#0 0x55d0dfa8341a &lt;unknown&gt;
+#1 0x55d0df45b689 &lt;unknown&gt;
+#2 0x55d0df44321a &lt;unknown&gt;
+#3 0x55d0df442e96 &lt;unknown&gt;
+#4 0x55d0df440a7e &lt;unknown&gt;
+#5 0x55d0df4413ff &lt;unknown&gt;
+#6 0x55d0df4504e0 &lt;unknown&gt;
+#7 0x55d0df46a3e7 &lt;unknown&gt;
+#8 0x55d0df471c5b &lt;unknown&gt;
+#9 0x55d0df441b59 &lt;unknown&gt;
+</t>
+        </is>
+      </c>
     </row>
     <row r="750">
       <c r="A750" t="inlineStr">
@@ -19872,8 +22962,29 @@
       <c r="D750" t="inlineStr"/>
       <c r="E750" t="inlineStr"/>
       <c r="F750" t="inlineStr"/>
-      <c r="G750" t="inlineStr"/>
-      <c r="H750" t="inlineStr"/>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="H750" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
+  (Session info: chrome=150.0.7871.114)
+Stacktrace:
+#0 0x55d0dfa8341a &lt;unknown&gt;
+#1 0x55d0df45b689 &lt;unknown&gt;
+#2 0x55d0df44321a &lt;unknown&gt;
+#3 0x55d0df442e96 &lt;unknown&gt;
+#4 0x55d0df440a7e &lt;unknown&gt;
+#5 0x55d0df4413ff &lt;unknown&gt;
+#6 0x55d0df4504e0 &lt;unknown&gt;
+#7 0x55d0df46a3e7 &lt;unknown&gt;
+#8 0x55d0df471c5b &lt;unknown&gt;
+#9 0x55d0df441b59 &lt;unknown&gt;
+</t>
+        </is>
+      </c>
     </row>
     <row r="751">
       <c r="A751" t="inlineStr">
@@ -19890,8 +23001,29 @@
       <c r="D751" t="inlineStr"/>
       <c r="E751" t="inlineStr"/>
       <c r="F751" t="inlineStr"/>
-      <c r="G751" t="inlineStr"/>
-      <c r="H751" t="inlineStr"/>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="H751" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
+  (Session info: chrome=150.0.7871.114)
+Stacktrace:
+#0 0x55d0dfa8341a &lt;unknown&gt;
+#1 0x55d0df45b689 &lt;unknown&gt;
+#2 0x55d0df44321a &lt;unknown&gt;
+#3 0x55d0df442e96 &lt;unknown&gt;
+#4 0x55d0df440a7e &lt;unknown&gt;
+#5 0x55d0df4413ff &lt;unknown&gt;
+#6 0x55d0df4504e0 &lt;unknown&gt;
+#7 0x55d0df46a3e7 &lt;unknown&gt;
+#8 0x55d0df471c5b &lt;unknown&gt;
+#9 0x55d0df441b59 &lt;unknown&gt;
+</t>
+        </is>
+      </c>
     </row>
     <row r="752">
       <c r="A752" t="inlineStr">
@@ -19908,8 +23040,29 @@
       <c r="D752" t="inlineStr"/>
       <c r="E752" t="inlineStr"/>
       <c r="F752" t="inlineStr"/>
-      <c r="G752" t="inlineStr"/>
-      <c r="H752" t="inlineStr"/>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="H752" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
+  (Session info: chrome=150.0.7871.114)
+Stacktrace:
+#0 0x55d0dfa8341a &lt;unknown&gt;
+#1 0x55d0df45b689 &lt;unknown&gt;
+#2 0x55d0df44321a &lt;unknown&gt;
+#3 0x55d0df442e96 &lt;unknown&gt;
+#4 0x55d0df440a7e &lt;unknown&gt;
+#5 0x55d0df4413ff &lt;unknown&gt;
+#6 0x55d0df4504e0 &lt;unknown&gt;
+#7 0x55d0df46a3e7 &lt;unknown&gt;
+#8 0x55d0df471c5b &lt;unknown&gt;
+#9 0x55d0df441b59 &lt;unknown&gt;
+</t>
+        </is>
+      </c>
     </row>
     <row r="753">
       <c r="A753" t="inlineStr">
@@ -19926,8 +23079,29 @@
       <c r="D753" t="inlineStr"/>
       <c r="E753" t="inlineStr"/>
       <c r="F753" t="inlineStr"/>
-      <c r="G753" t="inlineStr"/>
-      <c r="H753" t="inlineStr"/>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="H753" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
+  (Session info: chrome=150.0.7871.114)
+Stacktrace:
+#0 0x55d0dfa8341a &lt;unknown&gt;
+#1 0x55d0df45b689 &lt;unknown&gt;
+#2 0x55d0df44321a &lt;unknown&gt;
+#3 0x55d0df442e96 &lt;unknown&gt;
+#4 0x55d0df440a7e &lt;unknown&gt;
+#5 0x55d0df4413ff &lt;unknown&gt;
+#6 0x55d0df4504e0 &lt;unknown&gt;
+#7 0x55d0df46a3e7 &lt;unknown&gt;
+#8 0x55d0df471c5b &lt;unknown&gt;
+#9 0x55d0df441b59 &lt;unknown&gt;
+</t>
+        </is>
+      </c>
     </row>
     <row r="754">
       <c r="A754" t="inlineStr">
@@ -19944,8 +23118,29 @@
       <c r="D754" t="inlineStr"/>
       <c r="E754" t="inlineStr"/>
       <c r="F754" t="inlineStr"/>
-      <c r="G754" t="inlineStr"/>
-      <c r="H754" t="inlineStr"/>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="H754" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
+  (Session info: chrome=150.0.7871.114)
+Stacktrace:
+#0 0x55d0dfa8341a &lt;unknown&gt;
+#1 0x55d0df45b689 &lt;unknown&gt;
+#2 0x55d0df44321a &lt;unknown&gt;
+#3 0x55d0df442e96 &lt;unknown&gt;
+#4 0x55d0df440a7e &lt;unknown&gt;
+#5 0x55d0df4413ff &lt;unknown&gt;
+#6 0x55d0df4504e0 &lt;unknown&gt;
+#7 0x55d0df46a3e7 &lt;unknown&gt;
+#8 0x55d0df471c5b &lt;unknown&gt;
+#9 0x55d0df441b59 &lt;unknown&gt;
+</t>
+        </is>
+      </c>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
@@ -19962,8 +23157,29 @@
       <c r="D755" t="inlineStr"/>
       <c r="E755" t="inlineStr"/>
       <c r="F755" t="inlineStr"/>
-      <c r="G755" t="inlineStr"/>
-      <c r="H755" t="inlineStr"/>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="H755" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
+  (Session info: chrome=150.0.7871.114)
+Stacktrace:
+#0 0x55d0dfa8341a &lt;unknown&gt;
+#1 0x55d0df45b689 &lt;unknown&gt;
+#2 0x55d0df44321a &lt;unknown&gt;
+#3 0x55d0df442e96 &lt;unknown&gt;
+#4 0x55d0df440a7e &lt;unknown&gt;
+#5 0x55d0df4413ff &lt;unknown&gt;
+#6 0x55d0df4504e0 &lt;unknown&gt;
+#7 0x55d0df46a3e7 &lt;unknown&gt;
+#8 0x55d0df471c5b &lt;unknown&gt;
+#9 0x55d0df441b59 &lt;unknown&gt;
+</t>
+        </is>
+      </c>
     </row>
     <row r="756">
       <c r="A756" t="inlineStr">
@@ -19980,8 +23196,29 @@
       <c r="D756" t="inlineStr"/>
       <c r="E756" t="inlineStr"/>
       <c r="F756" t="inlineStr"/>
-      <c r="G756" t="inlineStr"/>
-      <c r="H756" t="inlineStr"/>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="H756" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
+  (Session info: chrome=150.0.7871.114)
+Stacktrace:
+#0 0x55d0dfa8341a &lt;unknown&gt;
+#1 0x55d0df45b689 &lt;unknown&gt;
+#2 0x55d0df44321a &lt;unknown&gt;
+#3 0x55d0df442e96 &lt;unknown&gt;
+#4 0x55d0df440a7e &lt;unknown&gt;
+#5 0x55d0df4413ff &lt;unknown&gt;
+#6 0x55d0df4504e0 &lt;unknown&gt;
+#7 0x55d0df46a3e7 &lt;unknown&gt;
+#8 0x55d0df471c5b &lt;unknown&gt;
+#9 0x55d0df441b59 &lt;unknown&gt;
+</t>
+        </is>
+      </c>
     </row>
     <row r="757">
       <c r="A757" t="inlineStr">
@@ -19998,8 +23235,29 @@
       <c r="D757" t="inlineStr"/>
       <c r="E757" t="inlineStr"/>
       <c r="F757" t="inlineStr"/>
-      <c r="G757" t="inlineStr"/>
-      <c r="H757" t="inlineStr"/>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="H757" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
+  (Session info: chrome=150.0.7871.114)
+Stacktrace:
+#0 0x55d0dfa8341a &lt;unknown&gt;
+#1 0x55d0df45b689 &lt;unknown&gt;
+#2 0x55d0df44321a &lt;unknown&gt;
+#3 0x55d0df442e96 &lt;unknown&gt;
+#4 0x55d0df440a7e &lt;unknown&gt;
+#5 0x55d0df4413ff &lt;unknown&gt;
+#6 0x55d0df4504e0 &lt;unknown&gt;
+#7 0x55d0df46a3e7 &lt;unknown&gt;
+#8 0x55d0df471c5b &lt;unknown&gt;
+#9 0x55d0df441b59 &lt;unknown&gt;
+</t>
+        </is>
+      </c>
     </row>
     <row r="758">
       <c r="A758" t="inlineStr">
@@ -20016,8 +23274,29 @@
       <c r="D758" t="inlineStr"/>
       <c r="E758" t="inlineStr"/>
       <c r="F758" t="inlineStr"/>
-      <c r="G758" t="inlineStr"/>
-      <c r="H758" t="inlineStr"/>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="H758" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Message: timeout: Timed out receiving message from renderer: 60.000
+  (Session info: chrome=150.0.7871.114)
+Stacktrace:
+#0 0x55d0dfa8341a &lt;unknown&gt;
+#1 0x55d0df45b689 &lt;unknown&gt;
+#2 0x55d0df44321a &lt;unknown&gt;
+#3 0x55d0df442e96 &lt;unknown&gt;
+#4 0x55d0df440a7e &lt;unknown&gt;
+#5 0x55d0df4413ff &lt;unknown&gt;
+#6 0x55d0df4504e0 &lt;unknown&gt;
+#7 0x55d0df46a3e7 &lt;unknown&gt;
+#8 0x55d0df471c5b &lt;unknown&gt;
+#9 0x55d0df441b59 &lt;unknown&gt;
+</t>
+        </is>
+      </c>
     </row>
     <row r="759">
       <c r="A759" t="inlineStr">

--- a/output.xlsx
+++ b/output.xlsx
@@ -21096,21 +21096,9 @@
         </is>
       </c>
       <c r="C749" t="inlineStr"/>
-      <c r="D749" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E749" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F749" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D749" t="inlineStr"/>
+      <c r="E749" t="inlineStr"/>
+      <c r="F749" t="inlineStr"/>
       <c r="G749" t="inlineStr">
         <is>
           <t>OK</t>
@@ -21130,21 +21118,9 @@
         </is>
       </c>
       <c r="C750" t="inlineStr"/>
-      <c r="D750" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E750" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F750" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D750" t="inlineStr"/>
+      <c r="E750" t="inlineStr"/>
+      <c r="F750" t="inlineStr"/>
       <c r="G750" t="inlineStr">
         <is>
           <t>OK</t>
@@ -21164,21 +21140,9 @@
         </is>
       </c>
       <c r="C751" t="inlineStr"/>
-      <c r="D751" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E751" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F751" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D751" t="inlineStr"/>
+      <c r="E751" t="inlineStr"/>
+      <c r="F751" t="inlineStr"/>
       <c r="G751" t="inlineStr">
         <is>
           <t>OK</t>
@@ -21198,21 +21162,9 @@
         </is>
       </c>
       <c r="C752" t="inlineStr"/>
-      <c r="D752" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E752" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F752" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D752" t="inlineStr"/>
+      <c r="E752" t="inlineStr"/>
+      <c r="F752" t="inlineStr"/>
       <c r="G752" t="inlineStr">
         <is>
           <t>OK</t>
@@ -21232,21 +21184,9 @@
         </is>
       </c>
       <c r="C753" t="inlineStr"/>
-      <c r="D753" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E753" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F753" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D753" t="inlineStr"/>
+      <c r="E753" t="inlineStr"/>
+      <c r="F753" t="inlineStr"/>
       <c r="G753" t="inlineStr">
         <is>
           <t>OK</t>
@@ -21266,21 +21206,9 @@
         </is>
       </c>
       <c r="C754" t="inlineStr"/>
-      <c r="D754" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E754" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F754" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D754" t="inlineStr"/>
+      <c r="E754" t="inlineStr"/>
+      <c r="F754" t="inlineStr"/>
       <c r="G754" t="inlineStr">
         <is>
           <t>OK</t>
@@ -21300,21 +21228,9 @@
         </is>
       </c>
       <c r="C755" t="inlineStr"/>
-      <c r="D755" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E755" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F755" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D755" t="inlineStr"/>
+      <c r="E755" t="inlineStr"/>
+      <c r="F755" t="inlineStr"/>
       <c r="G755" t="inlineStr">
         <is>
           <t>OK</t>
@@ -21334,21 +21250,9 @@
         </is>
       </c>
       <c r="C756" t="inlineStr"/>
-      <c r="D756" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E756" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F756" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D756" t="inlineStr"/>
+      <c r="E756" t="inlineStr"/>
+      <c r="F756" t="inlineStr"/>
       <c r="G756" t="inlineStr">
         <is>
           <t>OK</t>
@@ -21368,21 +21272,9 @@
         </is>
       </c>
       <c r="C757" t="inlineStr"/>
-      <c r="D757" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E757" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F757" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D757" t="inlineStr"/>
+      <c r="E757" t="inlineStr"/>
+      <c r="F757" t="inlineStr"/>
       <c r="G757" t="inlineStr">
         <is>
           <t>OK</t>
@@ -21402,21 +21294,9 @@
         </is>
       </c>
       <c r="C758" t="inlineStr"/>
-      <c r="D758" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E758" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F758" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D758" t="inlineStr"/>
+      <c r="E758" t="inlineStr"/>
+      <c r="F758" t="inlineStr"/>
       <c r="G758" t="inlineStr">
         <is>
           <t>OK</t>
@@ -21436,21 +21316,9 @@
         </is>
       </c>
       <c r="C759" t="inlineStr"/>
-      <c r="D759" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E759" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F759" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D759" t="inlineStr"/>
+      <c r="E759" t="inlineStr"/>
+      <c r="F759" t="inlineStr"/>
       <c r="G759" t="inlineStr">
         <is>
           <t>OK</t>
@@ -21470,21 +21338,9 @@
         </is>
       </c>
       <c r="C760" t="inlineStr"/>
-      <c r="D760" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E760" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F760" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D760" t="inlineStr"/>
+      <c r="E760" t="inlineStr"/>
+      <c r="F760" t="inlineStr"/>
       <c r="G760" t="inlineStr">
         <is>
           <t>OK</t>
@@ -21504,21 +21360,9 @@
         </is>
       </c>
       <c r="C761" t="inlineStr"/>
-      <c r="D761" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E761" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F761" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D761" t="inlineStr"/>
+      <c r="E761" t="inlineStr"/>
+      <c r="F761" t="inlineStr"/>
       <c r="G761" t="inlineStr">
         <is>
           <t>OK</t>
@@ -21538,21 +21382,9 @@
         </is>
       </c>
       <c r="C762" t="inlineStr"/>
-      <c r="D762" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E762" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F762" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D762" t="inlineStr"/>
+      <c r="E762" t="inlineStr"/>
+      <c r="F762" t="inlineStr"/>
       <c r="G762" t="inlineStr">
         <is>
           <t>OK</t>
@@ -21572,21 +21404,9 @@
         </is>
       </c>
       <c r="C763" t="inlineStr"/>
-      <c r="D763" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E763" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F763" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D763" t="inlineStr"/>
+      <c r="E763" t="inlineStr"/>
+      <c r="F763" t="inlineStr"/>
       <c r="G763" t="inlineStr">
         <is>
           <t>OK</t>
@@ -21606,21 +21426,9 @@
         </is>
       </c>
       <c r="C764" t="inlineStr"/>
-      <c r="D764" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E764" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F764" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D764" t="inlineStr"/>
+      <c r="E764" t="inlineStr"/>
+      <c r="F764" t="inlineStr"/>
       <c r="G764" t="inlineStr">
         <is>
           <t>OK</t>
@@ -21640,21 +21448,9 @@
         </is>
       </c>
       <c r="C765" t="inlineStr"/>
-      <c r="D765" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E765" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F765" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D765" t="inlineStr"/>
+      <c r="E765" t="inlineStr"/>
+      <c r="F765" t="inlineStr"/>
       <c r="G765" t="inlineStr">
         <is>
           <t>OK</t>
@@ -21674,21 +21470,9 @@
         </is>
       </c>
       <c r="C766" t="inlineStr"/>
-      <c r="D766" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E766" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F766" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D766" t="inlineStr"/>
+      <c r="E766" t="inlineStr"/>
+      <c r="F766" t="inlineStr"/>
       <c r="G766" t="inlineStr">
         <is>
           <t>OK</t>
@@ -21708,21 +21492,9 @@
         </is>
       </c>
       <c r="C767" t="inlineStr"/>
-      <c r="D767" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E767" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F767" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D767" t="inlineStr"/>
+      <c r="E767" t="inlineStr"/>
+      <c r="F767" t="inlineStr"/>
       <c r="G767" t="inlineStr">
         <is>
           <t>OK</t>
@@ -21742,21 +21514,9 @@
         </is>
       </c>
       <c r="C768" t="inlineStr"/>
-      <c r="D768" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E768" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F768" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D768" t="inlineStr"/>
+      <c r="E768" t="inlineStr"/>
+      <c r="F768" t="inlineStr"/>
       <c r="G768" t="inlineStr">
         <is>
           <t>OK</t>
@@ -21776,21 +21536,9 @@
         </is>
       </c>
       <c r="C769" t="inlineStr"/>
-      <c r="D769" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E769" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F769" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D769" t="inlineStr"/>
+      <c r="E769" t="inlineStr"/>
+      <c r="F769" t="inlineStr"/>
       <c r="G769" t="inlineStr">
         <is>
           <t>OK</t>
@@ -21810,21 +21558,9 @@
         </is>
       </c>
       <c r="C770" t="inlineStr"/>
-      <c r="D770" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E770" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F770" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D770" t="inlineStr"/>
+      <c r="E770" t="inlineStr"/>
+      <c r="F770" t="inlineStr"/>
       <c r="G770" t="inlineStr">
         <is>
           <t>OK</t>
@@ -21844,21 +21580,9 @@
         </is>
       </c>
       <c r="C771" t="inlineStr"/>
-      <c r="D771" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E771" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F771" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D771" t="inlineStr"/>
+      <c r="E771" t="inlineStr"/>
+      <c r="F771" t="inlineStr"/>
       <c r="G771" t="inlineStr">
         <is>
           <t>OK</t>
@@ -21878,21 +21602,9 @@
         </is>
       </c>
       <c r="C772" t="inlineStr"/>
-      <c r="D772" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E772" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F772" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D772" t="inlineStr"/>
+      <c r="E772" t="inlineStr"/>
+      <c r="F772" t="inlineStr"/>
       <c r="G772" t="inlineStr">
         <is>
           <t>OK</t>
@@ -21912,21 +21624,9 @@
         </is>
       </c>
       <c r="C773" t="inlineStr"/>
-      <c r="D773" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E773" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F773" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D773" t="inlineStr"/>
+      <c r="E773" t="inlineStr"/>
+      <c r="F773" t="inlineStr"/>
       <c r="G773" t="inlineStr">
         <is>
           <t>OK</t>
@@ -21946,21 +21646,9 @@
         </is>
       </c>
       <c r="C774" t="inlineStr"/>
-      <c r="D774" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E774" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F774" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D774" t="inlineStr"/>
+      <c r="E774" t="inlineStr"/>
+      <c r="F774" t="inlineStr"/>
       <c r="G774" t="inlineStr">
         <is>
           <t>OK</t>
@@ -21980,21 +21668,9 @@
         </is>
       </c>
       <c r="C775" t="inlineStr"/>
-      <c r="D775" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E775" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F775" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D775" t="inlineStr"/>
+      <c r="E775" t="inlineStr"/>
+      <c r="F775" t="inlineStr"/>
       <c r="G775" t="inlineStr">
         <is>
           <t>OK</t>
@@ -22014,21 +21690,9 @@
         </is>
       </c>
       <c r="C776" t="inlineStr"/>
-      <c r="D776" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E776" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F776" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D776" t="inlineStr"/>
+      <c r="E776" t="inlineStr"/>
+      <c r="F776" t="inlineStr"/>
       <c r="G776" t="inlineStr">
         <is>
           <t>OK</t>
@@ -22048,21 +21712,9 @@
         </is>
       </c>
       <c r="C777" t="inlineStr"/>
-      <c r="D777" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E777" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F777" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D777" t="inlineStr"/>
+      <c r="E777" t="inlineStr"/>
+      <c r="F777" t="inlineStr"/>
       <c r="G777" t="inlineStr">
         <is>
           <t>OK</t>
@@ -22082,21 +21734,9 @@
         </is>
       </c>
       <c r="C778" t="inlineStr"/>
-      <c r="D778" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E778" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F778" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D778" t="inlineStr"/>
+      <c r="E778" t="inlineStr"/>
+      <c r="F778" t="inlineStr"/>
       <c r="G778" t="inlineStr">
         <is>
           <t>OK</t>
@@ -22116,21 +21756,9 @@
         </is>
       </c>
       <c r="C779" t="inlineStr"/>
-      <c r="D779" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E779" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F779" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D779" t="inlineStr"/>
+      <c r="E779" t="inlineStr"/>
+      <c r="F779" t="inlineStr"/>
       <c r="G779" t="inlineStr">
         <is>
           <t>OK</t>
@@ -22150,21 +21778,9 @@
         </is>
       </c>
       <c r="C780" t="inlineStr"/>
-      <c r="D780" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E780" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F780" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D780" t="inlineStr"/>
+      <c r="E780" t="inlineStr"/>
+      <c r="F780" t="inlineStr"/>
       <c r="G780" t="inlineStr">
         <is>
           <t>OK</t>
@@ -22184,21 +21800,9 @@
         </is>
       </c>
       <c r="C781" t="inlineStr"/>
-      <c r="D781" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E781" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F781" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D781" t="inlineStr"/>
+      <c r="E781" t="inlineStr"/>
+      <c r="F781" t="inlineStr"/>
       <c r="G781" t="inlineStr">
         <is>
           <t>OK</t>
@@ -22218,21 +21822,9 @@
         </is>
       </c>
       <c r="C782" t="inlineStr"/>
-      <c r="D782" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E782" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F782" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D782" t="inlineStr"/>
+      <c r="E782" t="inlineStr"/>
+      <c r="F782" t="inlineStr"/>
       <c r="G782" t="inlineStr">
         <is>
           <t>OK</t>
@@ -22252,21 +21844,9 @@
         </is>
       </c>
       <c r="C783" t="inlineStr"/>
-      <c r="D783" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E783" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F783" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D783" t="inlineStr"/>
+      <c r="E783" t="inlineStr"/>
+      <c r="F783" t="inlineStr"/>
       <c r="G783" t="inlineStr">
         <is>
           <t>OK</t>
@@ -22286,21 +21866,9 @@
         </is>
       </c>
       <c r="C784" t="inlineStr"/>
-      <c r="D784" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E784" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F784" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D784" t="inlineStr"/>
+      <c r="E784" t="inlineStr"/>
+      <c r="F784" t="inlineStr"/>
       <c r="G784" t="inlineStr">
         <is>
           <t>OK</t>
@@ -22320,21 +21888,9 @@
         </is>
       </c>
       <c r="C785" t="inlineStr"/>
-      <c r="D785" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E785" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F785" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D785" t="inlineStr"/>
+      <c r="E785" t="inlineStr"/>
+      <c r="F785" t="inlineStr"/>
       <c r="G785" t="inlineStr">
         <is>
           <t>OK</t>
@@ -22354,21 +21910,9 @@
         </is>
       </c>
       <c r="C786" t="inlineStr"/>
-      <c r="D786" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E786" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F786" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D786" t="inlineStr"/>
+      <c r="E786" t="inlineStr"/>
+      <c r="F786" t="inlineStr"/>
       <c r="G786" t="inlineStr">
         <is>
           <t>OK</t>
@@ -22388,21 +21932,9 @@
         </is>
       </c>
       <c r="C787" t="inlineStr"/>
-      <c r="D787" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E787" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F787" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D787" t="inlineStr"/>
+      <c r="E787" t="inlineStr"/>
+      <c r="F787" t="inlineStr"/>
       <c r="G787" t="inlineStr">
         <is>
           <t>OK</t>
@@ -22422,21 +21954,9 @@
         </is>
       </c>
       <c r="C788" t="inlineStr"/>
-      <c r="D788" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E788" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F788" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D788" t="inlineStr"/>
+      <c r="E788" t="inlineStr"/>
+      <c r="F788" t="inlineStr"/>
       <c r="G788" t="inlineStr">
         <is>
           <t>OK</t>
@@ -22456,21 +21976,9 @@
         </is>
       </c>
       <c r="C789" t="inlineStr"/>
-      <c r="D789" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E789" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F789" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D789" t="inlineStr"/>
+      <c r="E789" t="inlineStr"/>
+      <c r="F789" t="inlineStr"/>
       <c r="G789" t="inlineStr">
         <is>
           <t>OK</t>
@@ -22490,21 +21998,9 @@
         </is>
       </c>
       <c r="C790" t="inlineStr"/>
-      <c r="D790" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E790" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F790" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D790" t="inlineStr"/>
+      <c r="E790" t="inlineStr"/>
+      <c r="F790" t="inlineStr"/>
       <c r="G790" t="inlineStr">
         <is>
           <t>OK</t>
@@ -22524,21 +22020,9 @@
         </is>
       </c>
       <c r="C791" t="inlineStr"/>
-      <c r="D791" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E791" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F791" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D791" t="inlineStr"/>
+      <c r="E791" t="inlineStr"/>
+      <c r="F791" t="inlineStr"/>
       <c r="G791" t="inlineStr">
         <is>
           <t>OK</t>
@@ -22558,21 +22042,9 @@
         </is>
       </c>
       <c r="C792" t="inlineStr"/>
-      <c r="D792" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E792" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F792" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D792" t="inlineStr"/>
+      <c r="E792" t="inlineStr"/>
+      <c r="F792" t="inlineStr"/>
       <c r="G792" t="inlineStr">
         <is>
           <t>OK</t>
@@ -22592,21 +22064,9 @@
         </is>
       </c>
       <c r="C793" t="inlineStr"/>
-      <c r="D793" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E793" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F793" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D793" t="inlineStr"/>
+      <c r="E793" t="inlineStr"/>
+      <c r="F793" t="inlineStr"/>
       <c r="G793" t="inlineStr">
         <is>
           <t>OK</t>
@@ -22698,11 +22158,7 @@
       <c r="E796" t="n">
         <v>184</v>
       </c>
-      <c r="F796" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F796" t="inlineStr"/>
       <c r="G796" t="inlineStr">
         <is>
           <t>OK</t>
@@ -22730,11 +22186,7 @@
       <c r="E797" t="n">
         <v>184</v>
       </c>
-      <c r="F797" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F797" t="inlineStr"/>
       <c r="G797" t="inlineStr">
         <is>
           <t>OK</t>
@@ -22762,11 +22214,7 @@
       <c r="E798" t="n">
         <v>24</v>
       </c>
-      <c r="F798" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F798" t="inlineStr"/>
       <c r="G798" t="inlineStr">
         <is>
           <t>OK</t>
@@ -22858,11 +22306,7 @@
       <c r="E801" t="n">
         <v>11</v>
       </c>
-      <c r="F801" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F801" t="inlineStr"/>
       <c r="G801" t="inlineStr">
         <is>
           <t>OK</t>
@@ -22890,11 +22334,7 @@
       <c r="E802" t="n">
         <v>11</v>
       </c>
-      <c r="F802" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F802" t="inlineStr"/>
       <c r="G802" t="inlineStr">
         <is>
           <t>OK</t>
@@ -22922,11 +22362,7 @@
       <c r="E803" t="n">
         <v>11</v>
       </c>
-      <c r="F803" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F803" t="inlineStr"/>
       <c r="G803" t="inlineStr">
         <is>
           <t>OK</t>
@@ -22954,11 +22390,7 @@
       <c r="E804" t="n">
         <v>11</v>
       </c>
-      <c r="F804" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F804" t="inlineStr"/>
       <c r="G804" t="inlineStr">
         <is>
           <t>OK</t>
@@ -22986,11 +22418,7 @@
       <c r="E805" t="n">
         <v>11</v>
       </c>
-      <c r="F805" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F805" t="inlineStr"/>
       <c r="G805" t="inlineStr">
         <is>
           <t>OK</t>
@@ -23018,11 +22446,7 @@
       <c r="E806" t="n">
         <v>1</v>
       </c>
-      <c r="F806" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F806" t="inlineStr"/>
       <c r="G806" t="inlineStr">
         <is>
           <t>OK</t>
@@ -23050,11 +22474,7 @@
       <c r="E807" t="n">
         <v>1</v>
       </c>
-      <c r="F807" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F807" t="inlineStr"/>
       <c r="G807" t="inlineStr">
         <is>
           <t>OK</t>
@@ -23082,11 +22502,7 @@
       <c r="E808" t="n">
         <v>1</v>
       </c>
-      <c r="F808" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F808" t="inlineStr"/>
       <c r="G808" t="inlineStr">
         <is>
           <t>OK</t>
@@ -23114,11 +22530,7 @@
       <c r="E809" t="n">
         <v>11</v>
       </c>
-      <c r="F809" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F809" t="inlineStr"/>
       <c r="G809" t="inlineStr">
         <is>
           <t>OK</t>
@@ -23146,11 +22558,7 @@
       <c r="E810" t="n">
         <v>11</v>
       </c>
-      <c r="F810" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F810" t="inlineStr"/>
       <c r="G810" t="inlineStr">
         <is>
           <t>OK</t>
@@ -23178,11 +22586,7 @@
       <c r="E811" t="n">
         <v>11</v>
       </c>
-      <c r="F811" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F811" t="inlineStr"/>
       <c r="G811" t="inlineStr">
         <is>
           <t>OK</t>
@@ -23210,11 +22614,7 @@
       <c r="E812" t="n">
         <v>11</v>
       </c>
-      <c r="F812" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F812" t="inlineStr"/>
       <c r="G812" t="inlineStr">
         <is>
           <t>OK</t>
@@ -23242,11 +22642,7 @@
       <c r="E813" t="n">
         <v>11</v>
       </c>
-      <c r="F813" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F813" t="inlineStr"/>
       <c r="G813" t="inlineStr">
         <is>
           <t>OK</t>
@@ -23274,11 +22670,7 @@
       <c r="E814" t="n">
         <v>11</v>
       </c>
-      <c r="F814" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F814" t="inlineStr"/>
       <c r="G814" t="inlineStr">
         <is>
           <t>OK</t>
@@ -23306,11 +22698,7 @@
       <c r="E815" t="n">
         <v>2</v>
       </c>
-      <c r="F815" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F815" t="inlineStr"/>
       <c r="G815" t="inlineStr">
         <is>
           <t>OK</t>
@@ -23338,11 +22726,7 @@
       <c r="E816" t="n">
         <v>2</v>
       </c>
-      <c r="F816" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F816" t="inlineStr"/>
       <c r="G816" t="inlineStr">
         <is>
           <t>OK</t>
@@ -23370,11 +22754,7 @@
       <c r="E817" t="n">
         <v>2</v>
       </c>
-      <c r="F817" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F817" t="inlineStr"/>
       <c r="G817" t="inlineStr">
         <is>
           <t>OK</t>
@@ -23530,11 +22910,7 @@
       <c r="E822" t="n">
         <v>2</v>
       </c>
-      <c r="F822" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F822" t="inlineStr"/>
       <c r="G822" t="inlineStr">
         <is>
           <t>OK</t>
@@ -23562,11 +22938,7 @@
       <c r="E823" t="n">
         <v>2</v>
       </c>
-      <c r="F823" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F823" t="inlineStr"/>
       <c r="G823" t="inlineStr">
         <is>
           <t>OK</t>
@@ -23586,21 +22958,9 @@
         </is>
       </c>
       <c r="C824" t="inlineStr"/>
-      <c r="D824" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E824" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F824" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D824" t="inlineStr"/>
+      <c r="E824" t="inlineStr"/>
+      <c r="F824" t="inlineStr"/>
       <c r="G824" t="inlineStr">
         <is>
           <t>OK</t>
@@ -23622,21 +22982,9 @@
       <c r="C825" t="n">
         <v>8559</v>
       </c>
-      <c r="D825" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E825" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F825" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D825" t="inlineStr"/>
+      <c r="E825" t="inlineStr"/>
+      <c r="F825" t="inlineStr"/>
       <c r="G825" t="inlineStr">
         <is>
           <t>OK</t>
@@ -23658,21 +23006,9 @@
       <c r="C826" t="n">
         <v>8559</v>
       </c>
-      <c r="D826" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E826" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F826" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D826" t="inlineStr"/>
+      <c r="E826" t="inlineStr"/>
+      <c r="F826" t="inlineStr"/>
       <c r="G826" t="inlineStr">
         <is>
           <t>OK</t>
@@ -23694,21 +23030,9 @@
       <c r="C827" t="n">
         <v>8559</v>
       </c>
-      <c r="D827" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E827" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F827" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D827" t="inlineStr"/>
+      <c r="E827" t="inlineStr"/>
+      <c r="F827" t="inlineStr"/>
       <c r="G827" t="inlineStr">
         <is>
           <t>OK</t>
@@ -23730,21 +23054,9 @@
       <c r="C828" t="n">
         <v>8559</v>
       </c>
-      <c r="D828" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E828" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F828" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D828" t="inlineStr"/>
+      <c r="E828" t="inlineStr"/>
+      <c r="F828" t="inlineStr"/>
       <c r="G828" t="inlineStr">
         <is>
           <t>OK</t>
@@ -23772,11 +23084,7 @@
       <c r="E829" t="n">
         <v>2</v>
       </c>
-      <c r="F829" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F829" t="inlineStr"/>
       <c r="G829" t="inlineStr">
         <is>
           <t>OK</t>
@@ -23804,11 +23112,7 @@
       <c r="E830" t="n">
         <v>2</v>
       </c>
-      <c r="F830" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F830" t="inlineStr"/>
       <c r="G830" t="inlineStr">
         <is>
           <t>OK</t>
@@ -23836,11 +23140,7 @@
       <c r="E831" t="n">
         <v>2</v>
       </c>
-      <c r="F831" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F831" t="inlineStr"/>
       <c r="G831" t="inlineStr">
         <is>
           <t>OK</t>
@@ -23868,11 +23168,7 @@
       <c r="E832" t="n">
         <v>2</v>
       </c>
-      <c r="F832" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F832" t="inlineStr"/>
       <c r="G832" t="inlineStr">
         <is>
           <t>OK</t>
@@ -23892,21 +23188,9 @@
         </is>
       </c>
       <c r="C833" t="inlineStr"/>
-      <c r="D833" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E833" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F833" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D833" t="inlineStr"/>
+      <c r="E833" t="inlineStr"/>
+      <c r="F833" t="inlineStr"/>
       <c r="G833" t="inlineStr">
         <is>
           <t>OK</t>
@@ -23926,21 +23210,9 @@
         </is>
       </c>
       <c r="C834" t="inlineStr"/>
-      <c r="D834" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E834" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F834" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D834" t="inlineStr"/>
+      <c r="E834" t="inlineStr"/>
+      <c r="F834" t="inlineStr"/>
       <c r="G834" t="inlineStr">
         <is>
           <t>OK</t>
@@ -23968,11 +23240,7 @@
       <c r="E835" t="n">
         <v>30</v>
       </c>
-      <c r="F835" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F835" t="inlineStr"/>
       <c r="G835" t="inlineStr">
         <is>
           <t>OK</t>
@@ -24000,11 +23268,7 @@
       <c r="E836" t="n">
         <v>17</v>
       </c>
-      <c r="F836" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F836" t="inlineStr"/>
       <c r="G836" t="inlineStr">
         <is>
           <t>OK</t>
@@ -24032,11 +23296,7 @@
       <c r="E837" t="n">
         <v>30</v>
       </c>
-      <c r="F837" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F837" t="inlineStr"/>
       <c r="G837" t="inlineStr">
         <is>
           <t>OK</t>
@@ -24056,21 +23316,9 @@
         </is>
       </c>
       <c r="C838" t="inlineStr"/>
-      <c r="D838" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E838" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F838" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D838" t="inlineStr"/>
+      <c r="E838" t="inlineStr"/>
+      <c r="F838" t="inlineStr"/>
       <c r="G838" t="inlineStr">
         <is>
           <t>OK</t>
@@ -24122,21 +23370,9 @@
         </is>
       </c>
       <c r="C840" t="inlineStr"/>
-      <c r="D840" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E840" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F840" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D840" t="inlineStr"/>
+      <c r="E840" t="inlineStr"/>
+      <c r="F840" t="inlineStr"/>
       <c r="G840" t="inlineStr">
         <is>
           <t>OK</t>
@@ -24156,21 +23392,9 @@
         </is>
       </c>
       <c r="C841" t="inlineStr"/>
-      <c r="D841" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E841" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F841" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D841" t="inlineStr"/>
+      <c r="E841" t="inlineStr"/>
+      <c r="F841" t="inlineStr"/>
       <c r="G841" t="inlineStr">
         <is>
           <t>OK</t>
@@ -24262,11 +23486,7 @@
       <c r="E844" t="n">
         <v>3</v>
       </c>
-      <c r="F844" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F844" t="inlineStr"/>
       <c r="G844" t="inlineStr">
         <is>
           <t>OK</t>
@@ -24294,11 +23514,7 @@
       <c r="E845" t="n">
         <v>5</v>
       </c>
-      <c r="F845" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F845" t="inlineStr"/>
       <c r="G845" t="inlineStr">
         <is>
           <t>OK</t>
@@ -24326,11 +23542,7 @@
       <c r="E846" t="n">
         <v>7078</v>
       </c>
-      <c r="F846" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F846" t="inlineStr"/>
       <c r="G846" t="inlineStr">
         <is>
           <t>OK</t>
@@ -24358,11 +23570,7 @@
       <c r="E847" t="n">
         <v>38</v>
       </c>
-      <c r="F847" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F847" t="inlineStr"/>
       <c r="G847" t="inlineStr">
         <is>
           <t>OK</t>
@@ -24390,11 +23598,7 @@
       <c r="E848" t="n">
         <v>2</v>
       </c>
-      <c r="F848" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F848" t="inlineStr"/>
       <c r="G848" t="inlineStr">
         <is>
           <t>OK</t>
@@ -24414,21 +23618,9 @@
         </is>
       </c>
       <c r="C849" t="inlineStr"/>
-      <c r="D849" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E849" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F849" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D849" t="inlineStr"/>
+      <c r="E849" t="inlineStr"/>
+      <c r="F849" t="inlineStr"/>
       <c r="G849" t="inlineStr">
         <is>
           <t>OK</t>
@@ -24456,11 +23648,7 @@
       <c r="E850" t="n">
         <v>1</v>
       </c>
-      <c r="F850" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F850" t="inlineStr"/>
       <c r="G850" t="inlineStr">
         <is>
           <t>OK</t>
@@ -24488,11 +23676,7 @@
       <c r="E851" t="n">
         <v>336</v>
       </c>
-      <c r="F851" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F851" t="inlineStr"/>
       <c r="G851" t="inlineStr">
         <is>
           <t>OK</t>
@@ -24512,21 +23696,9 @@
         </is>
       </c>
       <c r="C852" t="inlineStr"/>
-      <c r="D852" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E852" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F852" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D852" t="inlineStr"/>
+      <c r="E852" t="inlineStr"/>
+      <c r="F852" t="inlineStr"/>
       <c r="G852" t="inlineStr">
         <is>
           <t>OK</t>
@@ -24554,11 +23726,7 @@
       <c r="E853" t="n">
         <v>164</v>
       </c>
-      <c r="F853" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F853" t="inlineStr"/>
       <c r="G853" t="inlineStr">
         <is>
           <t>OK</t>
@@ -24586,11 +23754,7 @@
       <c r="E854" t="n">
         <v>7078</v>
       </c>
-      <c r="F854" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F854" t="inlineStr"/>
       <c r="G854" t="inlineStr">
         <is>
           <t>OK</t>
@@ -24618,11 +23782,7 @@
       <c r="E855" t="n">
         <v>268</v>
       </c>
-      <c r="F855" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F855" t="inlineStr"/>
       <c r="G855" t="inlineStr">
         <is>
           <t>OK</t>
@@ -24650,11 +23810,7 @@
       <c r="E856" t="n">
         <v>14</v>
       </c>
-      <c r="F856" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F856" t="inlineStr"/>
       <c r="G856" t="inlineStr">
         <is>
           <t>OK</t>
@@ -24682,11 +23838,7 @@
       <c r="E857" t="n">
         <v>1</v>
       </c>
-      <c r="F857" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F857" t="inlineStr"/>
       <c r="G857" t="inlineStr">
         <is>
           <t>OK</t>
@@ -24714,11 +23866,7 @@
       <c r="E858" t="n">
         <v>7078</v>
       </c>
-      <c r="F858" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F858" t="inlineStr"/>
       <c r="G858" t="inlineStr">
         <is>
           <t>OK</t>
@@ -24746,11 +23894,7 @@
       <c r="E859" t="n">
         <v>95</v>
       </c>
-      <c r="F859" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F859" t="inlineStr"/>
       <c r="G859" t="inlineStr">
         <is>
           <t>OK</t>
@@ -24778,11 +23922,7 @@
       <c r="E860" t="n">
         <v>5</v>
       </c>
-      <c r="F860" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F860" t="inlineStr"/>
       <c r="G860" t="inlineStr">
         <is>
           <t>OK</t>
@@ -24902,11 +24042,7 @@
       <c r="E864" t="n">
         <v>7078</v>
       </c>
-      <c r="F864" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F864" t="inlineStr"/>
       <c r="G864" t="inlineStr">
         <is>
           <t>OK</t>
@@ -24998,11 +24134,7 @@
       <c r="E867" t="n">
         <v>20</v>
       </c>
-      <c r="F867" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F867" t="inlineStr"/>
       <c r="G867" t="inlineStr">
         <is>
           <t>OK</t>
@@ -25118,21 +24250,9 @@
         </is>
       </c>
       <c r="C871" t="inlineStr"/>
-      <c r="D871" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E871" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F871" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D871" t="inlineStr"/>
+      <c r="E871" t="inlineStr"/>
+      <c r="F871" t="inlineStr"/>
       <c r="G871" t="inlineStr">
         <is>
           <t>OK</t>
@@ -25152,21 +24272,9 @@
         </is>
       </c>
       <c r="C872" t="inlineStr"/>
-      <c r="D872" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E872" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F872" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D872" t="inlineStr"/>
+      <c r="E872" t="inlineStr"/>
+      <c r="F872" t="inlineStr"/>
       <c r="G872" t="inlineStr">
         <is>
           <t>OK</t>
@@ -25186,21 +24294,9 @@
         </is>
       </c>
       <c r="C873" t="inlineStr"/>
-      <c r="D873" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E873" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F873" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D873" t="inlineStr"/>
+      <c r="E873" t="inlineStr"/>
+      <c r="F873" t="inlineStr"/>
       <c r="G873" t="inlineStr">
         <is>
           <t>OK</t>
@@ -25220,21 +24316,9 @@
         </is>
       </c>
       <c r="C874" t="inlineStr"/>
-      <c r="D874" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E874" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F874" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D874" t="inlineStr"/>
+      <c r="E874" t="inlineStr"/>
+      <c r="F874" t="inlineStr"/>
       <c r="G874" t="inlineStr">
         <is>
           <t>OK</t>
@@ -25254,21 +24338,9 @@
         </is>
       </c>
       <c r="C875" t="inlineStr"/>
-      <c r="D875" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E875" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F875" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D875" t="inlineStr"/>
+      <c r="E875" t="inlineStr"/>
+      <c r="F875" t="inlineStr"/>
       <c r="G875" t="inlineStr">
         <is>
           <t>OK</t>
@@ -25288,21 +24360,9 @@
         </is>
       </c>
       <c r="C876" t="inlineStr"/>
-      <c r="D876" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E876" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F876" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D876" t="inlineStr"/>
+      <c r="E876" t="inlineStr"/>
+      <c r="F876" t="inlineStr"/>
       <c r="G876" t="inlineStr">
         <is>
           <t>OK</t>
@@ -25322,21 +24382,9 @@
         </is>
       </c>
       <c r="C877" t="inlineStr"/>
-      <c r="D877" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E877" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F877" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D877" t="inlineStr"/>
+      <c r="E877" t="inlineStr"/>
+      <c r="F877" t="inlineStr"/>
       <c r="G877" t="inlineStr">
         <is>
           <t>OK</t>
@@ -25356,21 +24404,9 @@
         </is>
       </c>
       <c r="C878" t="inlineStr"/>
-      <c r="D878" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E878" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F878" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D878" t="inlineStr"/>
+      <c r="E878" t="inlineStr"/>
+      <c r="F878" t="inlineStr"/>
       <c r="G878" t="inlineStr">
         <is>
           <t>OK</t>
@@ -25390,21 +24426,9 @@
         </is>
       </c>
       <c r="C879" t="inlineStr"/>
-      <c r="D879" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E879" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F879" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D879" t="inlineStr"/>
+      <c r="E879" t="inlineStr"/>
+      <c r="F879" t="inlineStr"/>
       <c r="G879" t="inlineStr">
         <is>
           <t>OK</t>
@@ -25424,21 +24448,9 @@
         </is>
       </c>
       <c r="C880" t="inlineStr"/>
-      <c r="D880" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E880" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F880" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D880" t="inlineStr"/>
+      <c r="E880" t="inlineStr"/>
+      <c r="F880" t="inlineStr"/>
       <c r="G880" t="inlineStr">
         <is>
           <t>OK</t>
@@ -25458,21 +24470,9 @@
         </is>
       </c>
       <c r="C881" t="inlineStr"/>
-      <c r="D881" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E881" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F881" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D881" t="inlineStr"/>
+      <c r="E881" t="inlineStr"/>
+      <c r="F881" t="inlineStr"/>
       <c r="G881" t="inlineStr">
         <is>
           <t>OK</t>
@@ -25492,21 +24492,9 @@
         </is>
       </c>
       <c r="C882" t="inlineStr"/>
-      <c r="D882" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E882" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F882" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D882" t="inlineStr"/>
+      <c r="E882" t="inlineStr"/>
+      <c r="F882" t="inlineStr"/>
       <c r="G882" t="inlineStr">
         <is>
           <t>OK</t>
@@ -25534,11 +24522,7 @@
       <c r="E883" t="n">
         <v>420</v>
       </c>
-      <c r="F883" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F883" t="inlineStr"/>
       <c r="G883" t="inlineStr">
         <is>
           <t>OK</t>
@@ -25598,11 +24582,7 @@
       <c r="E885" t="n">
         <v>2</v>
       </c>
-      <c r="F885" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F885" t="inlineStr"/>
       <c r="G885" t="inlineStr">
         <is>
           <t>OK</t>
@@ -25630,11 +24610,7 @@
       <c r="E886" t="n">
         <v>4</v>
       </c>
-      <c r="F886" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F886" t="inlineStr"/>
       <c r="G886" t="inlineStr">
         <is>
           <t>OK</t>
@@ -25662,11 +24638,7 @@
       <c r="E887" t="n">
         <v>4</v>
       </c>
-      <c r="F887" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F887" t="inlineStr"/>
       <c r="G887" t="inlineStr">
         <is>
           <t>OK</t>
@@ -25694,11 +24666,7 @@
       <c r="E888" t="n">
         <v>4</v>
       </c>
-      <c r="F888" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F888" t="inlineStr"/>
       <c r="G888" t="inlineStr">
         <is>
           <t>OK</t>
@@ -25750,21 +24718,9 @@
         </is>
       </c>
       <c r="C890" t="inlineStr"/>
-      <c r="D890" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E890" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F890" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D890" t="inlineStr"/>
+      <c r="E890" t="inlineStr"/>
+      <c r="F890" t="inlineStr"/>
       <c r="G890" t="inlineStr">
         <is>
           <t>OK</t>
@@ -25784,21 +24740,9 @@
         </is>
       </c>
       <c r="C891" t="inlineStr"/>
-      <c r="D891" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E891" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F891" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D891" t="inlineStr"/>
+      <c r="E891" t="inlineStr"/>
+      <c r="F891" t="inlineStr"/>
       <c r="G891" t="inlineStr">
         <is>
           <t>OK</t>
@@ -25826,11 +24770,7 @@
       <c r="E892" t="n">
         <v>3</v>
       </c>
-      <c r="F892" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F892" t="inlineStr"/>
       <c r="G892" t="inlineStr">
         <is>
           <t>OK</t>
@@ -25858,11 +24798,7 @@
       <c r="E893" t="n">
         <v>3</v>
       </c>
-      <c r="F893" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F893" t="inlineStr"/>
       <c r="G893" t="inlineStr">
         <is>
           <t>OK</t>
@@ -25922,11 +24858,7 @@
       <c r="E895" t="n">
         <v>3</v>
       </c>
-      <c r="F895" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F895" t="inlineStr"/>
       <c r="G895" t="inlineStr">
         <is>
           <t>OK</t>
@@ -25954,11 +24886,7 @@
       <c r="E896" t="n">
         <v>11</v>
       </c>
-      <c r="F896" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F896" t="inlineStr"/>
       <c r="G896" t="inlineStr">
         <is>
           <t>OK</t>
@@ -25986,11 +24914,7 @@
       <c r="E897" t="n">
         <v>11</v>
       </c>
-      <c r="F897" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F897" t="inlineStr"/>
       <c r="G897" t="inlineStr">
         <is>
           <t>OK</t>
@@ -26018,11 +24942,7 @@
       <c r="E898" t="n">
         <v>6</v>
       </c>
-      <c r="F898" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F898" t="inlineStr"/>
       <c r="G898" t="inlineStr">
         <is>
           <t>OK</t>
@@ -26044,16 +24964,8 @@
       <c r="C899" t="n">
         <v>1169</v>
       </c>
-      <c r="D899" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E899" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D899" t="inlineStr"/>
+      <c r="E899" t="inlineStr"/>
       <c r="F899" t="inlineStr">
         <is>
           <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
@@ -26078,21 +24990,9 @@
         </is>
       </c>
       <c r="C900" t="inlineStr"/>
-      <c r="D900" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E900" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F900" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D900" t="inlineStr"/>
+      <c r="E900" t="inlineStr"/>
+      <c r="F900" t="inlineStr"/>
       <c r="G900" t="inlineStr">
         <is>
           <t>OK</t>
@@ -26120,11 +25020,7 @@
       <c r="E901" t="n">
         <v>1576</v>
       </c>
-      <c r="F901" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F901" t="inlineStr"/>
       <c r="G901" t="inlineStr">
         <is>
           <t>OK</t>
@@ -26152,11 +25048,7 @@
       <c r="E902" t="n">
         <v>6</v>
       </c>
-      <c r="F902" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F902" t="inlineStr"/>
       <c r="G902" t="inlineStr">
         <is>
           <t>OK</t>
@@ -26184,11 +25076,7 @@
       <c r="E903" t="n">
         <v>14</v>
       </c>
-      <c r="F903" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F903" t="inlineStr"/>
       <c r="G903" t="inlineStr">
         <is>
           <t>OK</t>
@@ -26216,11 +25104,7 @@
       <c r="E904" t="n">
         <v>473</v>
       </c>
-      <c r="F904" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F904" t="inlineStr"/>
       <c r="G904" t="inlineStr">
         <is>
           <t>OK</t>
@@ -26240,21 +25124,9 @@
         </is>
       </c>
       <c r="C905" t="inlineStr"/>
-      <c r="D905" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E905" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F905" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D905" t="inlineStr"/>
+      <c r="E905" t="inlineStr"/>
+      <c r="F905" t="inlineStr"/>
       <c r="G905" t="inlineStr">
         <is>
           <t>OK</t>
@@ -26274,21 +25146,9 @@
         </is>
       </c>
       <c r="C906" t="inlineStr"/>
-      <c r="D906" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E906" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F906" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D906" t="inlineStr"/>
+      <c r="E906" t="inlineStr"/>
+      <c r="F906" t="inlineStr"/>
       <c r="G906" t="inlineStr">
         <is>
           <t>OK</t>
@@ -26308,21 +25168,9 @@
         </is>
       </c>
       <c r="C907" t="inlineStr"/>
-      <c r="D907" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E907" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F907" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D907" t="inlineStr"/>
+      <c r="E907" t="inlineStr"/>
+      <c r="F907" t="inlineStr"/>
       <c r="G907" t="inlineStr">
         <is>
           <t>OK</t>
@@ -26344,16 +25192,8 @@
       <c r="C908" t="n">
         <v>2329</v>
       </c>
-      <c r="D908" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E908" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D908" t="inlineStr"/>
+      <c r="E908" t="inlineStr"/>
       <c r="F908" t="inlineStr">
         <is>
           <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
@@ -26386,11 +25226,7 @@
       <c r="E909" t="n">
         <v>8</v>
       </c>
-      <c r="F909" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F909" t="inlineStr"/>
       <c r="G909" t="inlineStr">
         <is>
           <t>OK</t>
@@ -26410,21 +25246,9 @@
         </is>
       </c>
       <c r="C910" t="inlineStr"/>
-      <c r="D910" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E910" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F910" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D910" t="inlineStr"/>
+      <c r="E910" t="inlineStr"/>
+      <c r="F910" t="inlineStr"/>
       <c r="G910" t="inlineStr">
         <is>
           <t>OK</t>
@@ -26444,21 +25268,9 @@
         </is>
       </c>
       <c r="C911" t="inlineStr"/>
-      <c r="D911" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E911" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F911" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D911" t="inlineStr"/>
+      <c r="E911" t="inlineStr"/>
+      <c r="F911" t="inlineStr"/>
       <c r="G911" t="inlineStr">
         <is>
           <t>OK</t>
@@ -26486,11 +25298,7 @@
       <c r="E912" t="n">
         <v>5</v>
       </c>
-      <c r="F912" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F912" t="inlineStr"/>
       <c r="G912" t="inlineStr">
         <is>
           <t>OK</t>
@@ -26518,11 +25326,7 @@
       <c r="E913" t="n">
         <v>12</v>
       </c>
-      <c r="F913" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F913" t="inlineStr"/>
       <c r="G913" t="inlineStr">
         <is>
           <t>OK</t>
@@ -26574,21 +25378,9 @@
         </is>
       </c>
       <c r="C915" t="inlineStr"/>
-      <c r="D915" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E915" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F915" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D915" t="inlineStr"/>
+      <c r="E915" t="inlineStr"/>
+      <c r="F915" t="inlineStr"/>
       <c r="G915" t="inlineStr">
         <is>
           <t>OK</t>
@@ -26608,21 +25400,9 @@
         </is>
       </c>
       <c r="C916" t="inlineStr"/>
-      <c r="D916" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E916" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F916" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D916" t="inlineStr"/>
+      <c r="E916" t="inlineStr"/>
+      <c r="F916" t="inlineStr"/>
       <c r="G916" t="inlineStr">
         <is>
           <t>OK</t>
@@ -26642,21 +25422,9 @@
         </is>
       </c>
       <c r="C917" t="inlineStr"/>
-      <c r="D917" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E917" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F917" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D917" t="inlineStr"/>
+      <c r="E917" t="inlineStr"/>
+      <c r="F917" t="inlineStr"/>
       <c r="G917" t="inlineStr">
         <is>
           <t>OK</t>
@@ -26676,21 +25444,9 @@
         </is>
       </c>
       <c r="C918" t="inlineStr"/>
-      <c r="D918" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E918" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F918" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D918" t="inlineStr"/>
+      <c r="E918" t="inlineStr"/>
+      <c r="F918" t="inlineStr"/>
       <c r="G918" t="inlineStr">
         <is>
           <t>OK</t>
@@ -26710,21 +25466,9 @@
         </is>
       </c>
       <c r="C919" t="inlineStr"/>
-      <c r="D919" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E919" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F919" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D919" t="inlineStr"/>
+      <c r="E919" t="inlineStr"/>
+      <c r="F919" t="inlineStr"/>
       <c r="G919" t="inlineStr">
         <is>
           <t>OK</t>
@@ -26744,21 +25488,9 @@
         </is>
       </c>
       <c r="C920" t="inlineStr"/>
-      <c r="D920" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E920" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F920" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D920" t="inlineStr"/>
+      <c r="E920" t="inlineStr"/>
+      <c r="F920" t="inlineStr"/>
       <c r="G920" t="inlineStr">
         <is>
           <t>OK</t>
@@ -26786,11 +25518,7 @@
       <c r="E921" t="n">
         <v>10</v>
       </c>
-      <c r="F921" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F921" t="inlineStr"/>
       <c r="G921" t="inlineStr">
         <is>
           <t>OK</t>
@@ -26812,16 +25540,8 @@
       <c r="C922" t="n">
         <v>3999</v>
       </c>
-      <c r="D922" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E922" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D922" t="inlineStr"/>
+      <c r="E922" t="inlineStr"/>
       <c r="F922" t="inlineStr">
         <is>
           <t>Currently unavailable. We don't know when or if this item will be back in stock.</t>
@@ -26854,11 +25574,7 @@
       <c r="E923" t="n">
         <v>5</v>
       </c>
-      <c r="F923" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F923" t="inlineStr"/>
       <c r="G923" t="inlineStr">
         <is>
           <t>OK</t>
@@ -26886,11 +25602,7 @@
       <c r="E924" t="n">
         <v>2</v>
       </c>
-      <c r="F924" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F924" t="inlineStr"/>
       <c r="G924" t="inlineStr">
         <is>
           <t>OK</t>
@@ -26912,21 +25624,9 @@
       <c r="C925" t="n">
         <v>4869</v>
       </c>
-      <c r="D925" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E925" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F925" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D925" t="inlineStr"/>
+      <c r="E925" t="inlineStr"/>
+      <c r="F925" t="inlineStr"/>
       <c r="G925" t="inlineStr">
         <is>
           <t>OK</t>
@@ -26986,11 +25686,7 @@
       <c r="E927" t="n">
         <v>3</v>
       </c>
-      <c r="F927" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F927" t="inlineStr"/>
       <c r="G927" t="inlineStr">
         <is>
           <t>OK</t>
@@ -27018,11 +25714,7 @@
       <c r="E928" t="n">
         <v>3</v>
       </c>
-      <c r="F928" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F928" t="inlineStr"/>
       <c r="G928" t="inlineStr">
         <is>
           <t>OK</t>
@@ -27050,11 +25742,7 @@
       <c r="E929" t="n">
         <v>3</v>
       </c>
-      <c r="F929" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F929" t="inlineStr"/>
       <c r="G929" t="inlineStr">
         <is>
           <t>OK</t>
@@ -27106,21 +25794,9 @@
         </is>
       </c>
       <c r="C931" t="inlineStr"/>
-      <c r="D931" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E931" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F931" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D931" t="inlineStr"/>
+      <c r="E931" t="inlineStr"/>
+      <c r="F931" t="inlineStr"/>
       <c r="G931" t="inlineStr">
         <is>
           <t>OK</t>
@@ -27148,11 +25824,7 @@
       <c r="E932" t="n">
         <v>10</v>
       </c>
-      <c r="F932" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F932" t="inlineStr"/>
       <c r="G932" t="inlineStr">
         <is>
           <t>OK</t>
@@ -27180,11 +25852,7 @@
       <c r="E933" t="n">
         <v>10</v>
       </c>
-      <c r="F933" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F933" t="inlineStr"/>
       <c r="G933" t="inlineStr">
         <is>
           <t>OK</t>
@@ -27268,21 +25936,9 @@
         </is>
       </c>
       <c r="C936" t="inlineStr"/>
-      <c r="D936" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E936" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F936" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D936" t="inlineStr"/>
+      <c r="E936" t="inlineStr"/>
+      <c r="F936" t="inlineStr"/>
       <c r="G936" t="inlineStr">
         <is>
           <t>OK</t>
@@ -27302,21 +25958,9 @@
         </is>
       </c>
       <c r="C937" t="inlineStr"/>
-      <c r="D937" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E937" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F937" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D937" t="inlineStr"/>
+      <c r="E937" t="inlineStr"/>
+      <c r="F937" t="inlineStr"/>
       <c r="G937" t="inlineStr">
         <is>
           <t>OK</t>
@@ -27336,21 +25980,9 @@
         </is>
       </c>
       <c r="C938" t="inlineStr"/>
-      <c r="D938" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E938" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F938" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D938" t="inlineStr"/>
+      <c r="E938" t="inlineStr"/>
+      <c r="F938" t="inlineStr"/>
       <c r="G938" t="inlineStr">
         <is>
           <t>OK</t>
@@ -27378,11 +26010,7 @@
       <c r="E939" t="n">
         <v>2</v>
       </c>
-      <c r="F939" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F939" t="inlineStr"/>
       <c r="G939" t="inlineStr">
         <is>
           <t>OK</t>
@@ -27410,11 +26038,7 @@
       <c r="E940" t="n">
         <v>3</v>
       </c>
-      <c r="F940" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F940" t="inlineStr"/>
       <c r="G940" t="inlineStr">
         <is>
           <t>OK</t>
@@ -27442,11 +26066,7 @@
       <c r="E941" t="n">
         <v>2</v>
       </c>
-      <c r="F941" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F941" t="inlineStr"/>
       <c r="G941" t="inlineStr">
         <is>
           <t>OK</t>
@@ -27500,16 +26120,8 @@
       <c r="C943" t="n">
         <v>3239</v>
       </c>
-      <c r="D943" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E943" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D943" t="inlineStr"/>
+      <c r="E943" t="inlineStr"/>
       <c r="F943" t="inlineStr">
         <is>
           <t>Only 2 left in stock.</t>
@@ -27542,11 +26154,7 @@
       <c r="E944" t="n">
         <v>2</v>
       </c>
-      <c r="F944" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F944" t="inlineStr"/>
       <c r="G944" t="inlineStr">
         <is>
           <t>OK</t>
@@ -27574,11 +26182,7 @@
       <c r="E945" t="n">
         <v>2</v>
       </c>
-      <c r="F945" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F945" t="inlineStr"/>
       <c r="G945" t="inlineStr">
         <is>
           <t>OK</t>
@@ -27606,11 +26210,7 @@
       <c r="E946" t="n">
         <v>3</v>
       </c>
-      <c r="F946" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F946" t="inlineStr"/>
       <c r="G946" t="inlineStr">
         <is>
           <t>OK</t>
@@ -27638,11 +26238,7 @@
       <c r="E947" t="n">
         <v>2</v>
       </c>
-      <c r="F947" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F947" t="inlineStr"/>
       <c r="G947" t="inlineStr">
         <is>
           <t>OK</t>
@@ -27696,16 +26292,8 @@
       <c r="C949" t="n">
         <v>3239</v>
       </c>
-      <c r="D949" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E949" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D949" t="inlineStr"/>
+      <c r="E949" t="inlineStr"/>
       <c r="F949" t="inlineStr">
         <is>
           <t>Only 2 left in stock.</t>
@@ -27738,11 +26326,7 @@
       <c r="E950" t="n">
         <v>2</v>
       </c>
-      <c r="F950" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F950" t="inlineStr"/>
       <c r="G950" t="inlineStr">
         <is>
           <t>OK</t>
@@ -27770,11 +26354,7 @@
       <c r="E951" t="n">
         <v>2</v>
       </c>
-      <c r="F951" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F951" t="inlineStr"/>
       <c r="G951" t="inlineStr">
         <is>
           <t>OK</t>
@@ -27802,11 +26382,7 @@
       <c r="E952" t="n">
         <v>3</v>
       </c>
-      <c r="F952" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F952" t="inlineStr"/>
       <c r="G952" t="inlineStr">
         <is>
           <t>OK</t>
@@ -27834,11 +26410,7 @@
       <c r="E953" t="n">
         <v>2</v>
       </c>
-      <c r="F953" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F953" t="inlineStr"/>
       <c r="G953" t="inlineStr">
         <is>
           <t>OK</t>
@@ -27890,16 +26462,8 @@
       <c r="C955" t="n">
         <v>3239</v>
       </c>
-      <c r="D955" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E955" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D955" t="inlineStr"/>
+      <c r="E955" t="inlineStr"/>
       <c r="F955" t="inlineStr">
         <is>
           <t>Only 2 left in stock.</t>
@@ -27932,11 +26496,7 @@
       <c r="E956" t="n">
         <v>2</v>
       </c>
-      <c r="F956" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F956" t="inlineStr"/>
       <c r="G956" t="inlineStr">
         <is>
           <t>OK</t>
@@ -27964,11 +26524,7 @@
       <c r="E957" t="n">
         <v>2</v>
       </c>
-      <c r="F957" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F957" t="inlineStr"/>
       <c r="G957" t="inlineStr">
         <is>
           <t>OK</t>
@@ -27996,11 +26552,7 @@
       <c r="E958" t="n">
         <v>3</v>
       </c>
-      <c r="F958" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F958" t="inlineStr"/>
       <c r="G958" t="inlineStr">
         <is>
           <t>OK</t>
@@ -28028,11 +26580,7 @@
       <c r="E959" t="n">
         <v>2</v>
       </c>
-      <c r="F959" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F959" t="inlineStr"/>
       <c r="G959" t="inlineStr">
         <is>
           <t>OK</t>
@@ -28086,16 +26634,8 @@
       <c r="C961" t="n">
         <v>3239</v>
       </c>
-      <c r="D961" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E961" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D961" t="inlineStr"/>
+      <c r="E961" t="inlineStr"/>
       <c r="F961" t="inlineStr">
         <is>
           <t>Only 2 left in stock.</t>
@@ -28128,11 +26668,7 @@
       <c r="E962" t="n">
         <v>2</v>
       </c>
-      <c r="F962" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F962" t="inlineStr"/>
       <c r="G962" t="inlineStr">
         <is>
           <t>OK</t>
@@ -28160,11 +26696,7 @@
       <c r="E963" t="n">
         <v>2</v>
       </c>
-      <c r="F963" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F963" t="inlineStr"/>
       <c r="G963" t="inlineStr">
         <is>
           <t>OK</t>
@@ -28192,11 +26724,7 @@
       <c r="E964" t="n">
         <v>3</v>
       </c>
-      <c r="F964" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F964" t="inlineStr"/>
       <c r="G964" t="inlineStr">
         <is>
           <t>OK</t>
@@ -28224,11 +26752,7 @@
       <c r="E965" t="n">
         <v>2</v>
       </c>
-      <c r="F965" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F965" t="inlineStr"/>
       <c r="G965" t="inlineStr">
         <is>
           <t>OK</t>
@@ -28282,16 +26806,8 @@
       <c r="C967" t="n">
         <v>3239</v>
       </c>
-      <c r="D967" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E967" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D967" t="inlineStr"/>
+      <c r="E967" t="inlineStr"/>
       <c r="F967" t="inlineStr">
         <is>
           <t>Only 2 left in stock.</t>
